--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1186,9 +1186,19 @@
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="F28" s="5" t="n">
+        <v>657</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>53% (72/135)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -17845,7 +17855,11 @@
       </c>
       <c r="E690" s="2" t="n"/>
       <c r="F690" s="4" t="n"/>
-      <c r="G690" s="2" t="n"/>
+      <c r="G690" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n"/>
@@ -17866,7 +17880,11 @@
       </c>
       <c r="E691" s="2" t="n"/>
       <c r="F691" s="4" t="n"/>
-      <c r="G691" s="2" t="n"/>
+      <c r="G691" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 5次)</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n"/>
@@ -17887,9 +17905,13 @@
       </c>
       <c r="E692" s="2" t="n"/>
       <c r="F692" s="4" t="n"/>
-      <c r="G692" s="2" t="n"/>
-    </row>
-    <row r="693">
+      <c r="G692" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 5次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="693" ht="64" customHeight="1">
       <c r="A693" s="2" t="n"/>
       <c r="B693" s="2" t="inlineStr">
         <is>
@@ -17907,10 +17929,21 @@
         </is>
       </c>
       <c r="E693" s="2" t="n"/>
-      <c r="F693" s="4" t="n"/>
-      <c r="G693" s="2" t="n"/>
-    </row>
-    <row r="694">
+      <c r="F693" s="7" t="inlineStr">
+        <is>
+          <t>reportType=1 — 84.1%
+reportType=0 — 11.0%
+reportType=2 — 3.7%
+reportType=3 — 1.2%</t>
+        </is>
+      </c>
+      <c r="G693" s="4" t="inlineStr">
+        <is>
+          <t>reportType=2场景实测HTTP 500 SQL语法错误("Incorrect syntax near keyword as/DC")，疑似真实后端bug，已如实记FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="694" ht="48" customHeight="1">
       <c r="A694" s="2" t="n"/>
       <c r="B694" s="2" t="inlineStr">
         <is>
@@ -17928,10 +17961,16 @@
         </is>
       </c>
       <c r="E694" s="2" t="n"/>
-      <c r="F694" s="4" t="n"/>
+      <c r="F694" s="7" t="inlineStr">
+        <is>
+          <t>reportType=1 — 87.2%
+reportType=0 — 11.5%
+reportType=3 — 1.3%</t>
+        </is>
+      </c>
       <c r="G694" s="2" t="n"/>
     </row>
-    <row r="695">
+    <row r="695" ht="96" customHeight="1">
       <c r="A695" s="2" t="n"/>
       <c r="B695" s="2" t="inlineStr">
         <is>
@@ -17949,7 +17988,16 @@
         </is>
       </c>
       <c r="E695" s="2" t="n"/>
-      <c r="F695" s="4" t="n"/>
+      <c r="F695" s="7" t="inlineStr">
+        <is>
+          <t>不传market+无AdGroup过滤 — 57.7%
+market=US+无AdGroup过滤 — 20.0%
+不传market+按AdGroup过滤 — 7.7%
+不传market+不传adGroupIds — 5.4%
+market=US+不传adGroupIds — 4.6%
+market=US+按AdGroup过滤 — 4.6%</t>
+        </is>
+      </c>
       <c r="G695" s="2" t="n"/>
     </row>
     <row r="696">
@@ -17971,9 +18019,13 @@
       </c>
       <c r="E696" s="2" t="n"/>
       <c r="F696" s="4" t="n"/>
-      <c r="G696" s="2" t="n"/>
-    </row>
-    <row r="697">
+      <c r="G696" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="697" ht="96" customHeight="1">
       <c r="A697" s="2" t="n"/>
       <c r="B697" s="2" t="inlineStr">
         <is>
@@ -17991,10 +18043,19 @@
         </is>
       </c>
       <c r="E697" s="2" t="n"/>
-      <c r="F697" s="4" t="n"/>
+      <c r="F697" s="7" t="inlineStr">
+        <is>
+          <t>不传market+无AdGroup过滤 — 51.0%
+market=US+无AdGroup过滤 — 25.2%
+market=US+不传adGroupIds — 6.8%
+不传market+按AdGroup过滤 — 6.8%
+不传market+不传adGroupIds — 6.1%
+market=US+按AdGroup过滤 — 4.1%</t>
+        </is>
+      </c>
       <c r="G697" s="2" t="n"/>
     </row>
-    <row r="698">
+    <row r="698" ht="96" customHeight="1">
       <c r="A698" s="2" t="n"/>
       <c r="B698" s="2" t="inlineStr">
         <is>
@@ -18012,10 +18073,19 @@
         </is>
       </c>
       <c r="E698" s="2" t="n"/>
-      <c r="F698" s="4" t="n"/>
+      <c r="F698" s="7" t="inlineStr">
+        <is>
+          <t>不传market+无AdGroup过滤 — 53.6%
+market=US+无AdGroup过滤 — 25.4%
+不传market+按AdGroup过滤 — 7.2%
+不传market+不传adGroupIds — 5.1%
+market=US+按AdGroup过滤 — 4.3%
+market=US+不传adGroupIds — 4.3%</t>
+        </is>
+      </c>
       <c r="G698" s="2" t="n"/>
     </row>
-    <row r="699">
+    <row r="699" ht="64" customHeight="1">
       <c r="A699" s="2" t="n"/>
       <c r="B699" s="2" t="inlineStr">
         <is>
@@ -18033,7 +18103,14 @@
         </is>
       </c>
       <c r="E699" s="2" t="n"/>
-      <c r="F699" s="4" t="n"/>
+      <c r="F699" s="7" t="inlineStr">
+        <is>
+          <t>onlyShowOOBRows=false+无Campaign过滤 — 51.4%
+onlyShowOOBRows=true+无Campaign过滤 — 26.9%
+onlyShowOOBRows=false+按Campaign过滤 — 20.2%
+onlyShowOOBRows=true+按Campaign过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G699" s="2" t="n"/>
     </row>
     <row r="700">
@@ -18055,7 +18132,11 @@
       </c>
       <c r="E700" s="2" t="n"/>
       <c r="F700" s="4" t="n"/>
-      <c r="G700" s="2" t="n"/>
+      <c r="G700" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n"/>
@@ -18076,7 +18157,11 @@
       </c>
       <c r="E701" s="2" t="n"/>
       <c r="F701" s="4" t="n"/>
-      <c r="G701" s="2" t="n"/>
+      <c r="G701" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 4次)</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n"/>
@@ -18097,9 +18182,13 @@
       </c>
       <c r="E702" s="2" t="n"/>
       <c r="F702" s="4" t="n"/>
-      <c r="G702" s="2" t="n"/>
-    </row>
-    <row r="703">
+      <c r="G702" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 4次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703" ht="64" customHeight="1">
       <c r="A703" s="2" t="n"/>
       <c r="B703" s="2" t="inlineStr">
         <is>
@@ -18117,10 +18206,17 @@
         </is>
       </c>
       <c r="E703" s="2" t="n"/>
-      <c r="F703" s="4" t="n"/>
+      <c r="F703" s="7" t="inlineStr">
+        <is>
+          <t>onlyShowOOBRows=false+无Campaign过滤 — 52.4%
+onlyShowOOBRows=true+无Campaign过滤 — 26.4%
+onlyShowOOBRows=false+按Campaign过滤 — 19.8%
+onlyShowOOBRows=true+按Campaign过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G703" s="2" t="n"/>
     </row>
-    <row r="704">
+    <row r="704" ht="64" customHeight="1">
       <c r="A704" s="2" t="n"/>
       <c r="B704" s="2" t="inlineStr">
         <is>
@@ -18138,7 +18234,14 @@
         </is>
       </c>
       <c r="E704" s="2" t="n"/>
-      <c r="F704" s="4" t="n"/>
+      <c r="F704" s="7" t="inlineStr">
+        <is>
+          <t>onlyShowOOBRows=false+无Campaign过滤 — 51.9%
+onlyShowOOBRows=true+无Campaign过滤 — 26.7%
+onlyShowOOBRows=false+按Campaign过滤 — 20.0%
+onlyShowOOBRows=true+按Campaign过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G704" s="2" t="n"/>
     </row>
     <row r="705">
@@ -18160,7 +18263,11 @@
       </c>
       <c r="E705" s="2" t="n"/>
       <c r="F705" s="4" t="n"/>
-      <c r="G705" s="2" t="n"/>
+      <c r="G705" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n"/>
@@ -18181,7 +18288,11 @@
       </c>
       <c r="E706" s="2" t="n"/>
       <c r="F706" s="4" t="n"/>
-      <c r="G706" s="2" t="n"/>
+      <c r="G706" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n"/>
@@ -18202,7 +18313,11 @@
       </c>
       <c r="E707" s="2" t="n"/>
       <c r="F707" s="4" t="n"/>
-      <c r="G707" s="2" t="n"/>
+      <c r="G707" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n"/>
@@ -18223,7 +18338,11 @@
       </c>
       <c r="E708" s="2" t="n"/>
       <c r="F708" s="4" t="n"/>
-      <c r="G708" s="2" t="n"/>
+      <c r="G708" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 258次)</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n"/>
@@ -18244,7 +18363,11 @@
       </c>
       <c r="E709" s="2" t="n"/>
       <c r="F709" s="4" t="n"/>
-      <c r="G709" s="2" t="n"/>
+      <c r="G709" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 264次)</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n"/>
@@ -18265,9 +18388,13 @@
       </c>
       <c r="E710" s="2" t="n"/>
       <c r="F710" s="4" t="n"/>
-      <c r="G710" s="2" t="n"/>
-    </row>
-    <row r="711">
+      <c r="G710" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="711" ht="192" customHeight="1">
       <c r="A711" s="2" t="n"/>
       <c r="B711" s="2" t="inlineStr">
         <is>
@@ -18285,10 +18412,25 @@
         </is>
       </c>
       <c r="E711" s="2" t="n"/>
-      <c r="F711" s="4" t="n"/>
+      <c r="F711" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 24.8%
+不传reportAdType+channelType=0 — 22.2%
+reportAdType=1+channelType=0 — 16.4%
+reportAdType=2+channelType=2 — 8.6%
+reportAdType=1+channelType=2 — 5.2%
+reportAdType=0+channelType=0 — 4.8%
+reportAdType=1+channelType=1 — 4.0%
+reportAdType=2+channelType=1 — 3.8%
+reportAdType=0+channelType=2 — 3.2%
+reportAdType=2+不传channelType — 3.2%
+不传reportAdType+channelType=2 — 1.6%
+reportAdType=0+channelType=1 — 1.6%</t>
+        </is>
+      </c>
       <c r="G711" s="2" t="n"/>
     </row>
-    <row r="712">
+    <row r="712" ht="176" customHeight="1">
       <c r="A712" s="2" t="n"/>
       <c r="B712" s="2" t="inlineStr">
         <is>
@@ -18306,10 +18448,24 @@
         </is>
       </c>
       <c r="E712" s="2" t="n"/>
-      <c r="F712" s="4" t="n"/>
+      <c r="F712" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 26.2%
+不传reportAdType+channelType=0 — 20.0%
+reportAdType=1+channelType=0 — 14.4%
+reportAdType=2+channelType=2 — 8.2%
+reportAdType=0+channelType=0 — 5.8%
+reportAdType=1+channelType=1 — 5.8%
+reportAdType=1+channelType=2 — 5.4%
+reportAdType=2+不传channelType — 5.2%
+reportAdType=0+channelType=2 — 3.4%
+reportAdType=2+channelType=1 — 2.8%
+不传reportAdType+channelType=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G712" s="2" t="n"/>
     </row>
-    <row r="713">
+    <row r="713" ht="128" customHeight="1">
       <c r="A713" s="2" t="n"/>
       <c r="B713" s="2" t="inlineStr">
         <is>
@@ -18327,10 +18483,21 @@
         </is>
       </c>
       <c r="E713" s="2" t="n"/>
-      <c r="F713" s="4" t="n"/>
+      <c r="F713" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 41.4%
+不传reportAdType+channelType=0 — 28.8%
+reportAdType=2+channelType=2 — 10.8%
+reportAdType=2+不传channelType — 8.4%
+reportAdType=2+channelType=1 — 5.6%
+不传reportAdType+channelType=2 — 2.0%
+不传reportAdType+channelType=1 — 1.6%
+不传reportAdType+不传channelType — 1.2%</t>
+        </is>
+      </c>
       <c r="G713" s="2" t="n"/>
     </row>
-    <row r="714">
+    <row r="714" ht="192" customHeight="1">
       <c r="A714" s="2" t="n"/>
       <c r="B714" s="2" t="inlineStr">
         <is>
@@ -18348,10 +18515,25 @@
         </is>
       </c>
       <c r="E714" s="2" t="n"/>
-      <c r="F714" s="4" t="n"/>
+      <c r="F714" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 24.0%
+不传reportAdType+channelType=0 — 20.4%
+reportAdType=1+channelType=0 — 14.4%
+reportAdType=2+channelType=2 — 10.2%
+reportAdType=1+channelType=2 — 6.2%
+reportAdType=2+不传channelType — 5.8%
+reportAdType=0+channelType=0 — 4.4%
+reportAdType=1+channelType=1 — 3.2%
+reportAdType=0+channelType=2 — 3.2%
+reportAdType=2+channelType=1 — 2.8%
+reportAdType=0+channelType=1 — 2.4%
+不传reportAdType+channelType=2 — 1.2%</t>
+        </is>
+      </c>
       <c r="G714" s="2" t="n"/>
     </row>
-    <row r="715">
+    <row r="715" ht="192" customHeight="1">
       <c r="A715" s="2" t="n"/>
       <c r="B715" s="2" t="inlineStr">
         <is>
@@ -18369,10 +18551,25 @@
         </is>
       </c>
       <c r="E715" s="2" t="n"/>
-      <c r="F715" s="4" t="n"/>
+      <c r="F715" s="7" t="inlineStr">
+        <is>
+          <t>不传reportAdType+channelType=0 — 28.6%
+reportAdType=2+channelType=0 — 21.2%
+reportAdType=1+channelType=0 — 11.8%
+不传reportAdType+channelType=2 — 7.6%
+reportAdType=2+channelType=2 — 5.4%
+reportAdType=2+不传channelType — 4.4%
+reportAdType=1+channelType=1 — 4.2%
+reportAdType=1+channelType=2 — 4.2%
+reportAdType=0+channelType=0 — 3.6%
+reportAdType=0+channelType=2 — 3.4%
+reportAdType=2+channelType=1 — 3.0%
+reportAdType=0+channelType=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G715" s="2" t="n"/>
     </row>
-    <row r="716">
+    <row r="716" ht="160" customHeight="1">
       <c r="A716" s="2" t="n"/>
       <c r="B716" s="2" t="inlineStr">
         <is>
@@ -18390,10 +18587,23 @@
         </is>
       </c>
       <c r="E716" s="2" t="n"/>
-      <c r="F716" s="4" t="n"/>
+      <c r="F716" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 27.4%
+不传reportAdType+channelType=0 — 22.2%
+reportAdType=1+channelType=0 — 16.4%
+reportAdType=2+channelType=2 — 10.2%
+reportAdType=1+channelType=2 — 6.2%
+reportAdType=2+channelType=1 — 5.0%
+reportAdType=2+不传channelType — 5.0%
+reportAdType=1+channelType=1 — 4.6%
+不传reportAdType+channelType=2 — 1.2%
+不传reportAdType+不传channelType — 1.2%</t>
+        </is>
+      </c>
       <c r="G716" s="2" t="n"/>
     </row>
-    <row r="717">
+    <row r="717" ht="176" customHeight="1">
       <c r="A717" s="2" t="n"/>
       <c r="B717" s="2" t="inlineStr">
         <is>
@@ -18411,7 +18621,21 @@
         </is>
       </c>
       <c r="E717" s="2" t="n"/>
-      <c r="F717" s="4" t="n"/>
+      <c r="F717" s="7" t="inlineStr">
+        <is>
+          <t>不传reportAdType+channelType=0 — 31.4%
+reportAdType=2+channelType=0 — 18.6%
+reportAdType=1+channelType=0 — 18.4%
+reportAdType=2+channelType=2 — 5.2%
+reportAdType=2+channelType=1 — 4.8%
+reportAdType=1+channelType=2 — 4.4%
+reportAdType=0+channelType=0 — 4.0%
+reportAdType=1+channelType=1 — 3.6%
+reportAdType=2+不传channelType — 3.4%
+不传reportAdType+channelType=2 — 2.8%
+reportAdType=0+channelType=1 — 2.0%</t>
+        </is>
+      </c>
       <c r="G717" s="2" t="n"/>
     </row>
     <row r="718">
@@ -18433,9 +18657,13 @@
       </c>
       <c r="E718" s="2" t="n"/>
       <c r="F718" s="4" t="n"/>
-      <c r="G718" s="2" t="n"/>
-    </row>
-    <row r="719">
+      <c r="G718" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="719" ht="192" customHeight="1">
       <c r="A719" s="2" t="n"/>
       <c r="B719" s="2" t="inlineStr">
         <is>
@@ -18453,10 +18681,25 @@
         </is>
       </c>
       <c r="E719" s="2" t="n"/>
-      <c r="F719" s="4" t="n"/>
+      <c r="F719" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 24.6%
+不传reportAdType+channelType=0 — 19.8%
+reportAdType=1+channelType=0 — 15.4%
+reportAdType=2+channelType=2 — 7.6%
+reportAdType=1+channelType=1 — 5.6%
+reportAdType=1+channelType=2 — 5.6%
+reportAdType=0+channelType=2 — 5.0%
+reportAdType=0+channelType=0 — 4.6%
+reportAdType=2+不传channelType — 4.0%
+reportAdType=2+channelType=1 — 3.4%
+reportAdType=0+channelType=1 — 1.4%
+不传reportAdType+channelType=2 — 1.4%</t>
+        </is>
+      </c>
       <c r="G719" s="2" t="n"/>
     </row>
-    <row r="720">
+    <row r="720" ht="192" customHeight="1">
       <c r="A720" s="2" t="n"/>
       <c r="B720" s="2" t="inlineStr">
         <is>
@@ -18474,10 +18717,25 @@
         </is>
       </c>
       <c r="E720" s="2" t="n"/>
-      <c r="F720" s="4" t="n"/>
+      <c r="F720" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 26.6%
+不传reportAdType+channelType=0 — 19.0%
+reportAdType=1+channelType=0 — 12.2%
+reportAdType=2+channelType=2 — 7.6%
+reportAdType=1+channelType=2 — 6.8%
+reportAdType=1+channelType=1 — 5.4%
+reportAdType=0+channelType=0 — 5.0%
+reportAdType=2+不传channelType — 4.8%
+reportAdType=0+channelType=2 — 3.6%
+reportAdType=2+channelType=1 — 3.4%
+不传reportAdType+channelType=2 — 2.0%
+reportAdType=0+channelType=1 — 2.0%</t>
+        </is>
+      </c>
       <c r="G720" s="2" t="n"/>
     </row>
-    <row r="721">
+    <row r="721" ht="192" customHeight="1">
       <c r="A721" s="2" t="n"/>
       <c r="B721" s="2" t="inlineStr">
         <is>
@@ -18495,10 +18753,25 @@
         </is>
       </c>
       <c r="E721" s="2" t="n"/>
-      <c r="F721" s="4" t="n"/>
+      <c r="F721" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 33.0%
+不传reportAdType+channelType=0 — 19.2%
+reportAdType=1+channelType=0 — 12.0%
+reportAdType=2+channelType=2 — 11.0%
+reportAdType=2+不传channelType — 5.0%
+reportAdType=0+channelType=0 — 4.6%
+reportAdType=2+channelType=1 — 3.8%
+reportAdType=1+channelType=2 — 3.2%
+reportAdType=0+channelType=2 — 2.6%
+不传reportAdType+channelType=2 — 1.6%
+不传reportAdType+不传channelType — 1.4%
+reportAdType=1+channelType=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G721" s="2" t="n"/>
     </row>
-    <row r="722">
+    <row r="722" ht="112" customHeight="1">
       <c r="A722" s="2" t="n"/>
       <c r="B722" s="2" t="inlineStr">
         <is>
@@ -18516,10 +18789,20 @@
         </is>
       </c>
       <c r="E722" s="2" t="n"/>
-      <c r="F722" s="4" t="n"/>
+      <c r="F722" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 42.2%
+不传reportAdType+channelType=0 — 29.6%
+reportAdType=2+channelType=2 — 13.4%
+reportAdType=2+channelType=1 — 6.0%
+reportAdType=2+不传channelType — 5.0%
+不传reportAdType+不传channelType — 1.6%
+不传reportAdType+channelType=2 — 1.4%</t>
+        </is>
+      </c>
       <c r="G722" s="2" t="n"/>
     </row>
-    <row r="723">
+    <row r="723" ht="192" customHeight="1">
       <c r="A723" s="2" t="n"/>
       <c r="B723" s="2" t="inlineStr">
         <is>
@@ -18537,7 +18820,22 @@
         </is>
       </c>
       <c r="E723" s="2" t="n"/>
-      <c r="F723" s="4" t="n"/>
+      <c r="F723" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+channelType=0 — 25.6%
+不传reportAdType+channelType=0 — 19.8%
+reportAdType=1+channelType=0 — 17.8%
+reportAdType=1+channelType=2 — 7.4%
+reportAdType=2+channelType=2 — 6.6%
+reportAdType=1+channelType=1 — 4.8%
+reportAdType=2+不传channelType — 4.0%
+reportAdType=0+channelType=0 — 3.6%
+reportAdType=2+channelType=1 — 3.0%
+不传reportAdType+channelType=2 — 2.6%
+reportAdType=0+channelType=2 — 2.4%
+reportAdType=0+channelType=1 — 1.6%</t>
+        </is>
+      </c>
       <c r="G723" s="2" t="n"/>
     </row>
     <row r="724">
@@ -18559,7 +18857,11 @@
       </c>
       <c r="E724" s="2" t="n"/>
       <c r="F724" s="4" t="n"/>
-      <c r="G724" s="2" t="n"/>
+      <c r="G724" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n"/>
@@ -18580,7 +18882,11 @@
       </c>
       <c r="E725" s="2" t="n"/>
       <c r="F725" s="4" t="n"/>
-      <c r="G725" s="2" t="n"/>
+      <c r="G725" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n"/>
@@ -18601,7 +18907,11 @@
       </c>
       <c r="E726" s="2" t="n"/>
       <c r="F726" s="4" t="n"/>
-      <c r="G726" s="2" t="n"/>
+      <c r="G726" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n"/>
@@ -18622,7 +18932,11 @@
       </c>
       <c r="E727" s="2" t="n"/>
       <c r="F727" s="4" t="n"/>
-      <c r="G727" s="2" t="n"/>
+      <c r="G727" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n"/>
@@ -18643,7 +18957,11 @@
       </c>
       <c r="E728" s="2" t="n"/>
       <c r="F728" s="4" t="n"/>
-      <c r="G728" s="2" t="n"/>
+      <c r="G728" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n"/>
@@ -18664,7 +18982,11 @@
       </c>
       <c r="E729" s="2" t="n"/>
       <c r="F729" s="4" t="n"/>
-      <c r="G729" s="2" t="n"/>
+      <c r="G729" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n"/>
@@ -18685,7 +19007,11 @@
       </c>
       <c r="E730" s="2" t="n"/>
       <c r="F730" s="4" t="n"/>
-      <c r="G730" s="2" t="n"/>
+      <c r="G730" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n"/>
@@ -18706,7 +19032,11 @@
       </c>
       <c r="E731" s="2" t="n"/>
       <c r="F731" s="4" t="n"/>
-      <c r="G731" s="2" t="n"/>
+      <c r="G731" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n"/>
@@ -18727,7 +19057,11 @@
       </c>
       <c r="E732" s="2" t="n"/>
       <c r="F732" s="4" t="n"/>
-      <c r="G732" s="2" t="n"/>
+      <c r="G732" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n"/>
@@ -18748,7 +19082,11 @@
       </c>
       <c r="E733" s="2" t="n"/>
       <c r="F733" s="4" t="n"/>
-      <c r="G733" s="2" t="n"/>
+      <c r="G733" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 72次)</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n"/>
@@ -18769,9 +19107,13 @@
       </c>
       <c r="E734" s="2" t="n"/>
       <c r="F734" s="4" t="n"/>
-      <c r="G734" s="2" t="n"/>
-    </row>
-    <row r="735">
+      <c r="G734" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 69次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="735" ht="176" customHeight="1">
       <c r="A735" s="2" t="n"/>
       <c r="B735" s="2" t="inlineStr">
         <is>
@@ -18789,10 +19131,24 @@
         </is>
       </c>
       <c r="E735" s="2" t="n"/>
-      <c r="F735" s="4" t="n"/>
+      <c r="F735" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 37.0%
+ReportAdType=1+channelType=0 — 16.8%
+不传ReportAdType+channelType=0 — 15.0%
+ReportAdType=2+channelType=2 — 10.6%
+ReportAdType=1+channelType=2 — 5.6%
+不传ReportAdType+channelType=2 — 3.4%
+ReportAdType=0+channelType=2 — 2.6%
+ReportAdType=1+channelType=1 — 2.4%
+ReportAdType=2+channelType=1 — 2.4%
+ReportAdType=0+channelType=0 — 2.0%
+ReportAdType=2+不传channelType — 1.2%</t>
+        </is>
+      </c>
       <c r="G735" s="2" t="n"/>
     </row>
-    <row r="736">
+    <row r="736" ht="192" customHeight="1">
       <c r="A736" s="2" t="n"/>
       <c r="B736" s="2" t="inlineStr">
         <is>
@@ -18810,10 +19166,25 @@
         </is>
       </c>
       <c r="E736" s="2" t="n"/>
-      <c r="F736" s="4" t="n"/>
+      <c r="F736" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 38.0%
+ReportAdType=1+channelType=0 — 16.2%
+不传ReportAdType+channelType=0 — 13.8%
+ReportAdType=2+channelType=2 — 10.8%
+ReportAdType=1+channelType=2 — 5.0%
+ReportAdType=0+channelType=0 — 3.6%
+ReportAdType=1+channelType=1 — 3.6%
+不传ReportAdType+channelType=2 — 2.6%
+ReportAdType=2+channelType=1 — 1.8%
+ReportAdType=0+channelType=2 — 1.8%
+ReportAdType=2+不传channelType — 1.6%
+ReportAdType=0+channelType=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G736" s="2" t="n"/>
     </row>
-    <row r="737">
+    <row r="737" ht="176" customHeight="1">
       <c r="A737" s="2" t="n"/>
       <c r="B737" s="2" t="inlineStr">
         <is>
@@ -18831,10 +19202,24 @@
         </is>
       </c>
       <c r="E737" s="2" t="n"/>
-      <c r="F737" s="4" t="n"/>
+      <c r="F737" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 37.6%
+ReportAdType=1+channelType=0 — 16.8%
+不传ReportAdType+channelType=0 — 15.8%
+ReportAdType=2+channelType=2 — 10.6%
+ReportAdType=1+channelType=2 — 5.2%
+ReportAdType=0+channelType=0 — 3.2%
+ReportAdType=0+channelType=2 — 2.4%
+ReportAdType=2+channelType=1 — 2.4%
+不传ReportAdType+channelType=2 — 2.2%
+ReportAdType=1+channelType=1 — 2.0%
+ReportAdType=2+不传channelType — 1.4%</t>
+        </is>
+      </c>
       <c r="G737" s="2" t="n"/>
     </row>
-    <row r="738">
+    <row r="738" ht="176" customHeight="1">
       <c r="A738" s="2" t="n"/>
       <c r="B738" s="2" t="inlineStr">
         <is>
@@ -18852,10 +19237,24 @@
         </is>
       </c>
       <c r="E738" s="2" t="n"/>
-      <c r="F738" s="4" t="n"/>
+      <c r="F738" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 36.0%
+不传ReportAdType+channelType=0 — 17.0%
+ReportAdType=1+channelType=0 — 15.0%
+ReportAdType=2+channelType=2 — 9.8%
+ReportAdType=1+channelType=2 — 6.0%
+ReportAdType=0+channelType=0 — 3.6%
+不传ReportAdType+channelType=2 — 3.4%
+ReportAdType=1+channelType=1 — 2.4%
+ReportAdType=2+channelType=1 — 2.0%
+ReportAdType=0+channelType=2 — 2.0%
+ReportAdType=2+不传channelType — 1.6%</t>
+        </is>
+      </c>
       <c r="G738" s="2" t="n"/>
     </row>
-    <row r="739">
+    <row r="739" ht="176" customHeight="1">
       <c r="A739" s="2" t="n"/>
       <c r="B739" s="2" t="inlineStr">
         <is>
@@ -18873,10 +19272,24 @@
         </is>
       </c>
       <c r="E739" s="2" t="n"/>
-      <c r="F739" s="4" t="n"/>
+      <c r="F739" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 35.2%
+ReportAdType=1+channelType=0 — 18.6%
+不传ReportAdType+channelType=0 — 16.2%
+ReportAdType=2+channelType=2 — 11.0%
+ReportAdType=1+channelType=2 — 5.2%
+不传ReportAdType+channelType=2 — 3.2%
+ReportAdType=0+channelType=0 — 3.2%
+ReportAdType=0+channelType=2 — 2.4%
+ReportAdType=1+channelType=1 — 1.6%
+ReportAdType=2+不传channelType — 1.4%
+ReportAdType=2+channelType=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G739" s="2" t="n"/>
     </row>
-    <row r="740">
+    <row r="740" ht="176" customHeight="1">
       <c r="A740" s="2" t="n"/>
       <c r="B740" s="2" t="inlineStr">
         <is>
@@ -18894,10 +19307,24 @@
         </is>
       </c>
       <c r="E740" s="2" t="n"/>
-      <c r="F740" s="4" t="n"/>
+      <c r="F740" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 32.8%
+不传ReportAdType+channelType=0 — 19.8%
+ReportAdType=1+channelType=0 — 16.2%
+ReportAdType=2+channelType=2 — 11.4%
+ReportAdType=1+channelType=2 — 4.6%
+ReportAdType=0+channelType=0 — 3.6%
+不传ReportAdType+channelType=2 — 3.0%
+ReportAdType=2+channelType=1 — 2.4%
+ReportAdType=0+channelType=2 — 2.4%
+ReportAdType=1+channelType=1 — 1.8%
+ReportAdType=2+不传channelType — 1.0%</t>
+        </is>
+      </c>
       <c r="G740" s="2" t="n"/>
     </row>
-    <row r="741">
+    <row r="741" ht="176" customHeight="1">
       <c r="A741" s="2" t="n"/>
       <c r="B741" s="2" t="inlineStr">
         <is>
@@ -18915,10 +19342,24 @@
         </is>
       </c>
       <c r="E741" s="2" t="n"/>
-      <c r="F741" s="4" t="n"/>
+      <c r="F741" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 36.6%
+ReportAdType=1+channelType=0 — 16.2%
+不传ReportAdType+channelType=0 — 15.0%
+ReportAdType=2+channelType=2 — 11.0%
+ReportAdType=1+channelType=2 — 5.0%
+不传ReportAdType+channelType=2 — 4.8%
+ReportAdType=0+channelType=0 — 3.2%
+ReportAdType=1+channelType=1 — 2.4%
+ReportAdType=0+channelType=2 — 2.0%
+ReportAdType=2+channelType=1 — 1.4%
+ReportAdType=2+不传channelType — 1.4%</t>
+        </is>
+      </c>
       <c r="G741" s="2" t="n"/>
     </row>
-    <row r="742">
+    <row r="742" ht="176" customHeight="1">
       <c r="A742" s="2" t="n"/>
       <c r="B742" s="2" t="inlineStr">
         <is>
@@ -18936,10 +19377,24 @@
         </is>
       </c>
       <c r="E742" s="2" t="n"/>
-      <c r="F742" s="4" t="n"/>
+      <c r="F742" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 31.6%
+ReportAdType=1+channelType=0 — 17.4%
+ReportAdType=2+channelType=2 — 13.6%
+不传ReportAdType+channelType=0 — 13.4%
+ReportAdType=1+channelType=2 — 9.0%
+ReportAdType=1+channelType=1 — 3.2%
+不传ReportAdType+channelType=2 — 2.8%
+ReportAdType=0+channelType=0 — 2.8%
+ReportAdType=2+channelType=1 — 2.4%
+ReportAdType=0+channelType=2 — 2.0%
+ReportAdType=2+不传channelType — 1.4%</t>
+        </is>
+      </c>
       <c r="G742" s="2" t="n"/>
     </row>
-    <row r="743">
+    <row r="743" ht="176" customHeight="1">
       <c r="A743" s="2" t="n"/>
       <c r="B743" s="2" t="inlineStr">
         <is>
@@ -18957,10 +19412,24 @@
         </is>
       </c>
       <c r="E743" s="2" t="n"/>
-      <c r="F743" s="4" t="n"/>
+      <c r="F743" s="7" t="inlineStr">
+        <is>
+          <t>ReportAdType=2+channelType=0 — 29.4%
+ReportAdType=1+channelType=0 — 16.4%
+ReportAdType=2+channelType=2 — 16.2%
+不传ReportAdType+channelType=0 — 13.0%
+ReportAdType=1+channelType=2 — 8.0%
+ReportAdType=0+channelType=0 — 3.6%
+ReportAdType=0+channelType=2 — 3.2%
+不传ReportAdType+channelType=2 — 3.2%
+ReportAdType=1+channelType=1 — 2.8%
+ReportAdType=2+channelType=1 — 2.4%
+ReportAdType=2+不传channelType — 1.2%</t>
+        </is>
+      </c>
       <c r="G743" s="2" t="n"/>
     </row>
-    <row r="744">
+    <row r="744" ht="144" customHeight="1">
       <c r="A744" s="2" t="n"/>
       <c r="B744" s="2" t="inlineStr">
         <is>
@@ -18978,7 +19447,19 @@
         </is>
       </c>
       <c r="E744" s="2" t="n"/>
-      <c r="F744" s="4" t="n"/>
+      <c r="F744" s="7" t="inlineStr">
+        <is>
+          <t>CampaignTypes=[]+channelType=0 — 31.5%
+不传CampaignTypes+channelType=0 — 17.8%
+不传CampaignTypes+channelType=1 — 14.3%
+不传CampaignTypes+channelType=2 — 10.8%
+CampaignTypes=[]+不传channelType — 10.2%
+不传CampaignTypes+不传channelType — 6.1%
+CampaignTypes=[]+channelType=2 — 4.7%
+CampaignTypes=[]+channelType=1 — 1.7%
+CampaignTypes=[ids+]+channelType=2 — 1.5%</t>
+        </is>
+      </c>
       <c r="G744" s="2" t="n"/>
     </row>
     <row r="745">
@@ -19000,7 +19481,11 @@
       </c>
       <c r="E745" s="2" t="n"/>
       <c r="F745" s="4" t="n"/>
-      <c r="G745" s="2" t="n"/>
+      <c r="G745" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 12次)</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n"/>
@@ -19021,9 +19506,13 @@
       </c>
       <c r="E746" s="2" t="n"/>
       <c r="F746" s="4" t="n"/>
-      <c r="G746" s="2" t="n"/>
-    </row>
-    <row r="747">
+      <c r="G746" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 12次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="747" ht="128" customHeight="1">
       <c r="A747" s="2" t="n"/>
       <c r="B747" s="2" t="inlineStr">
         <is>
@@ -19041,10 +19530,21 @@
         </is>
       </c>
       <c r="E747" s="2" t="n"/>
-      <c r="F747" s="4" t="n"/>
+      <c r="F747" s="7" t="inlineStr">
+        <is>
+          <t>无Tag过滤+campaignStatus=[]+ReportAdType=2 — 44.4%
+按Tag过滤+campaignStatus=[]+ReportAdType=2 — 17.8%
+无Tag过滤+campaignStatus=[]+不传ReportAdType — 14.4%
+按Tag过滤+campaignStatus=[]+不传ReportAdType — 8.0%
+无Tag过滤+campaignStatus=[]+ReportAdType=1 — 7.6%
+按Tag过滤+campaignStatus=[ids+]+ReportAdType=2 — 1.6%
+无Tag过滤+campaignStatus=[]+ReportAdType=0 — 1.6%
+按Tag过滤+campaignStatus=[]+不传ReportAdType — 1.0%</t>
+        </is>
+      </c>
       <c r="G747" s="2" t="n"/>
     </row>
-    <row r="748">
+    <row r="748" ht="112" customHeight="1">
       <c r="A748" s="2" t="n"/>
       <c r="B748" s="2" t="inlineStr">
         <is>
@@ -19062,7 +19562,17 @@
         </is>
       </c>
       <c r="E748" s="2" t="n"/>
-      <c r="F748" s="4" t="n"/>
+      <c r="F748" s="7" t="inlineStr">
+        <is>
+          <t>按Tag过滤+不传market — 33.6%
+无Tag过滤+不传market — 31.4%
+无Tag过滤+market=US — 19.8%
+按Tag过滤+market=US — 7.8%
+按Tag过滤+不传market — 4.0%
+无Tag过滤+market=CA — 1.6%
+按Tag过滤+不传market — 1.0%</t>
+        </is>
+      </c>
       <c r="G748" s="2" t="n"/>
     </row>
     <row r="749">
@@ -19084,7 +19594,11 @@
       </c>
       <c r="E749" s="2" t="n"/>
       <c r="F749" s="4" t="n"/>
-      <c r="G749" s="2" t="n"/>
+      <c r="G749" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 161次)</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n"/>
@@ -19105,9 +19619,13 @@
       </c>
       <c r="E750" s="2" t="n"/>
       <c r="F750" s="4" t="n"/>
-      <c r="G750" s="2" t="n"/>
-    </row>
-    <row r="751">
+      <c r="G750" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 154次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="751" ht="128" customHeight="1">
       <c r="A751" s="2" t="n"/>
       <c r="B751" s="2" t="inlineStr">
         <is>
@@ -19125,10 +19643,21 @@
         </is>
       </c>
       <c r="E751" s="2" t="n"/>
-      <c r="F751" s="4" t="n"/>
+      <c r="F751" s="7" t="inlineStr">
+        <is>
+          <t>不传market+ReportAdType=2 — 48.0%
+market=US+ReportAdType=2 — 30.6%
+不传market+ReportAdType=1 — 6.8%
+market=US+ReportAdType=1 — 4.0%
+不传market+不传ReportAdType — 3.0%
+不传market+ReportAdType=0 — 2.4%
+market=US+不传ReportAdType — 2.2%
+market=US+ReportAdType=0 — 1.2%</t>
+        </is>
+      </c>
       <c r="G751" s="2" t="n"/>
     </row>
-    <row r="752">
+    <row r="752" ht="64" customHeight="1">
       <c r="A752" s="2" t="n"/>
       <c r="B752" s="2" t="inlineStr">
         <is>
@@ -19146,7 +19675,14 @@
         </is>
       </c>
       <c r="E752" s="2" t="n"/>
-      <c r="F752" s="4" t="n"/>
+      <c r="F752" s="7" t="inlineStr">
+        <is>
+          <t>不传market+无Tag过滤 — 44.8%
+market=US+无Tag过滤 — 29.0%
+不传market+按Tag过滤 — 18.8%
+market=US+按Tag过滤 — 5.4%</t>
+        </is>
+      </c>
       <c r="G752" s="2" t="n"/>
     </row>
     <row r="753">
@@ -19168,7 +19704,11 @@
       </c>
       <c r="E753" s="2" t="n"/>
       <c r="F753" s="4" t="n"/>
-      <c r="G753" s="2" t="n"/>
+      <c r="G753" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 255次)</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n"/>
@@ -19189,9 +19729,13 @@
       </c>
       <c r="E754" s="2" t="n"/>
       <c r="F754" s="4" t="n"/>
-      <c r="G754" s="2" t="n"/>
-    </row>
-    <row r="755">
+      <c r="G754" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 256次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="755" ht="112" customHeight="1">
       <c r="A755" s="2" t="n"/>
       <c r="B755" s="2" t="inlineStr">
         <is>
@@ -19209,10 +19753,20 @@
         </is>
       </c>
       <c r="E755" s="2" t="n"/>
-      <c r="F755" s="4" t="n"/>
+      <c r="F755" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2+itemSet=0 — 44.4%
+不传reportAdType+不传itemSet — 26.0%
+不传reportAdType+itemSet=0 — 13.0%
+不传reportAdType+itemSet=1 — 7.1%
+reportAdType=2+itemSet=1 — 5.9%
+不传reportAdType+itemSet=2 — 1.8%
+reportAdType=1+itemSet=0 — 1.8%</t>
+        </is>
+      </c>
       <c r="G755" s="2" t="n"/>
     </row>
-    <row r="756">
+    <row r="756" ht="192" customHeight="1">
       <c r="A756" s="2" t="n"/>
       <c r="B756" s="2" t="inlineStr">
         <is>
@@ -19230,10 +19784,25 @@
         </is>
       </c>
       <c r="E756" s="2" t="n"/>
-      <c r="F756" s="4" t="n"/>
+      <c r="F756" s="7" t="inlineStr">
+        <is>
+          <t>channelType=0+itemSet=0 — 44.0%
+不传channelType+itemSet=0 — 13.6%
+channelType=0+不传itemSet — 12.8%
+channelType=2+不传itemSet — 9.6%
+channelType=2+itemSet=0 — 6.4%
+channelType=0+itemSet=1 — 4.8%
+channelType=2+itemSet=1 — 2.4%
+channelType=1+itemSet=1 — 1.2%
+channelType=2+itemSet=2 — 1.2%
+channelType=1+itemSet=0 — 1.0%
+不传channelType+不传itemSet — 1.0%
+channelType=0+itemSet=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G756" s="2" t="n"/>
     </row>
-    <row r="757">
+    <row r="757" ht="176" customHeight="1">
       <c r="A757" s="2" t="n"/>
       <c r="B757" s="2" t="inlineStr">
         <is>
@@ -19251,10 +19820,24 @@
         </is>
       </c>
       <c r="E757" s="2" t="n"/>
-      <c r="F757" s="4" t="n"/>
+      <c r="F757" s="7" t="inlineStr">
+        <is>
+          <t>channelType=0+itemSet=0 — 41.4%
+不传channelType+itemSet=0 — 14.2%
+channelType=0+不传itemSet — 13.6%
+channelType=2+不传itemSet — 11.4%
+channelType=2+itemSet=0 — 5.8%
+channelType=0+itemSet=1 — 4.4%
+不传channelType+不传itemSet — 2.2%
+channelType=2+itemSet=1 — 2.0%
+channelType=1+itemSet=1 — 1.4%
+channelType=0+itemSet=2 — 1.0%
+channelType=2+itemSet=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G757" s="2" t="n"/>
     </row>
-    <row r="758">
+    <row r="758" ht="192" customHeight="1">
       <c r="A758" s="2" t="n"/>
       <c r="B758" s="2" t="inlineStr">
         <is>
@@ -19272,10 +19855,25 @@
         </is>
       </c>
       <c r="E758" s="2" t="n"/>
-      <c r="F758" s="4" t="n"/>
+      <c r="F758" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 37.2%
+不传itemSet+channelType=0 — 16.2%
+itemSet=0+不传channelType — 13.0%
+不传itemSet+channelType=2 — 11.0%
+itemSet=0+channelType=2 — 5.0%
+itemSet=1+channelType=0 — 3.4%
+不传itemSet+不传channelType — 3.2%
+itemSet=1+channelType=1 — 2.6%
+itemSet=1+channelType=2 — 2.2%
+itemSet=2+channelType=2 — 2.0%
+itemSet=0+channelType=1 — 1.6%
+itemSet=2+channelType=0 — 1.0%</t>
+        </is>
+      </c>
       <c r="G758" s="2" t="n"/>
     </row>
-    <row r="759">
+    <row r="759" ht="176" customHeight="1">
       <c r="A759" s="2" t="n"/>
       <c r="B759" s="2" t="inlineStr">
         <is>
@@ -19293,10 +19891,24 @@
         </is>
       </c>
       <c r="E759" s="2" t="n"/>
-      <c r="F759" s="4" t="n"/>
+      <c r="F759" s="7" t="inlineStr">
+        <is>
+          <t>channelType=0+不传itemSet — 35.7%
+channelType=2+不传itemSet — 22.1%
+channelType=0+itemSet=0 — 20.3%
+不传channelType+不传itemSet — 4.5%
+channelType=1+itemSet=1 — 3.4%
+channelType=2+itemSet=1 — 3.4%
+channelType=0+itemSet=1 — 2.7%
+channelType=2+itemSet=2 — 2.5%
+channelType=2+itemSet=0 — 2.3%
+channelType=0+itemSet=2 — 1.4%
+channelType=1+itemSet=2 — 1.1%</t>
+        </is>
+      </c>
       <c r="G759" s="2" t="n"/>
     </row>
-    <row r="760">
+    <row r="760" ht="240" customHeight="1">
       <c r="A760" s="2" t="n"/>
       <c r="B760" s="2" t="inlineStr">
         <is>
@@ -19314,10 +19926,28 @@
         </is>
       </c>
       <c r="E760" s="2" t="n"/>
-      <c r="F760" s="4" t="n"/>
+      <c r="F760" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 38.2%
+不传itemSet+channelType=0 — 16.0%
+itemSet=0+不传channelType — 9.6%
+不传itemSet+channelType=2 — 9.2%
+itemSet=1+channelType=0 — 7.0%
+itemSet=0+channelType=2 — 6.8%
+itemSet=1+channelType=1 — 2.6%
+itemSet=1+channelType=2 — 2.4%
+itemSet=2+channelType=2 — 1.8%
+不传itemSet+不传channelType — 1.2%
+itemSet=0+channelType=1 — 1.2%
+itemSet=1+不传channelType — 1.0%
+itemSet=2+channelType=0 — 1.0%
+itemSet=2+channelType=1 — 1.0%
+itemSet=2+不传channelType — 1.0%</t>
+        </is>
+      </c>
       <c r="G760" s="2" t="n"/>
     </row>
-    <row r="761">
+    <row r="761" ht="48" customHeight="1">
       <c r="A761" s="2" t="n"/>
       <c r="B761" s="2" t="inlineStr">
         <is>
@@ -19335,7 +19965,13 @@
         </is>
       </c>
       <c r="E761" s="2" t="n"/>
-      <c r="F761" s="4" t="n"/>
+      <c r="F761" s="7" t="inlineStr">
+        <is>
+          <t>不传advertisedItemType+首页 — 74.4%
+advertisedItemType=0+首页 — 24.4%
+advertisedItemType=1+首页 — 1.2%</t>
+        </is>
+      </c>
       <c r="G761" s="2" t="n"/>
     </row>
     <row r="762">
@@ -19357,7 +19993,11 @@
       </c>
       <c r="E762" s="2" t="n"/>
       <c r="F762" s="4" t="n"/>
-      <c r="G762" s="2" t="n"/>
+      <c r="G762" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n"/>
@@ -19378,7 +20018,11 @@
       </c>
       <c r="E763" s="2" t="n"/>
       <c r="F763" s="4" t="n"/>
-      <c r="G763" s="2" t="n"/>
+      <c r="G763" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 27次)</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n"/>
@@ -19399,9 +20043,13 @@
       </c>
       <c r="E764" s="2" t="n"/>
       <c r="F764" s="4" t="n"/>
-      <c r="G764" s="2" t="n"/>
-    </row>
-    <row r="765">
+      <c r="G764" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="765" ht="32" customHeight="1">
       <c r="A765" s="2" t="n"/>
       <c r="B765" s="2" t="inlineStr">
         <is>
@@ -19419,8 +20067,17 @@
         </is>
       </c>
       <c r="E765" s="2" t="n"/>
-      <c r="F765" s="4" t="n"/>
-      <c r="G765" s="2" t="n"/>
+      <c r="F765" s="7" t="inlineStr">
+        <is>
+          <t>不传advertisedItemType+首页 — 66.7%
+advertisedItemType=0+首页 — 33.3%</t>
+        </is>
+      </c>
+      <c r="G765" s="4" t="inlineStr">
+        <is>
+          <t>advertisedItemType=0场景实测HTTP 500"Sequence contains no elements"，疑似真实后端bug(对空集合取首元素)，已如实记FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n"/>
@@ -19441,7 +20098,11 @@
       </c>
       <c r="E766" s="2" t="n"/>
       <c r="F766" s="4" t="n"/>
-      <c r="G766" s="2" t="n"/>
+      <c r="G766" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n"/>
@@ -19462,7 +20123,11 @@
       </c>
       <c r="E767" s="2" t="n"/>
       <c r="F767" s="4" t="n"/>
-      <c r="G767" s="2" t="n"/>
+      <c r="G767" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 170次)</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n"/>
@@ -19483,9 +20148,13 @@
       </c>
       <c r="E768" s="2" t="n"/>
       <c r="F768" s="4" t="n"/>
-      <c r="G768" s="2" t="n"/>
-    </row>
-    <row r="769">
+      <c r="G768" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 171次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="769" ht="176" customHeight="1">
       <c r="A769" s="2" t="n"/>
       <c r="B769" s="2" t="inlineStr">
         <is>
@@ -19503,10 +20172,24 @@
         </is>
       </c>
       <c r="E769" s="2" t="n"/>
-      <c r="F769" s="4" t="n"/>
+      <c r="F769" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 50.4%
+不传itemSet+channelType=0 — 21.6%
+itemSet=0+channelType=2 — 6.6%
+itemSet=1+channelType=0 — 4.2%
+itemSet=0+channelType=1 — 3.8%
+不传itemSet+channelType=2 — 3.4%
+不传itemSet+不传channelType — 2.0%
+itemSet=1+channelType=1 — 2.0%
+itemSet=1+channelType=2 — 1.8%
+itemSet=0+不传channelType — 1.8%
+itemSet=2+channelType=0 — 1.6%</t>
+        </is>
+      </c>
       <c r="G769" s="2" t="n"/>
     </row>
-    <row r="770">
+    <row r="770" ht="96" customHeight="1">
       <c r="A770" s="2" t="n"/>
       <c r="B770" s="2" t="inlineStr">
         <is>
@@ -19524,8 +20207,21 @@
         </is>
       </c>
       <c r="E770" s="2" t="n"/>
-      <c r="F770" s="4" t="n"/>
-      <c r="G770" s="2" t="n"/>
+      <c r="F770" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+按天(dim=1) — 51.4%
+不传itemSet+按天(dim=1) — 19.4%
+itemSet=0+按周(dim=2) — 10.8%
+不传itemSet+按周(dim=2) — 7.8%
+itemSet=1+按天(dim=1) — 7.2%
+itemSet=2+按天(dim=1) — 2.4%</t>
+        </is>
+      </c>
+      <c r="G770" s="4" t="inlineStr">
+        <is>
+          <t>itemSet=2场景实测HTTP 500 buyBoxPct=NaN解析失败，疑似真实后端数据/解析bug，已如实记FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n"/>
@@ -19546,7 +20242,11 @@
       </c>
       <c r="E771" s="2" t="n"/>
       <c r="F771" s="4" t="n"/>
-      <c r="G771" s="2" t="n"/>
+      <c r="G771" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n"/>
@@ -19567,7 +20267,11 @@
       </c>
       <c r="E772" s="2" t="n"/>
       <c r="F772" s="4" t="n"/>
-      <c r="G772" s="2" t="n"/>
+      <c r="G772" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 83次)</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n"/>
@@ -19588,7 +20292,11 @@
       </c>
       <c r="E773" s="2" t="n"/>
       <c r="F773" s="4" t="n"/>
-      <c r="G773" s="2" t="n"/>
+      <c r="G773" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 83次)</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n"/>
@@ -19609,9 +20317,13 @@
       </c>
       <c r="E774" s="2" t="n"/>
       <c r="F774" s="4" t="n"/>
-      <c r="G774" s="2" t="n"/>
-    </row>
-    <row r="775">
+      <c r="G774" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="775" ht="176" customHeight="1">
       <c r="A775" s="2" t="n"/>
       <c r="B775" s="2" t="inlineStr">
         <is>
@@ -19629,10 +20341,24 @@
         </is>
       </c>
       <c r="E775" s="2" t="n"/>
-      <c r="F775" s="4" t="n"/>
+      <c r="F775" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 32.8%
+不传itemSet+channelType=0 — 23.0%
+不传itemSet+channelType=2 — 12.2%
+itemSet=0+不传channelType — 9.8%
+itemSet=0+channelType=2 — 6.6%
+itemSet=1+channelType=1 — 2.8%
+itemSet=1+channelType=0 — 2.6%
+itemSet=1+不传channelType — 2.6%
+itemSet=0+channelType=1 — 2.2%
+不传itemSet+不传channelType — 1.2%
+不传itemSet+channelType=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G775" s="2" t="n"/>
     </row>
-    <row r="776">
+    <row r="776" ht="160" customHeight="1">
       <c r="A776" s="2" t="n"/>
       <c r="B776" s="2" t="inlineStr">
         <is>
@@ -19650,10 +20376,23 @@
         </is>
       </c>
       <c r="E776" s="2" t="n"/>
-      <c r="F776" s="4" t="n"/>
+      <c r="F776" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 33.6%
+不传itemSet+channelType=0 — 23.0%
+不传itemSet+channelType=2 — 11.8%
+itemSet=0+不传channelType — 9.8%
+itemSet=0+channelType=2 — 6.4%
+itemSet=1+channelType=1 — 3.2%
+itemSet=1+channelType=0 — 2.8%
+itemSet=1+不传channelType — 2.4%
+itemSet=0+channelType=1 — 1.8%
+不传itemSet+不传channelType — 1.2%</t>
+        </is>
+      </c>
       <c r="G776" s="2" t="n"/>
     </row>
-    <row r="777">
+    <row r="777" ht="192" customHeight="1">
       <c r="A777" s="2" t="n"/>
       <c r="B777" s="2" t="inlineStr">
         <is>
@@ -19671,10 +20410,25 @@
         </is>
       </c>
       <c r="E777" s="2" t="n"/>
-      <c r="F777" s="4" t="n"/>
+      <c r="F777" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 32.8%
+不传itemSet+channelType=0 — 23.0%
+不传itemSet+channelType=2 — 11.8%
+itemSet=0+不传channelType — 10.2%
+itemSet=0+channelType=2 — 6.8%
+itemSet=1+channelType=1 — 3.4%
+itemSet=1+不传channelType — 2.6%
+itemSet=1+channelType=0 — 2.4%
+itemSet=0+channelType=1 — 1.8%
+不传itemSet+channelType=1 — 1.0%
+不传itemSet+不传channelType — 1.0%
+itemSet=1+channelType=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G777" s="2" t="n"/>
     </row>
-    <row r="778">
+    <row r="778" ht="80" customHeight="1">
       <c r="A778" s="2" t="n"/>
       <c r="B778" s="2" t="inlineStr">
         <is>
@@ -19692,10 +20446,18 @@
         </is>
       </c>
       <c r="E778" s="2" t="n"/>
-      <c r="F778" s="4" t="n"/>
+      <c r="F778" s="7" t="inlineStr">
+        <is>
+          <t>reportType=5+dim=0(汇总) — 50.8%
+reportType=1+dim=&lt;MISSING&gt; — 39.6%
+reportType=3+dim=&lt;MISSING&gt; — 4.6%
+reportType=2+dim=&lt;MISSING&gt; — 3.6%
+reportType=0+dim=&lt;MISSING&gt; — 1.4%</t>
+        </is>
+      </c>
       <c r="G778" s="2" t="n"/>
     </row>
-    <row r="779">
+    <row r="779" ht="192" customHeight="1">
       <c r="A779" s="2" t="n"/>
       <c r="B779" s="2" t="inlineStr">
         <is>
@@ -19713,10 +20475,25 @@
         </is>
       </c>
       <c r="E779" s="2" t="n"/>
-      <c r="F779" s="4" t="n"/>
+      <c r="F779" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 33.0%
+不传itemSet+channelType=0 — 22.4%
+不传itemSet+channelType=2 — 11.8%
+itemSet=0+不传channelType — 10.4%
+itemSet=0+channelType=2 — 6.4%
+itemSet=1+channelType=1 — 3.0%
+itemSet=1+不传channelType — 2.8%
+itemSet=0+channelType=1 — 2.4%
+itemSet=1+channelType=0 — 2.4%
+itemSet=1+channelType=2 — 1.0%
+不传itemSet+不传channelType — 1.0%
+不传itemSet+channelType=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G779" s="2" t="n"/>
     </row>
-    <row r="780">
+    <row r="780" ht="176" customHeight="1">
       <c r="A780" s="2" t="n"/>
       <c r="B780" s="2" t="inlineStr">
         <is>
@@ -19734,10 +20511,24 @@
         </is>
       </c>
       <c r="E780" s="2" t="n"/>
-      <c r="F780" s="4" t="n"/>
+      <c r="F780" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 33.4%
+不传itemSet+channelType=0 — 23.0%
+不传itemSet+channelType=2 — 11.6%
+itemSet=0+不传channelType — 11.2%
+itemSet=0+channelType=2 — 5.8%
+itemSet=1+channelType=1 — 3.4%
+itemSet=1+不传channelType — 3.4%
+itemSet=1+channelType=0 — 2.0%
+itemSet=0+channelType=1 — 1.8%
+itemSet=1+channelType=2 — 1.0%
+不传itemSet+channelType=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G780" s="2" t="n"/>
     </row>
-    <row r="781">
+    <row r="781" ht="128" customHeight="1">
       <c r="A781" s="2" t="n"/>
       <c r="B781" s="2" t="inlineStr">
         <is>
@@ -19755,10 +20546,21 @@
         </is>
       </c>
       <c r="E781" s="2" t="n"/>
-      <c r="F781" s="4" t="n"/>
+      <c r="F781" s="7" t="inlineStr">
+        <is>
+          <t>不传itemSet+reportType=1 — 48.4%
+itemSet=0+reportType=1 — 22.1%
+不传itemSet+reportType=3 — 8.4%
+不传itemSet+reportType=2 — 7.4%
+itemSet=0+reportType=2 — 5.3%
+不传itemSet+reportType=0 — 4.2%
+itemSet=0+reportType=3 — 3.2%
+itemSet=1+reportType=1 — 1.1%</t>
+        </is>
+      </c>
       <c r="G781" s="2" t="n"/>
     </row>
-    <row r="782">
+    <row r="782" ht="80" customHeight="1">
       <c r="A782" s="2" t="n"/>
       <c r="B782" s="2" t="inlineStr">
         <is>
@@ -19776,10 +20578,18 @@
         </is>
       </c>
       <c r="E782" s="2" t="n"/>
-      <c r="F782" s="4" t="n"/>
+      <c r="F782" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+不传market — 40.6%
+不传itemSet+不传market — 31.2%
+itemSet=0+market=US — 18.6%
+不传itemSet+market=US — 5.4%
+itemSet=1+market=US — 2.4%</t>
+        </is>
+      </c>
       <c r="G782" s="2" t="n"/>
     </row>
-    <row r="783">
+    <row r="783" ht="32" customHeight="1">
       <c r="A783" s="2" t="n"/>
       <c r="B783" s="2" t="inlineStr">
         <is>
@@ -19797,7 +20607,12 @@
         </is>
       </c>
       <c r="E783" s="2" t="n"/>
-      <c r="F783" s="4" t="n"/>
+      <c r="F783" s="7" t="inlineStr">
+        <is>
+          <t>channelType=0+按Campaign过滤 — 74.2%
+不传channelType+无Campaign过滤 — 25.8%</t>
+        </is>
+      </c>
       <c r="G783" s="2" t="n"/>
     </row>
     <row r="784">
@@ -19819,7 +20634,11 @@
       </c>
       <c r="E784" s="2" t="n"/>
       <c r="F784" s="4" t="n"/>
-      <c r="G784" s="2" t="n"/>
+      <c r="G784" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 275次)</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n"/>
@@ -19840,9 +20659,13 @@
       </c>
       <c r="E785" s="2" t="n"/>
       <c r="F785" s="4" t="n"/>
-      <c r="G785" s="2" t="n"/>
-    </row>
-    <row r="786">
+      <c r="G785" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 276次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="786" ht="80" customHeight="1">
       <c r="A786" s="2" t="n"/>
       <c r="B786" s="2" t="inlineStr">
         <is>
@@ -19860,10 +20683,18 @@
         </is>
       </c>
       <c r="E786" s="2" t="n"/>
-      <c r="F786" s="4" t="n"/>
+      <c r="F786" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+不传market — 44.6%
+不传itemSet+不传market — 28.6%
+itemSet=0+market=US — 19.8%
+不传itemSet+market=US — 5.4%
+itemSet=1+market=US — 1.4%</t>
+        </is>
+      </c>
       <c r="G786" s="2" t="n"/>
     </row>
-    <row r="787">
+    <row r="787" ht="112" customHeight="1">
       <c r="A787" s="2" t="n"/>
       <c r="B787" s="2" t="inlineStr">
         <is>
@@ -19881,7 +20712,17 @@
         </is>
       </c>
       <c r="E787" s="2" t="n"/>
-      <c r="F787" s="4" t="n"/>
+      <c r="F787" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+按Campaign过滤 — 41.4%
+不传itemSet+按Campaign过滤 — 28.6%
+itemSet=0+不传campaignIds — 10.8%
+itemSet=0+无Campaign过滤 — 10.0%
+不传itemSet+无Campaign过滤 — 5.0%
+不传itemSet+不传campaignIds — 2.2%
+itemSet=1+按Campaign过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G787" s="2" t="n"/>
     </row>
     <row r="788">
@@ -19903,7 +20744,11 @@
       </c>
       <c r="E788" s="2" t="n"/>
       <c r="F788" s="4" t="n"/>
-      <c r="G788" s="2" t="n"/>
+      <c r="G788" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 36次)</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n"/>
@@ -19924,9 +20769,13 @@
       </c>
       <c r="E789" s="2" t="n"/>
       <c r="F789" s="4" t="n"/>
-      <c r="G789" s="2" t="n"/>
-    </row>
-    <row r="790">
+      <c r="G789" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 36次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="790" ht="192" customHeight="1">
       <c r="A790" s="2" t="n"/>
       <c r="B790" s="2" t="inlineStr">
         <is>
@@ -19944,10 +20793,25 @@
         </is>
       </c>
       <c r="E790" s="2" t="n"/>
-      <c r="F790" s="4" t="n"/>
+      <c r="F790" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 35.9%
+不传itemSet+channelType=0 — 32.5%
+itemSet=0+不传channelType — 7.2%
+itemSet=0+channelType=1 — 5.3%
+不传itemSet+channelType=1 — 2.9%
+itemSet=1+channelType=0 — 2.4%
+itemSet=0+channelType=2 — 2.4%
+itemSet=1+不传channelType — 2.4%
+itemSet=1+channelType=2 — 2.4%
+itemSet=2+channelType=0 — 1.9%
+itemSet=1+channelType=1 — 1.9%
+itemSet=2+不传channelType — 1.4%</t>
+        </is>
+      </c>
       <c r="G790" s="2" t="n"/>
     </row>
-    <row r="791">
+    <row r="791" ht="192" customHeight="1">
       <c r="A791" s="2" t="n"/>
       <c r="B791" s="2" t="inlineStr">
         <is>
@@ -19965,10 +20829,25 @@
         </is>
       </c>
       <c r="E791" s="2" t="n"/>
-      <c r="F791" s="4" t="n"/>
+      <c r="F791" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 35.9%
+不传itemSet+channelType=0 — 32.5%
+itemSet=0+不传channelType — 7.2%
+itemSet=0+channelType=1 — 5.3%
+不传itemSet+channelType=1 — 2.9%
+itemSet=0+channelType=2 — 2.4%
+itemSet=1+channelType=0 — 2.4%
+itemSet=1+channelType=2 — 2.4%
+itemSet=1+不传channelType — 2.4%
+itemSet=2+channelType=0 — 1.9%
+itemSet=1+channelType=1 — 1.9%
+itemSet=2+不传channelType — 1.4%</t>
+        </is>
+      </c>
       <c r="G791" s="2" t="n"/>
     </row>
-    <row r="792">
+    <row r="792" ht="192" customHeight="1">
       <c r="A792" s="2" t="n"/>
       <c r="B792" s="2" t="inlineStr">
         <is>
@@ -19986,10 +20865,25 @@
         </is>
       </c>
       <c r="E792" s="2" t="n"/>
-      <c r="F792" s="4" t="n"/>
+      <c r="F792" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 35.9%
+不传itemSet+channelType=0 — 32.5%
+itemSet=0+不传channelType — 7.2%
+itemSet=0+channelType=1 — 5.3%
+不传itemSet+channelType=1 — 2.9%
+itemSet=1+channelType=0 — 2.4%
+itemSet=1+不传channelType — 2.4%
+itemSet=1+channelType=2 — 2.4%
+itemSet=0+channelType=2 — 2.4%
+itemSet=2+channelType=0 — 1.9%
+itemSet=1+channelType=1 — 1.9%
+itemSet=2+不传channelType — 1.4%</t>
+        </is>
+      </c>
       <c r="G792" s="2" t="n"/>
     </row>
-    <row r="793">
+    <row r="793" ht="192" customHeight="1">
       <c r="A793" s="2" t="n"/>
       <c r="B793" s="2" t="inlineStr">
         <is>
@@ -20007,7 +20901,22 @@
         </is>
       </c>
       <c r="E793" s="2" t="n"/>
-      <c r="F793" s="4" t="n"/>
+      <c r="F793" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 35.9%
+不传itemSet+channelType=0 — 32.5%
+itemSet=0+不传channelType — 7.2%
+itemSet=0+channelType=1 — 5.3%
+不传itemSet+channelType=1 — 2.9%
+itemSet=1+不传channelType — 2.4%
+itemSet=1+channelType=2 — 2.4%
+itemSet=1+channelType=0 — 2.4%
+itemSet=0+channelType=2 — 2.4%
+itemSet=1+channelType=1 — 1.9%
+itemSet=2+channelType=0 — 1.9%
+itemSet=2+不传channelType — 1.4%</t>
+        </is>
+      </c>
       <c r="G793" s="2" t="n"/>
     </row>
     <row r="794">
@@ -20029,7 +20938,11 @@
       </c>
       <c r="E794" s="2" t="n"/>
       <c r="F794" s="4" t="n"/>
-      <c r="G794" s="2" t="n"/>
+      <c r="G794" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n"/>
@@ -20050,7 +20963,11 @@
       </c>
       <c r="E795" s="2" t="n"/>
       <c r="F795" s="4" t="n"/>
-      <c r="G795" s="2" t="n"/>
+      <c r="G795" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n"/>
@@ -20071,7 +20988,11 @@
       </c>
       <c r="E796" s="2" t="n"/>
       <c r="F796" s="4" t="n"/>
-      <c r="G796" s="2" t="n"/>
+      <c r="G796" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n"/>
@@ -20092,7 +21013,11 @@
       </c>
       <c r="E797" s="2" t="n"/>
       <c r="F797" s="4" t="n"/>
-      <c r="G797" s="2" t="n"/>
+      <c r="G797" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n"/>
@@ -20113,7 +21038,11 @@
       </c>
       <c r="E798" s="2" t="n"/>
       <c r="F798" s="4" t="n"/>
-      <c r="G798" s="2" t="n"/>
+      <c r="G798" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 83次)</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n"/>
@@ -20134,9 +21063,13 @@
       </c>
       <c r="E799" s="2" t="n"/>
       <c r="F799" s="4" t="n"/>
-      <c r="G799" s="2" t="n"/>
-    </row>
-    <row r="800">
+      <c r="G799" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 83次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="800" ht="176" customHeight="1">
       <c r="A800" s="2" t="n"/>
       <c r="B800" s="2" t="inlineStr">
         <is>
@@ -20154,10 +21087,24 @@
         </is>
       </c>
       <c r="E800" s="2" t="n"/>
-      <c r="F800" s="4" t="n"/>
+      <c r="F800" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 44.8%
+不传itemSet+channelType=0 — 17.8%
+itemSet=1+channelType=2 — 7.7%
+itemSet=0+channelType=2 — 5.4%
+itemSet=0+不传channelType — 5.4%
+itemSet=1+channelType=0 — 5.4%
+不传itemSet+channelType=2 — 4.7%
+itemSet=2+channelType=2 — 2.4%
+itemSet=1+channelType=1 — 1.9%
+itemSet=0+channelType=1 — 1.5%
+itemSet=2+channelType=0 — 1.3%</t>
+        </is>
+      </c>
       <c r="G800" s="2" t="n"/>
     </row>
-    <row r="801">
+    <row r="801" ht="176" customHeight="1">
       <c r="A801" s="2" t="n"/>
       <c r="B801" s="2" t="inlineStr">
         <is>
@@ -20175,10 +21122,24 @@
         </is>
       </c>
       <c r="E801" s="2" t="n"/>
-      <c r="F801" s="4" t="n"/>
+      <c r="F801" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 44.8%
+不传itemSet+channelType=0 — 17.8%
+itemSet=1+channelType=2 — 7.7%
+itemSet=0+不传channelType — 5.4%
+itemSet=0+channelType=2 — 5.4%
+itemSet=1+channelType=0 — 5.4%
+不传itemSet+channelType=2 — 4.7%
+itemSet=2+channelType=2 — 2.4%
+itemSet=1+channelType=1 — 1.9%
+itemSet=0+channelType=1 — 1.5%
+itemSet=2+channelType=0 — 1.3%</t>
+        </is>
+      </c>
       <c r="G801" s="2" t="n"/>
     </row>
-    <row r="802">
+    <row r="802" ht="176" customHeight="1">
       <c r="A802" s="2" t="n"/>
       <c r="B802" s="2" t="inlineStr">
         <is>
@@ -20196,10 +21157,24 @@
         </is>
       </c>
       <c r="E802" s="2" t="n"/>
-      <c r="F802" s="4" t="n"/>
+      <c r="F802" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 44.8%
+不传itemSet+channelType=0 — 17.8%
+itemSet=1+channelType=2 — 7.7%
+itemSet=0+不传channelType — 5.4%
+itemSet=0+channelType=2 — 5.4%
+itemSet=1+channelType=0 — 5.4%
+不传itemSet+channelType=2 — 4.7%
+itemSet=2+channelType=2 — 2.4%
+itemSet=1+channelType=1 — 1.9%
+itemSet=0+channelType=1 — 1.5%
+itemSet=2+channelType=0 — 1.3%</t>
+        </is>
+      </c>
       <c r="G802" s="2" t="n"/>
     </row>
-    <row r="803">
+    <row r="803" ht="176" customHeight="1">
       <c r="A803" s="2" t="n"/>
       <c r="B803" s="2" t="inlineStr">
         <is>
@@ -20217,7 +21192,21 @@
         </is>
       </c>
       <c r="E803" s="2" t="n"/>
-      <c r="F803" s="4" t="n"/>
+      <c r="F803" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+channelType=0 — 45.0%
+不传itemSet+channelType=0 — 17.8%
+itemSet=1+channelType=2 — 7.7%
+itemSet=0+不传channelType — 5.4%
+itemSet=1+channelType=0 — 5.4%
+itemSet=0+channelType=2 — 5.4%
+不传itemSet+channelType=2 — 4.7%
+itemSet=2+channelType=2 — 2.4%
+itemSet=1+channelType=1 — 1.9%
+itemSet=0+channelType=1 — 1.5%
+itemSet=2+channelType=0 — 1.3%</t>
+        </is>
+      </c>
       <c r="G803" s="2" t="n"/>
     </row>
     <row r="804">
@@ -20239,7 +21228,11 @@
       </c>
       <c r="E804" s="2" t="n"/>
       <c r="F804" s="4" t="n"/>
-      <c r="G804" s="2" t="n"/>
+      <c r="G804" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 33次)</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n"/>
@@ -20260,9 +21253,13 @@
       </c>
       <c r="E805" s="2" t="n"/>
       <c r="F805" s="4" t="n"/>
-      <c r="G805" s="2" t="n"/>
-    </row>
-    <row r="806">
+      <c r="G805" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 33次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806" ht="112" customHeight="1">
       <c r="A806" s="2" t="n"/>
       <c r="B806" s="2" t="inlineStr">
         <is>
@@ -20280,10 +21277,24 @@
         </is>
       </c>
       <c r="E806" s="2" t="n"/>
-      <c r="F806" s="4" t="n"/>
-      <c r="G806" s="2" t="n"/>
-    </row>
-    <row r="807">
+      <c r="F806" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+无CampaignTag过滤 — 46.1%
+itemSet=0+按CampaignTag过滤 — 18.6%
+不传itemSet+无CampaignTag过滤 — 17.4%
+itemSet=1+无CampaignTag过滤 — 7.8%
+itemSet=2+无CampaignTag过滤 — 3.6%
+不传itemSet+按CampaignTag过滤 — 3.0%
+itemSet=0+按CampaignTag过滤 — 1.2%</t>
+        </is>
+      </c>
+      <c r="G806" s="4" t="inlineStr">
+        <is>
+          <t>不加CampaignTag过滤时全部itemSet取值实测HTTP 500"Arithmetic overflow error"，稳定复现，疑似真实后端bug，已如实记FAIL(4/7场景)</t>
+        </is>
+      </c>
+    </row>
+    <row r="807" ht="112" customHeight="1">
       <c r="A807" s="2" t="n"/>
       <c r="B807" s="2" t="inlineStr">
         <is>
@@ -20301,10 +21312,20 @@
         </is>
       </c>
       <c r="E807" s="2" t="n"/>
-      <c r="F807" s="4" t="n"/>
+      <c r="F807" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+无CampaignTag过滤 — 45.8%
+itemSet=0+按CampaignTag过滤 — 18.7%
+不传itemSet+无CampaignTag过滤 — 17.5%
+itemSet=1+无CampaignTag过滤 — 7.8%
+itemSet=2+无CampaignTag过滤 — 3.6%
+不传itemSet+按CampaignTag过滤 — 3.0%
+itemSet=0+按CampaignTag过滤 — 1.2%</t>
+        </is>
+      </c>
       <c r="G807" s="2" t="n"/>
     </row>
-    <row r="808">
+    <row r="808" ht="112" customHeight="1">
       <c r="A808" s="2" t="n"/>
       <c r="B808" s="2" t="inlineStr">
         <is>
@@ -20322,10 +21343,20 @@
         </is>
       </c>
       <c r="E808" s="2" t="n"/>
-      <c r="F808" s="4" t="n"/>
+      <c r="F808" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+无CampaignTag过滤 — 45.8%
+itemSet=0+按CampaignTag过滤 — 18.7%
+不传itemSet+无CampaignTag过滤 — 17.5%
+itemSet=1+无CampaignTag过滤 — 7.8%
+itemSet=2+无CampaignTag过滤 — 3.6%
+不传itemSet+按CampaignTag过滤 — 3.0%
+itemSet=0+按CampaignTag过滤 — 1.2%</t>
+        </is>
+      </c>
       <c r="G808" s="2" t="n"/>
     </row>
-    <row r="809">
+    <row r="809" ht="112" customHeight="1">
       <c r="A809" s="2" t="n"/>
       <c r="B809" s="2" t="inlineStr">
         <is>
@@ -20343,7 +21374,17 @@
         </is>
       </c>
       <c r="E809" s="2" t="n"/>
-      <c r="F809" s="4" t="n"/>
+      <c r="F809" s="7" t="inlineStr">
+        <is>
+          <t>itemSet=0+无CampaignTag过滤 — 45.8%
+itemSet=0+按CampaignTag过滤 — 18.7%
+不传itemSet+无CampaignTag过滤 — 17.5%
+itemSet=1+无CampaignTag过滤 — 7.8%
+itemSet=2+无CampaignTag过滤 — 3.6%
+不传itemSet+按CampaignTag过滤 — 3.0%
+itemSet=0+按CampaignTag过滤 — 1.2%</t>
+        </is>
+      </c>
       <c r="G809" s="2" t="n"/>
     </row>
     <row r="810">
@@ -20365,7 +21406,11 @@
       </c>
       <c r="E810" s="2" t="n"/>
       <c r="F810" s="4" t="n"/>
-      <c r="G810" s="2" t="n"/>
+      <c r="G810" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n"/>
@@ -20386,7 +21431,11 @@
       </c>
       <c r="E811" s="2" t="n"/>
       <c r="F811" s="4" t="n"/>
-      <c r="G811" s="2" t="n"/>
+      <c r="G811" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n"/>
@@ -20407,7 +21456,11 @@
       </c>
       <c r="E812" s="2" t="n"/>
       <c r="F812" s="4" t="n"/>
-      <c r="G812" s="2" t="n"/>
+      <c r="G812" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 58次)</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n"/>
@@ -20428,9 +21481,13 @@
       </c>
       <c r="E813" s="2" t="n"/>
       <c r="F813" s="4" t="n"/>
-      <c r="G813" s="2" t="n"/>
-    </row>
-    <row r="814">
+      <c r="G813" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 58次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="814" ht="176" customHeight="1">
       <c r="A814" s="2" t="n"/>
       <c r="B814" s="2" t="inlineStr">
         <is>
@@ -20448,7 +21505,21 @@
         </is>
       </c>
       <c r="E814" s="2" t="n"/>
-      <c r="F814" s="4" t="n"/>
+      <c r="F814" s="7" t="inlineStr">
+        <is>
+          <t>不传adType+不传itemSet — 37.8%
+adType=2+itemSet=0 — 21.8%
+adType=2+不传itemSet — 11.6%
+adType=0+不传itemSet — 6.6%
+adType=1+不传itemSet — 6.6%
+adType=1+itemSet=1 — 6.0%
+adType=0+itemSet=0 — 2.2%
+adType=2+itemSet=1 — 2.2%
+adType=2+itemSet=2 — 1.6%
+adType=1+itemSet=2 — 1.6%
+adType=1+itemSet=0 — 1.2%</t>
+        </is>
+      </c>
       <c r="G814" s="2" t="n"/>
     </row>
     <row r="815">
@@ -20470,9 +21541,13 @@
       </c>
       <c r="E815" s="2" t="n"/>
       <c r="F815" s="4" t="n"/>
-      <c r="G815" s="2" t="n"/>
-    </row>
-    <row r="816">
+      <c r="G815" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="816" ht="176" customHeight="1">
       <c r="A816" s="2" t="n"/>
       <c r="B816" s="2" t="inlineStr">
         <is>
@@ -20490,10 +21565,24 @@
         </is>
       </c>
       <c r="E816" s="2" t="n"/>
-      <c r="F816" s="4" t="n"/>
+      <c r="F816" s="7" t="inlineStr">
+        <is>
+          <t>不传adType+不传itemSet — 36.6%
+adType=2+itemSet=0 — 23.6%
+adType=2+不传itemSet — 9.8%
+adType=1+不传itemSet — 7.0%
+adType=1+itemSet=1 — 6.8%
+adType=0+不传itemSet — 6.6%
+adType=0+itemSet=0 — 2.6%
+adType=2+itemSet=1 — 2.0%
+adType=1+itemSet=2 — 1.6%
+adType=2+itemSet=2 — 1.0%
+adType=0+itemSet=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G816" s="2" t="n"/>
     </row>
-    <row r="817">
+    <row r="817" ht="176" customHeight="1">
       <c r="A817" s="2" t="n"/>
       <c r="B817" s="2" t="inlineStr">
         <is>
@@ -20511,10 +21600,24 @@
         </is>
       </c>
       <c r="E817" s="2" t="n"/>
-      <c r="F817" s="4" t="n"/>
+      <c r="F817" s="7" t="inlineStr">
+        <is>
+          <t>不传adType+不传itemSet — 36.2%
+adType=2+itemSet=0 — 22.2%
+adType=2+不传itemSet — 10.0%
+adType=1+itemSet=1 — 7.2%
+adType=1+不传itemSet — 6.6%
+adType=0+不传itemSet — 6.0%
+adType=2+itemSet=1 — 3.0%
+adType=0+itemSet=0 — 2.8%
+adType=2+itemSet=2 — 2.2%
+adType=1+itemSet=2 — 1.8%
+adType=1+itemSet=0 — 1.4%</t>
+        </is>
+      </c>
       <c r="G817" s="2" t="n"/>
     </row>
-    <row r="818">
+    <row r="818" ht="176" customHeight="1">
       <c r="A818" s="2" t="n"/>
       <c r="B818" s="2" t="inlineStr">
         <is>
@@ -20532,10 +21635,24 @@
         </is>
       </c>
       <c r="E818" s="2" t="n"/>
-      <c r="F818" s="4" t="n"/>
+      <c r="F818" s="7" t="inlineStr">
+        <is>
+          <t>不传adType+不传itemSet — 35.4%
+adType=2+itemSet=0 — 24.2%
+adType=2+不传itemSet — 8.8%
+adType=1+itemSet=1 — 7.6%
+adType=1+不传itemSet — 7.6%
+adType=0+不传itemSet — 5.4%
+adType=0+itemSet=0 — 2.4%
+adType=2+itemSet=2 — 2.4%
+adType=2+itemSet=1 — 2.4%
+adType=1+itemSet=2 — 1.6%
+adType=1+itemSet=0 — 1.2%</t>
+        </is>
+      </c>
       <c r="G818" s="2" t="n"/>
     </row>
-    <row r="819">
+    <row r="819" ht="176" customHeight="1">
       <c r="A819" s="2" t="n"/>
       <c r="B819" s="2" t="inlineStr">
         <is>
@@ -20553,7 +21670,21 @@
         </is>
       </c>
       <c r="E819" s="2" t="n"/>
-      <c r="F819" s="4" t="n"/>
+      <c r="F819" s="7" t="inlineStr">
+        <is>
+          <t>不传adType+不传itemSet — 31.8%
+adType=2+itemSet=0 — 22.8%
+adType=2+不传itemSet — 11.4%
+adType=0+不传itemSet — 8.8%
+adType=1+itemSet=1 — 8.0%
+adType=1+不传itemSet — 6.6%
+adType=0+itemSet=0 — 2.8%
+adType=2+itemSet=1 — 2.8%
+adType=2+itemSet=2 — 2.2%
+adType=1+itemSet=0 — 1.2%
+adType=1+itemSet=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G819" s="2" t="n"/>
     </row>
     <row r="820">
@@ -20575,7 +21706,11 @@
       </c>
       <c r="E820" s="2" t="n"/>
       <c r="F820" s="4" t="n"/>
-      <c r="G820" s="2" t="n"/>
+      <c r="G820" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n"/>
@@ -20596,7 +21731,11 @@
       </c>
       <c r="E821" s="2" t="n"/>
       <c r="F821" s="4" t="n"/>
-      <c r="G821" s="2" t="n"/>
+      <c r="G821" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n"/>
@@ -20617,7 +21756,11 @@
       </c>
       <c r="E822" s="2" t="n"/>
       <c r="F822" s="4" t="n"/>
-      <c r="G822" s="2" t="n"/>
+      <c r="G822" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n"/>
@@ -20638,7 +21781,11 @@
       </c>
       <c r="E823" s="2" t="n"/>
       <c r="F823" s="4" t="n"/>
-      <c r="G823" s="2" t="n"/>
+      <c r="G823" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n"/>
@@ -20659,7 +21806,11 @@
       </c>
       <c r="E824" s="2" t="n"/>
       <c r="F824" s="4" t="n"/>
-      <c r="G824" s="2" t="n"/>
+      <c r="G824" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,6 +125,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -956,9 +959,19 @@
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="F18" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>96%(22执行,写操作21条未执行不计入)</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>48% (31/65)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9972,7 +9985,11 @@
       </c>
       <c r="E338" s="2" t="n"/>
       <c r="F338" s="4" t="n"/>
-      <c r="G338" s="2" t="n"/>
+      <c r="G338" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -9992,8 +10009,16 @@
         </is>
       </c>
       <c r="E339" s="2" t="n"/>
-      <c r="F339" s="4" t="n"/>
-      <c r="G339" s="2" t="n"/>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】创建/更新Campaign(单条，含campaignId表示更新)</t>
+        </is>
+      </c>
+      <c r="G339" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -10013,8 +10038,16 @@
         </is>
       </c>
       <c r="E340" s="2" t="n"/>
-      <c r="F340" s="4" t="n"/>
-      <c r="G340" s="2" t="n"/>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】更新Campaign(如结束日期/竞价策略)</t>
+        </is>
+      </c>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -10035,7 +10068,11 @@
       </c>
       <c r="E341" s="2" t="n"/>
       <c r="F341" s="4" t="n"/>
-      <c r="G341" s="2" t="n"/>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -10056,7 +10093,11 @@
       </c>
       <c r="E342" s="2" t="n"/>
       <c r="F342" s="4" t="n"/>
-      <c r="G342" s="2" t="n"/>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -10076,8 +10117,16 @@
         </is>
       </c>
       <c r="E343" s="2" t="n"/>
-      <c r="F343" s="4" t="n"/>
-      <c r="G343" s="2" t="n"/>
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】复制AdGroup(创建新AdGroup)</t>
+        </is>
+      </c>
+      <c r="G343" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -10097,8 +10146,16 @@
         </is>
       </c>
       <c r="E344" s="2" t="n"/>
-      <c r="F344" s="4" t="n"/>
-      <c r="G344" s="2" t="n"/>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按Placement设置竞价乘数</t>
+        </is>
+      </c>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -10118,8 +10175,16 @@
         </is>
       </c>
       <c r="E345" s="2" t="n"/>
-      <c r="F345" s="4" t="n"/>
-      <c r="G345" s="2" t="n"/>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量设置Placement竞价乘数</t>
+        </is>
+      </c>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -10140,7 +10205,11 @@
       </c>
       <c r="E346" s="2" t="n"/>
       <c r="F346" s="4" t="n"/>
-      <c r="G346" s="2" t="n"/>
+      <c r="G346" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -10161,7 +10230,11 @@
       </c>
       <c r="E347" s="2" t="n"/>
       <c r="F347" s="4" t="n"/>
-      <c r="G347" s="2" t="n"/>
+      <c r="G347" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -10182,7 +10255,11 @@
       </c>
       <c r="E348" s="2" t="n"/>
       <c r="F348" s="4" t="n"/>
-      <c r="G348" s="2" t="n"/>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -10202,8 +10279,16 @@
         </is>
       </c>
       <c r="E349" s="2" t="n"/>
-      <c r="F349" s="4" t="n"/>
-      <c r="G349" s="2" t="n"/>
+      <c r="F349" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按Platform(Desktop/App/Mobile)设置竞价乘数</t>
+        </is>
+      </c>
+      <c r="G349" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -10223,8 +10308,16 @@
         </is>
       </c>
       <c r="E350" s="2" t="n"/>
-      <c r="F350" s="4" t="n"/>
-      <c r="G350" s="2" t="n"/>
+      <c r="F350" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量设置Platform竞价乘数</t>
+        </is>
+      </c>
+      <c r="G350" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -10245,7 +10338,11 @@
       </c>
       <c r="E351" s="2" t="n"/>
       <c r="F351" s="4" t="n"/>
-      <c r="G351" s="2" t="n"/>
+      <c r="G351" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -10265,8 +10362,16 @@
         </is>
       </c>
       <c r="E352" s="2" t="n"/>
-      <c r="F352" s="4" t="n"/>
-      <c r="G352" s="2" t="n"/>
+      <c r="F352" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量修改日预算</t>
+        </is>
+      </c>
+      <c r="G352" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -10286,8 +10391,16 @@
         </is>
       </c>
       <c r="E353" s="2" t="n"/>
-      <c r="F353" s="4" t="n"/>
-      <c r="G353" s="2" t="n"/>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量修改日预算</t>
+        </is>
+      </c>
+      <c r="G353" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -10307,10 +10420,18 @@
         </is>
       </c>
       <c r="E354" s="2" t="n"/>
-      <c r="F354" s="4" t="n"/>
-      <c r="G354" s="2" t="n"/>
-    </row>
-    <row r="355">
+      <c r="F354" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量修改结束日期</t>
+        </is>
+      </c>
+      <c r="G354" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="16" customHeight="1">
       <c r="A355" s="2" t="n"/>
       <c r="B355" s="2" t="inlineStr">
         <is>
@@ -10328,10 +10449,14 @@
         </is>
       </c>
       <c r="E355" s="2" t="n"/>
-      <c r="F355" s="4" t="n"/>
+      <c r="F355" s="7" t="inlineStr">
+        <is>
+          <t>默认分页查询 — 100.0%</t>
+        </is>
+      </c>
       <c r="G355" s="2" t="n"/>
     </row>
-    <row r="356">
+    <row r="356" ht="144" customHeight="1">
       <c r="A356" s="2" t="n"/>
       <c r="B356" s="2" t="inlineStr">
         <is>
@@ -10349,10 +10474,22 @@
         </is>
       </c>
       <c r="E356" s="2" t="n"/>
-      <c r="F356" s="4" t="n"/>
+      <c r="F356" s="7" t="inlineStr">
+        <is>
+          <t>pageType=campaign+含patchIds — 31.7%
+pageType=campaign+不含patchIds — 18.0%
+pageType=adGroup+含patchIds — 13.4%
+pageType=keyword+不含patchIds — 8.8%
+pageType=keyword+含patchIds — 8.3%
+pageType=adItem+含patchIds — 8.0%
+pageType=negativeKeyword+含patchIds — 4.6%
+pageType=adItem+不含patchIds — 3.7%
+pageType=adGroup+不含patchIds — 2.4%</t>
+        </is>
+      </c>
       <c r="G356" s="2" t="n"/>
     </row>
-    <row r="357">
+    <row r="357" ht="64" customHeight="1">
       <c r="A357" s="2" t="n"/>
       <c r="B357" s="2" t="inlineStr">
         <is>
@@ -10370,7 +10507,14 @@
         </is>
       </c>
       <c r="E357" s="2" t="n"/>
-      <c r="F357" s="4" t="n"/>
+      <c r="F357" s="7" t="inlineStr">
+        <is>
+          <t>不含campaignSetting+impr=0 — 73.8%
+含campaignSetting+impr=0 — 19.2%
+不含campaignSetting+impr=1 — 6.0%
+含campaignSetting+impr=1 — 1.0%</t>
+        </is>
+      </c>
       <c r="G357" s="2" t="n"/>
     </row>
     <row r="358">
@@ -10392,7 +10536,11 @@
       </c>
       <c r="E358" s="2" t="n"/>
       <c r="F358" s="4" t="n"/>
-      <c r="G358" s="2" t="n"/>
+      <c r="G358" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -10413,7 +10561,11 @@
       </c>
       <c r="E359" s="2" t="n"/>
       <c r="F359" s="4" t="n"/>
-      <c r="G359" s="2" t="n"/>
+      <c r="G359" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 492次)</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -10434,7 +10586,11 @@
       </c>
       <c r="E360" s="2" t="n"/>
       <c r="F360" s="4" t="n"/>
-      <c r="G360" s="2" t="n"/>
+      <c r="G360" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -10455,7 +10611,11 @@
       </c>
       <c r="E361" s="2" t="n"/>
       <c r="F361" s="4" t="n"/>
-      <c r="G361" s="2" t="n"/>
+      <c r="G361" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 173次)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -10476,7 +10636,11 @@
       </c>
       <c r="E362" s="2" t="n"/>
       <c r="F362" s="4" t="n"/>
-      <c r="G362" s="2" t="n"/>
+      <c r="G362" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 56次)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -10497,7 +10661,11 @@
       </c>
       <c r="E363" s="2" t="n"/>
       <c r="F363" s="4" t="n"/>
-      <c r="G363" s="2" t="n"/>
+      <c r="G363" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 40次)</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -10518,7 +10686,11 @@
       </c>
       <c r="E364" s="2" t="n"/>
       <c r="F364" s="4" t="n"/>
-      <c r="G364" s="2" t="n"/>
+      <c r="G364" s="4" t="inlineStr">
+        <is>
+          <t>依赖用户预先上传的Bulk文件(fileName由上传步骤生成，具时效性)，无法脱离上传步骤单独重放，暂不覆盖(365d 2596次)</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -10539,7 +10711,11 @@
       </c>
       <c r="E365" s="2" t="n"/>
       <c r="F365" s="4" t="n"/>
-      <c r="G365" s="2" t="n"/>
+      <c r="G365" s="4" t="inlineStr">
+        <is>
+          <t>依赖用户预先上传的Bulk文件(fileName由上传步骤生成，具时效性)，无法脱离上传步骤单独重放，暂不覆盖(365d 86次)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -10560,7 +10736,11 @@
       </c>
       <c r="E366" s="2" t="n"/>
       <c r="F366" s="4" t="n"/>
-      <c r="G366" s="2" t="n"/>
+      <c r="G366" s="4" t="inlineStr">
+        <is>
+          <t>依赖用户预先上传的Bulk文件(fileName由上传步骤生成，具时效性)，无法脱离上传步骤单独重放，暂不覆盖(365d 55次)</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -10580,8 +10760,16 @@
         </is>
       </c>
       <c r="E367" s="2" t="n"/>
-      <c r="F367" s="4" t="n"/>
-      <c r="G367" s="2" t="n"/>
+      <c r="F367" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】上传Bulk批量操作文件</t>
+        </is>
+      </c>
+      <c r="G367" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -10601,8 +10789,16 @@
         </is>
       </c>
       <c r="E368" s="2" t="n"/>
-      <c r="F368" s="4" t="n"/>
-      <c r="G368" s="2" t="n"/>
+      <c r="F368" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量修改总预算</t>
+        </is>
+      </c>
+      <c r="G368" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -10622,8 +10818,16 @@
         </is>
       </c>
       <c r="E369" s="2" t="n"/>
-      <c r="F369" s="4" t="n"/>
-      <c r="G369" s="2" t="n"/>
+      <c r="F369" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量修改总预算</t>
+        </is>
+      </c>
+      <c r="G369" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -10643,8 +10847,16 @@
         </is>
       </c>
       <c r="E370" s="2" t="n"/>
-      <c r="F370" s="4" t="n"/>
-      <c r="G370" s="2" t="n"/>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】复制Campaign(创建新Campaign)</t>
+        </is>
+      </c>
+      <c r="G370" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -10665,7 +10877,11 @@
       </c>
       <c r="E371" s="2" t="n"/>
       <c r="F371" s="4" t="n"/>
-      <c r="G371" s="2" t="n"/>
+      <c r="G371" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -10686,7 +10902,11 @@
       </c>
       <c r="E372" s="2" t="n"/>
       <c r="F372" s="4" t="n"/>
-      <c r="G372" s="2" t="n"/>
+      <c r="G372" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -10706,8 +10926,16 @@
         </is>
       </c>
       <c r="E373" s="2" t="n"/>
-      <c r="F373" s="4" t="n"/>
-      <c r="G373" s="2" t="n"/>
+      <c r="F373" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】设置Campaign的Placement投放开关</t>
+        </is>
+      </c>
+      <c r="G373" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -10728,7 +10956,11 @@
       </c>
       <c r="E374" s="2" t="n"/>
       <c r="F374" s="4" t="n"/>
-      <c r="G374" s="2" t="n"/>
+      <c r="G374" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -10749,7 +10981,11 @@
       </c>
       <c r="E375" s="2" t="n"/>
       <c r="F375" s="4" t="n"/>
-      <c r="G375" s="2" t="n"/>
+      <c r="G375" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -10769,10 +11005,18 @@
         </is>
       </c>
       <c r="E376" s="2" t="n"/>
-      <c r="F376" s="4" t="n"/>
-      <c r="G376" s="2" t="n"/>
-    </row>
-    <row r="377">
+      <c r="F376" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】Campaign创建向导(批量创建Campaign+AdGroup)</t>
+        </is>
+      </c>
+      <c r="G376" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="16" customHeight="1">
       <c r="A377" s="2" t="n"/>
       <c r="B377" s="2" t="inlineStr">
         <is>
@@ -10790,10 +11034,14 @@
         </is>
       </c>
       <c r="E377" s="2" t="n"/>
-      <c r="F377" s="4" t="n"/>
+      <c r="F377" s="7" t="inlineStr">
+        <is>
+          <t>按真实历史名称校验 — 100.0%</t>
+        </is>
+      </c>
       <c r="G377" s="2" t="n"/>
     </row>
-    <row r="378">
+    <row r="378" ht="32" customHeight="1">
       <c r="A378" s="2" t="n"/>
       <c r="B378" s="2" t="inlineStr">
         <is>
@@ -10811,8 +11059,17 @@
         </is>
       </c>
       <c r="E378" s="2" t="n"/>
-      <c r="F378" s="4" t="n"/>
-      <c r="G378" s="2" t="n"/>
+      <c r="F378" s="7" t="inlineStr">
+        <is>
+          <t>按真实高频traffic格式(纯ID字符串数组)调用 — 99.2%
+按Swagger契约格式(profileId+campaignId对象数组)调用 — 0.8%</t>
+        </is>
+      </c>
+      <c r="G378" s="4" t="inlineStr">
+        <is>
+          <t>⚠️发现:99.2%真实流量使用纯ID字符串数组格式调用，但当前Swagger契约要求{profileId,campaignId}对象数组；实测纯字符串格式被后端拒绝(HTTP 400)，疑似历史客户端与现网契约不一致，建议核实是否为真实回归问题</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -10833,9 +11090,13 @@
       </c>
       <c r="E379" s="2" t="n"/>
       <c r="F379" s="4" t="n"/>
-      <c r="G379" s="2" t="n"/>
-    </row>
-    <row r="380">
+      <c r="G379" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="16" customHeight="1">
       <c r="A380" s="2" t="n"/>
       <c r="B380" s="2" t="inlineStr">
         <is>
@@ -10853,10 +11114,18 @@
         </is>
       </c>
       <c r="E380" s="2" t="n"/>
-      <c r="F380" s="4" t="n"/>
-      <c r="G380" s="2" t="n"/>
-    </row>
-    <row r="381">
+      <c r="F380" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】设置账号级自定义关键词类型</t>
+        </is>
+      </c>
+      <c r="G380" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="16" customHeight="1">
       <c r="A381" s="2" t="n"/>
       <c r="B381" s="2" t="inlineStr">
         <is>
@@ -10874,7 +11143,11 @@
         </is>
       </c>
       <c r="E381" s="2" t="n"/>
-      <c r="F381" s="4" t="n"/>
+      <c r="F381" s="7" t="inlineStr">
+        <is>
+          <t>查询自定义关键词类型配置 — 100%</t>
+        </is>
+      </c>
       <c r="G381" s="2" t="n"/>
     </row>
     <row r="382">
@@ -10896,7 +11169,11 @@
       </c>
       <c r="E382" s="2" t="n"/>
       <c r="F382" s="4" t="n"/>
-      <c r="G382" s="2" t="n"/>
+      <c r="G382" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -10916,8 +11193,16 @@
         </is>
       </c>
       <c r="E383" s="2" t="n"/>
-      <c r="F383" s="4" t="n"/>
-      <c r="G383" s="2" t="n"/>
+      <c r="F383" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量删除(归档)Campaign</t>
+        </is>
+      </c>
+      <c r="G383" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行。⚠️同源问题:该接口84次流量中2/3为纯ID字符串数组格式，与Swagger对象数组契约不一致(与CheckTargetROASToggling同一问题模式)，建议一并排查</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -10938,7 +11223,11 @@
       </c>
       <c r="E384" s="2" t="n"/>
       <c r="F384" s="4" t="n"/>
-      <c r="G384" s="2" t="n"/>
+      <c r="G384" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -10959,9 +11248,13 @@
       </c>
       <c r="E385" s="2" t="n"/>
       <c r="F385" s="4" t="n"/>
-      <c r="G385" s="2" t="n"/>
-    </row>
-    <row r="386">
+      <c r="G385" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="16" customHeight="1">
       <c r="A386" s="2" t="n"/>
       <c r="B386" s="2" t="inlineStr">
         <is>
@@ -10979,10 +11272,14 @@
         </is>
       </c>
       <c r="E386" s="2" t="n"/>
-      <c r="F386" s="4" t="n"/>
+      <c r="F386" s="7" t="inlineStr">
+        <is>
+          <t>按真实ID查询单个Campaign详情 — 100%</t>
+        </is>
+      </c>
       <c r="G386" s="2" t="n"/>
     </row>
-    <row r="387">
+    <row r="387" ht="32" customHeight="1">
       <c r="A387" s="2" t="n"/>
       <c r="B387" s="2" t="inlineStr">
         <is>
@@ -11000,7 +11297,12 @@
         </is>
       </c>
       <c r="E387" s="2" t="n"/>
-      <c r="F387" s="4" t="n"/>
+      <c r="F387" s="7" t="inlineStr">
+        <is>
+          <t>按campaignId查询历史花费(不传profileId) — 95.8%
+按profileId+campaignId查询历史花费 — 4.2%</t>
+        </is>
+      </c>
       <c r="G387" s="2" t="n"/>
     </row>
     <row r="388">
@@ -11022,7 +11324,11 @@
       </c>
       <c r="E388" s="2" t="n"/>
       <c r="F388" s="4" t="n"/>
-      <c r="G388" s="2" t="n"/>
+      <c r="G388" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -11043,7 +11349,11 @@
       </c>
       <c r="E389" s="2" t="n"/>
       <c r="F389" s="4" t="n"/>
-      <c r="G389" s="2" t="n"/>
+      <c r="G389" s="4" t="inlineStr">
+        <is>
+          <t>极低流量(365d 1次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -11064,7 +11374,11 @@
       </c>
       <c r="E390" s="2" t="n"/>
       <c r="F390" s="4" t="n"/>
-      <c r="G390" s="2" t="n"/>
+      <c r="G390" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -11085,7 +11399,11 @@
       </c>
       <c r="E391" s="2" t="n"/>
       <c r="F391" s="4" t="n"/>
-      <c r="G391" s="2" t="n"/>
+      <c r="G391" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -11106,7 +11424,11 @@
       </c>
       <c r="E392" s="2" t="n"/>
       <c r="F392" s="4" t="n"/>
-      <c r="G392" s="2" t="n"/>
+      <c r="G392" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -11127,7 +11449,11 @@
       </c>
       <c r="E393" s="2" t="n"/>
       <c r="F393" s="4" t="n"/>
-      <c r="G393" s="2" t="n"/>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -11147,8 +11473,16 @@
         </is>
       </c>
       <c r="E394" s="2" t="n"/>
-      <c r="F394" s="4" t="n"/>
-      <c r="G394" s="2" t="n"/>
+      <c r="F394" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量修改Campaign状态(0/1，真实取值)</t>
+        </is>
+      </c>
+      <c r="G394" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -11168,8 +11502,16 @@
         </is>
       </c>
       <c r="E395" s="2" t="n"/>
-      <c r="F395" s="4" t="n"/>
-      <c r="G395" s="2" t="n"/>
+      <c r="F395" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量修改状态</t>
+        </is>
+      </c>
+      <c r="G395" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -11190,7 +11532,11 @@
       </c>
       <c r="E396" s="2" t="n"/>
       <c r="F396" s="4" t="n"/>
-      <c r="G396" s="2" t="n"/>
+      <c r="G396" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -11211,7 +11557,11 @@
       </c>
       <c r="E397" s="2" t="n"/>
       <c r="F397" s="4" t="n"/>
-      <c r="G397" s="2" t="n"/>
+      <c r="G397" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -11232,7 +11582,11 @@
       </c>
       <c r="E398" s="2" t="n"/>
       <c r="F398" s="4" t="n"/>
-      <c r="G398" s="2" t="n"/>
+      <c r="G398" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -11252,8 +11606,16 @@
         </is>
       </c>
       <c r="E399" s="2" t="n"/>
-      <c r="F399" s="4" t="n"/>
-      <c r="G399" s="2" t="n"/>
+      <c r="F399" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】设置Target ROAS/ACOS目标</t>
+        </is>
+      </c>
+      <c r="G399" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -11274,9 +11636,13 @@
       </c>
       <c r="E400" s="2" t="n"/>
       <c r="F400" s="4" t="n"/>
-      <c r="G400" s="2" t="n"/>
-    </row>
-    <row r="401">
+      <c r="G400" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="16" customHeight="1">
       <c r="A401" s="2" t="n"/>
       <c r="B401" s="2" t="inlineStr">
         <is>
@@ -11294,10 +11660,14 @@
         </is>
       </c>
       <c r="E401" s="2" t="n"/>
-      <c r="F401" s="4" t="n"/>
+      <c r="F401" s="7" t="inlineStr">
+        <is>
+          <t>默认分页查询 — 100.0%</t>
+        </is>
+      </c>
       <c r="G401" s="2" t="n"/>
     </row>
-    <row r="402">
+    <row r="402" ht="16" customHeight="1">
       <c r="A402" s="2" t="n"/>
       <c r="B402" s="2" t="inlineStr">
         <is>
@@ -11315,7 +11685,11 @@
         </is>
       </c>
       <c r="E402" s="2" t="n"/>
-      <c r="F402" s="4" t="n"/>
+      <c r="F402" s="7" t="inlineStr">
+        <is>
+          <t>默认分页查询 — 100.0%</t>
+        </is>
+      </c>
       <c r="G402" s="2" t="n"/>
     </row>
     <row r="403">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1891,9 +1891,19 @@
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
+      <c r="F59" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>42% (27/64)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -31233,7 +31243,11 @@
       </c>
       <c r="E1249" s="2" t="n"/>
       <c r="F1249" s="4" t="n"/>
-      <c r="G1249" s="2" t="n"/>
+      <c r="G1249" s="4" t="inlineStr">
+        <is>
+          <t>极低流量(365d 2次)，暂不覆盖(注: 功能等同的/report-mcp/data已覆盖)</t>
+        </is>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" s="2" t="n"/>
@@ -31254,7 +31268,11 @@
       </c>
       <c r="E1250" s="2" t="n"/>
       <c r="F1250" s="4" t="n"/>
-      <c r="G1250" s="2" t="n"/>
+      <c r="G1250" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" s="2" t="n"/>
@@ -31275,9 +31293,13 @@
       </c>
       <c r="E1251" s="2" t="n"/>
       <c r="F1251" s="4" t="n"/>
-      <c r="G1251" s="2" t="n"/>
-    </row>
-    <row r="1252">
+      <c r="G1251" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252" ht="32" customHeight="1">
       <c r="A1252" s="2" t="n"/>
       <c r="B1252" s="2" t="inlineStr">
         <is>
@@ -31295,10 +31317,15 @@
         </is>
       </c>
       <c r="E1252" s="2" t="n"/>
-      <c r="F1252" s="4" t="n"/>
+      <c r="F1252" s="7" t="inlineStr">
+        <is>
+          <t>无Campaign过滤 — 82.4%
+按Campaign过滤 — 17.6%</t>
+        </is>
+      </c>
       <c r="G1252" s="2" t="n"/>
     </row>
-    <row r="1253">
+    <row r="1253" ht="80" customHeight="1">
       <c r="A1253" s="2" t="n"/>
       <c r="B1253" s="2" t="inlineStr">
         <is>
@@ -31316,7 +31343,15 @@
         </is>
       </c>
       <c r="E1253" s="2" t="n"/>
-      <c r="F1253" s="4" t="n"/>
+      <c r="F1253" s="7" t="inlineStr">
+        <is>
+          <t>按周(dim=2)+timeType=week — 47.8%
+按天(dim=1)+timeType=date — 26.1%
+dim=0(汇总)+不传timeType — 13.0%
+按月(dim=3)+timeType=month — 8.7%
+dim=0(汇总)+timeType=ytd — 4.3%</t>
+        </is>
+      </c>
       <c r="G1253" s="2" t="n"/>
     </row>
     <row r="1254">
@@ -31338,7 +31373,11 @@
       </c>
       <c r="E1254" s="2" t="n"/>
       <c r="F1254" s="4" t="n"/>
-      <c r="G1254" s="2" t="n"/>
+      <c r="G1254" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 40次)</t>
+        </is>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" s="2" t="n"/>
@@ -31359,9 +31398,13 @@
       </c>
       <c r="E1255" s="2" t="n"/>
       <c r="F1255" s="4" t="n"/>
-      <c r="G1255" s="2" t="n"/>
-    </row>
-    <row r="1256">
+      <c r="G1255" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 8348次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256" ht="112" customHeight="1">
       <c r="A1256" s="2" t="n"/>
       <c r="B1256" s="2" t="inlineStr">
         <is>
@@ -31379,10 +31422,20 @@
         </is>
       </c>
       <c r="E1256" s="2" t="n"/>
-      <c r="F1256" s="4" t="n"/>
+      <c r="F1256" s="7" t="inlineStr">
+        <is>
+          <t>不传targetingTypes+不传campaignTagIds — 62.4%
+targetingTypes=[]+按CampaignTag过滤 — 14.0%
+targetingTypes=[]+无CampaignTag过滤 — 9.8%
+targetingTypes=[]+不传campaignTagIds — 7.8%
+不传targetingTypes+按CampaignTag过滤 — 2.2%
+不传targetingTypes+无CampaignTag过滤 — 2.0%
+targetingTypes=[ids+]+无CampaignTag过滤 — 1.6%</t>
+        </is>
+      </c>
       <c r="G1256" s="2" t="n"/>
     </row>
-    <row r="1257">
+    <row r="1257" ht="144" customHeight="1">
       <c r="A1257" s="2" t="n"/>
       <c r="B1257" s="2" t="inlineStr">
         <is>
@@ -31400,10 +31453,22 @@
         </is>
       </c>
       <c r="E1257" s="2" t="n"/>
-      <c r="F1257" s="4" t="n"/>
+      <c r="F1257" s="7" t="inlineStr">
+        <is>
+          <t>按天(dim=1)+不传brands — 28.0%
+按天(dim=1)+brands=[] — 24.6%
+按月(dim=3)+不传brands — 18.8%
+按月(dim=3)+brands=[] — 11.6%
+按周(dim=2)+不传brands — 9.0%
+按周(dim=2)+brands=[] — 4.4%
+dim=5+不传brands — 1.2%
+dim=5+brands=[] — 1.0%
+dim=4+不传brands — 1.0%</t>
+        </is>
+      </c>
       <c r="G1257" s="2" t="n"/>
     </row>
-    <row r="1258">
+    <row r="1258" ht="96" customHeight="1">
       <c r="A1258" s="2" t="n"/>
       <c r="B1258" s="2" t="inlineStr">
         <is>
@@ -31421,7 +31486,16 @@
         </is>
       </c>
       <c r="E1258" s="2" t="n"/>
-      <c r="F1258" s="4" t="n"/>
+      <c r="F1258" s="7" t="inlineStr">
+        <is>
+          <t>不传targetingTypes+status=[] — 53.2%
+targetingTypes=[]+不传status — 24.8%
+targetingTypes=[]+status=[] — 13.0%
+targetingTypes=[]+status=[ids+] — 4.8%
+targetingTypes=[ids+]+status=[] — 1.8%
+targetingTypes=[ids+]+status=[ids+] — 1.0%</t>
+        </is>
+      </c>
       <c r="G1258" s="2" t="n"/>
     </row>
     <row r="1259">
@@ -31443,7 +31517,11 @@
       </c>
       <c r="E1259" s="2" t="n"/>
       <c r="F1259" s="4" t="n"/>
-      <c r="G1259" s="2" t="n"/>
+      <c r="G1259" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1260">
       <c r="A1260" s="2" t="n"/>
@@ -31464,7 +31542,11 @@
       </c>
       <c r="E1260" s="2" t="n"/>
       <c r="F1260" s="4" t="n"/>
-      <c r="G1260" s="2" t="n"/>
+      <c r="G1260" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" s="2" t="n"/>
@@ -31485,9 +31567,13 @@
       </c>
       <c r="E1261" s="2" t="n"/>
       <c r="F1261" s="4" t="n"/>
-      <c r="G1261" s="2" t="n"/>
-    </row>
-    <row r="1262">
+      <c r="G1261" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 49次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262" ht="32" customHeight="1">
       <c r="A1262" s="2" t="n"/>
       <c r="B1262" s="2" t="inlineStr">
         <is>
@@ -31505,10 +31591,15 @@
         </is>
       </c>
       <c r="E1262" s="2" t="n"/>
-      <c r="F1262" s="4" t="n"/>
+      <c r="F1262" s="7" t="inlineStr">
+        <is>
+          <t>不传itemHealthFilters+不传bidFilters — 79.6%
+itemHealthFilters=None+bidFilters=None — 20.4%</t>
+        </is>
+      </c>
       <c r="G1262" s="2" t="n"/>
     </row>
-    <row r="1263">
+    <row r="1263" ht="32" customHeight="1">
       <c r="A1263" s="2" t="n"/>
       <c r="B1263" s="2" t="inlineStr">
         <is>
@@ -31526,10 +31617,15 @@
         </is>
       </c>
       <c r="E1263" s="2" t="n"/>
-      <c r="F1263" s="4" t="n"/>
+      <c r="F1263" s="7" t="inlineStr">
+        <is>
+          <t>不传itemHealthFilters+不传bidFilters — 81.8%
+itemHealthFilters=None+bidFilters=None — 18.2%</t>
+        </is>
+      </c>
       <c r="G1263" s="2" t="n"/>
     </row>
-    <row r="1264">
+    <row r="1264" ht="32" customHeight="1">
       <c r="A1264" s="2" t="n"/>
       <c r="B1264" s="2" t="inlineStr">
         <is>
@@ -31547,7 +31643,12 @@
         </is>
       </c>
       <c r="E1264" s="2" t="n"/>
-      <c r="F1264" s="4" t="n"/>
+      <c r="F1264" s="7" t="inlineStr">
+        <is>
+          <t>不传itemHealthFilters+不传bidFilters — 79.0%
+itemHealthFilters=None+bidFilters=None — 21.0%</t>
+        </is>
+      </c>
       <c r="G1264" s="2" t="n"/>
     </row>
     <row r="1265">
@@ -31569,7 +31670,11 @@
       </c>
       <c r="E1265" s="2" t="n"/>
       <c r="F1265" s="4" t="n"/>
-      <c r="G1265" s="2" t="n"/>
+      <c r="G1265" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1266">
       <c r="A1266" s="2" t="n"/>
@@ -31590,7 +31695,11 @@
       </c>
       <c r="E1266" s="2" t="n"/>
       <c r="F1266" s="4" t="n"/>
-      <c r="G1266" s="2" t="n"/>
+      <c r="G1266" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" s="2" t="n"/>
@@ -31611,9 +31720,13 @@
       </c>
       <c r="E1267" s="2" t="n"/>
       <c r="F1267" s="4" t="n"/>
-      <c r="G1267" s="2" t="n"/>
-    </row>
-    <row r="1268">
+      <c r="G1267" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268" ht="32" customHeight="1">
       <c r="A1268" s="2" t="n"/>
       <c r="B1268" s="2" t="inlineStr">
         <is>
@@ -31631,10 +31744,15 @@
         </is>
       </c>
       <c r="E1268" s="2" t="n"/>
-      <c r="F1268" s="4" t="n"/>
+      <c r="F1268" s="7" t="inlineStr">
+        <is>
+          <t>不传itemHealthFilters+不传bidFilters — 75.8%
+itemHealthFilters=None+bidFilters=None — 24.2%</t>
+        </is>
+      </c>
       <c r="G1268" s="2" t="n"/>
     </row>
-    <row r="1269">
+    <row r="1269" ht="32" customHeight="1">
       <c r="A1269" s="2" t="n"/>
       <c r="B1269" s="2" t="inlineStr">
         <is>
@@ -31652,10 +31770,15 @@
         </is>
       </c>
       <c r="E1269" s="2" t="n"/>
-      <c r="F1269" s="4" t="n"/>
+      <c r="F1269" s="7" t="inlineStr">
+        <is>
+          <t>不传itemHealthFilters+不传bidFilters — 74.4%
+itemHealthFilters=None+bidFilters=None — 25.6%</t>
+        </is>
+      </c>
       <c r="G1269" s="2" t="n"/>
     </row>
-    <row r="1270">
+    <row r="1270" ht="32" customHeight="1">
       <c r="A1270" s="2" t="n"/>
       <c r="B1270" s="2" t="inlineStr">
         <is>
@@ -31673,7 +31796,12 @@
         </is>
       </c>
       <c r="E1270" s="2" t="n"/>
-      <c r="F1270" s="4" t="n"/>
+      <c r="F1270" s="7" t="inlineStr">
+        <is>
+          <t>不传itemHealthFilters+不传bidFilters — 75.4%
+itemHealthFilters=None+bidFilters=None — 24.6%</t>
+        </is>
+      </c>
       <c r="G1270" s="2" t="n"/>
     </row>
     <row r="1271">
@@ -31695,7 +31823,11 @@
       </c>
       <c r="E1271" s="2" t="n"/>
       <c r="F1271" s="4" t="n"/>
-      <c r="G1271" s="2" t="n"/>
+      <c r="G1271" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" s="2" t="n"/>
@@ -31716,7 +31848,11 @@
       </c>
       <c r="E1272" s="2" t="n"/>
       <c r="F1272" s="4" t="n"/>
-      <c r="G1272" s="2" t="n"/>
+      <c r="G1272" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 18次)</t>
+        </is>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" s="2" t="n"/>
@@ -31737,9 +31873,13 @@
       </c>
       <c r="E1273" s="2" t="n"/>
       <c r="F1273" s="4" t="n"/>
-      <c r="G1273" s="2" t="n"/>
-    </row>
-    <row r="1274">
+      <c r="G1273" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 18次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274" ht="96" customHeight="1">
       <c r="A1274" s="2" t="n"/>
       <c r="B1274" s="2" t="inlineStr">
         <is>
@@ -31757,10 +31897,19 @@
         </is>
       </c>
       <c r="E1274" s="2" t="n"/>
-      <c r="F1274" s="4" t="n"/>
+      <c r="F1274" s="7" t="inlineStr">
+        <is>
+          <t>customMetricLevels=[Pagetype]+不传campaignTagIds — 34.0%
+不传customMetricLevels+不传campaignTagIds — 27.2%
+customMetricLevels=[]+无CampaignTag过滤 — 12.4%
+customMetricLevels=[Pagetype]+无CampaignTag过滤 — 11.6%
+customMetricLevels=[Pagetype]+按CampaignTag过滤 — 10.2%
+customMetricLevels=[]+按CampaignTag过滤 — 3.8%</t>
+        </is>
+      </c>
       <c r="G1274" s="2" t="n"/>
     </row>
-    <row r="1275">
+    <row r="1275" ht="112" customHeight="1">
       <c r="A1275" s="2" t="n"/>
       <c r="B1275" s="2" t="inlineStr">
         <is>
@@ -31778,10 +31927,20 @@
         </is>
       </c>
       <c r="E1275" s="2" t="n"/>
-      <c r="F1275" s="4" t="n"/>
+      <c r="F1275" s="7" t="inlineStr">
+        <is>
+          <t>customMetricLevels=[Pagetype]+不传campaignTagIds — 33.8%
+不传customMetricLevels+不传campaignTagIds — 29.4%
+customMetricLevels=[Pagetype]+按CampaignTag过滤 — 12.4%
+customMetricLevels=[Pagetype]+无CampaignTag过滤 — 11.2%
+customMetricLevels=[]+无CampaignTag过滤 — 7.8%
+customMetricLevels=[]+按CampaignTag过滤 — 4.0%
+customMetricLevels=[]+不传campaignTagIds — 1.4%</t>
+        </is>
+      </c>
       <c r="G1275" s="2" t="n"/>
     </row>
-    <row r="1276">
+    <row r="1276" ht="112" customHeight="1">
       <c r="A1276" s="2" t="n"/>
       <c r="B1276" s="2" t="inlineStr">
         <is>
@@ -31799,7 +31958,17 @@
         </is>
       </c>
       <c r="E1276" s="2" t="n"/>
-      <c r="F1276" s="4" t="n"/>
+      <c r="F1276" s="7" t="inlineStr">
+        <is>
+          <t>customMetricLevels=[Pagetype]+不传campaignTagIds — 32.6%
+不传customMetricLevels+不传campaignTagIds — 28.6%
+customMetricLevels=[Pagetype]+无CampaignTag过滤 — 12.8%
+customMetricLevels=[Pagetype]+按CampaignTag过滤 — 11.0%
+customMetricLevels=[]+无CampaignTag过滤 — 9.8%
+customMetricLevels=[]+按CampaignTag过滤 — 3.8%
+customMetricLevels=[]+不传campaignTagIds — 1.4%</t>
+        </is>
+      </c>
       <c r="G1276" s="2" t="n"/>
     </row>
     <row r="1277">
@@ -31821,7 +31990,11 @@
       </c>
       <c r="E1277" s="2" t="n"/>
       <c r="F1277" s="4" t="n"/>
-      <c r="G1277" s="2" t="n"/>
+      <c r="G1277" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" s="2" t="n"/>
@@ -31842,7 +32015,11 @@
       </c>
       <c r="E1278" s="2" t="n"/>
       <c r="F1278" s="4" t="n"/>
-      <c r="G1278" s="2" t="n"/>
+      <c r="G1278" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1279">
       <c r="A1279" s="2" t="n"/>
@@ -31863,7 +32040,11 @@
       </c>
       <c r="E1279" s="2" t="n"/>
       <c r="F1279" s="4" t="n"/>
-      <c r="G1279" s="2" t="n"/>
+      <c r="G1279" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 165次)</t>
+        </is>
+      </c>
     </row>
     <row r="1280">
       <c r="A1280" s="2" t="n"/>
@@ -31884,7 +32065,11 @@
       </c>
       <c r="E1280" s="2" t="n"/>
       <c r="F1280" s="4" t="n"/>
-      <c r="G1280" s="2" t="n"/>
+      <c r="G1280" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1281">
       <c r="A1281" s="2" t="n"/>
@@ -31905,7 +32090,11 @@
       </c>
       <c r="E1281" s="2" t="n"/>
       <c r="F1281" s="4" t="n"/>
-      <c r="G1281" s="2" t="n"/>
+      <c r="G1281" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1282">
       <c r="A1282" s="2" t="n"/>
@@ -31926,7 +32115,11 @@
       </c>
       <c r="E1282" s="2" t="n"/>
       <c r="F1282" s="4" t="n"/>
-      <c r="G1282" s="2" t="n"/>
+      <c r="G1282" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" s="2" t="n"/>
@@ -31947,7 +32140,11 @@
       </c>
       <c r="E1283" s="2" t="n"/>
       <c r="F1283" s="4" t="n"/>
-      <c r="G1283" s="2" t="n"/>
+      <c r="G1283" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1284">
       <c r="A1284" s="2" t="n"/>
@@ -31968,7 +32165,11 @@
       </c>
       <c r="E1284" s="2" t="n"/>
       <c r="F1284" s="4" t="n"/>
-      <c r="G1284" s="2" t="n"/>
+      <c r="G1284" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 62次)</t>
+        </is>
+      </c>
     </row>
     <row r="1285">
       <c r="A1285" s="2" t="n"/>
@@ -31989,9 +32190,13 @@
       </c>
       <c r="E1285" s="2" t="n"/>
       <c r="F1285" s="4" t="n"/>
-      <c r="G1285" s="2" t="n"/>
-    </row>
-    <row r="1286">
+      <c r="G1285" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 62次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286" ht="96" customHeight="1">
       <c r="A1286" s="2" t="n"/>
       <c r="B1286" s="2" t="inlineStr">
         <is>
@@ -32009,10 +32214,19 @@
         </is>
       </c>
       <c r="E1286" s="2" t="n"/>
-      <c r="F1286" s="4" t="n"/>
+      <c r="F1286" s="7" t="inlineStr">
+        <is>
+          <t>adGroupStatus=[]+无AdGroup过滤 — 43.0%
+不传adGroupStatus+不传adGroupIds — 24.2%
+adGroupStatus=[ids+]+按AdGroup过滤 — 16.8%
+adGroupStatus=[ids+]+无AdGroup过滤 — 10.6%
+不传adGroupStatus+无AdGroup过滤 — 4.2%
+adGroupStatus=[]+按AdGroup过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1286" s="2" t="n"/>
     </row>
-    <row r="1287">
+    <row r="1287" ht="80" customHeight="1">
       <c r="A1287" s="2" t="n"/>
       <c r="B1287" s="2" t="inlineStr">
         <is>
@@ -32030,10 +32244,18 @@
         </is>
       </c>
       <c r="E1287" s="2" t="n"/>
-      <c r="F1287" s="4" t="n"/>
+      <c r="F1287" s="7" t="inlineStr">
+        <is>
+          <t>adGroupStatus=[]+无AdGroup过滤 — 39.2%
+不传adGroupStatus+不传adGroupIds — 27.6%
+adGroupStatus=[ids+]+按AdGroup过滤 — 20.6%
+adGroupStatus=[ids+]+无AdGroup过滤 — 9.2%
+不传adGroupStatus+无AdGroup过滤 — 2.6%</t>
+        </is>
+      </c>
       <c r="G1287" s="2" t="n"/>
     </row>
-    <row r="1288">
+    <row r="1288" ht="96" customHeight="1">
       <c r="A1288" s="2" t="n"/>
       <c r="B1288" s="2" t="inlineStr">
         <is>
@@ -32051,7 +32273,16 @@
         </is>
       </c>
       <c r="E1288" s="2" t="n"/>
-      <c r="F1288" s="4" t="n"/>
+      <c r="F1288" s="7" t="inlineStr">
+        <is>
+          <t>adGroupStatus=[]+无AdGroup过滤 — 38.6%
+不传adGroupStatus+不传adGroupIds — 29.6%
+adGroupStatus=[ids+]+按AdGroup过滤 — 19.4%
+adGroupStatus=[ids+]+无AdGroup过滤 — 8.0%
+不传adGroupStatus+无AdGroup过滤 — 3.4%
+adGroupStatus=[]+按AdGroup过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1288" s="2" t="n"/>
     </row>
     <row r="1289">
@@ -32073,9 +32304,13 @@
       </c>
       <c r="E1289" s="2" t="n"/>
       <c r="F1289" s="4" t="n"/>
-      <c r="G1289" s="2" t="n"/>
-    </row>
-    <row r="1290">
+      <c r="G1289" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290" ht="96" customHeight="1">
       <c r="A1290" s="2" t="n"/>
       <c r="B1290" s="2" t="inlineStr">
         <is>
@@ -32093,10 +32328,19 @@
         </is>
       </c>
       <c r="E1290" s="2" t="n"/>
-      <c r="F1290" s="4" t="n"/>
+      <c r="F1290" s="7" t="inlineStr">
+        <is>
+          <t>不传campaignTagIds+不传isExplorer — 41.8%
+不传campaignTagIds+isExplorer=true — 22.0%
+无CampaignTag过滤+不传isExplorer — 14.0%
+按CampaignTag过滤+不传isExplorer — 11.4%
+无CampaignTag过滤+isExplorer=true — 6.6%
+按CampaignTag过滤+isExplorer=true — 4.2%</t>
+        </is>
+      </c>
       <c r="G1290" s="2" t="n"/>
     </row>
-    <row r="1291">
+    <row r="1291" ht="80" customHeight="1">
       <c r="A1291" s="2" t="n"/>
       <c r="B1291" s="2" t="inlineStr">
         <is>
@@ -32114,10 +32358,18 @@
         </is>
       </c>
       <c r="E1291" s="2" t="n"/>
-      <c r="F1291" s="4" t="n"/>
+      <c r="F1291" s="7" t="inlineStr">
+        <is>
+          <t>不传 taggingIds+不传 taggingSubIds — 48.3%
+ taggingIds=[]+ taggingSubIds=[] — 20.7%
+ taggingIds=[ids+]+ taggingSubIds=[ids+] — 13.8%
+ taggingIds=[ids+]+ taggingSubIds=[] — 13.8%
+ taggingIds=[]+ taggingSubIds=[ids+] — 3.4%</t>
+        </is>
+      </c>
       <c r="G1291" s="2" t="n"/>
     </row>
-    <row r="1292">
+    <row r="1292" ht="112" customHeight="1">
       <c r="A1292" s="2" t="n"/>
       <c r="B1292" s="2" t="inlineStr">
         <is>
@@ -32135,10 +32387,20 @@
         </is>
       </c>
       <c r="E1292" s="2" t="n"/>
-      <c r="F1292" s="4" t="n"/>
+      <c r="F1292" s="7" t="inlineStr">
+        <is>
+          <t>不传status+adGroupStatus=[] — 31.7%
+status=[]+不传adGroupStatus — 24.4%
+不传status+不传adGroupStatus — 19.5%
+status=[]+adGroupStatus=[] — 14.6%
+status=[ids+]+adGroupStatus=[] — 4.9%
+status=[ids+]+不传adGroupStatus — 2.4%
+status=[]+adGroupStatus=[ids+] — 2.4%</t>
+        </is>
+      </c>
       <c r="G1292" s="2" t="n"/>
     </row>
-    <row r="1293">
+    <row r="1293" ht="32" customHeight="1">
       <c r="A1293" s="2" t="n"/>
       <c r="B1293" s="2" t="inlineStr">
         <is>
@@ -32156,7 +32418,12 @@
         </is>
       </c>
       <c r="E1293" s="2" t="n"/>
-      <c r="F1293" s="4" t="n"/>
+      <c r="F1293" s="7" t="inlineStr">
+        <is>
+          <t>无Campaign过滤 — 74.4%
+按Campaign过滤 — 25.6%</t>
+        </is>
+      </c>
       <c r="G1293" s="2" t="n"/>
     </row>
     <row r="1294">
@@ -32178,7 +32445,11 @@
       </c>
       <c r="E1294" s="2" t="n"/>
       <c r="F1294" s="4" t="n"/>
-      <c r="G1294" s="2" t="n"/>
+      <c r="G1294" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1295">
       <c r="A1295" s="2" t="n"/>
@@ -32199,9 +32470,13 @@
       </c>
       <c r="E1295" s="2" t="n"/>
       <c r="F1295" s="4" t="n"/>
-      <c r="G1295" s="2" t="n"/>
-    </row>
-    <row r="1296">
+      <c r="G1295" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296" ht="112" customHeight="1">
       <c r="A1296" s="2" t="n"/>
       <c r="B1296" s="2" t="inlineStr">
         <is>
@@ -32219,7 +32494,17 @@
         </is>
       </c>
       <c r="E1296" s="2" t="n"/>
-      <c r="F1296" s="4" t="n"/>
+      <c r="F1296" s="7" t="inlineStr">
+        <is>
+          <t>不传targetingTypes+customMetricIds=[] — 39.8%
+targetingTypes=[]+不传customMetricIds — 33.8%
+targetingTypes=[]+customMetricIds=[] — 14.2%
+targetingTypes=[ids+]+不传customMetricIds — 5.4%
+不传targetingTypes+不传customMetricIds — 3.6%
+targetingTypes=[ids+]+customMetricIds=[] — 1.8%
+不传targetingTypes+customMetricIds=[ids+] — 1.4%</t>
+        </is>
+      </c>
       <c r="G1296" s="2" t="n"/>
     </row>
     <row r="1297">
@@ -32241,7 +32526,11 @@
       </c>
       <c r="E1297" s="2" t="n"/>
       <c r="F1297" s="4" t="n"/>
-      <c r="G1297" s="2" t="n"/>
+      <c r="G1297" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" s="2" t="n"/>
@@ -32262,7 +32551,11 @@
       </c>
       <c r="E1298" s="2" t="n"/>
       <c r="F1298" s="4" t="n"/>
-      <c r="G1298" s="2" t="n"/>
+      <c r="G1298" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" s="2" t="n"/>
@@ -32283,7 +32576,11 @@
       </c>
       <c r="E1299" s="2" t="n"/>
       <c r="F1299" s="4" t="n"/>
-      <c r="G1299" s="2" t="n"/>
+      <c r="G1299" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" s="2" t="n"/>
@@ -32304,7 +32601,11 @@
       </c>
       <c r="E1300" s="2" t="n"/>
       <c r="F1300" s="4" t="n"/>
-      <c r="G1300" s="2" t="n"/>
+      <c r="G1300" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" s="2" t="n"/>
@@ -32325,7 +32626,11 @@
       </c>
       <c r="E1301" s="2" t="n"/>
       <c r="F1301" s="4" t="n"/>
-      <c r="G1301" s="2" t="n"/>
+      <c r="G1301" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1302">
       <c r="A1302" s="2" t="n"/>
@@ -32346,7 +32651,11 @@
       </c>
       <c r="E1302" s="2" t="n"/>
       <c r="F1302" s="4" t="n"/>
-      <c r="G1302" s="2" t="n"/>
+      <c r="G1302" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1303">
       <c r="A1303" s="2" t="n"/>
@@ -32367,7 +32676,11 @@
       </c>
       <c r="E1303" s="2" t="n"/>
       <c r="F1303" s="4" t="n"/>
-      <c r="G1303" s="2" t="n"/>
+      <c r="G1303" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" s="2" t="n"/>
@@ -32388,7 +32701,11 @@
       </c>
       <c r="E1304" s="2" t="n"/>
       <c r="F1304" s="4" t="n"/>
-      <c r="G1304" s="2" t="n"/>
+      <c r="G1304" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 38次)</t>
+        </is>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" s="2" t="n"/>
@@ -32409,9 +32726,13 @@
       </c>
       <c r="E1305" s="2" t="n"/>
       <c r="F1305" s="4" t="n"/>
-      <c r="G1305" s="2" t="n"/>
-    </row>
-    <row r="1306">
+      <c r="G1305" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306" ht="16" customHeight="1">
       <c r="A1306" s="2" t="n"/>
       <c r="B1306" s="2" t="inlineStr">
         <is>
@@ -32429,10 +32750,14 @@
         </is>
       </c>
       <c r="E1306" s="2" t="n"/>
-      <c r="F1306" s="4" t="n"/>
+      <c r="F1306" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1306" s="2" t="n"/>
     </row>
-    <row r="1307">
+    <row r="1307" ht="16" customHeight="1">
       <c r="A1307" s="2" t="n"/>
       <c r="B1307" s="2" t="inlineStr">
         <is>
@@ -32450,7 +32775,11 @@
         </is>
       </c>
       <c r="E1307" s="2" t="n"/>
-      <c r="F1307" s="4" t="n"/>
+      <c r="F1307" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1307" s="2" t="n"/>
     </row>
     <row r="1308">
@@ -32472,7 +32801,11 @@
       </c>
       <c r="E1308" s="2" t="n"/>
       <c r="F1308" s="4" t="n"/>
-      <c r="G1308" s="2" t="n"/>
+      <c r="G1308" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" s="2" t="n"/>
@@ -32493,9 +32826,13 @@
       </c>
       <c r="E1309" s="2" t="n"/>
       <c r="F1309" s="4" t="n"/>
-      <c r="G1309" s="2" t="n"/>
-    </row>
-    <row r="1310">
+      <c r="G1309" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310" ht="176" customHeight="1">
       <c r="A1310" s="2" t="n"/>
       <c r="B1310" s="2" t="inlineStr">
         <is>
@@ -32513,10 +32850,24 @@
         </is>
       </c>
       <c r="E1310" s="2" t="n"/>
-      <c r="F1310" s="4" t="n"/>
+      <c r="F1310" s="7" t="inlineStr">
+        <is>
+          <t>reportType=QueryReport — 26.2%
+reportType=ProfileReport — 24.4%
+reportType=ItemReport — 14.2%
+reportType=CampaignReport — 8.6%
+reportType=PurchasedItemReport — 5.4%
+reportType=PlacementReport — 5.4%
+reportType=PlatformReport — 4.0%
+reportType=PageTypeReport — 3.2%
+reportType=KeywordReport — 3.0%
+reportType=CampaignOutOfDailyBudgetReport — 2.8%
+reportType=TagReport — 1.0%</t>
+        </is>
+      </c>
       <c r="G1310" s="2" t="n"/>
     </row>
-    <row r="1311">
+    <row r="1311" ht="64" customHeight="1">
       <c r="A1311" s="2" t="n"/>
       <c r="B1311" s="2" t="inlineStr">
         <is>
@@ -32534,10 +32885,21 @@
         </is>
       </c>
       <c r="E1311" s="2" t="n"/>
-      <c r="F1311" s="4" t="n"/>
-      <c r="G1311" s="2" t="n"/>
-    </row>
-    <row r="1312">
+      <c r="F1311" s="7" t="inlineStr">
+        <is>
+          <t>materialType=Profile — 69.8%
+materialType=profile — 17.8%
+materialType=CampaignTag — 6.0%
+materialType=Campaign — 4.4%</t>
+        </is>
+      </c>
+      <c r="G1311" s="4" t="inlineStr">
+        <is>
+          <t>⚠️发现:materialType真实取值同时存在"Profile"和"profile"两种大小写(分别占比69.8%/17.8%)，疑似不同前端版本传参不一致，建议核实后端是否统一处理大小写</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312" ht="176" customHeight="1">
       <c r="A1312" s="2" t="n"/>
       <c r="B1312" s="2" t="inlineStr">
         <is>
@@ -32555,7 +32917,21 @@
         </is>
       </c>
       <c r="E1312" s="2" t="n"/>
-      <c r="F1312" s="4" t="n"/>
+      <c r="F1312" s="7" t="inlineStr">
+        <is>
+          <t>reportType=ProfileReport — 48.2%
+reportType=QueryReport — 15.2%
+reportType=ItemReport — 10.8%
+reportType=CampaignReport — 6.8%
+reportType=CampaignOutOfDailyBudgetReport — 4.2%
+reportType=PlacementReport — 4.0%
+reportType=PurchasedItemReport — 2.0%
+reportType=PlatformReport — 1.8%
+reportType=KeywordReport — 1.8%
+reportType=PageTypeReport — 1.2%
+reportType=TagReport — 1.0%</t>
+        </is>
+      </c>
       <c r="G1312" s="2" t="n"/>
     </row>
     <row r="1313">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1803,9 +1803,19 @@
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
+      <c r="F55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>49% (21/43)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -29419,7 +29429,7 @@
       <c r="F1163" s="4" t="n"/>
       <c r="G1163" s="2" t="n"/>
     </row>
-    <row r="1164">
+    <row r="1164" ht="16" customHeight="1">
       <c r="A1164" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29441,10 +29451,14 @@
         </is>
       </c>
       <c r="E1164" s="2" t="n"/>
-      <c r="F1164" s="4" t="n"/>
+      <c r="F1164" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1164" s="2" t="n"/>
     </row>
-    <row r="1165">
+    <row r="1165" ht="16" customHeight="1">
       <c r="A1165" s="2" t="n"/>
       <c r="B1165" s="2" t="inlineStr">
         <is>
@@ -29462,7 +29476,11 @@
         </is>
       </c>
       <c r="E1165" s="2" t="n"/>
-      <c r="F1165" s="4" t="n"/>
+      <c r="F1165" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1165" s="2" t="n"/>
     </row>
     <row r="1166">
@@ -29484,9 +29502,13 @@
       </c>
       <c r="E1166" s="2" t="n"/>
       <c r="F1166" s="4" t="n"/>
-      <c r="G1166" s="2" t="n"/>
-    </row>
-    <row r="1167">
+      <c r="G1166" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167" ht="16" customHeight="1">
       <c r="A1167" s="2" t="n"/>
       <c r="B1167" s="2" t="inlineStr">
         <is>
@@ -29504,7 +29526,11 @@
         </is>
       </c>
       <c r="E1167" s="2" t="n"/>
-      <c r="F1167" s="4" t="n"/>
+      <c r="F1167" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1167" s="2" t="n"/>
     </row>
     <row r="1168">
@@ -29526,9 +29552,13 @@
       </c>
       <c r="E1168" s="2" t="n"/>
       <c r="F1168" s="4" t="n"/>
-      <c r="G1168" s="2" t="n"/>
-    </row>
-    <row r="1169">
+      <c r="G1168" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169" ht="96" customHeight="1">
       <c r="A1169" s="2" t="n"/>
       <c r="B1169" s="2" t="inlineStr">
         <is>
@@ -29546,7 +29576,16 @@
         </is>
       </c>
       <c r="E1169" s="2" t="n"/>
-      <c r="F1169" s="4" t="n"/>
+      <c r="F1169" s="7" t="inlineStr">
+        <is>
+          <t>不传itemNameOperand+不传fieldOrFilterSet — 37.8%
+itemNameOperand=Like+不传fieldOrFilterSet — 29.8%
+itemNameOperand=Like+fieldOrFilterSet={"isShowItemTag": false} — 25.2%
+不传itemNameOperand+fieldOrFilterSet={"isShowItemTag": false} — 2.6%
+itemNameOperand=Equal+不传fieldOrFilterSet — 1.4%
+itemNameOperand=LikeOr+fieldOrFilterSet={"isShowItemTag": false} — 1.0%</t>
+        </is>
+      </c>
       <c r="G1169" s="2" t="n"/>
     </row>
     <row r="1170">
@@ -29568,7 +29607,11 @@
       </c>
       <c r="E1170" s="2" t="n"/>
       <c r="F1170" s="4" t="n"/>
-      <c r="G1170" s="2" t="n"/>
+      <c r="G1170" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1171">
       <c r="A1171" s="2" t="n"/>
@@ -29589,9 +29632,13 @@
       </c>
       <c r="E1171" s="2" t="n"/>
       <c r="F1171" s="4" t="n"/>
-      <c r="G1171" s="2" t="n"/>
-    </row>
-    <row r="1172">
+      <c r="G1171" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172" ht="32" customHeight="1">
       <c r="A1172" s="2" t="n"/>
       <c r="B1172" s="2" t="inlineStr">
         <is>
@@ -29609,7 +29656,12 @@
         </is>
       </c>
       <c r="E1172" s="2" t="n"/>
-      <c r="F1172" s="4" t="n"/>
+      <c r="F1172" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[] — 66.2%
+itemTags=[ids+] — 33.8%</t>
+        </is>
+      </c>
       <c r="G1172" s="2" t="n"/>
     </row>
     <row r="1173">
@@ -29631,9 +29683,13 @@
       </c>
       <c r="E1173" s="2" t="n"/>
       <c r="F1173" s="4" t="n"/>
-      <c r="G1173" s="2" t="n"/>
-    </row>
-    <row r="1174">
+      <c r="G1173" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174" ht="32" customHeight="1">
       <c r="A1174" s="2" t="n"/>
       <c r="B1174" s="2" t="inlineStr">
         <is>
@@ -29651,10 +29707,15 @@
         </is>
       </c>
       <c r="E1174" s="2" t="n"/>
-      <c r="F1174" s="4" t="n"/>
+      <c r="F1174" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[]+brands=[] — 63.0%
+itemTags=[ids+]+brands=[] — 35.2%</t>
+        </is>
+      </c>
       <c r="G1174" s="2" t="n"/>
     </row>
-    <row r="1175">
+    <row r="1175" ht="48" customHeight="1">
       <c r="A1175" s="2" t="n"/>
       <c r="B1175" s="2" t="inlineStr">
         <is>
@@ -29672,10 +29733,16 @@
         </is>
       </c>
       <c r="E1175" s="2" t="n"/>
-      <c r="F1175" s="4" t="n"/>
+      <c r="F1175" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[]+brands=[] — 63.4%
+itemTags=[ids+]+brands=[] — 34.0%
+itemTags=[]+brands=[Fabletics] — 1.2%</t>
+        </is>
+      </c>
       <c r="G1175" s="2" t="n"/>
     </row>
-    <row r="1176">
+    <row r="1176" ht="32" customHeight="1">
       <c r="A1176" s="2" t="n"/>
       <c r="B1176" s="2" t="inlineStr">
         <is>
@@ -29693,7 +29760,12 @@
         </is>
       </c>
       <c r="E1176" s="2" t="n"/>
-      <c r="F1176" s="4" t="n"/>
+      <c r="F1176" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[] — 60.2%
+itemTags=[ids+] — 39.6%</t>
+        </is>
+      </c>
       <c r="G1176" s="2" t="n"/>
     </row>
     <row r="1177">
@@ -29715,7 +29787,11 @@
       </c>
       <c r="E1177" s="2" t="n"/>
       <c r="F1177" s="4" t="n"/>
-      <c r="G1177" s="2" t="n"/>
+      <c r="G1177" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" s="2" t="n"/>
@@ -29736,7 +29812,11 @@
       </c>
       <c r="E1178" s="2" t="n"/>
       <c r="F1178" s="4" t="n"/>
-      <c r="G1178" s="2" t="n"/>
+      <c r="G1178" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1179">
       <c r="A1179" s="2" t="n"/>
@@ -29757,9 +29837,13 @@
       </c>
       <c r="E1179" s="2" t="n"/>
       <c r="F1179" s="4" t="n"/>
-      <c r="G1179" s="2" t="n"/>
-    </row>
-    <row r="1180">
+      <c r="G1179" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180" ht="16" customHeight="1">
       <c r="A1180" s="2" t="n"/>
       <c r="B1180" s="2" t="inlineStr">
         <is>
@@ -29777,7 +29861,11 @@
         </is>
       </c>
       <c r="E1180" s="2" t="n"/>
-      <c r="F1180" s="4" t="n"/>
+      <c r="F1180" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1180" s="2" t="n"/>
     </row>
     <row r="1181">
@@ -29799,9 +29887,13 @@
       </c>
       <c r="E1181" s="2" t="n"/>
       <c r="F1181" s="4" t="n"/>
-      <c r="G1181" s="2" t="n"/>
-    </row>
-    <row r="1182">
+      <c r="G1181" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182" ht="16" customHeight="1">
       <c r="A1182" s="2" t="n"/>
       <c r="B1182" s="2" t="inlineStr">
         <is>
@@ -29819,7 +29911,11 @@
         </is>
       </c>
       <c r="E1182" s="2" t="n"/>
-      <c r="F1182" s="4" t="n"/>
+      <c r="F1182" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1182" s="2" t="n"/>
     </row>
     <row r="1183">
@@ -29841,7 +29937,11 @@
       </c>
       <c r="E1183" s="2" t="n"/>
       <c r="F1183" s="4" t="n"/>
-      <c r="G1183" s="2" t="n"/>
+      <c r="G1183" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 12次)</t>
+        </is>
+      </c>
     </row>
     <row r="1184">
       <c r="A1184" s="2" t="n"/>
@@ -29862,9 +29962,13 @@
       </c>
       <c r="E1184" s="2" t="n"/>
       <c r="F1184" s="4" t="n"/>
-      <c r="G1184" s="2" t="n"/>
-    </row>
-    <row r="1185">
+      <c r="G1184" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 12次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185" ht="32" customHeight="1">
       <c r="A1185" s="2" t="n"/>
       <c r="B1185" s="2" t="inlineStr">
         <is>
@@ -29882,10 +29986,15 @@
         </is>
       </c>
       <c r="E1185" s="2" t="n"/>
-      <c r="F1185" s="4" t="n"/>
+      <c r="F1185" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[]+brands=[] — 64.8%
+itemTags=[ids+]+brands=[] — 33.2%</t>
+        </is>
+      </c>
       <c r="G1185" s="2" t="n"/>
     </row>
-    <row r="1186">
+    <row r="1186" ht="32" customHeight="1">
       <c r="A1186" s="2" t="n"/>
       <c r="B1186" s="2" t="inlineStr">
         <is>
@@ -29903,7 +30012,12 @@
         </is>
       </c>
       <c r="E1186" s="2" t="n"/>
-      <c r="F1186" s="4" t="n"/>
+      <c r="F1186" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[] — 59.8%
+itemTags=[ids+] — 40.2%</t>
+        </is>
+      </c>
       <c r="G1186" s="2" t="n"/>
     </row>
     <row r="1187">
@@ -29925,7 +30039,11 @@
       </c>
       <c r="E1187" s="2" t="n"/>
       <c r="F1187" s="4" t="n"/>
-      <c r="G1187" s="2" t="n"/>
+      <c r="G1187" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1188">
       <c r="A1188" s="2" t="n"/>
@@ -29946,7 +30064,11 @@
       </c>
       <c r="E1188" s="2" t="n"/>
       <c r="F1188" s="4" t="n"/>
-      <c r="G1188" s="2" t="n"/>
+      <c r="G1188" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1189">
       <c r="A1189" s="2" t="n"/>
@@ -29967,9 +30089,13 @@
       </c>
       <c r="E1189" s="2" t="n"/>
       <c r="F1189" s="4" t="n"/>
-      <c r="G1189" s="2" t="n"/>
-    </row>
-    <row r="1190">
+      <c r="G1189" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190" ht="32" customHeight="1">
       <c r="A1190" s="2" t="n"/>
       <c r="B1190" s="2" t="inlineStr">
         <is>
@@ -29987,7 +30113,12 @@
         </is>
       </c>
       <c r="E1190" s="2" t="n"/>
-      <c r="F1190" s="4" t="n"/>
+      <c r="F1190" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[] — 66.7%
+itemTags=[ids+] — 33.3%</t>
+        </is>
+      </c>
       <c r="G1190" s="2" t="n"/>
     </row>
     <row r="1191">
@@ -30009,9 +30140,13 @@
       </c>
       <c r="E1191" s="2" t="n"/>
       <c r="F1191" s="4" t="n"/>
-      <c r="G1191" s="2" t="n"/>
-    </row>
-    <row r="1192">
+      <c r="G1191" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192" ht="32" customHeight="1">
       <c r="A1192" s="2" t="n"/>
       <c r="B1192" s="2" t="inlineStr">
         <is>
@@ -30029,10 +30164,15 @@
         </is>
       </c>
       <c r="E1192" s="2" t="n"/>
-      <c r="F1192" s="4" t="n"/>
+      <c r="F1192" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[ids+] — 71.7%
+itemTags=[] — 28.3%</t>
+        </is>
+      </c>
       <c r="G1192" s="2" t="n"/>
     </row>
-    <row r="1193">
+    <row r="1193" ht="48" customHeight="1">
       <c r="A1193" s="2" t="n"/>
       <c r="B1193" s="2" t="inlineStr">
         <is>
@@ -30050,7 +30190,13 @@
         </is>
       </c>
       <c r="E1193" s="2" t="n"/>
-      <c r="F1193" s="4" t="n"/>
+      <c r="F1193" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[]+timeType=1 — 83.1%
+itemTags=[ids+]+timeType=1 — 14.9%
+itemTags=[]+timeType=2 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1193" s="2" t="n"/>
     </row>
     <row r="1194">
@@ -30072,9 +30218,13 @@
       </c>
       <c r="E1194" s="2" t="n"/>
       <c r="F1194" s="4" t="n"/>
-      <c r="G1194" s="2" t="n"/>
-    </row>
-    <row r="1195">
+      <c r="G1194" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195" ht="48" customHeight="1">
       <c r="A1195" s="2" t="n"/>
       <c r="B1195" s="2" t="inlineStr">
         <is>
@@ -30092,7 +30242,13 @@
         </is>
       </c>
       <c r="E1195" s="2" t="n"/>
-      <c r="F1195" s="4" t="n"/>
+      <c r="F1195" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[]+categorys=[] — 63.0%
+itemTags=[ids+]+categorys=[] — 32.2%
+不传itemTags+不传categorys — 4.6%</t>
+        </is>
+      </c>
       <c r="G1195" s="2" t="n"/>
     </row>
     <row r="1196">
@@ -30114,9 +30270,13 @@
       </c>
       <c r="E1196" s="2" t="n"/>
       <c r="F1196" s="4" t="n"/>
-      <c r="G1196" s="2" t="n"/>
-    </row>
-    <row r="1197">
+      <c r="G1196" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197" ht="32" customHeight="1">
       <c r="A1197" s="2" t="n"/>
       <c r="B1197" s="2" t="inlineStr">
         <is>
@@ -30134,10 +30294,15 @@
         </is>
       </c>
       <c r="E1197" s="2" t="n"/>
-      <c r="F1197" s="4" t="n"/>
+      <c r="F1197" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[]+brands=[] — 63.6%
+itemTags=[ids+]+brands=[] — 35.4%</t>
+        </is>
+      </c>
       <c r="G1197" s="2" t="n"/>
     </row>
-    <row r="1198">
+    <row r="1198" ht="32" customHeight="1">
       <c r="A1198" s="2" t="n"/>
       <c r="B1198" s="2" t="inlineStr">
         <is>
@@ -30155,7 +30320,12 @@
         </is>
       </c>
       <c r="E1198" s="2" t="n"/>
-      <c r="F1198" s="4" t="n"/>
+      <c r="F1198" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[] — 66.2%
+itemTags=[ids+] — 33.8%</t>
+        </is>
+      </c>
       <c r="G1198" s="2" t="n"/>
     </row>
     <row r="1199">
@@ -30177,9 +30347,13 @@
       </c>
       <c r="E1199" s="2" t="n"/>
       <c r="F1199" s="4" t="n"/>
-      <c r="G1199" s="2" t="n"/>
-    </row>
-    <row r="1200">
+      <c r="G1199" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200" ht="96" customHeight="1">
       <c r="A1200" s="2" t="n"/>
       <c r="B1200" s="2" t="inlineStr">
         <is>
@@ -30197,7 +30371,16 @@
         </is>
       </c>
       <c r="E1200" s="2" t="n"/>
-      <c r="F1200" s="4" t="n"/>
+      <c r="F1200" s="7" t="inlineStr">
+        <is>
+          <t>fieldOrFilterSet={"isShowItemTag": false}+不传campaignTagIds — 43.2%
+不传fieldOrFilterSet+不传campaignTagIds — 30.6%
+不传fieldOrFilterSet+无CampaignTag过滤 — 20.6%
+fieldOrFilterSet={"isShowItemTag": true}+无CampaignTag过滤 — 2.0%
+fieldOrFilterSet={"isShowItemTag": true}+不传campaignTagIds — 1.6%
+fieldOrFilterSet={"isShowItemTag": false}+无CampaignTag过滤 — 1.2%</t>
+        </is>
+      </c>
       <c r="G1200" s="2" t="n"/>
     </row>
     <row r="1201">
@@ -30219,7 +30402,11 @@
       </c>
       <c r="E1201" s="2" t="n"/>
       <c r="F1201" s="4" t="n"/>
-      <c r="G1201" s="2" t="n"/>
+      <c r="G1201" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/下载接口，无同步响应，暂不覆盖(365d 198次)</t>
+        </is>
+      </c>
     </row>
     <row r="1202">
       <c r="A1202" s="2" t="n"/>
@@ -30240,7 +30427,11 @@
       </c>
       <c r="E1202" s="2" t="n"/>
       <c r="F1202" s="4" t="n"/>
-      <c r="G1202" s="2" t="n"/>
+      <c r="G1202" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 829次)</t>
+        </is>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" s="2" t="n"/>
@@ -30261,7 +30452,11 @@
       </c>
       <c r="E1203" s="2" t="n"/>
       <c r="F1203" s="4" t="n"/>
-      <c r="G1203" s="2" t="n"/>
+      <c r="G1203" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1204">
       <c r="A1204" s="2" t="n"/>
@@ -30282,9 +30477,13 @@
       </c>
       <c r="E1204" s="2" t="n"/>
       <c r="F1204" s="4" t="n"/>
-      <c r="G1204" s="2" t="n"/>
-    </row>
-    <row r="1205">
+      <c r="G1204" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205" ht="32" customHeight="1">
       <c r="A1205" s="2" t="n"/>
       <c r="B1205" s="2" t="inlineStr">
         <is>
@@ -30302,10 +30501,15 @@
         </is>
       </c>
       <c r="E1205" s="2" t="n"/>
-      <c r="F1205" s="4" t="n"/>
+      <c r="F1205" s="7" t="inlineStr">
+        <is>
+          <t>itemTags=[] — 62.0%
+itemTags=[ids+] — 37.6%</t>
+        </is>
+      </c>
       <c r="G1205" s="2" t="n"/>
     </row>
-    <row r="1206">
+    <row r="1206" ht="64" customHeight="1">
       <c r="A1206" s="2" t="n"/>
       <c r="B1206" s="2" t="inlineStr">
         <is>
@@ -30323,7 +30527,14 @@
         </is>
       </c>
       <c r="E1206" s="2" t="n"/>
-      <c r="F1206" s="4" t="n"/>
+      <c r="F1206" s="7" t="inlineStr">
+        <is>
+          <t>fieldOrFilterSet={"isShowItemTag": false}+不传targetingTypes — 41.9%
+不传fieldOrFilterSet+targetingTypes=[] — 30.2%
+不传fieldOrFilterSet+不传targetingTypes — 25.6%
+fieldOrFilterSet={"isShowItemTag": false}+targetingTypes=[] — 2.3%</t>
+        </is>
+      </c>
       <c r="G1206" s="2" t="n"/>
     </row>
     <row r="1207">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1649,9 +1649,19 @@
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
+      <c r="F48" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>100%(29执行,写操作8条未执行不计入)</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>57% (20/35)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -26728,7 +26738,11 @@
       </c>
       <c r="E1036" s="2" t="n"/>
       <c r="F1036" s="4" t="n"/>
-      <c r="G1036" s="2" t="n"/>
+      <c r="G1036" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" s="2" t="n"/>
@@ -26748,8 +26762,16 @@
         </is>
       </c>
       <c r="E1037" s="2" t="n"/>
-      <c r="F1037" s="4" t="n"/>
-      <c r="G1037" s="2" t="n"/>
+      <c r="F1037" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量创建关键词</t>
+        </is>
+      </c>
+      <c r="G1037" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="n"/>
@@ -26770,7 +26792,11 @@
       </c>
       <c r="E1038" s="2" t="n"/>
       <c r="F1038" s="4" t="n"/>
-      <c r="G1038" s="2" t="n"/>
+      <c r="G1038" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="n"/>
@@ -26790,8 +26816,16 @@
         </is>
       </c>
       <c r="E1039" s="2" t="n"/>
-      <c r="F1039" s="4" t="n"/>
-      <c r="G1039" s="2" t="n"/>
+      <c r="F1039" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量修改关键词出价(按keywordId)</t>
+        </is>
+      </c>
+      <c r="G1039" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" s="2" t="n"/>
@@ -26811,8 +26845,16 @@
         </is>
       </c>
       <c r="E1040" s="2" t="n"/>
-      <c r="F1040" s="4" t="n"/>
-      <c r="G1040" s="2" t="n"/>
+      <c r="F1040" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量修改关键词出价</t>
+        </is>
+      </c>
+      <c r="G1040" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="n"/>
@@ -26833,7 +26875,11 @@
       </c>
       <c r="E1041" s="2" t="n"/>
       <c r="F1041" s="4" t="n"/>
-      <c r="G1041" s="2" t="n"/>
+      <c r="G1041" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="n"/>
@@ -26854,7 +26900,11 @@
       </c>
       <c r="E1042" s="2" t="n"/>
       <c r="F1042" s="4" t="n"/>
-      <c r="G1042" s="2" t="n"/>
+      <c r="G1042" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" s="2" t="n"/>
@@ -26875,7 +26925,11 @@
       </c>
       <c r="E1043" s="2" t="n"/>
       <c r="F1043" s="4" t="n"/>
-      <c r="G1043" s="2" t="n"/>
+      <c r="G1043" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" s="2" t="n"/>
@@ -26896,7 +26950,11 @@
       </c>
       <c r="E1044" s="2" t="n"/>
       <c r="F1044" s="4" t="n"/>
-      <c r="G1044" s="2" t="n"/>
+      <c r="G1044" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="n"/>
@@ -26917,9 +26975,13 @@
       </c>
       <c r="E1045" s="2" t="n"/>
       <c r="F1045" s="4" t="n"/>
-      <c r="G1045" s="2" t="n"/>
-    </row>
-    <row r="1046">
+      <c r="G1045" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046" ht="48" customHeight="1">
       <c r="A1046" s="2" t="n"/>
       <c r="B1046" s="2" t="inlineStr">
         <is>
@@ -26937,10 +26999,16 @@
         </is>
       </c>
       <c r="E1046" s="2" t="n"/>
-      <c r="F1046" s="4" t="n"/>
+      <c r="F1046" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2 — 93.3%
+reportType=1 — 5.2%
+reportType=0 — 1.5%</t>
+        </is>
+      </c>
       <c r="G1046" s="2" t="n"/>
     </row>
-    <row r="1047">
+    <row r="1047" ht="48" customHeight="1">
       <c r="A1047" s="2" t="n"/>
       <c r="B1047" s="2" t="inlineStr">
         <is>
@@ -26958,10 +27026,16 @@
         </is>
       </c>
       <c r="E1047" s="2" t="n"/>
-      <c r="F1047" s="4" t="n"/>
+      <c r="F1047" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2+首页 — 80.0%
+reportType=1+首页 — 10.6%
+reportType=0+首页 — 8.2%</t>
+        </is>
+      </c>
       <c r="G1047" s="2" t="n"/>
     </row>
-    <row r="1048">
+    <row r="1048" ht="48" customHeight="1">
       <c r="A1048" s="2" t="n"/>
       <c r="B1048" s="2" t="inlineStr">
         <is>
@@ -26979,7 +27053,13 @@
         </is>
       </c>
       <c r="E1048" s="2" t="n"/>
-      <c r="F1048" s="4" t="n"/>
+      <c r="F1048" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2+无KeywordTag过滤 — 81.4%
+reportType=1+无KeywordTag过滤 — 8.6%
+reportType=0+无KeywordTag过滤 — 8.4%</t>
+        </is>
+      </c>
       <c r="G1048" s="2" t="n"/>
     </row>
     <row r="1049">
@@ -27001,7 +27081,11 @@
       </c>
       <c r="E1049" s="2" t="n"/>
       <c r="F1049" s="4" t="n"/>
-      <c r="G1049" s="2" t="n"/>
+      <c r="G1049" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 76次)</t>
+        </is>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" s="2" t="n"/>
@@ -27022,9 +27106,13 @@
       </c>
       <c r="E1050" s="2" t="n"/>
       <c r="F1050" s="4" t="n"/>
-      <c r="G1050" s="2" t="n"/>
-    </row>
-    <row r="1051">
+      <c r="G1050" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 76次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051" ht="48" customHeight="1">
       <c r="A1051" s="2" t="n"/>
       <c r="B1051" s="2" t="inlineStr">
         <is>
@@ -27042,10 +27130,16 @@
         </is>
       </c>
       <c r="E1051" s="2" t="n"/>
-      <c r="F1051" s="4" t="n"/>
+      <c r="F1051" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2 — 81.0%
+reportType=1 — 9.8%
+reportType=0 — 9.2%</t>
+        </is>
+      </c>
       <c r="G1051" s="2" t="n"/>
     </row>
-    <row r="1052">
+    <row r="1052" ht="48" customHeight="1">
       <c r="A1052" s="2" t="n"/>
       <c r="B1052" s="2" t="inlineStr">
         <is>
@@ -27063,10 +27157,16 @@
         </is>
       </c>
       <c r="E1052" s="2" t="n"/>
-      <c r="F1052" s="4" t="n"/>
+      <c r="F1052" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2 — 81.6%
+reportType=0 — 10.0%
+reportType=1 — 8.4%</t>
+        </is>
+      </c>
       <c r="G1052" s="2" t="n"/>
     </row>
-    <row r="1053">
+    <row r="1053" ht="16" customHeight="1">
       <c r="A1053" s="2" t="n"/>
       <c r="B1053" s="2" t="inlineStr">
         <is>
@@ -27084,10 +27184,14 @@
         </is>
       </c>
       <c r="E1053" s="2" t="n"/>
-      <c r="F1053" s="4" t="n"/>
+      <c r="F1053" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1053" s="2" t="n"/>
     </row>
-    <row r="1054">
+    <row r="1054" ht="48" customHeight="1">
       <c r="A1054" s="2" t="n"/>
       <c r="B1054" s="2" t="inlineStr">
         <is>
@@ -27105,10 +27209,16 @@
         </is>
       </c>
       <c r="E1054" s="2" t="n"/>
-      <c r="F1054" s="4" t="n"/>
+      <c r="F1054" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2 — 82.4%
+reportType=1 — 9.2%
+reportType=0 — 8.4%</t>
+        </is>
+      </c>
       <c r="G1054" s="2" t="n"/>
     </row>
-    <row r="1055">
+    <row r="1055" ht="48" customHeight="1">
       <c r="A1055" s="2" t="n"/>
       <c r="B1055" s="2" t="inlineStr">
         <is>
@@ -27126,7 +27236,13 @@
         </is>
       </c>
       <c r="E1055" s="2" t="n"/>
-      <c r="F1055" s="4" t="n"/>
+      <c r="F1055" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2 — 79.2%
+reportType=1 — 10.4%
+reportType=0 — 10.4%</t>
+        </is>
+      </c>
       <c r="G1055" s="2" t="n"/>
     </row>
     <row r="1056">
@@ -27148,7 +27264,11 @@
       </c>
       <c r="E1056" s="2" t="n"/>
       <c r="F1056" s="4" t="n"/>
-      <c r="G1056" s="2" t="n"/>
+      <c r="G1056" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="n"/>
@@ -27169,7 +27289,11 @@
       </c>
       <c r="E1057" s="2" t="n"/>
       <c r="F1057" s="4" t="n"/>
-      <c r="G1057" s="2" t="n"/>
+      <c r="G1057" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="n"/>
@@ -27190,7 +27314,11 @@
       </c>
       <c r="E1058" s="2" t="n"/>
       <c r="F1058" s="4" t="n"/>
-      <c r="G1058" s="2" t="n"/>
+      <c r="G1058" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="n"/>
@@ -27211,9 +27339,13 @@
       </c>
       <c r="E1059" s="2" t="n"/>
       <c r="F1059" s="4" t="n"/>
-      <c r="G1059" s="2" t="n"/>
-    </row>
-    <row r="1060">
+      <c r="G1059" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060" ht="64" customHeight="1">
       <c r="A1060" s="2" t="n"/>
       <c r="B1060" s="2" t="inlineStr">
         <is>
@@ -27231,7 +27363,14 @@
         </is>
       </c>
       <c r="E1060" s="2" t="n"/>
-      <c r="F1060" s="4" t="n"/>
+      <c r="F1060" s="7" t="inlineStr">
+        <is>
+          <t>reportType=2+不传ChangeFilter — 78.8%
+reportType=1+不传ChangeFilter — 10.8%
+reportType=0+不传ChangeFilter — 9.4%
+reportType=2+ChangeFilter=tosSearchedKeywordImpressionShareChange — 1.0%</t>
+        </is>
+      </c>
       <c r="G1060" s="2" t="n"/>
     </row>
     <row r="1061">
@@ -27253,7 +27392,11 @@
       </c>
       <c r="E1061" s="2" t="n"/>
       <c r="F1061" s="4" t="n"/>
-      <c r="G1061" s="2" t="n"/>
+      <c r="G1061" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 4次)</t>
+        </is>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="n"/>
@@ -27274,9 +27417,13 @@
       </c>
       <c r="E1062" s="2" t="n"/>
       <c r="F1062" s="4" t="n"/>
-      <c r="G1062" s="2" t="n"/>
-    </row>
-    <row r="1063">
+      <c r="G1062" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 4次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063" ht="16" customHeight="1">
       <c r="A1063" s="2" t="n"/>
       <c r="B1063" s="2" t="inlineStr">
         <is>
@@ -27294,7 +27441,11 @@
         </is>
       </c>
       <c r="E1063" s="2" t="n"/>
-      <c r="F1063" s="4" t="n"/>
+      <c r="F1063" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1063" s="2" t="n"/>
     </row>
     <row r="1064">
@@ -27315,8 +27466,16 @@
         </is>
       </c>
       <c r="E1064" s="2" t="n"/>
-      <c r="F1064" s="4" t="n"/>
-      <c r="G1064" s="2" t="n"/>
+      <c r="F1064" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量移除关键词标签</t>
+        </is>
+      </c>
+      <c r="G1064" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="n"/>
@@ -27336,10 +27495,18 @@
         </is>
       </c>
       <c r="E1065" s="2" t="n"/>
-      <c r="F1065" s="4" t="n"/>
-      <c r="G1065" s="2" t="n"/>
-    </row>
-    <row r="1066">
+      <c r="F1065" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量打关键词标签</t>
+        </is>
+      </c>
+      <c r="G1065" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066" ht="16" customHeight="1">
       <c r="A1066" s="2" t="n"/>
       <c r="B1066" s="2" t="inlineStr">
         <is>
@@ -27357,7 +27524,11 @@
         </is>
       </c>
       <c r="E1066" s="2" t="n"/>
-      <c r="F1066" s="4" t="n"/>
+      <c r="F1066" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1066" s="2" t="n"/>
     </row>
     <row r="1067">
@@ -27378,8 +27549,16 @@
         </is>
       </c>
       <c r="E1067" s="2" t="n"/>
-      <c r="F1067" s="4" t="n"/>
-      <c r="G1067" s="2" t="n"/>
+      <c r="F1067" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】将搜索词转化为正式关键词(创建)</t>
+        </is>
+      </c>
+      <c r="G1067" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="n"/>
@@ -27399,8 +27578,16 @@
         </is>
       </c>
       <c r="E1068" s="2" t="n"/>
-      <c r="F1068" s="4" t="n"/>
-      <c r="G1068" s="2" t="n"/>
+      <c r="F1068" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量修改关键词状态(0/1)</t>
+        </is>
+      </c>
+      <c r="G1068" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="n"/>
@@ -27420,10 +27607,18 @@
         </is>
       </c>
       <c r="E1069" s="2" t="n"/>
-      <c r="F1069" s="4" t="n"/>
-      <c r="G1069" s="2" t="n"/>
-    </row>
-    <row r="1070">
+      <c r="F1069" s="4" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】按筛选条件批量修改关键词状态</t>
+        </is>
+      </c>
+      <c r="G1069" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070" ht="16" customHeight="1">
       <c r="A1070" s="2" t="n"/>
       <c r="B1070" s="2" t="inlineStr">
         <is>
@@ -27441,7 +27636,11 @@
         </is>
       </c>
       <c r="E1070" s="2" t="n"/>
-      <c r="F1070" s="4" t="n"/>
+      <c r="F1070" s="7" t="inlineStr">
+        <is>
+          <t>按adGroupId查询建议关键词 — 100%</t>
+        </is>
+      </c>
       <c r="G1070" s="2" t="n"/>
     </row>
     <row r="1071">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -915,9 +915,19 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="F16" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>50% (17/34)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -11745,7 +11755,11 @@
       </c>
       <c r="E403" s="2" t="n"/>
       <c r="F403" s="4" t="n"/>
-      <c r="G403" s="2" t="n"/>
+      <c r="G403" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -11766,9 +11780,13 @@
       </c>
       <c r="E404" s="2" t="n"/>
       <c r="F404" s="4" t="n"/>
-      <c r="G404" s="2" t="n"/>
-    </row>
-    <row r="405">
+      <c r="G404" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="16" customHeight="1">
       <c r="A405" s="2" t="n"/>
       <c r="B405" s="2" t="inlineStr">
         <is>
@@ -11786,10 +11804,18 @@
         </is>
       </c>
       <c r="E405" s="2" t="n"/>
-      <c r="F405" s="4" t="n"/>
-      <c r="G405" s="2" t="n"/>
-    </row>
-    <row r="406">
+      <c r="F405" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G405" s="4" t="inlineStr">
+        <is>
+          <t>⚠️实测HTTP 500 ClickHouse聚合函数嵌套错误(sum(IvtViewableImpressions)嵌套在另一聚合函数内)，与sponsor/Dashboard/CampaignTagGoalBySubTag同一根因，疑似所有SubTag下钻类接口共享的系统性后端bug，已如实记FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="16" customHeight="1">
       <c r="A406" s="2" t="n"/>
       <c r="B406" s="2" t="inlineStr">
         <is>
@@ -11807,8 +11833,16 @@
         </is>
       </c>
       <c r="E406" s="2" t="n"/>
-      <c r="F406" s="4" t="n"/>
-      <c r="G406" s="2" t="n"/>
+      <c r="F406" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G406" s="4" t="inlineStr">
+        <is>
+          <t>⚠️同上ClickHouse聚合函数嵌套错误，已如实记FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -11829,7 +11863,11 @@
       </c>
       <c r="E407" s="2" t="n"/>
       <c r="F407" s="4" t="n"/>
-      <c r="G407" s="2" t="n"/>
+      <c r="G407" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -11850,9 +11888,13 @@
       </c>
       <c r="E408" s="2" t="n"/>
       <c r="F408" s="4" t="n"/>
-      <c r="G408" s="2" t="n"/>
-    </row>
-    <row r="409">
+      <c r="G408" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 95次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="80" customHeight="1">
       <c r="A409" s="2" t="n"/>
       <c r="B409" s="2" t="inlineStr">
         <is>
@@ -11870,10 +11912,18 @@
         </is>
       </c>
       <c r="E409" s="2" t="n"/>
-      <c r="F409" s="4" t="n"/>
+      <c r="F409" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+customMetricIds=[] — 43.4%
+按CampaignTag过滤+customMetricIds=[] — 28.0%
+无CampaignTag过滤+不传customMetricIds — 24.0%
+不传campaignTagIds+customMetricIds=[] — 2.4%
+无CampaignTag过滤+customMetricIds=[ids+] — 1.6%</t>
+        </is>
+      </c>
       <c r="G409" s="2" t="n"/>
     </row>
-    <row r="410">
+    <row r="410" ht="112" customHeight="1">
       <c r="A410" s="2" t="n"/>
       <c r="B410" s="2" t="inlineStr">
         <is>
@@ -11891,10 +11941,20 @@
         </is>
       </c>
       <c r="E410" s="2" t="n"/>
-      <c r="F410" s="4" t="n"/>
+      <c r="F410" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+dim=0(汇总) — 50.0%
+按CampaignTag过滤+dim=0(汇总) — 36.2%
+按CampaignTag过滤+按月(dim=3) — 4.8%
+不传campaignTagIds+dim=0(汇总) — 2.6%
+按CampaignTag过滤+按天(dim=1) — 2.0%
+无CampaignTag过滤+按天(dim=1) — 1.4%
+无CampaignTag过滤+按月(dim=3) — 1.4%</t>
+        </is>
+      </c>
       <c r="G410" s="2" t="n"/>
     </row>
-    <row r="411">
+    <row r="411" ht="16" customHeight="1">
       <c r="A411" s="2" t="n"/>
       <c r="B411" s="2" t="inlineStr">
         <is>
@@ -11912,10 +11972,14 @@
         </is>
       </c>
       <c r="E411" s="2" t="n"/>
-      <c r="F411" s="4" t="n"/>
+      <c r="F411" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G411" s="2" t="n"/>
     </row>
-    <row r="412">
+    <row r="412" ht="96" customHeight="1">
       <c r="A412" s="2" t="n"/>
       <c r="B412" s="2" t="inlineStr">
         <is>
@@ -11933,10 +11997,19 @@
         </is>
       </c>
       <c r="E412" s="2" t="n"/>
-      <c r="F412" s="4" t="n"/>
+      <c r="F412" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+customMetricIds=[] — 42.0%
+按CampaignTag过滤+customMetricIds=[] — 28.8%
+无CampaignTag过滤+不传customMetricIds — 22.8%
+不传campaignTagIds+customMetricIds=[] — 3.4%
+按CampaignTag过滤+customMetricIds=[ids+] — 1.8%
+无CampaignTag过滤+customMetricIds=[ids+] — 1.2%</t>
+        </is>
+      </c>
       <c r="G412" s="2" t="n"/>
     </row>
-    <row r="413">
+    <row r="413" ht="96" customHeight="1">
       <c r="A413" s="2" t="n"/>
       <c r="B413" s="2" t="inlineStr">
         <is>
@@ -11954,7 +12027,16 @@
         </is>
       </c>
       <c r="E413" s="2" t="n"/>
-      <c r="F413" s="4" t="n"/>
+      <c r="F413" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+不传TableColumns — 51.4%
+按CampaignTag过滤+TableColumns=[totalCampaigns] — 23.0%
+无CampaignTag过滤+TableColumns=[totalCampaigns] — 12.2%
+按CampaignTag过滤+不传TableColumns — 9.6%
+不传campaignTagIds+不传TableColumns — 2.8%
+不传campaignTagIds+TableColumns=[totalCampaigns] — 1.0%</t>
+        </is>
+      </c>
       <c r="G413" s="2" t="n"/>
     </row>
     <row r="414">
@@ -11976,7 +12058,11 @@
       </c>
       <c r="E414" s="2" t="n"/>
       <c r="F414" s="4" t="n"/>
-      <c r="G414" s="2" t="n"/>
+      <c r="G414" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -11997,9 +12083,13 @@
       </c>
       <c r="E415" s="2" t="n"/>
       <c r="F415" s="4" t="n"/>
-      <c r="G415" s="2" t="n"/>
-    </row>
-    <row r="416">
+      <c r="G415" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="64" customHeight="1">
       <c r="A416" s="2" t="n"/>
       <c r="B416" s="2" t="inlineStr">
         <is>
@@ -12017,8 +12107,19 @@
         </is>
       </c>
       <c r="E416" s="2" t="n"/>
-      <c r="F416" s="4" t="n"/>
-      <c r="G416" s="2" t="n"/>
+      <c r="F416" s="7" t="inlineStr">
+        <is>
+          <t>按Tag过滤+不传routeType — 54.9%
+无Tag过滤+不传routeType — 18.1%
+无Tag过滤+routeType=0 — 14.6%
+按Tag过滤+routeType=0 — 12.4%</t>
+        </is>
+      </c>
+      <c r="G416" s="4" t="inlineStr">
+        <is>
+          <t>⚠️同上ClickHouse聚合函数嵌套错误，已如实记FAIL(4个场景全部FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -12039,7 +12140,11 @@
       </c>
       <c r="E417" s="2" t="n"/>
       <c r="F417" s="4" t="n"/>
-      <c r="G417" s="2" t="n"/>
+      <c r="G417" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -12060,7 +12165,11 @@
       </c>
       <c r="E418" s="2" t="n"/>
       <c r="F418" s="4" t="n"/>
-      <c r="G418" s="2" t="n"/>
+      <c r="G418" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -12081,7 +12190,11 @@
       </c>
       <c r="E419" s="2" t="n"/>
       <c r="F419" s="4" t="n"/>
-      <c r="G419" s="2" t="n"/>
+      <c r="G419" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -12102,9 +12215,13 @@
       </c>
       <c r="E420" s="2" t="n"/>
       <c r="F420" s="4" t="n"/>
-      <c r="G420" s="2" t="n"/>
-    </row>
-    <row r="421">
+      <c r="G420" s="4" t="inlineStr">
+        <is>
+          <t>异步回调接口，无同步响应，暂不覆盖(365d 1512次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="48" customHeight="1">
       <c r="A421" s="2" t="n"/>
       <c r="B421" s="2" t="inlineStr">
         <is>
@@ -12122,7 +12239,13 @@
         </is>
       </c>
       <c r="E421" s="2" t="n"/>
-      <c r="F421" s="4" t="n"/>
+      <c r="F421" s="7" t="inlineStr">
+        <is>
+          <t>不传targetingTypes+不传campaignTagIds — 49.4%
+targetingTypes=[]+按CampaignTag过滤 — 46.0%
+targetingTypes=[ids+]+按CampaignTag过滤 — 4.0%</t>
+        </is>
+      </c>
       <c r="G421" s="2" t="n"/>
     </row>
     <row r="422">
@@ -12144,7 +12267,11 @@
       </c>
       <c r="E422" s="2" t="n"/>
       <c r="F422" s="4" t="n"/>
-      <c r="G422" s="2" t="n"/>
+      <c r="G422" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -12165,9 +12292,13 @@
       </c>
       <c r="E423" s="2" t="n"/>
       <c r="F423" s="4" t="n"/>
-      <c r="G423" s="2" t="n"/>
-    </row>
-    <row r="424">
+      <c r="G423" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="64" customHeight="1">
       <c r="A424" s="2" t="n"/>
       <c r="B424" s="2" t="inlineStr">
         <is>
@@ -12185,10 +12316,17 @@
         </is>
       </c>
       <c r="E424" s="2" t="n"/>
-      <c r="F424" s="4" t="n"/>
+      <c r="F424" s="7" t="inlineStr">
+        <is>
+          <t>onlySubtags=true+targetingTypes=[] — 52.0%
+不传onlySubtags+targetingTypes=[] — 33.2%
+onlySubtags=true+targetingTypes=[ids+] — 13.4%
+不传onlySubtags+targetingTypes=[ids+] — 1.4%</t>
+        </is>
+      </c>
       <c r="G424" s="2" t="n"/>
     </row>
-    <row r="425">
+    <row r="425" ht="96" customHeight="1">
       <c r="A425" s="2" t="n"/>
       <c r="B425" s="2" t="inlineStr">
         <is>
@@ -12206,7 +12344,16 @@
         </is>
       </c>
       <c r="E425" s="2" t="n"/>
-      <c r="F425" s="4" t="n"/>
+      <c r="F425" s="7" t="inlineStr">
+        <is>
+          <t>按月(dim=3)+includeSubTags=true — 33.2%
+dim=0(汇总)+includeSubTags=true — 27.4%
+dim=0(汇总)+不传includeSubTags — 13.4%
+按周(dim=2)+includeSubTags=true — 13.0%
+按月(dim=3)+不传includeSubTags — 9.4%
+按周(dim=2)+不传includeSubTags — 3.0%</t>
+        </is>
+      </c>
       <c r="G425" s="2" t="n"/>
     </row>
     <row r="426">
@@ -12228,7 +12375,11 @@
       </c>
       <c r="E426" s="2" t="n"/>
       <c r="F426" s="4" t="n"/>
-      <c r="G426" s="2" t="n"/>
+      <c r="G426" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -12249,9 +12400,13 @@
       </c>
       <c r="E427" s="2" t="n"/>
       <c r="F427" s="4" t="n"/>
-      <c r="G427" s="2" t="n"/>
-    </row>
-    <row r="428">
+      <c r="G427" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="48" customHeight="1">
       <c r="A428" s="2" t="n"/>
       <c r="B428" s="2" t="inlineStr">
         <is>
@@ -12269,10 +12424,20 @@
         </is>
       </c>
       <c r="E428" s="2" t="n"/>
-      <c r="F428" s="4" t="n"/>
-      <c r="G428" s="2" t="n"/>
-    </row>
-    <row r="429">
+      <c r="F428" s="7" t="inlineStr">
+        <is>
+          <t>按天(dim=1) — 96.4%
+按周(dim=2) — 2.4%
+dim=5 — 1.2%</t>
+        </is>
+      </c>
+      <c r="G428" s="4" t="inlineStr">
+        <is>
+          <t>⚠️同上ClickHouse聚合函数嵌套错误，已如实记FAIL(3个场景全部FAIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="48" customHeight="1">
       <c r="A429" s="2" t="n"/>
       <c r="B429" s="2" t="inlineStr">
         <is>
@@ -12290,8 +12455,18 @@
         </is>
       </c>
       <c r="E429" s="2" t="n"/>
-      <c r="F429" s="4" t="n"/>
-      <c r="G429" s="2" t="n"/>
+      <c r="F429" s="7" t="inlineStr">
+        <is>
+          <t>按天(dim=1) — 88.4%
+按周(dim=2) — 6.2%
+按月(dim=3) — 4.7%</t>
+        </is>
+      </c>
+      <c r="G429" s="4" t="inlineStr">
+        <is>
+          <t>⚠️同上ClickHouse聚合函数嵌套错误，已如实记FAIL(3个场景全部FAIL)。【系统性发现】截至目前累计6个SubTag相关接口(含Dashboard模块的CampaignTagGoalBySubTag)均复现同一ClickHouse错误，强烈建议作为独立Jira排查SubTag下钻查询的SQL生成逻辑</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -12312,7 +12487,11 @@
       </c>
       <c r="E430" s="2" t="n"/>
       <c r="F430" s="4" t="n"/>
-      <c r="G430" s="2" t="n"/>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -12333,9 +12512,13 @@
       </c>
       <c r="E431" s="2" t="n"/>
       <c r="F431" s="4" t="n"/>
-      <c r="G431" s="2" t="n"/>
-    </row>
-    <row r="432">
+      <c r="G431" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 1416次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="112" customHeight="1">
       <c r="A432" s="2" t="n"/>
       <c r="B432" s="2" t="inlineStr">
         <is>
@@ -12353,10 +12536,20 @@
         </is>
       </c>
       <c r="E432" s="2" t="n"/>
-      <c r="F432" s="4" t="n"/>
+      <c r="F432" s="7" t="inlineStr">
+        <is>
+          <t>按CampaignTag过滤+不传campaignIds — 39.8%
+无CampaignTag过滤+不传campaignIds — 29.4%
+按CampaignTag过滤+无Campaign过滤 — 12.6%
+无CampaignTag过滤+无Campaign过滤 — 8.4%
+无CampaignTag过滤+按Campaign过滤 — 4.2%
+按CampaignTag过滤+按Campaign过滤 — 3.4%
+不传campaignTagIds+不传campaignIds — 2.2%</t>
+        </is>
+      </c>
       <c r="G432" s="2" t="n"/>
     </row>
-    <row r="433">
+    <row r="433" ht="112" customHeight="1">
       <c r="A433" s="2" t="n"/>
       <c r="B433" s="2" t="inlineStr">
         <is>
@@ -12374,7 +12567,17 @@
         </is>
       </c>
       <c r="E433" s="2" t="n"/>
-      <c r="F433" s="4" t="n"/>
+      <c r="F433" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+不传campaignStatus — 39.6%
+按CampaignTag过滤+不传campaignStatus — 30.2%
+按CampaignTag过滤+campaignStatus=[] — 14.8%
+无CampaignTag过滤+campaignStatus=[] — 9.6%
+不传campaignTagIds+不传campaignStatus — 3.0%
+按CampaignTag过滤+campaignStatus=[ids+] — 1.8%
+无CampaignTag过滤+campaignStatus=[ids+] — 1.0%</t>
+        </is>
+      </c>
       <c r="G433" s="2" t="n"/>
     </row>
     <row r="434">
@@ -12396,9 +12599,13 @@
       </c>
       <c r="E434" s="2" t="n"/>
       <c r="F434" s="4" t="n"/>
-      <c r="G434" s="2" t="n"/>
-    </row>
-    <row r="435">
+      <c r="G434" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="112" customHeight="1">
       <c r="A435" s="2" t="n"/>
       <c r="B435" s="2" t="inlineStr">
         <is>
@@ -12416,10 +12623,20 @@
         </is>
       </c>
       <c r="E435" s="2" t="n"/>
-      <c r="F435" s="4" t="n"/>
+      <c r="F435" s="7" t="inlineStr">
+        <is>
+          <t>按CampaignTag过滤+不传campaignIds — 36.4%
+无CampaignTag过滤+不传campaignIds — 29.0%
+按CampaignTag过滤+无Campaign过滤 — 14.8%
+无CampaignTag过滤+无Campaign过滤 — 10.4%
+无CampaignTag过滤+按Campaign过滤 — 3.4%
+按CampaignTag过滤+按Campaign过滤 — 3.2%
+不传campaignTagIds+不传campaignIds — 2.8%</t>
+        </is>
+      </c>
       <c r="G435" s="2" t="n"/>
     </row>
-    <row r="436">
+    <row r="436" ht="80" customHeight="1">
       <c r="A436" s="2" t="n"/>
       <c r="B436" s="2" t="inlineStr">
         <is>
@@ -12437,7 +12654,15 @@
         </is>
       </c>
       <c r="E436" s="2" t="n"/>
-      <c r="F436" s="4" t="n"/>
+      <c r="F436" s="7" t="inlineStr">
+        <is>
+          <t>TableColumns=[totalCampaigns]+按CampaignTag过滤 — 32.6%
+不传TableColumns+按CampaignTag过滤 — 27.6%
+不传TableColumns+无CampaignTag过滤 — 25.8%
+TableColumns=[totalCampaigns]+无CampaignTag过滤 — 11.6%
+不传TableColumns+不传campaignTagIds — 2.0%</t>
+        </is>
+      </c>
       <c r="G436" s="2" t="n"/>
     </row>
     <row r="437">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -10024,7 +10024,11 @@
         </is>
       </c>
       <c r="E338" s="2" t="n"/>
-      <c r="F338" s="4" t="n"/>
+      <c r="F338" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G338" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10107,7 +10111,11 @@
         </is>
       </c>
       <c r="E341" s="2" t="n"/>
-      <c r="F341" s="4" t="n"/>
+      <c r="F341" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G341" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10132,7 +10140,11 @@
         </is>
       </c>
       <c r="E342" s="2" t="n"/>
-      <c r="F342" s="4" t="n"/>
+      <c r="F342" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G342" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10244,7 +10256,11 @@
         </is>
       </c>
       <c r="E346" s="2" t="n"/>
-      <c r="F346" s="4" t="n"/>
+      <c r="F346" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G346" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10269,7 +10285,11 @@
         </is>
       </c>
       <c r="E347" s="2" t="n"/>
-      <c r="F347" s="4" t="n"/>
+      <c r="F347" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G347" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10294,7 +10314,11 @@
         </is>
       </c>
       <c r="E348" s="2" t="n"/>
-      <c r="F348" s="4" t="n"/>
+      <c r="F348" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G348" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10377,7 +10401,11 @@
         </is>
       </c>
       <c r="E351" s="2" t="n"/>
-      <c r="F351" s="4" t="n"/>
+      <c r="F351" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G351" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10575,7 +10603,11 @@
         </is>
       </c>
       <c r="E358" s="2" t="n"/>
-      <c r="F358" s="4" t="n"/>
+      <c r="F358" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G358" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10625,7 +10657,11 @@
         </is>
       </c>
       <c r="E360" s="2" t="n"/>
-      <c r="F360" s="4" t="n"/>
+      <c r="F360" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G360" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10916,7 +10952,11 @@
         </is>
       </c>
       <c r="E371" s="2" t="n"/>
-      <c r="F371" s="4" t="n"/>
+      <c r="F371" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G371" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10941,7 +10981,11 @@
         </is>
       </c>
       <c r="E372" s="2" t="n"/>
-      <c r="F372" s="4" t="n"/>
+      <c r="F372" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G372" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -10995,7 +11039,11 @@
         </is>
       </c>
       <c r="E374" s="2" t="n"/>
-      <c r="F374" s="4" t="n"/>
+      <c r="F374" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G374" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11020,7 +11068,11 @@
         </is>
       </c>
       <c r="E375" s="2" t="n"/>
-      <c r="F375" s="4" t="n"/>
+      <c r="F375" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G375" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11129,7 +11181,11 @@
         </is>
       </c>
       <c r="E379" s="2" t="n"/>
-      <c r="F379" s="4" t="n"/>
+      <c r="F379" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G379" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11208,7 +11264,11 @@
         </is>
       </c>
       <c r="E382" s="2" t="n"/>
-      <c r="F382" s="4" t="n"/>
+      <c r="F382" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G382" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11262,7 +11322,11 @@
         </is>
       </c>
       <c r="E384" s="2" t="n"/>
-      <c r="F384" s="4" t="n"/>
+      <c r="F384" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G384" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11287,7 +11351,11 @@
         </is>
       </c>
       <c r="E385" s="2" t="n"/>
-      <c r="F385" s="4" t="n"/>
+      <c r="F385" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G385" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11363,7 +11431,11 @@
         </is>
       </c>
       <c r="E388" s="2" t="n"/>
-      <c r="F388" s="4" t="n"/>
+      <c r="F388" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G388" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11413,7 +11485,11 @@
         </is>
       </c>
       <c r="E390" s="2" t="n"/>
-      <c r="F390" s="4" t="n"/>
+      <c r="F390" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G390" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11438,7 +11514,11 @@
         </is>
       </c>
       <c r="E391" s="2" t="n"/>
-      <c r="F391" s="4" t="n"/>
+      <c r="F391" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G391" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11463,7 +11543,11 @@
         </is>
       </c>
       <c r="E392" s="2" t="n"/>
-      <c r="F392" s="4" t="n"/>
+      <c r="F392" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G392" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11488,7 +11572,11 @@
         </is>
       </c>
       <c r="E393" s="2" t="n"/>
-      <c r="F393" s="4" t="n"/>
+      <c r="F393" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G393" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11571,7 +11659,11 @@
         </is>
       </c>
       <c r="E396" s="2" t="n"/>
-      <c r="F396" s="4" t="n"/>
+      <c r="F396" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G396" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11596,7 +11688,11 @@
         </is>
       </c>
       <c r="E397" s="2" t="n"/>
-      <c r="F397" s="4" t="n"/>
+      <c r="F397" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G397" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11621,7 +11717,11 @@
         </is>
       </c>
       <c r="E398" s="2" t="n"/>
-      <c r="F398" s="4" t="n"/>
+      <c r="F398" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G398" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11675,7 +11775,11 @@
         </is>
       </c>
       <c r="E400" s="2" t="n"/>
-      <c r="F400" s="4" t="n"/>
+      <c r="F400" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G400" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11754,7 +11858,11 @@
         </is>
       </c>
       <c r="E403" s="2" t="n"/>
-      <c r="F403" s="4" t="n"/>
+      <c r="F403" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G403" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11779,7 +11887,11 @@
         </is>
       </c>
       <c r="E404" s="2" t="n"/>
-      <c r="F404" s="4" t="n"/>
+      <c r="F404" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G404" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -11862,7 +11974,11 @@
         </is>
       </c>
       <c r="E407" s="2" t="n"/>
-      <c r="F407" s="4" t="n"/>
+      <c r="F407" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G407" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12057,7 +12173,11 @@
         </is>
       </c>
       <c r="E414" s="2" t="n"/>
-      <c r="F414" s="4" t="n"/>
+      <c r="F414" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G414" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12082,7 +12202,11 @@
         </is>
       </c>
       <c r="E415" s="2" t="n"/>
-      <c r="F415" s="4" t="n"/>
+      <c r="F415" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G415" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12139,7 +12263,11 @@
         </is>
       </c>
       <c r="E417" s="2" t="n"/>
-      <c r="F417" s="4" t="n"/>
+      <c r="F417" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G417" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12164,7 +12292,11 @@
         </is>
       </c>
       <c r="E418" s="2" t="n"/>
-      <c r="F418" s="4" t="n"/>
+      <c r="F418" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G418" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12189,7 +12321,11 @@
         </is>
       </c>
       <c r="E419" s="2" t="n"/>
-      <c r="F419" s="4" t="n"/>
+      <c r="F419" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G419" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12266,7 +12402,11 @@
         </is>
       </c>
       <c r="E422" s="2" t="n"/>
-      <c r="F422" s="4" t="n"/>
+      <c r="F422" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G422" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12291,7 +12431,11 @@
         </is>
       </c>
       <c r="E423" s="2" t="n"/>
-      <c r="F423" s="4" t="n"/>
+      <c r="F423" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G423" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12374,7 +12518,11 @@
         </is>
       </c>
       <c r="E426" s="2" t="n"/>
-      <c r="F426" s="4" t="n"/>
+      <c r="F426" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G426" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12399,7 +12547,11 @@
         </is>
       </c>
       <c r="E427" s="2" t="n"/>
-      <c r="F427" s="4" t="n"/>
+      <c r="F427" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G427" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12486,7 +12638,11 @@
         </is>
       </c>
       <c r="E430" s="2" t="n"/>
-      <c r="F430" s="4" t="n"/>
+      <c r="F430" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G430" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -12598,7 +12754,11 @@
         </is>
       </c>
       <c r="E434" s="2" t="n"/>
-      <c r="F434" s="4" t="n"/>
+      <c r="F434" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G434" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16235,7 +16395,11 @@
         </is>
       </c>
       <c r="E604" s="2" t="n"/>
-      <c r="F604" s="4" t="n"/>
+      <c r="F604" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G604" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16285,7 +16449,11 @@
         </is>
       </c>
       <c r="E606" s="2" t="n"/>
-      <c r="F606" s="4" t="n"/>
+      <c r="F606" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G606" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16310,7 +16478,11 @@
         </is>
       </c>
       <c r="E607" s="2" t="n"/>
-      <c r="F607" s="4" t="n"/>
+      <c r="F607" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G607" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16360,7 +16532,11 @@
         </is>
       </c>
       <c r="E609" s="2" t="n"/>
-      <c r="F609" s="4" t="n"/>
+      <c r="F609" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G609" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16410,7 +16586,11 @@
         </is>
       </c>
       <c r="E611" s="2" t="n"/>
-      <c r="F611" s="4" t="n"/>
+      <c r="F611" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G611" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16435,7 +16615,11 @@
         </is>
       </c>
       <c r="E612" s="2" t="n"/>
-      <c r="F612" s="4" t="n"/>
+      <c r="F612" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G612" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16460,7 +16644,11 @@
         </is>
       </c>
       <c r="E613" s="2" t="n"/>
-      <c r="F613" s="4" t="n"/>
+      <c r="F613" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G613" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16564,7 +16752,11 @@
         </is>
       </c>
       <c r="E617" s="2" t="n"/>
-      <c r="F617" s="4" t="n"/>
+      <c r="F617" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G617" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/CampaignGoal 已覆盖)</t>
@@ -16589,7 +16781,11 @@
         </is>
       </c>
       <c r="E618" s="2" t="n"/>
-      <c r="F618" s="4" t="n"/>
+      <c r="F618" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G618" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16639,7 +16835,11 @@
         </is>
       </c>
       <c r="E620" s="2" t="n"/>
-      <c r="F620" s="4" t="n"/>
+      <c r="F620" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G620" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16664,7 +16864,11 @@
         </is>
       </c>
       <c r="E621" s="2" t="n"/>
-      <c r="F621" s="4" t="n"/>
+      <c r="F621" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G621" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -16689,7 +16893,11 @@
         </is>
       </c>
       <c r="E622" s="2" t="n"/>
-      <c r="F622" s="4" t="n"/>
+      <c r="F622" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G622" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/CampaignTagGoal 已覆盖)</t>
@@ -16714,7 +16922,11 @@
         </is>
       </c>
       <c r="E623" s="2" t="n"/>
-      <c r="F623" s="4" t="n"/>
+      <c r="F623" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G623" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/CampaignTagGoalBySubTag 有流量已覆盖，实测HTTP 500 ClickHouse聚合函数嵌套错误，疑似后端bug)</t>
@@ -16819,7 +17031,11 @@
         </is>
       </c>
       <c r="E627" s="2" t="n"/>
-      <c r="F627" s="4" t="n"/>
+      <c r="F627" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G627" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: exportAllReport/Callback 有流量属异步回调)</t>
@@ -16895,7 +17111,11 @@
         </is>
       </c>
       <c r="E630" s="2" t="n"/>
-      <c r="F630" s="4" t="n"/>
+      <c r="F630" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G630" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/insufficientBudget 已覆盖)</t>
@@ -17109,7 +17329,11 @@
         </is>
       </c>
       <c r="E638" s="2" t="n"/>
-      <c r="F638" s="4" t="n"/>
+      <c r="F638" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G638" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/monthOverMonth 已覆盖)</t>
@@ -17134,7 +17358,11 @@
         </is>
       </c>
       <c r="E639" s="2" t="n"/>
-      <c r="F639" s="4" t="n"/>
+      <c r="F639" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G639" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/NewToBrand 已覆盖)</t>
@@ -17265,7 +17493,11 @@
         </is>
       </c>
       <c r="E644" s="2" t="n"/>
-      <c r="F644" s="4" t="n"/>
+      <c r="F644" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G644" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -17290,7 +17522,11 @@
         </is>
       </c>
       <c r="E645" s="2" t="n"/>
-      <c r="F645" s="4" t="n"/>
+      <c r="F645" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G645" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -17549,7 +17785,11 @@
         </is>
       </c>
       <c r="E655" s="2" t="n"/>
-      <c r="F655" s="4" t="n"/>
+      <c r="F655" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G655" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -17574,7 +17814,11 @@
         </is>
       </c>
       <c r="E656" s="2" t="n"/>
-      <c r="F656" s="4" t="n"/>
+      <c r="F656" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G656" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -17661,7 +17905,11 @@
         </is>
       </c>
       <c r="E659" s="2" t="n"/>
-      <c r="F659" s="4" t="n"/>
+      <c r="F659" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G659" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -17738,7 +17986,11 @@
         </is>
       </c>
       <c r="E662" s="2" t="n"/>
-      <c r="F662" s="4" t="n"/>
+      <c r="F662" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G662" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/topMovers 亦零流量)</t>
@@ -17763,7 +18015,11 @@
         </is>
       </c>
       <c r="E663" s="2" t="n"/>
-      <c r="F663" s="4" t="n"/>
+      <c r="F663" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G663" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -17788,7 +18044,11 @@
         </is>
       </c>
       <c r="E664" s="2" t="n"/>
-      <c r="F664" s="4" t="n"/>
+      <c r="F664" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G664" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -17813,7 +18073,11 @@
         </is>
       </c>
       <c r="E665" s="2" t="n"/>
-      <c r="F665" s="4" t="n"/>
+      <c r="F665" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G665" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: sponsor/Dashboard/weekOverWeek 已覆盖)</t>
@@ -17892,7 +18156,11 @@
         </is>
       </c>
       <c r="E668" s="2" t="n"/>
-      <c r="F668" s="4" t="n"/>
+      <c r="F668" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G668" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18030,7 +18298,11 @@
         </is>
       </c>
       <c r="E673" s="2" t="n"/>
-      <c r="F673" s="4" t="n"/>
+      <c r="F673" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G673" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18349,7 +18621,11 @@
         </is>
       </c>
       <c r="E685" s="2" t="n"/>
-      <c r="F685" s="4" t="n"/>
+      <c r="F685" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G685" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: Dashboard/RealTimeCampaign 已覆盖)</t>
@@ -18374,7 +18650,11 @@
         </is>
       </c>
       <c r="E686" s="2" t="n"/>
-      <c r="F686" s="4" t="n"/>
+      <c r="F686" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G686" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖(注: Dashboard/sales 已覆盖)</t>
@@ -18427,7 +18707,11 @@
         </is>
       </c>
       <c r="E688" s="2" t="n"/>
-      <c r="F688" s="4" t="n"/>
+      <c r="F688" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G688" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18483,7 +18767,11 @@
         </is>
       </c>
       <c r="E690" s="2" t="n"/>
-      <c r="F690" s="4" t="n"/>
+      <c r="F690" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G690" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18647,7 +18935,11 @@
         </is>
       </c>
       <c r="E696" s="2" t="n"/>
-      <c r="F696" s="4" t="n"/>
+      <c r="F696" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G696" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18760,7 +19052,11 @@
         </is>
       </c>
       <c r="E700" s="2" t="n"/>
-      <c r="F700" s="4" t="n"/>
+      <c r="F700" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G700" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18891,7 +19187,11 @@
         </is>
       </c>
       <c r="E705" s="2" t="n"/>
-      <c r="F705" s="4" t="n"/>
+      <c r="F705" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G705" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18916,7 +19216,11 @@
         </is>
       </c>
       <c r="E706" s="2" t="n"/>
-      <c r="F706" s="4" t="n"/>
+      <c r="F706" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G706" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -18941,7 +19245,11 @@
         </is>
       </c>
       <c r="E707" s="2" t="n"/>
-      <c r="F707" s="4" t="n"/>
+      <c r="F707" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G707" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19016,7 +19324,11 @@
         </is>
       </c>
       <c r="E710" s="2" t="n"/>
-      <c r="F710" s="4" t="n"/>
+      <c r="F710" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G710" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19285,7 +19597,11 @@
         </is>
       </c>
       <c r="E718" s="2" t="n"/>
-      <c r="F718" s="4" t="n"/>
+      <c r="F718" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G718" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19485,7 +19801,11 @@
         </is>
       </c>
       <c r="E724" s="2" t="n"/>
-      <c r="F724" s="4" t="n"/>
+      <c r="F724" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G724" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19510,7 +19830,11 @@
         </is>
       </c>
       <c r="E725" s="2" t="n"/>
-      <c r="F725" s="4" t="n"/>
+      <c r="F725" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G725" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19535,7 +19859,11 @@
         </is>
       </c>
       <c r="E726" s="2" t="n"/>
-      <c r="F726" s="4" t="n"/>
+      <c r="F726" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G726" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19560,7 +19888,11 @@
         </is>
       </c>
       <c r="E727" s="2" t="n"/>
-      <c r="F727" s="4" t="n"/>
+      <c r="F727" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G727" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19585,7 +19917,11 @@
         </is>
       </c>
       <c r="E728" s="2" t="n"/>
-      <c r="F728" s="4" t="n"/>
+      <c r="F728" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G728" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19610,7 +19946,11 @@
         </is>
       </c>
       <c r="E729" s="2" t="n"/>
-      <c r="F729" s="4" t="n"/>
+      <c r="F729" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G729" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19635,7 +19975,11 @@
         </is>
       </c>
       <c r="E730" s="2" t="n"/>
-      <c r="F730" s="4" t="n"/>
+      <c r="F730" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G730" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19660,7 +20004,11 @@
         </is>
       </c>
       <c r="E731" s="2" t="n"/>
-      <c r="F731" s="4" t="n"/>
+      <c r="F731" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G731" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -19685,7 +20033,11 @@
         </is>
       </c>
       <c r="E732" s="2" t="n"/>
-      <c r="F732" s="4" t="n"/>
+      <c r="F732" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G732" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -20621,7 +20973,11 @@
         </is>
       </c>
       <c r="E762" s="2" t="n"/>
-      <c r="F762" s="4" t="n"/>
+      <c r="F762" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G762" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -20671,7 +21027,11 @@
         </is>
       </c>
       <c r="E764" s="2" t="n"/>
-      <c r="F764" s="4" t="n"/>
+      <c r="F764" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G764" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -20726,7 +21086,11 @@
         </is>
       </c>
       <c r="E766" s="2" t="n"/>
-      <c r="F766" s="4" t="n"/>
+      <c r="F766" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G766" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -20870,7 +21234,11 @@
         </is>
       </c>
       <c r="E771" s="2" t="n"/>
-      <c r="F771" s="4" t="n"/>
+      <c r="F771" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G771" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -20945,7 +21313,11 @@
         </is>
       </c>
       <c r="E774" s="2" t="n"/>
-      <c r="F774" s="4" t="n"/>
+      <c r="F774" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G774" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -21566,7 +21938,11 @@
         </is>
       </c>
       <c r="E794" s="2" t="n"/>
-      <c r="F794" s="4" t="n"/>
+      <c r="F794" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G794" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -21591,7 +21967,11 @@
         </is>
       </c>
       <c r="E795" s="2" t="n"/>
-      <c r="F795" s="4" t="n"/>
+      <c r="F795" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G795" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -21616,7 +21996,11 @@
         </is>
       </c>
       <c r="E796" s="2" t="n"/>
-      <c r="F796" s="4" t="n"/>
+      <c r="F796" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G796" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -21641,7 +22025,11 @@
         </is>
       </c>
       <c r="E797" s="2" t="n"/>
-      <c r="F797" s="4" t="n"/>
+      <c r="F797" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G797" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22034,7 +22422,11 @@
         </is>
       </c>
       <c r="E810" s="2" t="n"/>
-      <c r="F810" s="4" t="n"/>
+      <c r="F810" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G810" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22059,7 +22451,11 @@
         </is>
       </c>
       <c r="E811" s="2" t="n"/>
-      <c r="F811" s="4" t="n"/>
+      <c r="F811" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G811" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22169,7 +22565,11 @@
         </is>
       </c>
       <c r="E815" s="2" t="n"/>
-      <c r="F815" s="4" t="n"/>
+      <c r="F815" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G815" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22334,7 +22734,11 @@
         </is>
       </c>
       <c r="E820" s="2" t="n"/>
-      <c r="F820" s="4" t="n"/>
+      <c r="F820" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G820" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22359,7 +22763,11 @@
         </is>
       </c>
       <c r="E821" s="2" t="n"/>
-      <c r="F821" s="4" t="n"/>
+      <c r="F821" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G821" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22384,7 +22792,11 @@
         </is>
       </c>
       <c r="E822" s="2" t="n"/>
-      <c r="F822" s="4" t="n"/>
+      <c r="F822" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G822" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22409,7 +22821,11 @@
         </is>
       </c>
       <c r="E823" s="2" t="n"/>
-      <c r="F823" s="4" t="n"/>
+      <c r="F823" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G823" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -22434,7 +22850,11 @@
         </is>
       </c>
       <c r="E824" s="2" t="n"/>
-      <c r="F824" s="4" t="n"/>
+      <c r="F824" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G824" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -26962,7 +27382,11 @@
         </is>
       </c>
       <c r="E1036" s="2" t="n"/>
-      <c r="F1036" s="4" t="n"/>
+      <c r="F1036" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1036" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27016,7 +27440,11 @@
         </is>
       </c>
       <c r="E1038" s="2" t="n"/>
-      <c r="F1038" s="4" t="n"/>
+      <c r="F1038" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1038" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27099,7 +27527,11 @@
         </is>
       </c>
       <c r="E1041" s="2" t="n"/>
-      <c r="F1041" s="4" t="n"/>
+      <c r="F1041" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1041" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27124,7 +27556,11 @@
         </is>
       </c>
       <c r="E1042" s="2" t="n"/>
-      <c r="F1042" s="4" t="n"/>
+      <c r="F1042" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1042" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27149,7 +27585,11 @@
         </is>
       </c>
       <c r="E1043" s="2" t="n"/>
-      <c r="F1043" s="4" t="n"/>
+      <c r="F1043" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1043" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27174,7 +27614,11 @@
         </is>
       </c>
       <c r="E1044" s="2" t="n"/>
-      <c r="F1044" s="4" t="n"/>
+      <c r="F1044" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1044" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27199,7 +27643,11 @@
         </is>
       </c>
       <c r="E1045" s="2" t="n"/>
-      <c r="F1045" s="4" t="n"/>
+      <c r="F1045" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1045" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27488,7 +27936,11 @@
         </is>
       </c>
       <c r="E1056" s="2" t="n"/>
-      <c r="F1056" s="4" t="n"/>
+      <c r="F1056" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1056" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27513,7 +27965,11 @@
         </is>
       </c>
       <c r="E1057" s="2" t="n"/>
-      <c r="F1057" s="4" t="n"/>
+      <c r="F1057" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1057" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27538,7 +27994,11 @@
         </is>
       </c>
       <c r="E1058" s="2" t="n"/>
-      <c r="F1058" s="4" t="n"/>
+      <c r="F1058" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1058" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -27563,7 +28023,11 @@
         </is>
       </c>
       <c r="E1059" s="2" t="n"/>
-      <c r="F1059" s="4" t="n"/>
+      <c r="F1059" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1059" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -29925,7 +30389,11 @@
         </is>
       </c>
       <c r="E1166" s="2" t="n"/>
-      <c r="F1166" s="4" t="n"/>
+      <c r="F1166" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1166" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -29975,7 +30443,11 @@
         </is>
       </c>
       <c r="E1168" s="2" t="n"/>
-      <c r="F1168" s="4" t="n"/>
+      <c r="F1168" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1168" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30030,7 +30502,11 @@
         </is>
       </c>
       <c r="E1170" s="2" t="n"/>
-      <c r="F1170" s="4" t="n"/>
+      <c r="F1170" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1170" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30055,7 +30531,11 @@
         </is>
       </c>
       <c r="E1171" s="2" t="n"/>
-      <c r="F1171" s="4" t="n"/>
+      <c r="F1171" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1171" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30106,7 +30586,11 @@
         </is>
       </c>
       <c r="E1173" s="2" t="n"/>
-      <c r="F1173" s="4" t="n"/>
+      <c r="F1173" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1173" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30210,7 +30694,11 @@
         </is>
       </c>
       <c r="E1177" s="2" t="n"/>
-      <c r="F1177" s="4" t="n"/>
+      <c r="F1177" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1177" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30235,7 +30723,11 @@
         </is>
       </c>
       <c r="E1178" s="2" t="n"/>
-      <c r="F1178" s="4" t="n"/>
+      <c r="F1178" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1178" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30260,7 +30752,11 @@
         </is>
       </c>
       <c r="E1179" s="2" t="n"/>
-      <c r="F1179" s="4" t="n"/>
+      <c r="F1179" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1179" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30310,7 +30806,11 @@
         </is>
       </c>
       <c r="E1181" s="2" t="n"/>
-      <c r="F1181" s="4" t="n"/>
+      <c r="F1181" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1181" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30462,7 +30962,11 @@
         </is>
       </c>
       <c r="E1187" s="2" t="n"/>
-      <c r="F1187" s="4" t="n"/>
+      <c r="F1187" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1187" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30487,7 +30991,11 @@
         </is>
       </c>
       <c r="E1188" s="2" t="n"/>
-      <c r="F1188" s="4" t="n"/>
+      <c r="F1188" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1188" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30512,7 +31020,11 @@
         </is>
       </c>
       <c r="E1189" s="2" t="n"/>
-      <c r="F1189" s="4" t="n"/>
+      <c r="F1189" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1189" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30563,7 +31075,11 @@
         </is>
       </c>
       <c r="E1191" s="2" t="n"/>
-      <c r="F1191" s="4" t="n"/>
+      <c r="F1191" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1191" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30641,7 +31157,11 @@
         </is>
       </c>
       <c r="E1194" s="2" t="n"/>
-      <c r="F1194" s="4" t="n"/>
+      <c r="F1194" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1194" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30693,7 +31213,11 @@
         </is>
       </c>
       <c r="E1196" s="2" t="n"/>
-      <c r="F1196" s="4" t="n"/>
+      <c r="F1196" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1196" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30770,7 +31294,11 @@
         </is>
       </c>
       <c r="E1199" s="2" t="n"/>
-      <c r="F1199" s="4" t="n"/>
+      <c r="F1199" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1199" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30875,7 +31403,11 @@
         </is>
       </c>
       <c r="E1203" s="2" t="n"/>
-      <c r="F1203" s="4" t="n"/>
+      <c r="F1203" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1203" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -30900,7 +31432,11 @@
         </is>
       </c>
       <c r="E1204" s="2" t="n"/>
-      <c r="F1204" s="4" t="n"/>
+      <c r="F1204" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1204" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -31902,7 +32438,11 @@
         </is>
       </c>
       <c r="E1250" s="2" t="n"/>
-      <c r="F1250" s="4" t="n"/>
+      <c r="F1250" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1250" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -31927,7 +32467,11 @@
         </is>
       </c>
       <c r="E1251" s="2" t="n"/>
-      <c r="F1251" s="4" t="n"/>
+      <c r="F1251" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1251" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32151,7 +32695,11 @@
         </is>
       </c>
       <c r="E1259" s="2" t="n"/>
-      <c r="F1259" s="4" t="n"/>
+      <c r="F1259" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1259" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32176,7 +32724,11 @@
         </is>
       </c>
       <c r="E1260" s="2" t="n"/>
-      <c r="F1260" s="4" t="n"/>
+      <c r="F1260" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1260" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32304,7 +32856,11 @@
         </is>
       </c>
       <c r="E1265" s="2" t="n"/>
-      <c r="F1265" s="4" t="n"/>
+      <c r="F1265" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1265" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32329,7 +32885,11 @@
         </is>
       </c>
       <c r="E1266" s="2" t="n"/>
-      <c r="F1266" s="4" t="n"/>
+      <c r="F1266" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1266" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32354,7 +32914,11 @@
         </is>
       </c>
       <c r="E1267" s="2" t="n"/>
-      <c r="F1267" s="4" t="n"/>
+      <c r="F1267" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1267" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32457,7 +33021,11 @@
         </is>
       </c>
       <c r="E1271" s="2" t="n"/>
-      <c r="F1271" s="4" t="n"/>
+      <c r="F1271" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1271" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32624,7 +33192,11 @@
         </is>
       </c>
       <c r="E1277" s="2" t="n"/>
-      <c r="F1277" s="4" t="n"/>
+      <c r="F1277" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1277" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32649,7 +33221,11 @@
         </is>
       </c>
       <c r="E1278" s="2" t="n"/>
-      <c r="F1278" s="4" t="n"/>
+      <c r="F1278" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1278" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32699,7 +33275,11 @@
         </is>
       </c>
       <c r="E1280" s="2" t="n"/>
-      <c r="F1280" s="4" t="n"/>
+      <c r="F1280" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1280" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32724,7 +33304,11 @@
         </is>
       </c>
       <c r="E1281" s="2" t="n"/>
-      <c r="F1281" s="4" t="n"/>
+      <c r="F1281" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1281" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32749,7 +33333,11 @@
         </is>
       </c>
       <c r="E1282" s="2" t="n"/>
-      <c r="F1282" s="4" t="n"/>
+      <c r="F1282" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1282" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32774,7 +33362,11 @@
         </is>
       </c>
       <c r="E1283" s="2" t="n"/>
-      <c r="F1283" s="4" t="n"/>
+      <c r="F1283" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1283" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -32938,7 +33530,11 @@
         </is>
       </c>
       <c r="E1289" s="2" t="n"/>
-      <c r="F1289" s="4" t="n"/>
+      <c r="F1289" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1289" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33079,7 +33675,11 @@
         </is>
       </c>
       <c r="E1294" s="2" t="n"/>
-      <c r="F1294" s="4" t="n"/>
+      <c r="F1294" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1294" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33104,7 +33704,11 @@
         </is>
       </c>
       <c r="E1295" s="2" t="n"/>
-      <c r="F1295" s="4" t="n"/>
+      <c r="F1295" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1295" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33160,7 +33764,11 @@
         </is>
       </c>
       <c r="E1297" s="2" t="n"/>
-      <c r="F1297" s="4" t="n"/>
+      <c r="F1297" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1297" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33185,7 +33793,11 @@
         </is>
       </c>
       <c r="E1298" s="2" t="n"/>
-      <c r="F1298" s="4" t="n"/>
+      <c r="F1298" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1298" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33210,7 +33822,11 @@
         </is>
       </c>
       <c r="E1299" s="2" t="n"/>
-      <c r="F1299" s="4" t="n"/>
+      <c r="F1299" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1299" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33235,7 +33851,11 @@
         </is>
       </c>
       <c r="E1300" s="2" t="n"/>
-      <c r="F1300" s="4" t="n"/>
+      <c r="F1300" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1300" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33260,7 +33880,11 @@
         </is>
       </c>
       <c r="E1301" s="2" t="n"/>
-      <c r="F1301" s="4" t="n"/>
+      <c r="F1301" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1301" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33285,7 +33909,11 @@
         </is>
       </c>
       <c r="E1302" s="2" t="n"/>
-      <c r="F1302" s="4" t="n"/>
+      <c r="F1302" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1302" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33310,7 +33938,11 @@
         </is>
       </c>
       <c r="E1303" s="2" t="n"/>
-      <c r="F1303" s="4" t="n"/>
+      <c r="F1303" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1303" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33360,7 +33992,11 @@
         </is>
       </c>
       <c r="E1305" s="2" t="n"/>
-      <c r="F1305" s="4" t="n"/>
+      <c r="F1305" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1305" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33435,7 +34071,11 @@
         </is>
       </c>
       <c r="E1308" s="2" t="n"/>
-      <c r="F1308" s="4" t="n"/>
+      <c r="F1308" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1308" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>
@@ -33460,7 +34100,11 @@
         </is>
       </c>
       <c r="E1309" s="2" t="n"/>
-      <c r="F1309" s="4" t="n"/>
+      <c r="F1309" s="6" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
       <c r="G1309" s="4" t="inlineStr">
         <is>
           <t>零流量(365d 0次)，暂不覆盖</t>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -20520,7 +20520,7 @@
 无Tag过滤+campaignStatus=[]+ReportAdType=1 — 7.6%
 按Tag过滤+campaignStatus=[ids+]+ReportAdType=2 — 1.6%
 无Tag过滤+campaignStatus=[]+ReportAdType=0 — 1.6%
-按Tag过滤+campaignStatus=[]+不传ReportAdType — 1.0%</t>
+按Tag过滤+campaignStatus=[]+不传ReportAdType(tagIds列表含-1·变体2) — 1.0%</t>
         </is>
       </c>
       <c r="G747" s="2" t="n"/>
@@ -20549,9 +20549,9 @@
 无Tag过滤+不传market — 31.4%
 无Tag过滤+market=US — 19.8%
 按Tag过滤+market=US — 7.8%
-按Tag过滤+不传market — 4.0%
+按Tag过滤+不传market(tagIds列表含-1·变体2) — 4.0%
 无Tag过滤+market=CA — 1.6%
-按Tag过滤+不传market — 1.0%</t>
+按Tag过滤+不传market(tagIds列表含-1·变体3) — 1.0%</t>
         </is>
       </c>
       <c r="G748" s="2" t="n"/>
@@ -22302,7 +22302,7 @@
 itemSet=1+无CampaignTag过滤 — 7.8%
 itemSet=2+无CampaignTag过滤 — 3.6%
 不传itemSet+按CampaignTag过滤 — 3.0%
-itemSet=0+按CampaignTag过滤 — 1.2%</t>
+itemSet=0+按CampaignTag过滤(campaignTagIds列表含-1·变体2) — 1.2%</t>
         </is>
       </c>
       <c r="G806" s="4" t="inlineStr">
@@ -22337,7 +22337,7 @@
 itemSet=1+无CampaignTag过滤 — 7.8%
 itemSet=2+无CampaignTag过滤 — 3.6%
 不传itemSet+按CampaignTag过滤 — 3.0%
-itemSet=0+按CampaignTag过滤 — 1.2%</t>
+itemSet=0+按CampaignTag过滤(campaignTagIds列表含-1·变体2) — 1.2%</t>
         </is>
       </c>
       <c r="G807" s="2" t="n"/>
@@ -22368,7 +22368,7 @@
 itemSet=1+无CampaignTag过滤 — 7.8%
 itemSet=2+无CampaignTag过滤 — 3.6%
 不传itemSet+按CampaignTag过滤 — 3.0%
-itemSet=0+按CampaignTag过滤 — 1.2%</t>
+itemSet=0+按CampaignTag过滤(campaignTagIds列表含-1·变体2) — 1.2%</t>
         </is>
       </c>
       <c r="G808" s="2" t="n"/>
@@ -22399,7 +22399,7 @@
 itemSet=1+无CampaignTag过滤 — 7.8%
 itemSet=2+无CampaignTag过滤 — 3.6%
 不传itemSet+按CampaignTag过滤 — 3.0%
-itemSet=0+按CampaignTag过滤 — 1.2%</t>
+itemSet=0+按CampaignTag过滤(campaignTagIds列表含-1·变体2) — 1.2%</t>
         </is>
       </c>
       <c r="G809" s="2" t="n"/>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>全状态广告组 — 86.8%
 Active状态过滤 — 11%
@@ -2377,7 +2377,7 @@
       </c>
       <c r="G3" s="2" t="n"/>
     </row>
-    <row r="4" ht="15.95" customHeight="1">
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>广告组下钻明细 — 100%</t>
         </is>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>全状态汇总 — 86.8%
 Active状态汇总 — 11%
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>全状态趋势图 — 86.8%
 Active状态趋势图 — 11%
@@ -2745,14 +2745,18 @@
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>全状态无标签过滤 — 53%
 Active状态过滤 — 37.8%
 Campaign标签过滤 — 8.4%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>所属模块 AdgroupReport(小写g)，case 在 AdgroupReport-sponsor-display/ 目录；与 AdGroupReport(大写G，/api/Report/adGroup* 路径)是两个不同 swagger tag，接口路径无重叠</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -2793,7 +2797,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>全状态无标签 — 53%
 Active状态过滤 — 37.8%
@@ -2841,7 +2845,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>按PageType维度 — 99.5%</t>
         </is>
@@ -2887,7 +2891,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>按PageType汇总 — 99.5%</t>
         </is>
@@ -2912,7 +2916,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>按PageType趋势图 — 99.5%</t>
         </is>
@@ -2958,7 +2962,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>按Platform维度 — 87.7%
 Campaign标签过滤 — 12.3%</t>
@@ -3005,7 +3009,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>按Platform汇总 — 87.7%
 Campaign标签过滤 — 12.3%</t>
@@ -3031,7 +3035,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>按Platform趋势图 — 87.7%
 Campaign标签过滤 — 12.3%</t>
@@ -3057,7 +3061,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>全状态趋势图 — 53%
 Active状态趋势图 — 37.8%
@@ -3163,16 +3167,20 @@
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>全状态Adgroup视图 — 76.2%
 Active状态过滤 — 10.4%
 Default下钻视图 — 10.2%</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>所属模块 AdGroupReport(大写G)，case 在 AdGroupReport-Report/ 目录；与 AdgroupReport(小写g，sponsor/display 产品线)是两个不同 swagger tag，因 Windows 文件夹不区分大小写故各自加产品线后缀区分</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
@@ -3190,7 +3198,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n"/>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>广告组下钻明细</t>
         </is>
@@ -3240,7 +3248,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>全状态汇总 — 76.2%
 Active状态过滤 — 10.4%
@@ -3324,7 +3332,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.95" customHeight="1">
+    <row r="42" ht="16" customHeight="1">
       <c r="A42" s="2" t="n"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
@@ -3342,14 +3350,14 @@
         </is>
       </c>
       <c r="E42" s="2" t="n"/>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>按PageType维度 — 100%</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
     </row>
-    <row r="43" ht="15.95" customHeight="1">
+    <row r="43" ht="16" customHeight="1">
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
@@ -3367,7 +3375,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n"/>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>按PageType广告组下钻明细 — 100%</t>
         </is>
@@ -3399,7 +3407,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.95" customHeight="1">
+    <row r="45" ht="16" customHeight="1">
       <c r="A45" s="2" t="n"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
@@ -3417,14 +3425,14 @@
         </is>
       </c>
       <c r="E45" s="2" t="n"/>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>按PageType汇总 — 100%</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
     </row>
-    <row r="46" ht="15.95" customHeight="1">
+    <row r="46" ht="16" customHeight="1">
       <c r="A46" s="2" t="n"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
@@ -3442,7 +3450,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n"/>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>按PageType趋势图 — 100%</t>
         </is>
@@ -3524,7 +3532,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15.95" customHeight="1">
+    <row r="50" ht="16" customHeight="1">
       <c r="A50" s="2" t="n"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
@@ -3542,14 +3550,14 @@
         </is>
       </c>
       <c r="E50" s="2" t="n"/>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>按Platform维度 — 100%</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
     </row>
-    <row r="51" ht="15.95" customHeight="1">
+    <row r="51" ht="16" customHeight="1">
       <c r="A51" s="2" t="n"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
@@ -3567,7 +3575,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n"/>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>按Platform广告组下钻明细 — 100%</t>
         </is>
@@ -3599,7 +3607,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15.95" customHeight="1">
+    <row r="53" ht="16" customHeight="1">
       <c r="A53" s="2" t="n"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
@@ -3617,14 +3625,14 @@
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>按Platform汇总 — 100%</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
     </row>
-    <row r="54" ht="15.95" customHeight="1">
+    <row r="54" ht="16" customHeight="1">
       <c r="A54" s="2" t="n"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
@@ -3642,7 +3650,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>按Platform趋势图 — 100%</t>
         </is>
@@ -3667,7 +3675,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n"/>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>全状态趋势图 — 76.2%
 Active状态趋势图 — 10.4%
@@ -3676,7 +3684,7 @@
       </c>
       <c r="G55" s="2" t="n"/>
     </row>
-    <row r="56" ht="15.95" customHeight="1">
+    <row r="56" ht="16" customHeight="1">
       <c r="A56" s="2" t="n"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
@@ -3694,7 +3702,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n"/>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>小时粒度探索数据</t>
         </is>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -751,9 +751,19 @@
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="F9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>2% (1/45)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5463,8 +5473,16 @@
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="2" t="n"/>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -5484,8 +5502,16 @@
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
-      <c r="F138" s="4" t="n"/>
-      <c r="G138" s="2" t="n"/>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -5505,8 +5531,16 @@
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
-      <c r="F139" s="4" t="n"/>
-      <c r="G139" s="2" t="n"/>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -5526,8 +5560,16 @@
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="2" t="n"/>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -5547,8 +5589,16 @@
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
-      <c r="F141" s="4" t="n"/>
-      <c r="G141" s="2" t="n"/>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -5568,8 +5618,16 @@
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
-      <c r="F142" s="4" t="n"/>
-      <c r="G142" s="2" t="n"/>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -5589,8 +5647,16 @@
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="2" t="n"/>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -5610,8 +5676,16 @@
         </is>
       </c>
       <c r="E144" s="2" t="n"/>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="2" t="n"/>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -5631,8 +5705,16 @@
         </is>
       </c>
       <c r="E145" s="2" t="n"/>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="2" t="n"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -5652,8 +5734,16 @@
         </is>
       </c>
       <c r="E146" s="2" t="n"/>
-      <c r="F146" s="4" t="n"/>
-      <c r="G146" s="2" t="n"/>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -5673,8 +5763,16 @@
         </is>
       </c>
       <c r="E147" s="2" t="n"/>
-      <c r="F147" s="4" t="n"/>
-      <c r="G147" s="2" t="n"/>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -5694,8 +5792,16 @@
         </is>
       </c>
       <c r="E148" s="2" t="n"/>
-      <c r="F148" s="4" t="n"/>
-      <c r="G148" s="2" t="n"/>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -5715,8 +5821,16 @@
         </is>
       </c>
       <c r="E149" s="2" t="n"/>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="2" t="n"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -5736,8 +5850,16 @@
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="2" t="n"/>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -5757,8 +5879,16 @@
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
-      <c r="F151" s="4" t="n"/>
-      <c r="G151" s="2" t="n"/>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -5778,8 +5908,16 @@
         </is>
       </c>
       <c r="E152" s="2" t="n"/>
-      <c r="F152" s="4" t="n"/>
-      <c r="G152" s="2" t="n"/>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -5799,8 +5937,16 @@
         </is>
       </c>
       <c r="E153" s="2" t="n"/>
-      <c r="F153" s="4" t="n"/>
-      <c r="G153" s="2" t="n"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -5820,8 +5966,16 @@
         </is>
       </c>
       <c r="E154" s="2" t="n"/>
-      <c r="F154" s="4" t="n"/>
-      <c r="G154" s="2" t="n"/>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -5841,8 +5995,16 @@
         </is>
       </c>
       <c r="E155" s="2" t="n"/>
-      <c r="F155" s="4" t="n"/>
-      <c r="G155" s="2" t="n"/>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -5862,8 +6024,16 @@
         </is>
       </c>
       <c r="E156" s="2" t="n"/>
-      <c r="F156" s="4" t="n"/>
-      <c r="G156" s="2" t="n"/>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -5883,8 +6053,16 @@
         </is>
       </c>
       <c r="E157" s="2" t="n"/>
-      <c r="F157" s="4" t="n"/>
-      <c r="G157" s="2" t="n"/>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -5904,8 +6082,16 @@
         </is>
       </c>
       <c r="E158" s="2" t="n"/>
-      <c r="F158" s="4" t="n"/>
-      <c r="G158" s="2" t="n"/>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -5925,8 +6111,16 @@
         </is>
       </c>
       <c r="E159" s="2" t="n"/>
-      <c r="F159" s="4" t="n"/>
-      <c r="G159" s="2" t="n"/>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -5946,8 +6140,16 @@
         </is>
       </c>
       <c r="E160" s="2" t="n"/>
-      <c r="F160" s="4" t="n"/>
-      <c r="G160" s="2" t="n"/>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -5967,8 +6169,16 @@
         </is>
       </c>
       <c r="E161" s="2" t="n"/>
-      <c r="F161" s="4" t="n"/>
-      <c r="G161" s="2" t="n"/>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -5988,8 +6198,16 @@
         </is>
       </c>
       <c r="E162" s="2" t="n"/>
-      <c r="F162" s="4" t="n"/>
-      <c r="G162" s="2" t="n"/>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -6009,8 +6227,16 @@
         </is>
       </c>
       <c r="E163" s="2" t="n"/>
-      <c r="F163" s="4" t="n"/>
-      <c r="G163" s="2" t="n"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -6030,8 +6256,16 @@
         </is>
       </c>
       <c r="E164" s="2" t="n"/>
-      <c r="F164" s="4" t="n"/>
-      <c r="G164" s="2" t="n"/>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -6051,8 +6285,16 @@
         </is>
       </c>
       <c r="E165" s="2" t="n"/>
-      <c r="F165" s="4" t="n"/>
-      <c r="G165" s="2" t="n"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -6072,8 +6314,16 @@
         </is>
       </c>
       <c r="E166" s="2" t="n"/>
-      <c r="F166" s="4" t="n"/>
-      <c r="G166" s="2" t="n"/>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -6093,8 +6343,16 @@
         </is>
       </c>
       <c r="E167" s="2" t="n"/>
-      <c r="F167" s="4" t="n"/>
-      <c r="G167" s="2" t="n"/>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -6114,8 +6372,16 @@
         </is>
       </c>
       <c r="E168" s="2" t="n"/>
-      <c r="F168" s="4" t="n"/>
-      <c r="G168" s="2" t="n"/>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -6135,8 +6401,16 @@
         </is>
       </c>
       <c r="E169" s="2" t="n"/>
-      <c r="F169" s="4" t="n"/>
-      <c r="G169" s="2" t="n"/>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -6156,8 +6430,16 @@
         </is>
       </c>
       <c r="E170" s="2" t="n"/>
-      <c r="F170" s="4" t="n"/>
-      <c r="G170" s="2" t="n"/>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -6177,8 +6459,16 @@
         </is>
       </c>
       <c r="E171" s="2" t="n"/>
-      <c r="F171" s="4" t="n"/>
-      <c r="G171" s="2" t="n"/>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -6198,8 +6488,16 @@
         </is>
       </c>
       <c r="E172" s="2" t="n"/>
-      <c r="F172" s="4" t="n"/>
-      <c r="G172" s="2" t="n"/>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -6219,8 +6517,16 @@
         </is>
       </c>
       <c r="E173" s="2" t="n"/>
-      <c r="F173" s="4" t="n"/>
-      <c r="G173" s="2" t="n"/>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -6240,8 +6546,16 @@
         </is>
       </c>
       <c r="E174" s="2" t="n"/>
-      <c r="F174" s="4" t="n"/>
-      <c r="G174" s="2" t="n"/>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -6261,8 +6575,16 @@
         </is>
       </c>
       <c r="E175" s="2" t="n"/>
-      <c r="F175" s="4" t="n"/>
-      <c r="G175" s="2" t="n"/>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -6282,8 +6604,16 @@
         </is>
       </c>
       <c r="E176" s="2" t="n"/>
-      <c r="F176" s="4" t="n"/>
-      <c r="G176" s="2" t="n"/>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -6303,8 +6633,16 @@
         </is>
       </c>
       <c r="E177" s="2" t="n"/>
-      <c r="F177" s="4" t="n"/>
-      <c r="G177" s="2" t="n"/>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -6324,10 +6662,18 @@
         </is>
       </c>
       <c r="E178" s="2" t="n"/>
-      <c r="F178" s="4" t="n"/>
-      <c r="G178" s="2" t="n"/>
-    </row>
-    <row r="179">
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="64" customHeight="1">
       <c r="A179" s="2" t="n"/>
       <c r="B179" s="2" t="inlineStr">
         <is>
@@ -6345,7 +6691,14 @@
         </is>
       </c>
       <c r="E179" s="2" t="n"/>
-      <c r="F179" s="4" t="n"/>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>默认调用(不带uniqueTimeZone) — 84.2%
+uniqueTimeZone=-5 — 7.6%
+uniqueTimeZone=-8 — 4.2%
+uniqueTimeZone=-6 — 1.8%</t>
+        </is>
+      </c>
       <c r="G179" s="2" t="n"/>
     </row>
     <row r="180">
@@ -6366,8 +6719,16 @@
         </is>
       </c>
       <c r="E180" s="2" t="n"/>
-      <c r="F180" s="4" t="n"/>
-      <c r="G180" s="2" t="n"/>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -6387,8 +6748,16 @@
         </is>
       </c>
       <c r="E181" s="2" t="n"/>
-      <c r="F181" s="4" t="n"/>
-      <c r="G181" s="2" t="n"/>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1405,9 +1405,19 @@
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="F36" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>50% (17/34)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -25219,7 +25229,7 @@
       <c r="F917" s="4" t="n"/>
       <c r="G917" s="2" t="n"/>
     </row>
-    <row r="918">
+    <row r="918" ht="16" customHeight="1">
       <c r="A918" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25241,10 +25251,14 @@
         </is>
       </c>
       <c r="E918" s="2" t="n"/>
-      <c r="F918" s="4" t="n"/>
+      <c r="F918" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G918" s="2" t="n"/>
     </row>
-    <row r="919">
+    <row r="919" ht="16" customHeight="1">
       <c r="A919" s="2" t="n"/>
       <c r="B919" s="2" t="inlineStr">
         <is>
@@ -25262,10 +25276,14 @@
         </is>
       </c>
       <c r="E919" s="2" t="n"/>
-      <c r="F919" s="4" t="n"/>
+      <c r="F919" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G919" s="2" t="n"/>
     </row>
-    <row r="920">
+    <row r="920" ht="16" customHeight="1">
       <c r="A920" s="2" t="n"/>
       <c r="B920" s="2" t="inlineStr">
         <is>
@@ -25283,7 +25301,11 @@
         </is>
       </c>
       <c r="E920" s="2" t="n"/>
-      <c r="F920" s="4" t="n"/>
+      <c r="F920" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G920" s="2" t="n"/>
     </row>
     <row r="921">
@@ -25304,8 +25326,16 @@
         </is>
       </c>
       <c r="E921" s="2" t="n"/>
-      <c r="F921" s="4" t="n"/>
-      <c r="G921" s="2" t="n"/>
+      <c r="F921" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G921" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n"/>
@@ -25325,10 +25355,18 @@
         </is>
       </c>
       <c r="E922" s="2" t="n"/>
-      <c r="F922" s="4" t="n"/>
-      <c r="G922" s="2" t="n"/>
-    </row>
-    <row r="923">
+      <c r="F922" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G922" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="923" ht="16" customHeight="1">
       <c r="A923" s="2" t="n"/>
       <c r="B923" s="2" t="inlineStr">
         <is>
@@ -25346,7 +25384,11 @@
         </is>
       </c>
       <c r="E923" s="2" t="n"/>
-      <c r="F923" s="4" t="n"/>
+      <c r="F923" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G923" s="2" t="n"/>
     </row>
     <row r="924">
@@ -25367,10 +25409,18 @@
         </is>
       </c>
       <c r="E924" s="2" t="n"/>
-      <c r="F924" s="4" t="n"/>
-      <c r="G924" s="2" t="n"/>
-    </row>
-    <row r="925">
+      <c r="F924" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G924" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="925" ht="64" customHeight="1">
       <c r="A925" s="2" t="n"/>
       <c r="B925" s="2" t="inlineStr">
         <is>
@@ -25388,10 +25438,17 @@
         </is>
       </c>
       <c r="E925" s="2" t="n"/>
-      <c r="F925" s="4" t="n"/>
+      <c r="F925" s="7" t="inlineStr">
+        <is>
+          <t>kindType=Default+  dim  =ytd — 75.2%
+kindType=DisplayItem+  dim  =ytd — 21.0%
+kindType=Default+  dim  =week — 2.0%
+kindType=Default+  dim  =date — 1.6%</t>
+        </is>
+      </c>
       <c r="G925" s="2" t="n"/>
     </row>
-    <row r="926">
+    <row r="926" ht="48" customHeight="1">
       <c r="A926" s="2" t="n"/>
       <c r="B926" s="2" t="inlineStr">
         <is>
@@ -25409,7 +25466,13 @@
         </is>
       </c>
       <c r="E926" s="2" t="n"/>
-      <c r="F926" s="4" t="n"/>
+      <c r="F926" s="7" t="inlineStr">
+        <is>
+          <t>kindType=Default+  dim  =ytd — 76.2%
+kindType=DisplayItem+  dim  =ytd — 21.4%
+kindType=Default+  dim  =week — 1.2%</t>
+        </is>
+      </c>
       <c r="G926" s="2" t="n"/>
     </row>
     <row r="927">
@@ -25430,8 +25493,16 @@
         </is>
       </c>
       <c r="E927" s="2" t="n"/>
-      <c r="F927" s="4" t="n"/>
-      <c r="G927" s="2" t="n"/>
+      <c r="F927" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G927" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 129次)</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n"/>
@@ -25451,10 +25522,18 @@
         </is>
       </c>
       <c r="E928" s="2" t="n"/>
-      <c r="F928" s="4" t="n"/>
-      <c r="G928" s="2" t="n"/>
-    </row>
-    <row r="929">
+      <c r="F928" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G928" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 128次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="929" ht="16" customHeight="1">
       <c r="A929" s="2" t="n"/>
       <c r="B929" s="2" t="inlineStr">
         <is>
@@ -25472,7 +25551,11 @@
         </is>
       </c>
       <c r="E929" s="2" t="n"/>
-      <c r="F929" s="4" t="n"/>
+      <c r="F929" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G929" s="2" t="n"/>
     </row>
     <row r="930">
@@ -25493,10 +25576,18 @@
         </is>
       </c>
       <c r="E930" s="2" t="n"/>
-      <c r="F930" s="4" t="n"/>
-      <c r="G930" s="2" t="n"/>
-    </row>
-    <row r="931">
+      <c r="F930" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G930" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="931" ht="64" customHeight="1">
       <c r="A931" s="2" t="n"/>
       <c r="B931" s="2" t="inlineStr">
         <is>
@@ -25514,10 +25605,17 @@
         </is>
       </c>
       <c r="E931" s="2" t="n"/>
-      <c r="F931" s="4" t="n"/>
+      <c r="F931" s="7" t="inlineStr">
+        <is>
+          <t>kindType=Default+  dim  =ytd — 75.4%
+kindType=DisplayItem+  dim  =ytd — 21.2%
+kindType=Default+  dim  =week — 1.6%
+kindType=Default+  dim  =date — 1.2%</t>
+        </is>
+      </c>
       <c r="G931" s="2" t="n"/>
     </row>
-    <row r="932">
+    <row r="932" ht="16" customHeight="1">
       <c r="A932" s="2" t="n"/>
       <c r="B932" s="2" t="inlineStr">
         <is>
@@ -25535,10 +25633,14 @@
         </is>
       </c>
       <c r="E932" s="2" t="n"/>
-      <c r="F932" s="4" t="n"/>
+      <c r="F932" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G932" s="2" t="n"/>
     </row>
-    <row r="933">
+    <row r="933" ht="16" customHeight="1">
       <c r="A933" s="2" t="n"/>
       <c r="B933" s="2" t="inlineStr">
         <is>
@@ -25556,10 +25658,14 @@
         </is>
       </c>
       <c r="E933" s="2" t="n"/>
-      <c r="F933" s="4" t="n"/>
+      <c r="F933" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G933" s="2" t="n"/>
     </row>
-    <row r="934">
+    <row r="934" ht="16" customHeight="1">
       <c r="A934" s="2" t="n"/>
       <c r="B934" s="2" t="inlineStr">
         <is>
@@ -25577,7 +25683,11 @@
         </is>
       </c>
       <c r="E934" s="2" t="n"/>
-      <c r="F934" s="4" t="n"/>
+      <c r="F934" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G934" s="2" t="n"/>
     </row>
     <row r="935">
@@ -25598,8 +25708,16 @@
         </is>
       </c>
       <c r="E935" s="2" t="n"/>
-      <c r="F935" s="4" t="n"/>
-      <c r="G935" s="2" t="n"/>
+      <c r="F935" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G935" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 2次)</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n"/>
@@ -25619,10 +25737,18 @@
         </is>
       </c>
       <c r="E936" s="2" t="n"/>
-      <c r="F936" s="4" t="n"/>
-      <c r="G936" s="2" t="n"/>
-    </row>
-    <row r="937">
+      <c r="F936" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G936" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 2次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="937" ht="16" customHeight="1">
       <c r="A937" s="2" t="n"/>
       <c r="B937" s="2" t="inlineStr">
         <is>
@@ -25640,10 +25766,14 @@
         </is>
       </c>
       <c r="E937" s="2" t="n"/>
-      <c r="F937" s="4" t="n"/>
+      <c r="F937" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G937" s="2" t="n"/>
     </row>
-    <row r="938">
+    <row r="938" ht="48" customHeight="1">
       <c r="A938" s="2" t="n"/>
       <c r="B938" s="2" t="inlineStr">
         <is>
@@ -25661,10 +25791,16 @@
         </is>
       </c>
       <c r="E938" s="2" t="n"/>
-      <c r="F938" s="4" t="n"/>
+      <c r="F938" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=TargetingStrategy+  dim  =ytd — 57.0%
+tabGroupBy=Campaign+  dim  =ytd — 39.8%
+tabGroupBy=Tactic+  dim  =ytd — 1.6%</t>
+        </is>
+      </c>
       <c r="G938" s="2" t="n"/>
     </row>
-    <row r="939">
+    <row r="939" ht="48" customHeight="1">
       <c r="A939" s="2" t="n"/>
       <c r="B939" s="2" t="inlineStr">
         <is>
@@ -25682,7 +25818,13 @@
         </is>
       </c>
       <c r="E939" s="2" t="n"/>
-      <c r="F939" s="4" t="n"/>
+      <c r="F939" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=TargetingStrategy+  dim  =ytd — 56.6%
+tabGroupBy=Campaign+  dim  =ytd — 40.6%
+tabGroupBy=Tactic+  dim  =ytd — 1.8%</t>
+        </is>
+      </c>
       <c r="G939" s="2" t="n"/>
     </row>
     <row r="940">
@@ -25703,8 +25845,16 @@
         </is>
       </c>
       <c r="E940" s="2" t="n"/>
-      <c r="F940" s="4" t="n"/>
-      <c r="G940" s="2" t="n"/>
+      <c r="F940" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G940" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 25次)</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n"/>
@@ -25724,10 +25874,18 @@
         </is>
       </c>
       <c r="E941" s="2" t="n"/>
-      <c r="F941" s="4" t="n"/>
-      <c r="G941" s="2" t="n"/>
-    </row>
-    <row r="942">
+      <c r="F941" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G941" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 25次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="942" ht="16" customHeight="1">
       <c r="A942" s="2" t="n"/>
       <c r="B942" s="2" t="inlineStr">
         <is>
@@ -25745,7 +25903,11 @@
         </is>
       </c>
       <c r="E942" s="2" t="n"/>
-      <c r="F942" s="4" t="n"/>
+      <c r="F942" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G942" s="2" t="n"/>
     </row>
     <row r="943">
@@ -25766,10 +25928,18 @@
         </is>
       </c>
       <c r="E943" s="2" t="n"/>
-      <c r="F943" s="4" t="n"/>
-      <c r="G943" s="2" t="n"/>
-    </row>
-    <row r="944">
+      <c r="F943" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G943" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="944" ht="48" customHeight="1">
       <c r="A944" s="2" t="n"/>
       <c r="B944" s="2" t="inlineStr">
         <is>
@@ -25787,10 +25957,16 @@
         </is>
       </c>
       <c r="E944" s="2" t="n"/>
-      <c r="F944" s="4" t="n"/>
+      <c r="F944" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=TargetingStrategy+  dim  =ytd — 58.2%
+tabGroupBy=Campaign+  dim  =ytd — 39.0%
+tabGroupBy=Tactic+  dim  =ytd — 1.6%</t>
+        </is>
+      </c>
       <c r="G944" s="2" t="n"/>
     </row>
-    <row r="945">
+    <row r="945" ht="64" customHeight="1">
       <c r="A945" s="2" t="n"/>
       <c r="B945" s="2" t="inlineStr">
         <is>
@@ -25808,7 +25984,14 @@
         </is>
       </c>
       <c r="E945" s="2" t="n"/>
-      <c r="F945" s="4" t="n"/>
+      <c r="F945" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无Campaign过滤 — 44.8%
+profileIds=[ids+]+按Campaign过滤 — 37.0%
+profileIds=[ids+]+无Campaign过滤 — 15.4%
+profileIds=[]+按Campaign过滤 — 2.8%</t>
+        </is>
+      </c>
       <c r="G945" s="2" t="n"/>
     </row>
     <row r="946">
@@ -25829,8 +26012,16 @@
         </is>
       </c>
       <c r="E946" s="2" t="n"/>
-      <c r="F946" s="4" t="n"/>
-      <c r="G946" s="2" t="n"/>
+      <c r="F946" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G946" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" s="2" t="n"/>
@@ -25850,8 +26041,16 @@
         </is>
       </c>
       <c r="E947" s="2" t="n"/>
-      <c r="F947" s="4" t="n"/>
-      <c r="G947" s="2" t="n"/>
+      <c r="F947" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G947" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n"/>
@@ -25871,8 +26070,16 @@
         </is>
       </c>
       <c r="E948" s="2" t="n"/>
-      <c r="F948" s="4" t="n"/>
-      <c r="G948" s="2" t="n"/>
+      <c r="F948" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G948" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n"/>
@@ -25892,8 +26099,16 @@
         </is>
       </c>
       <c r="E949" s="2" t="n"/>
-      <c r="F949" s="4" t="n"/>
-      <c r="G949" s="2" t="n"/>
+      <c r="F949" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G949" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n"/>
@@ -25913,8 +26128,16 @@
         </is>
       </c>
       <c r="E950" s="2" t="n"/>
-      <c r="F950" s="4" t="n"/>
-      <c r="G950" s="2" t="n"/>
+      <c r="F950" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G950" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" s="2" t="n"/>
@@ -25934,8 +26157,16 @@
         </is>
       </c>
       <c r="E951" s="2" t="n"/>
-      <c r="F951" s="4" t="n"/>
-      <c r="G951" s="2" t="n"/>
+      <c r="F951" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G951" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1273,9 +1273,19 @@
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="F30" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>78%(29执行,写操作9条未执行不计入)</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>84% (26/31)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -23248,7 +23258,7 @@
         </is>
       </c>
     </row>
-    <row r="825">
+    <row r="825" ht="16" customHeight="1">
       <c r="A825" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23270,10 +23280,18 @@
         </is>
       </c>
       <c r="E825" s="2" t="n"/>
-      <c r="F825" s="4" t="n"/>
-      <c r="G825" s="2" t="n"/>
-    </row>
-    <row r="826">
+      <c r="F825" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】创建广告组</t>
+        </is>
+      </c>
+      <c r="G825" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="826" ht="16" customHeight="1">
       <c r="A826" s="2" t="n"/>
       <c r="B826" s="2" t="inlineStr">
         <is>
@@ -23291,8 +23309,16 @@
         </is>
       </c>
       <c r="E826" s="2" t="n"/>
-      <c r="F826" s="4" t="n"/>
-      <c r="G826" s="2" t="n"/>
+      <c r="F826" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】更新广告组设置</t>
+        </is>
+      </c>
+      <c r="G826" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n"/>
@@ -23312,8 +23338,16 @@
         </is>
       </c>
       <c r="E827" s="2" t="n"/>
-      <c r="F827" s="4" t="n"/>
-      <c r="G827" s="2" t="n"/>
+      <c r="F827" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G827" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n"/>
@@ -23333,10 +23367,18 @@
         </is>
       </c>
       <c r="E828" s="2" t="n"/>
-      <c r="F828" s="4" t="n"/>
-      <c r="G828" s="2" t="n"/>
-    </row>
-    <row r="829">
+      <c r="F828" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G828" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="829" ht="32" customHeight="1">
       <c r="A829" s="2" t="n"/>
       <c r="B829" s="2" t="inlineStr">
         <is>
@@ -23354,10 +23396,15 @@
         </is>
       </c>
       <c r="E829" s="2" t="n"/>
-      <c r="F829" s="4" t="n"/>
+      <c r="F829" s="7" t="inlineStr">
+        <is>
+          <t>attribute=historical — 68.9%
+attribute=predictive — 31.1%</t>
+        </is>
+      </c>
       <c r="G829" s="2" t="n"/>
     </row>
-    <row r="830">
+    <row r="830" ht="112" customHeight="1">
       <c r="A830" s="2" t="n"/>
       <c r="B830" s="2" t="inlineStr">
         <is>
@@ -23375,10 +23422,20 @@
         </is>
       </c>
       <c r="E830" s="2" t="n"/>
-      <c r="F830" s="4" t="n"/>
+      <c r="F830" s="7" t="inlineStr">
+        <is>
+          <t>attribute=historical — 36.0%
+attribute=lifestyle — 31.8%
+attribute=lapsed buyers — 13.5%
+attribute=predictive — 7.1%
+attribute=shopping habits — 5.0%
+attribute=lifestage — 4.5%
+attribute=auto — 1.4%</t>
+        </is>
+      </c>
       <c r="G830" s="2" t="n"/>
     </row>
-    <row r="831">
+    <row r="831" ht="64" customHeight="1">
       <c r="A831" s="2" t="n"/>
       <c r="B831" s="2" t="inlineStr">
         <is>
@@ -23396,10 +23453,17 @@
         </is>
       </c>
       <c r="E831" s="2" t="n"/>
-      <c r="F831" s="4" t="n"/>
+      <c r="F831" s="7" t="inlineStr">
+        <is>
+          <t>guidanceType=1 — 62.6%
+guidanceType=2 — 34.0%
+guidanceType=3 — 2.4%
+guidanceType=0 — 1.0%</t>
+        </is>
+      </c>
       <c r="G831" s="2" t="n"/>
     </row>
-    <row r="832">
+    <row r="832" ht="16" customHeight="1">
       <c r="A832" s="2" t="n"/>
       <c r="B832" s="2" t="inlineStr">
         <is>
@@ -23417,10 +23481,18 @@
         </is>
       </c>
       <c r="E832" s="2" t="n"/>
-      <c r="F832" s="4" t="n"/>
-      <c r="G832" s="2" t="n"/>
-    </row>
-    <row r="833">
+      <c r="F832" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量设置BaseBid</t>
+        </is>
+      </c>
+      <c r="G832" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="833" ht="16" customHeight="1">
       <c r="A833" s="2" t="n"/>
       <c r="B833" s="2" t="inlineStr">
         <is>
@@ -23438,10 +23510,18 @@
         </is>
       </c>
       <c r="E833" s="2" t="n"/>
-      <c r="F833" s="4" t="n"/>
-      <c r="G833" s="2" t="n"/>
-    </row>
-    <row r="834">
+      <c r="F833" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量设置MaxBid</t>
+        </is>
+      </c>
+      <c r="G833" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="834" ht="16" customHeight="1">
       <c r="A834" s="2" t="n"/>
       <c r="B834" s="2" t="inlineStr">
         <is>
@@ -23459,10 +23539,14 @@
         </is>
       </c>
       <c r="E834" s="2" t="n"/>
-      <c r="F834" s="4" t="n"/>
+      <c r="F834" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G834" s="2" t="n"/>
     </row>
-    <row r="835">
+    <row r="835" ht="16" customHeight="1">
       <c r="A835" s="2" t="n"/>
       <c r="B835" s="2" t="inlineStr">
         <is>
@@ -23480,10 +23564,18 @@
         </is>
       </c>
       <c r="E835" s="2" t="n"/>
-      <c r="F835" s="4" t="n"/>
-      <c r="G835" s="2" t="n"/>
-    </row>
-    <row r="836">
+      <c r="F835" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】关联创意到广告组</t>
+        </is>
+      </c>
+      <c r="G835" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="836" ht="16" customHeight="1">
       <c r="A836" s="2" t="n"/>
       <c r="B836" s="2" t="inlineStr">
         <is>
@@ -23501,10 +23593,18 @@
         </is>
       </c>
       <c r="E836" s="2" t="n"/>
-      <c r="F836" s="4" t="n"/>
-      <c r="G836" s="2" t="n"/>
-    </row>
-    <row r="837">
+      <c r="F836" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】更新创意跟踪URL</t>
+        </is>
+      </c>
+      <c r="G836" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="837" ht="16" customHeight="1">
       <c r="A837" s="2" t="n"/>
       <c r="B837" s="2" t="inlineStr">
         <is>
@@ -23522,10 +23622,18 @@
         </is>
       </c>
       <c r="E837" s="2" t="n"/>
-      <c r="F837" s="4" t="n"/>
-      <c r="G837" s="2" t="n"/>
-    </row>
-    <row r="838">
+      <c r="F837" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】删除创意关联(不可逆)</t>
+        </is>
+      </c>
+      <c r="G837" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="838" ht="16" customHeight="1">
       <c r="A838" s="2" t="n"/>
       <c r="B838" s="2" t="inlineStr">
         <is>
@@ -23543,10 +23651,18 @@
         </is>
       </c>
       <c r="E838" s="2" t="n"/>
-      <c r="F838" s="4" t="n"/>
-      <c r="G838" s="2" t="n"/>
-    </row>
-    <row r="839">
+      <c r="F838" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G838" s="4" t="inlineStr">
+        <is>
+          <t>样本中behavioralArr/geoTargets等定向目标ID属于其他客户账号，测试账号调用返回业务码405(RESOURCE_NOT_FOUND)，非功能缺陷，断言已留空仅验证接口可达性</t>
+        </is>
+      </c>
+    </row>
+    <row r="839" ht="32" customHeight="1">
       <c r="A839" s="2" t="n"/>
       <c r="B839" s="2" t="inlineStr">
         <is>
@@ -23564,10 +23680,15 @@
         </is>
       </c>
       <c r="E839" s="2" t="n"/>
-      <c r="F839" s="4" t="n"/>
+      <c r="F839" s="7" t="inlineStr">
+        <is>
+          <t>action=1(暂停) — 40.0%
+action=0(启用) — 60.0%</t>
+        </is>
+      </c>
       <c r="G839" s="2" t="n"/>
     </row>
-    <row r="840">
+    <row r="840" ht="16" customHeight="1">
       <c r="A840" s="2" t="n"/>
       <c r="B840" s="2" t="inlineStr">
         <is>
@@ -23585,10 +23706,14 @@
         </is>
       </c>
       <c r="E840" s="2" t="n"/>
-      <c r="F840" s="4" t="n"/>
+      <c r="F840" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G840" s="2" t="n"/>
     </row>
-    <row r="841">
+    <row r="841" ht="16" customHeight="1">
       <c r="A841" s="2" t="n"/>
       <c r="B841" s="2" t="inlineStr">
         <is>
@@ -23606,8 +23731,16 @@
         </is>
       </c>
       <c r="E841" s="2" t="n"/>
-      <c r="F841" s="4" t="n"/>
-      <c r="G841" s="2" t="n"/>
+      <c r="F841" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】新建预测方案(无对应删除接口)</t>
+        </is>
+      </c>
+      <c r="G841" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n"/>
@@ -23627,10 +23760,18 @@
         </is>
       </c>
       <c r="E842" s="2" t="n"/>
-      <c r="F842" s="4" t="n"/>
-      <c r="G842" s="2" t="n"/>
-    </row>
-    <row r="843">
+      <c r="F842" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G842" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="843" ht="32" customHeight="1">
       <c r="A843" s="2" t="n"/>
       <c r="B843" s="2" t="inlineStr">
         <is>
@@ -23648,7 +23789,12 @@
         </is>
       </c>
       <c r="E843" s="2" t="n"/>
-      <c r="F843" s="4" t="n"/>
+      <c r="F843" s="7" t="inlineStr">
+        <is>
+          <t>filter[ItemsetIds]=[ids+] — 86.4%
+不传filter[ItemsetIds] — 13.6%</t>
+        </is>
+      </c>
       <c r="G843" s="2" t="n"/>
     </row>
     <row r="844">
@@ -23669,10 +23815,18 @@
         </is>
       </c>
       <c r="E844" s="2" t="n"/>
-      <c r="F844" s="4" t="n"/>
-      <c r="G844" s="2" t="n"/>
-    </row>
-    <row r="845">
+      <c r="F844" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G844" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="845" ht="16" customHeight="1">
       <c r="A845" s="2" t="n"/>
       <c r="B845" s="2" t="inlineStr">
         <is>
@@ -23690,10 +23844,14 @@
         </is>
       </c>
       <c r="E845" s="2" t="n"/>
-      <c r="F845" s="4" t="n"/>
+      <c r="F845" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G845" s="2" t="n"/>
     </row>
-    <row r="846">
+    <row r="846" ht="16" customHeight="1">
       <c r="A846" s="2" t="n"/>
       <c r="B846" s="2" t="inlineStr">
         <is>
@@ -23711,10 +23869,14 @@
         </is>
       </c>
       <c r="E846" s="2" t="n"/>
-      <c r="F846" s="4" t="n"/>
+      <c r="F846" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G846" s="2" t="n"/>
     </row>
-    <row r="847">
+    <row r="847" ht="32" customHeight="1">
       <c r="A847" s="2" t="n"/>
       <c r="B847" s="2" t="inlineStr">
         <is>
@@ -23732,10 +23894,15 @@
         </is>
       </c>
       <c r="E847" s="2" t="n"/>
-      <c r="F847" s="4" t="n"/>
+      <c r="F847" s="7" t="inlineStr">
+        <is>
+          <t>含adGroupId+不含campaignId — 73.0%
+不含adGroupId+含campaignId — 27.0%</t>
+        </is>
+      </c>
       <c r="G847" s="2" t="n"/>
     </row>
-    <row r="848">
+    <row r="848" ht="32" customHeight="1">
       <c r="A848" s="2" t="n"/>
       <c r="B848" s="2" t="inlineStr">
         <is>
@@ -23753,10 +23920,15 @@
         </is>
       </c>
       <c r="E848" s="2" t="n"/>
-      <c r="F848" s="4" t="n"/>
+      <c r="F848" s="7" t="inlineStr">
+        <is>
+          <t>首页 — 97.2%
+翻页(pageIndex&gt;1) — 2.8%</t>
+        </is>
+      </c>
       <c r="G848" s="2" t="n"/>
     </row>
-    <row r="849">
+    <row r="849" ht="16" customHeight="1">
       <c r="A849" s="2" t="n"/>
       <c r="B849" s="2" t="inlineStr">
         <is>
@@ -23774,10 +23946,18 @@
         </is>
       </c>
       <c r="E849" s="2" t="n"/>
-      <c r="F849" s="4" t="n"/>
-      <c r="G849" s="2" t="n"/>
-    </row>
-    <row r="850">
+      <c r="F849" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G849" s="4" t="inlineStr">
+        <is>
+          <t>样本中behavioralArr/geoTargets等定向目标ID属于其他客户账号，测试账号调用返回业务码405(RESOURCE_NOT_FOUND)，非功能缺陷，断言已留空仅验证接口可达性</t>
+        </is>
+      </c>
+    </row>
+    <row r="850" ht="32" customHeight="1">
       <c r="A850" s="2" t="n"/>
       <c r="B850" s="2" t="inlineStr">
         <is>
@@ -23795,10 +23975,15 @@
         </is>
       </c>
       <c r="E850" s="2" t="n"/>
-      <c r="F850" s="4" t="n"/>
+      <c r="F850" s="7" t="inlineStr">
+        <is>
+          <t>含adGroupId+不含campaignId — 67.7%
+不含adGroupId+含campaignId — 32.3%</t>
+        </is>
+      </c>
       <c r="G850" s="2" t="n"/>
     </row>
-    <row r="851">
+    <row r="851" ht="32" customHeight="1">
       <c r="A851" s="2" t="n"/>
       <c r="B851" s="2" t="inlineStr">
         <is>
@@ -23816,10 +24001,19 @@
         </is>
       </c>
       <c r="E851" s="2" t="n"/>
-      <c r="F851" s="4" t="n"/>
-      <c r="G851" s="2" t="n"/>
-    </row>
-    <row r="852">
+      <c r="F851" s="7" t="inlineStr">
+        <is>
+          <t>EstimateDateRangeType=0+首页 — 93.6%
+EstimateDateRangeType=0+翻页(pageIndex&gt;1) — 4.1%</t>
+        </is>
+      </c>
+      <c r="G851" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：NullReferenceException(Object reference not set to an instance of an object)，TargetingGuidance/MyTargeting/Suggested三个接口用真实历史adGroupId调用均稳定复现HTTP 500，建议合并报一个Jira排查</t>
+        </is>
+      </c>
+    </row>
+    <row r="852" ht="16" customHeight="1">
       <c r="A852" s="2" t="n"/>
       <c r="B852" s="2" t="inlineStr">
         <is>
@@ -23837,10 +24031,18 @@
         </is>
       </c>
       <c r="E852" s="2" t="n"/>
-      <c r="F852" s="4" t="n"/>
-      <c r="G852" s="2" t="n"/>
-    </row>
-    <row r="853">
+      <c r="F852" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】应用建议定向(覆盖当前定向配置)</t>
+        </is>
+      </c>
+      <c r="G852" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="853" ht="64" customHeight="1">
       <c r="A853" s="2" t="n"/>
       <c r="B853" s="2" t="inlineStr">
         <is>
@@ -23858,10 +24060,21 @@
         </is>
       </c>
       <c r="E853" s="2" t="n"/>
-      <c r="F853" s="4" t="n"/>
-      <c r="G853" s="2" t="n"/>
-    </row>
-    <row r="854">
+      <c r="F853" s="7" t="inlineStr">
+        <is>
+          <t>EstimateDateRangeType=0+首页 — 77.6%
+EstimateDateRangeType=1+首页 — 9.2%
+EstimateDateRangeType=0+翻页(pageIndex&gt;1) — 7.9%
+EstimateDateRangeType=2+首页 — 4.6%</t>
+        </is>
+      </c>
+      <c r="G853" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：NullReferenceException(Object reference not set to an instance of an object)，TargetingGuidance/MyTargeting/Suggested三个接口用真实历史adGroupId调用均稳定复现HTTP 500，建议合并报一个Jira排查</t>
+        </is>
+      </c>
+    </row>
+    <row r="854" ht="32" customHeight="1">
       <c r="A854" s="2" t="n"/>
       <c r="B854" s="2" t="inlineStr">
         <is>
@@ -23879,8 +24092,17 @@
         </is>
       </c>
       <c r="E854" s="2" t="n"/>
-      <c r="F854" s="4" t="n"/>
-      <c r="G854" s="2" t="n"/>
+      <c r="F854" s="7" t="inlineStr">
+        <is>
+          <t>EstimateDateRangeType=0+首页 — 98.5%
+EstimateDateRangeType=2+首页 — 1.2%</t>
+        </is>
+      </c>
+      <c r="G854" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：NullReferenceException(Object reference not set to an instance of an object)，TargetingGuidance/MyTargeting/Suggested三个接口用真实历史adGroupId调用均稳定复现HTTP 500，建议合并报一个Jira排查</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n"/>
@@ -23900,8 +24122,16 @@
         </is>
       </c>
       <c r="E855" s="2" t="n"/>
-      <c r="F855" s="4" t="n"/>
-      <c r="G855" s="2" t="n"/>
+      <c r="F855" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G855" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1327,9 +1327,19 @@
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="F32" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>87% (26/30)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -24435,7 +24445,7 @@
       <c r="F869" s="4" t="n"/>
       <c r="G869" s="2" t="n"/>
     </row>
-    <row r="870">
+    <row r="870" ht="48" customHeight="1">
       <c r="A870" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24457,10 +24467,16 @@
         </is>
       </c>
       <c r="E870" s="2" t="n"/>
-      <c r="F870" s="4" t="n"/>
+      <c r="F870" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 91.3%
+profileIds=[ids+]+无CampaignTag过滤 — 7.0%
+profileIds=[]+按CampaignTag过滤 — 1.7%</t>
+        </is>
+      </c>
       <c r="G870" s="2" t="n"/>
     </row>
-    <row r="871">
+    <row r="871" ht="48" customHeight="1">
       <c r="A871" s="2" t="n"/>
       <c r="B871" s="2" t="inlineStr">
         <is>
@@ -24478,10 +24494,16 @@
         </is>
       </c>
       <c r="E871" s="2" t="n"/>
-      <c r="F871" s="4" t="n"/>
+      <c r="F871" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 91.3%
+profileIds=[ids+]+无CampaignTag过滤 — 6.5%
+profileIds=[]+按CampaignTag过滤 — 2.2%</t>
+        </is>
+      </c>
       <c r="G871" s="2" t="n"/>
     </row>
-    <row r="872">
+    <row r="872" ht="64" customHeight="1">
       <c r="A872" s="2" t="n"/>
       <c r="B872" s="2" t="inlineStr">
         <is>
@@ -24499,10 +24521,17 @@
         </is>
       </c>
       <c r="E872" s="2" t="n"/>
-      <c r="F872" s="4" t="n"/>
+      <c r="F872" s="7" t="inlineStr">
+        <is>
+          <t>notificationType=0+profileIds=[] — 48.4%
+notificationType=1+profileIds=[] — 40.1%
+notificationType=1+profileIds=[ids+] — 7.6%
+notificationType=0+profileIds=[ids+] — 3.8%</t>
+        </is>
+      </c>
       <c r="G872" s="2" t="n"/>
     </row>
-    <row r="873">
+    <row r="873" ht="32" customHeight="1">
       <c r="A873" s="2" t="n"/>
       <c r="B873" s="2" t="inlineStr">
         <is>
@@ -24520,10 +24549,15 @@
         </is>
       </c>
       <c r="E873" s="2" t="n"/>
-      <c r="F873" s="4" t="n"/>
+      <c r="F873" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 95.7%
+profileIds=[ids+]+无CampaignTag过滤 — 3.7%</t>
+        </is>
+      </c>
       <c r="G873" s="2" t="n"/>
     </row>
-    <row r="874">
+    <row r="874" ht="32" customHeight="1">
       <c r="A874" s="2" t="n"/>
       <c r="B874" s="2" t="inlineStr">
         <is>
@@ -24541,10 +24575,15 @@
         </is>
       </c>
       <c r="E874" s="2" t="n"/>
-      <c r="F874" s="4" t="n"/>
+      <c r="F874" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 95.6%
+profileIds=[ids+]+无CampaignTag过滤 — 3.8%</t>
+        </is>
+      </c>
       <c r="G874" s="2" t="n"/>
     </row>
-    <row r="875">
+    <row r="875" ht="32" customHeight="1">
       <c r="A875" s="2" t="n"/>
       <c r="B875" s="2" t="inlineStr">
         <is>
@@ -24562,10 +24601,15 @@
         </is>
       </c>
       <c r="E875" s="2" t="n"/>
-      <c r="F875" s="4" t="n"/>
+      <c r="F875" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[] — 88.6%
+profileIds=[ids+] — 11.4%</t>
+        </is>
+      </c>
       <c r="G875" s="2" t="n"/>
     </row>
-    <row r="876">
+    <row r="876" ht="64" customHeight="1">
       <c r="A876" s="2" t="n"/>
       <c r="B876" s="2" t="inlineStr">
         <is>
@@ -24583,10 +24627,17 @@
         </is>
       </c>
       <c r="E876" s="2" t="n"/>
-      <c r="F876" s="4" t="n"/>
+      <c r="F876" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 61.8%
+profileIds=[]+按CampaignTag过滤 — 21.8%
+profileIds=[ids+]+无CampaignTag过滤 — 11.6%
+profileIds=[ids+]+按CampaignTag过滤 — 4.8%</t>
+        </is>
+      </c>
       <c r="G876" s="2" t="n"/>
     </row>
-    <row r="877">
+    <row r="877" ht="64" customHeight="1">
       <c r="A877" s="2" t="n"/>
       <c r="B877" s="2" t="inlineStr">
         <is>
@@ -24604,10 +24655,17 @@
         </is>
       </c>
       <c r="E877" s="2" t="n"/>
-      <c r="F877" s="4" t="n"/>
+      <c r="F877" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 76.6%
+profileIds=[ids+]+无CampaignTag过滤 — 11.0%
+profileIds=[]+按CampaignTag过滤 — 10.4%
+profileIds=[ids+]+按CampaignTag过滤 — 2.0%</t>
+        </is>
+      </c>
       <c r="G877" s="2" t="n"/>
     </row>
-    <row r="878">
+    <row r="878" ht="64" customHeight="1">
       <c r="A878" s="2" t="n"/>
       <c r="B878" s="2" t="inlineStr">
         <is>
@@ -24625,10 +24683,17 @@
         </is>
       </c>
       <c r="E878" s="2" t="n"/>
-      <c r="F878" s="4" t="n"/>
+      <c r="F878" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 76.4%
+profileIds=[]+按CampaignTag过滤 — 11.0%
+profileIds=[ids+]+无CampaignTag过滤 — 9.8%
+profileIds=[ids+]+按CampaignTag过滤 — 2.8%</t>
+        </is>
+      </c>
       <c r="G878" s="2" t="n"/>
     </row>
-    <row r="879">
+    <row r="879" ht="64" customHeight="1">
       <c r="A879" s="2" t="n"/>
       <c r="B879" s="2" t="inlineStr">
         <is>
@@ -24646,7 +24711,14 @@
         </is>
       </c>
       <c r="E879" s="2" t="n"/>
-      <c r="F879" s="4" t="n"/>
+      <c r="F879" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 73.6%
+profileIds=[]+按CampaignTag过滤 — 13.0%
+profileIds=[ids+]+无CampaignTag过滤 — 10.6%
+profileIds=[ids+]+按CampaignTag过滤 — 2.8%</t>
+        </is>
+      </c>
       <c r="G879" s="2" t="n"/>
     </row>
     <row r="880">
@@ -24667,10 +24739,18 @@
         </is>
       </c>
       <c r="E880" s="2" t="n"/>
-      <c r="F880" s="4" t="n"/>
-      <c r="G880" s="2" t="n"/>
-    </row>
-    <row r="881">
+      <c r="F880" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G880" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="881" ht="64" customHeight="1">
       <c r="A881" s="2" t="n"/>
       <c r="B881" s="2" t="inlineStr">
         <is>
@@ -24688,10 +24768,17 @@
         </is>
       </c>
       <c r="E881" s="2" t="n"/>
-      <c r="F881" s="4" t="n"/>
+      <c r="F881" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 76.0%
+profileIds=[ids+]+无CampaignTag过滤 — 11.8%
+profileIds=[]+按CampaignTag过滤 — 9.0%
+profileIds=[ids+]+按CampaignTag过滤 — 3.2%</t>
+        </is>
+      </c>
       <c r="G881" s="2" t="n"/>
     </row>
-    <row r="882">
+    <row r="882" ht="64" customHeight="1">
       <c r="A882" s="2" t="n"/>
       <c r="B882" s="2" t="inlineStr">
         <is>
@@ -24709,10 +24796,17 @@
         </is>
       </c>
       <c r="E882" s="2" t="n"/>
-      <c r="F882" s="4" t="n"/>
+      <c r="F882" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 58.4%
+profileIds=[]+按CampaignTag过滤 — 24.0%
+profileIds=[ids+]+无CampaignTag过滤 — 12.8%
+profileIds=[ids+]+按CampaignTag过滤 — 4.8%</t>
+        </is>
+      </c>
       <c r="G882" s="2" t="n"/>
     </row>
-    <row r="883">
+    <row r="883" ht="64" customHeight="1">
       <c r="A883" s="2" t="n"/>
       <c r="B883" s="2" t="inlineStr">
         <is>
@@ -24730,10 +24824,17 @@
         </is>
       </c>
       <c r="E883" s="2" t="n"/>
-      <c r="F883" s="4" t="n"/>
+      <c r="F883" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 64.8%
+profileIds=[]+按CampaignTag过滤 — 19.2%
+profileIds=[ids+]+无CampaignTag过滤 — 14.0%
+profileIds=[ids+]+按CampaignTag过滤 — 2.0%</t>
+        </is>
+      </c>
       <c r="G883" s="2" t="n"/>
     </row>
-    <row r="884">
+    <row r="884" ht="64" customHeight="1">
       <c r="A884" s="2" t="n"/>
       <c r="B884" s="2" t="inlineStr">
         <is>
@@ -24751,10 +24852,17 @@
         </is>
       </c>
       <c r="E884" s="2" t="n"/>
-      <c r="F884" s="4" t="n"/>
+      <c r="F884" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 62.8%
+profileIds=[]+按CampaignTag过滤 — 20.8%
+profileIds=[ids+]+无CampaignTag过滤 — 12.4%
+profileIds=[ids+]+按CampaignTag过滤 — 4.0%</t>
+        </is>
+      </c>
       <c r="G884" s="2" t="n"/>
     </row>
-    <row r="885">
+    <row r="885" ht="32" customHeight="1">
       <c r="A885" s="2" t="n"/>
       <c r="B885" s="2" t="inlineStr">
         <is>
@@ -24772,10 +24880,15 @@
         </is>
       </c>
       <c r="E885" s="2" t="n"/>
-      <c r="F885" s="4" t="n"/>
+      <c r="F885" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[] — 87.4%
+profileIds=[ids+] — 12.6%</t>
+        </is>
+      </c>
       <c r="G885" s="2" t="n"/>
     </row>
-    <row r="886">
+    <row r="886" ht="64" customHeight="1">
       <c r="A886" s="2" t="n"/>
       <c r="B886" s="2" t="inlineStr">
         <is>
@@ -24793,7 +24906,14 @@
         </is>
       </c>
       <c r="E886" s="2" t="n"/>
-      <c r="F886" s="4" t="n"/>
+      <c r="F886" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 56.4%
+profileIds=[]+按CampaignTag过滤 — 21.6%
+profileIds=[ids+]+无CampaignTag过滤 — 16.4%
+profileIds=[ids+]+按CampaignTag过滤 — 5.4%</t>
+        </is>
+      </c>
       <c r="G886" s="2" t="n"/>
     </row>
     <row r="887">
@@ -24814,10 +24934,18 @@
         </is>
       </c>
       <c r="E887" s="2" t="n"/>
-      <c r="F887" s="4" t="n"/>
-      <c r="G887" s="2" t="n"/>
-    </row>
-    <row r="888">
+      <c r="F887" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G887" s="4" t="inlineStr">
+        <is>
+          <t>异步导出任务接口(taskName+多widget配置打包)，无同步响应，暂不覆盖(365d 31次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="888" ht="48" customHeight="1">
       <c r="A888" s="2" t="n"/>
       <c r="B888" s="2" t="inlineStr">
         <is>
@@ -24835,10 +24963,16 @@
         </is>
       </c>
       <c r="E888" s="2" t="n"/>
-      <c r="F888" s="4" t="n"/>
+      <c r="F888" s="7" t="inlineStr">
+        <is>
+          <t>notificationType=0+profileIds=[] — 83.8%
+notificationType=0+profileIds=[ids+] — 14.2%
+notificationType=1+profileIds=[] — 1.8%</t>
+        </is>
+      </c>
       <c r="G888" s="2" t="n"/>
     </row>
-    <row r="889">
+    <row r="889" ht="64" customHeight="1">
       <c r="A889" s="2" t="n"/>
       <c r="B889" s="2" t="inlineStr">
         <is>
@@ -24856,10 +24990,17 @@
         </is>
       </c>
       <c r="E889" s="2" t="n"/>
-      <c r="F889" s="4" t="n"/>
+      <c r="F889" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+profileIds=[] — 61.4%
+按CampaignTag过滤+profileIds=[] — 20.6%
+无CampaignTag过滤+profileIds=[ids+] — 14.0%
+按CampaignTag过滤+profileIds=[ids+] — 4.0%</t>
+        </is>
+      </c>
       <c r="G889" s="2" t="n"/>
     </row>
-    <row r="890">
+    <row r="890" ht="64" customHeight="1">
       <c r="A890" s="2" t="n"/>
       <c r="B890" s="2" t="inlineStr">
         <is>
@@ -24877,10 +25018,17 @@
         </is>
       </c>
       <c r="E890" s="2" t="n"/>
-      <c r="F890" s="4" t="n"/>
+      <c r="F890" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 61.4%
+profileIds=[]+按CampaignTag过滤 — 19.4%
+profileIds=[ids+]+无CampaignTag过滤 — 14.0%
+profileIds=[ids+]+按CampaignTag过滤 — 5.2%</t>
+        </is>
+      </c>
       <c r="G890" s="2" t="n"/>
     </row>
-    <row r="891">
+    <row r="891" ht="64" customHeight="1">
       <c r="A891" s="2" t="n"/>
       <c r="B891" s="2" t="inlineStr">
         <is>
@@ -24898,10 +25046,17 @@
         </is>
       </c>
       <c r="E891" s="2" t="n"/>
-      <c r="F891" s="4" t="n"/>
+      <c r="F891" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 59.0%
+profileIds=[]+按CampaignTag过滤 — 23.0%
+profileIds=[ids+]+无CampaignTag过滤 — 14.0%
+profileIds=[ids+]+按CampaignTag过滤 — 4.0%</t>
+        </is>
+      </c>
       <c r="G891" s="2" t="n"/>
     </row>
-    <row r="892">
+    <row r="892" ht="64" customHeight="1">
       <c r="A892" s="2" t="n"/>
       <c r="B892" s="2" t="inlineStr">
         <is>
@@ -24919,10 +25074,17 @@
         </is>
       </c>
       <c r="E892" s="2" t="n"/>
-      <c r="F892" s="4" t="n"/>
+      <c r="F892" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 62.6%
+profileIds=[]+按CampaignTag过滤 — 21.4%
+profileIds=[ids+]+无CampaignTag过滤 — 10.6%
+profileIds=[ids+]+按CampaignTag过滤 — 5.4%</t>
+        </is>
+      </c>
       <c r="G892" s="2" t="n"/>
     </row>
-    <row r="893">
+    <row r="893" ht="64" customHeight="1">
       <c r="A893" s="2" t="n"/>
       <c r="B893" s="2" t="inlineStr">
         <is>
@@ -24940,10 +25102,17 @@
         </is>
       </c>
       <c r="E893" s="2" t="n"/>
-      <c r="F893" s="4" t="n"/>
+      <c r="F893" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+profileIds=[] — 58.6%
+按CampaignTag过滤+profileIds=[] — 23.2%
+无CampaignTag过滤+profileIds=[ids+] — 13.6%
+按CampaignTag过滤+profileIds=[ids+] — 4.6%</t>
+        </is>
+      </c>
       <c r="G893" s="2" t="n"/>
     </row>
-    <row r="894">
+    <row r="894" ht="64" customHeight="1">
       <c r="A894" s="2" t="n"/>
       <c r="B894" s="2" t="inlineStr">
         <is>
@@ -24961,10 +25130,17 @@
         </is>
       </c>
       <c r="E894" s="2" t="n"/>
-      <c r="F894" s="4" t="n"/>
+      <c r="F894" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+profileIds=[] — 64.8%
+按CampaignTag过滤+profileIds=[] — 20.0%
+无CampaignTag过滤+profileIds=[ids+] — 11.8%
+按CampaignTag过滤+profileIds=[ids+] — 3.4%</t>
+        </is>
+      </c>
       <c r="G894" s="2" t="n"/>
     </row>
-    <row r="895">
+    <row r="895" ht="64" customHeight="1">
       <c r="A895" s="2" t="n"/>
       <c r="B895" s="2" t="inlineStr">
         <is>
@@ -24982,7 +25158,14 @@
         </is>
       </c>
       <c r="E895" s="2" t="n"/>
-      <c r="F895" s="4" t="n"/>
+      <c r="F895" s="7" t="inlineStr">
+        <is>
+          <t>无CampaignTag过滤+profileIds=[] — 64.6%
+按CampaignTag过滤+profileIds=[] — 18.2%
+无CampaignTag过滤+profileIds=[ids+] — 13.2%
+按CampaignTag过滤+profileIds=[ids+] — 4.0%</t>
+        </is>
+      </c>
       <c r="G895" s="2" t="n"/>
     </row>
     <row r="896">
@@ -25003,8 +25186,16 @@
         </is>
       </c>
       <c r="E896" s="2" t="n"/>
-      <c r="F896" s="4" t="n"/>
-      <c r="G896" s="2" t="n"/>
+      <c r="F896" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G896" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n"/>
@@ -25024,10 +25215,18 @@
         </is>
       </c>
       <c r="E897" s="2" t="n"/>
-      <c r="F897" s="4" t="n"/>
-      <c r="G897" s="2" t="n"/>
-    </row>
-    <row r="898">
+      <c r="F897" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G897" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="898" ht="64" customHeight="1">
       <c r="A898" s="2" t="n"/>
       <c r="B898" s="2" t="inlineStr">
         <is>
@@ -25045,10 +25244,17 @@
         </is>
       </c>
       <c r="E898" s="2" t="n"/>
-      <c r="F898" s="4" t="n"/>
+      <c r="F898" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 60.4%
+profileIds=[]+按CampaignTag过滤 — 21.8%
+profileIds=[ids+]+无CampaignTag过滤 — 13.6%
+profileIds=[ids+]+按CampaignTag过滤 — 4.2%</t>
+        </is>
+      </c>
       <c r="G898" s="2" t="n"/>
     </row>
-    <row r="899">
+    <row r="899" ht="64" customHeight="1">
       <c r="A899" s="2" t="n"/>
       <c r="B899" s="2" t="inlineStr">
         <is>
@@ -25066,8 +25272,19 @@
         </is>
       </c>
       <c r="E899" s="2" t="n"/>
-      <c r="F899" s="4" t="n"/>
-      <c r="G899" s="2" t="n"/>
+      <c r="F899" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无CampaignTag过滤 — 43.6%
+profileIds=[]+按CampaignTag过滤 — 37.0%
+profileIds=[ids+]+无CampaignTag过滤 — 9.7%
+profileIds=[ids+]+按CampaignTag过滤 — 9.1%</t>
+        </is>
+      </c>
+      <c r="G899" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：ClickHouse DB::Exception "Code: 36. Element of set in IN, VALUES, or LIMIT, or aggregate..."，4种profileIds/campaignTagIds过滤组合下稳定复现HTTP 500，建议报Jira排查SQL生成逻辑</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -675,9 +675,19 @@
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="F6" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>54% (14/26)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4486,7 +4496,7 @@
       <c r="F89" s="4" t="n"/>
       <c r="G89" s="2" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" ht="16" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4508,7 +4518,11 @@
         </is>
       </c>
       <c r="E90" s="2" t="n"/>
-      <c r="F90" s="4" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="n"/>
     </row>
     <row r="91">
@@ -4529,8 +4543,16 @@
         </is>
       </c>
       <c r="E91" s="2" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="2" t="n"/>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 7124次)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -4550,10 +4572,18 @@
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="2" t="n"/>
-    </row>
-    <row r="93">
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 17743次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
       <c r="A93" s="2" t="n"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
@@ -4571,10 +4601,16 @@
         </is>
       </c>
       <c r="E93" s="2" t="n"/>
-      <c r="F93" s="4" t="n"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>kindType=Default+  dim  =ytd — 86.2%
+kindType=Item+不传  dim   — 8.0%
+kindType=Item+  dim  =ytd — 4.4%</t>
+        </is>
+      </c>
       <c r="G93" s="2" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" ht="96" customHeight="1">
       <c r="A94" s="2" t="n"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
@@ -4592,7 +4628,16 @@
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
-      <c r="F94" s="4" t="n"/>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=Item+  dim  =month — 35.4%
+tabGroupBy=Item+  dim  =week — 21.3%
+tabGroupBy=Item+  dim  =date — 13.5%
+tabGroupBy=AdGroup+  dim  =month — 12.4%
+tabGroupBy=AdGroup+  dim  =week — 7.9%
+tabGroupBy=AdGroup+  dim  =date — 6.2%</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
@@ -4613,10 +4658,18 @@
         </is>
       </c>
       <c r="E95" s="2" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="2" t="n"/>
-    </row>
-    <row r="96">
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="64" customHeight="1">
       <c r="A96" s="2" t="n"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
@@ -4634,7 +4687,14 @@
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
-      <c r="F96" s="4" t="n"/>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>kindType=Default+  dim  =ytd — 85.0%
+kindType=Item+不传  dim   — 8.2%
+kindType=Item+  dim  =ytd — 3.2%
+kindType=Default+  dim  =date — 2.2%</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
@@ -4655,8 +4715,16 @@
         </is>
       </c>
       <c r="E97" s="2" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="2" t="n"/>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -4676,8 +4744,16 @@
         </is>
       </c>
       <c r="E98" s="2" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="2" t="n"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -4697,10 +4773,18 @@
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="2" t="n"/>
-    </row>
-    <row r="100">
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
       <c r="A100" s="2" t="n"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
@@ -4718,10 +4802,15 @@
         </is>
       </c>
       <c r="E100" s="2" t="n"/>
-      <c r="F100" s="4" t="n"/>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>按Campaign过滤 — 98.2%
+无Campaign过滤 — 1.8%</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" ht="32" customHeight="1">
       <c r="A101" s="2" t="n"/>
       <c r="B101" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4828,15 @@
         </is>
       </c>
       <c r="E101" s="2" t="n"/>
-      <c r="F101" s="4" t="n"/>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>按Campaign过滤 — 98.0%
+无Campaign过滤 — 2.0%</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="64" customHeight="1">
       <c r="A102" s="2" t="n"/>
       <c r="B102" s="2" t="inlineStr">
         <is>
@@ -4760,10 +4854,17 @@
         </is>
       </c>
       <c r="E102" s="2" t="n"/>
-      <c r="F102" s="4" t="n"/>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>kindType=Default+  dim  =ytd — 91.4%
+kindType=Item+  dim  =ytd — 3.6%
+kindType=Default+  dim  =date — 1.8%
+不传kindType+不传  dim   — 1.2%</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="32" customHeight="1">
       <c r="A103" s="2" t="n"/>
       <c r="B103" s="2" t="inlineStr">
         <is>
@@ -4781,7 +4882,12 @@
         </is>
       </c>
       <c r="E103" s="2" t="n"/>
-      <c r="F103" s="4" t="n"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>按天(dim=1) — 92.7%
+按周(dim=2) — 7.3%</t>
+        </is>
+      </c>
       <c r="G103" s="2" t="n"/>
     </row>
     <row r="104">
@@ -4802,8 +4908,16 @@
         </is>
       </c>
       <c r="E104" s="2" t="n"/>
-      <c r="F104" s="4" t="n"/>
-      <c r="G104" s="2" t="n"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -4823,8 +4937,16 @@
         </is>
       </c>
       <c r="E105" s="2" t="n"/>
-      <c r="F105" s="4" t="n"/>
-      <c r="G105" s="2" t="n"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -4844,8 +4966,16 @@
         </is>
       </c>
       <c r="E106" s="2" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="2" t="n"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -4865,10 +4995,18 @@
         </is>
       </c>
       <c r="E107" s="2" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="2" t="n"/>
-    </row>
-    <row r="108">
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
       <c r="A108" s="2" t="n"/>
       <c r="B108" s="2" t="inlineStr">
         <is>
@@ -4886,10 +5024,14 @@
         </is>
       </c>
       <c r="E108" s="2" t="n"/>
-      <c r="F108" s="4" t="n"/>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="16" customHeight="1">
       <c r="A109" s="2" t="n"/>
       <c r="B109" s="2" t="inlineStr">
         <is>
@@ -4907,10 +5049,14 @@
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
-      <c r="F109" s="4" t="n"/>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="16" customHeight="1">
       <c r="A110" s="2" t="n"/>
       <c r="B110" s="2" t="inlineStr">
         <is>
@@ -4928,10 +5074,14 @@
         </is>
       </c>
       <c r="E110" s="2" t="n"/>
-      <c r="F110" s="4" t="n"/>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" ht="32" customHeight="1">
       <c r="A111" s="2" t="n"/>
       <c r="B111" s="2" t="inlineStr">
         <is>
@@ -4949,10 +5099,15 @@
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
-      <c r="F111" s="4" t="n"/>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>无ItemTag过滤 — 96.8%
+按ItemTag过滤 — 3.0%</t>
+        </is>
+      </c>
       <c r="G111" s="2" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" ht="48" customHeight="1">
       <c r="A112" s="2" t="n"/>
       <c r="B112" s="2" t="inlineStr">
         <is>
@@ -4970,7 +5125,13 @@
         </is>
       </c>
       <c r="E112" s="2" t="n"/>
-      <c r="F112" s="4" t="n"/>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>无ItemTag过滤 — 96.2%
+按ItemTag过滤 — 2.8%
+按ItemTag过滤(列表含-1) — 1.0%</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="n"/>
     </row>
     <row r="113">
@@ -4991,8 +5152,16 @@
         </is>
       </c>
       <c r="E113" s="2" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="2" t="n"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 6次)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -5012,10 +5181,18 @@
         </is>
       </c>
       <c r="E114" s="2" t="n"/>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="2" t="n"/>
-    </row>
-    <row r="115">
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 6次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="64" customHeight="1">
       <c r="A115" s="2" t="n"/>
       <c r="B115" s="2" t="inlineStr">
         <is>
@@ -5033,7 +5210,14 @@
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
-      <c r="F115" s="4" t="n"/>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[ids+]+无Tag过滤 — 65.8%
+profileIds=[]+无Tag过滤 — 19.8%
+profileIds=[ids+]+按Tag过滤 — 8.8%
+profileIds=[]+按Tag过滤 — 5.0%</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="n"/>
     </row>
     <row r="116">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1065,9 +1065,19 @@
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="F21" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>96%(47执行,写操作2条未执行不计入)</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>83% (20/24)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -14226,7 +14236,7 @@
       <c r="F474" s="4" t="n"/>
       <c r="G474" s="2" t="n"/>
     </row>
-    <row r="475">
+    <row r="475" ht="48" customHeight="1">
       <c r="A475" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14248,10 +14258,16 @@
         </is>
       </c>
       <c r="E475" s="2" t="n"/>
-      <c r="F475" s="4" t="n"/>
+      <c r="F475" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 77.6%
+ReportType=1 — 21.4%
+ReportType=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G475" s="2" t="n"/>
     </row>
-    <row r="476">
+    <row r="476" ht="48" customHeight="1">
       <c r="A476" s="2" t="n"/>
       <c r="B476" s="2" t="inlineStr">
         <is>
@@ -14269,10 +14285,16 @@
         </is>
       </c>
       <c r="E476" s="2" t="n"/>
-      <c r="F476" s="4" t="n"/>
+      <c r="F476" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 80.4%
+ReportType=1 — 17.0%
+ReportType=2 — 2.6%</t>
+        </is>
+      </c>
       <c r="G476" s="2" t="n"/>
     </row>
-    <row r="477">
+    <row r="477" ht="48" customHeight="1">
       <c r="A477" s="2" t="n"/>
       <c r="B477" s="2" t="inlineStr">
         <is>
@@ -14290,10 +14312,16 @@
         </is>
       </c>
       <c r="E477" s="2" t="n"/>
-      <c r="F477" s="4" t="n"/>
+      <c r="F477" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 80.4%
+ReportType=1 — 17.0%
+ReportType=2 — 2.6%</t>
+        </is>
+      </c>
       <c r="G477" s="2" t="n"/>
     </row>
-    <row r="478">
+    <row r="478" ht="48" customHeight="1">
       <c r="A478" s="2" t="n"/>
       <c r="B478" s="2" t="inlineStr">
         <is>
@@ -14311,7 +14339,13 @@
         </is>
       </c>
       <c r="E478" s="2" t="n"/>
-      <c r="F478" s="4" t="n"/>
+      <c r="F478" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 76.4%
+ReportType=1 — 21.2%
+ReportType=2 — 2.4%</t>
+        </is>
+      </c>
       <c r="G478" s="2" t="n"/>
     </row>
     <row r="479">
@@ -14332,10 +14366,18 @@
         </is>
       </c>
       <c r="E479" s="2" t="n"/>
-      <c r="F479" s="4" t="n"/>
-      <c r="G479" s="2" t="n"/>
-    </row>
-    <row r="480">
+      <c r="F479" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G479" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调接口，无同步响应，暂不覆盖(365d 8次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="48" customHeight="1">
       <c r="A480" s="2" t="n"/>
       <c r="B480" s="2" t="inlineStr">
         <is>
@@ -14353,10 +14395,16 @@
         </is>
       </c>
       <c r="E480" s="2" t="n"/>
-      <c r="F480" s="4" t="n"/>
+      <c r="F480" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 80.4%
+ReportType=1 — 17.0%
+ReportType=2 — 2.6%</t>
+        </is>
+      </c>
       <c r="G480" s="2" t="n"/>
     </row>
-    <row r="481">
+    <row r="481" ht="48" customHeight="1">
       <c r="A481" s="2" t="n"/>
       <c r="B481" s="2" t="inlineStr">
         <is>
@@ -14374,10 +14422,16 @@
         </is>
       </c>
       <c r="E481" s="2" t="n"/>
-      <c r="F481" s="4" t="n"/>
+      <c r="F481" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0+含Brands — 81.2%
+ReportType=1+含Brands — 17.5%
+ReportType=2+含Brands — 1.3%</t>
+        </is>
+      </c>
       <c r="G481" s="2" t="n"/>
     </row>
-    <row r="482">
+    <row r="482" ht="16" customHeight="1">
       <c r="A482" s="2" t="n"/>
       <c r="B482" s="2" t="inlineStr">
         <is>
@@ -14395,10 +14449,18 @@
         </is>
       </c>
       <c r="E482" s="2" t="n"/>
-      <c r="F482" s="4" t="n"/>
-      <c r="G482" s="2" t="n"/>
-    </row>
-    <row r="483">
+      <c r="F482" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】关注搜索词</t>
+        </is>
+      </c>
+      <c r="G482" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="16" customHeight="1">
       <c r="A483" s="2" t="n"/>
       <c r="B483" s="2" t="inlineStr">
         <is>
@@ -14416,10 +14478,18 @@
         </is>
       </c>
       <c r="E483" s="2" t="n"/>
-      <c r="F483" s="4" t="n"/>
-      <c r="G483" s="2" t="n"/>
-    </row>
-    <row r="484">
+      <c r="F483" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】取消关注搜索词</t>
+        </is>
+      </c>
+      <c r="G483" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="48" customHeight="1">
       <c r="A484" s="2" t="n"/>
       <c r="B484" s="2" t="inlineStr">
         <is>
@@ -14437,10 +14507,16 @@
         </is>
       </c>
       <c r="E484" s="2" t="n"/>
-      <c r="F484" s="4" t="n"/>
+      <c r="F484" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 80.4%
+ReportType=1 — 15.8%
+ReportType=2 — 3.8%</t>
+        </is>
+      </c>
       <c r="G484" s="2" t="n"/>
     </row>
-    <row r="485">
+    <row r="485" ht="32" customHeight="1">
       <c r="A485" s="2" t="n"/>
       <c r="B485" s="2" t="inlineStr">
         <is>
@@ -14458,10 +14534,15 @@
         </is>
       </c>
       <c r="E485" s="2" t="n"/>
-      <c r="F485" s="4" t="n"/>
+      <c r="F485" s="7" t="inlineStr">
+        <is>
+          <t>ProfileIds=[] — 63.8%
+ProfileIds=[ids+] — 36.2%</t>
+        </is>
+      </c>
       <c r="G485" s="2" t="n"/>
     </row>
-    <row r="486">
+    <row r="486" ht="16" customHeight="1">
       <c r="A486" s="2" t="n"/>
       <c r="B486" s="2" t="inlineStr">
         <is>
@@ -14479,10 +14560,14 @@
         </is>
       </c>
       <c r="E486" s="2" t="n"/>
-      <c r="F486" s="4" t="n"/>
+      <c r="F486" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G486" s="2" t="n"/>
     </row>
-    <row r="487">
+    <row r="487" ht="48" customHeight="1">
       <c r="A487" s="2" t="n"/>
       <c r="B487" s="2" t="inlineStr">
         <is>
@@ -14500,10 +14585,20 @@
         </is>
       </c>
       <c r="E487" s="2" t="n"/>
-      <c r="F487" s="4" t="n"/>
-      <c r="G487" s="2" t="n"/>
-    </row>
-    <row r="488">
+      <c r="F487" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 80.4%
+ReportType=1 — 17.0%
+ReportType=2 — 2.6%</t>
+        </is>
+      </c>
+      <c r="G487" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：ReportType=2时报错"Must be positive (Parameter NumberOfClusters)"，聚类簇数计算为非正数未做校验，建议报Jira</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="48" customHeight="1">
       <c r="A488" s="2" t="n"/>
       <c r="B488" s="2" t="inlineStr">
         <is>
@@ -14521,7 +14616,13 @@
         </is>
       </c>
       <c r="E488" s="2" t="n"/>
-      <c r="F488" s="4" t="n"/>
+      <c r="F488" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 74.8%
+ReportType=1 — 24.2%
+ReportType=2 — 1.0%</t>
+        </is>
+      </c>
       <c r="G488" s="2" t="n"/>
     </row>
     <row r="489">
@@ -14542,8 +14643,16 @@
         </is>
       </c>
       <c r="E489" s="2" t="n"/>
-      <c r="F489" s="4" t="n"/>
-      <c r="G489" s="2" t="n"/>
+      <c r="F489" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G489" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调接口，无同步响应，暂不覆盖(365d 129次)</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -14563,10 +14672,18 @@
         </is>
       </c>
       <c r="E490" s="2" t="n"/>
-      <c r="F490" s="4" t="n"/>
-      <c r="G490" s="2" t="n"/>
-    </row>
-    <row r="491">
+      <c r="F490" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G490" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="32" customHeight="1">
       <c r="A491" s="2" t="n"/>
       <c r="B491" s="2" t="inlineStr">
         <is>
@@ -14584,10 +14701,15 @@
         </is>
       </c>
       <c r="E491" s="2" t="n"/>
-      <c r="F491" s="4" t="n"/>
+      <c r="F491" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=1 — 50.0%
+ReportType=0 — 50.0%</t>
+        </is>
+      </c>
       <c r="G491" s="2" t="n"/>
     </row>
-    <row r="492">
+    <row r="492" ht="16" customHeight="1">
       <c r="A492" s="2" t="n"/>
       <c r="B492" s="2" t="inlineStr">
         <is>
@@ -14605,10 +14727,14 @@
         </is>
       </c>
       <c r="E492" s="2" t="n"/>
-      <c r="F492" s="4" t="n"/>
+      <c r="F492" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G492" s="2" t="n"/>
     </row>
-    <row r="493">
+    <row r="493" ht="48" customHeight="1">
       <c r="A493" s="2" t="n"/>
       <c r="B493" s="2" t="inlineStr">
         <is>
@@ -14626,10 +14752,16 @@
         </is>
       </c>
       <c r="E493" s="2" t="n"/>
-      <c r="F493" s="4" t="n"/>
+      <c r="F493" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 70.0%
+ReportType=1 — 27.8%
+ReportType=2 — 2.2%</t>
+        </is>
+      </c>
       <c r="G493" s="2" t="n"/>
     </row>
-    <row r="494">
+    <row r="494" ht="80" customHeight="1">
       <c r="A494" s="2" t="n"/>
       <c r="B494" s="2" t="inlineStr">
         <is>
@@ -14647,8 +14779,20 @@
         </is>
       </c>
       <c r="E494" s="2" t="n"/>
-      <c r="F494" s="4" t="n"/>
-      <c r="G494" s="2" t="n"/>
+      <c r="F494" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0+searchType=0 — 56.2%
+ReportType=1+searchType=0 — 36.8%
+ReportType=1+searchType=1 — 4.0%
+ReportType=2+searchType=0 — 1.6%
+ReportType=0+searchType=1 — 1.4%</t>
+        </is>
+      </c>
+      <c r="G494" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：ReportType=2+searchType=0时报错"Sequence contains no elements"，对空集合调用First()未做判空，建议报Jira(与priceRegion的ReportType=2报错疑似同一批次功能上线的缺陷，可合并排查)</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -14668,10 +14812,18 @@
         </is>
       </c>
       <c r="E495" s="2" t="n"/>
-      <c r="F495" s="4" t="n"/>
-      <c r="G495" s="2" t="n"/>
-    </row>
-    <row r="496">
+      <c r="F495" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G495" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调接口，无同步响应，暂不覆盖(365d 3043次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="32" customHeight="1">
       <c r="A496" s="2" t="n"/>
       <c r="B496" s="2" t="inlineStr">
         <is>
@@ -14689,10 +14841,15 @@
         </is>
       </c>
       <c r="E496" s="2" t="n"/>
-      <c r="F496" s="4" t="n"/>
+      <c r="F496" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 73.3%
+ReportType=1 — 26.7%</t>
+        </is>
+      </c>
       <c r="G496" s="2" t="n"/>
     </row>
-    <row r="497">
+    <row r="497" ht="64" customHeight="1">
       <c r="A497" s="2" t="n"/>
       <c r="B497" s="2" t="inlineStr">
         <is>
@@ -14710,10 +14867,17 @@
         </is>
       </c>
       <c r="E497" s="2" t="n"/>
-      <c r="F497" s="4" t="n"/>
+      <c r="F497" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0+TrendLength=12 — 47.2%
+ReportType=1+TrendLength=12 — 33.5%
+ReportType=0+TrendLength=4 — 14.6%
+ReportType=1+TrendLength=4 — 4.7%</t>
+        </is>
+      </c>
       <c r="G497" s="2" t="n"/>
     </row>
-    <row r="498">
+    <row r="498" ht="32" customHeight="1">
       <c r="A498" s="2" t="n"/>
       <c r="B498" s="2" t="inlineStr">
         <is>
@@ -14731,7 +14895,12 @@
         </is>
       </c>
       <c r="E498" s="2" t="n"/>
-      <c r="F498" s="4" t="n"/>
+      <c r="F498" s="7" t="inlineStr">
+        <is>
+          <t>ReportType=0 — 76.9%
+ReportType=1 — 23.1%</t>
+        </is>
+      </c>
       <c r="G498" s="2" t="n"/>
     </row>
     <row r="499">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -967,9 +967,19 @@
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="F17" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>86%(6执行,写操作7条未执行不计入)</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>65% (13/20)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -13426,7 +13436,7 @@
       </c>
       <c r="G436" s="2" t="n"/>
     </row>
-    <row r="437">
+    <row r="437" ht="16" customHeight="1">
       <c r="A437" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -13448,10 +13458,18 @@
         </is>
       </c>
       <c r="E437" s="2" t="n"/>
-      <c r="F437" s="4" t="n"/>
-      <c r="G437" s="2" t="n"/>
-    </row>
-    <row r="438">
+      <c r="F437" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】创建标签</t>
+        </is>
+      </c>
+      <c r="G437" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="16" customHeight="1">
       <c r="A438" s="2" t="n"/>
       <c r="B438" s="2" t="inlineStr">
         <is>
@@ -13469,10 +13487,14 @@
         </is>
       </c>
       <c r="E438" s="2" t="n"/>
-      <c r="F438" s="4" t="n"/>
+      <c r="F438" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 99.4%</t>
+        </is>
+      </c>
       <c r="G438" s="2" t="n"/>
     </row>
-    <row r="439">
+    <row r="439" ht="16" customHeight="1">
       <c r="A439" s="2" t="n"/>
       <c r="B439" s="2" t="inlineStr">
         <is>
@@ -13490,10 +13512,18 @@
         </is>
       </c>
       <c r="E439" s="2" t="n"/>
-      <c r="F439" s="4" t="n"/>
-      <c r="G439" s="2" t="n"/>
-    </row>
-    <row r="440">
+      <c r="F439" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】删除标签(不可逆)</t>
+        </is>
+      </c>
+      <c r="G439" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="16" customHeight="1">
       <c r="A440" s="2" t="n"/>
       <c r="B440" s="2" t="inlineStr">
         <is>
@@ -13511,10 +13541,18 @@
         </is>
       </c>
       <c r="E440" s="2" t="n"/>
-      <c r="F440" s="4" t="n"/>
-      <c r="G440" s="2" t="n"/>
-    </row>
-    <row r="441">
+      <c r="F440" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】更新标签(改名/改绑定Campaign)</t>
+        </is>
+      </c>
+      <c r="G440" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="16" customHeight="1">
       <c r="A441" s="2" t="n"/>
       <c r="B441" s="2" t="inlineStr">
         <is>
@@ -13532,8 +13570,16 @@
         </is>
       </c>
       <c r="E441" s="2" t="n"/>
-      <c r="F441" s="4" t="n"/>
-      <c r="G441" s="2" t="n"/>
+      <c r="F441" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】批量删除标签(不可逆)</t>
+        </is>
+      </c>
+      <c r="G441" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -13553,8 +13599,16 @@
         </is>
       </c>
       <c r="E442" s="2" t="n"/>
-      <c r="F442" s="4" t="n"/>
-      <c r="G442" s="2" t="n"/>
+      <c r="F442" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G442" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -13574,8 +13628,16 @@
         </is>
       </c>
       <c r="E443" s="2" t="n"/>
-      <c r="F443" s="4" t="n"/>
-      <c r="G443" s="2" t="n"/>
+      <c r="F443" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G443" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -13595,10 +13657,18 @@
         </is>
       </c>
       <c r="E444" s="2" t="n"/>
-      <c r="F444" s="4" t="n"/>
-      <c r="G444" s="2" t="n"/>
-    </row>
-    <row r="445">
+      <c r="F444" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G444" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="16" customHeight="1">
       <c r="A445" s="2" t="n"/>
       <c r="B445" s="2" t="inlineStr">
         <is>
@@ -13616,10 +13686,14 @@
         </is>
       </c>
       <c r="E445" s="2" t="n"/>
-      <c r="F445" s="4" t="n"/>
+      <c r="F445" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G445" s="2" t="n"/>
     </row>
-    <row r="446">
+    <row r="446" ht="16" customHeight="1">
       <c r="A446" s="2" t="n"/>
       <c r="B446" s="2" t="inlineStr">
         <is>
@@ -13637,10 +13711,18 @@
         </is>
       </c>
       <c r="E446" s="2" t="n"/>
-      <c r="F446" s="4" t="n"/>
-      <c r="G446" s="2" t="n"/>
-    </row>
-    <row r="447">
+      <c r="F446" s="8" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G446" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="16" customHeight="1">
       <c r="A447" s="2" t="n"/>
       <c r="B447" s="2" t="inlineStr">
         <is>
@@ -13658,10 +13740,18 @@
         </is>
       </c>
       <c r="E447" s="2" t="n"/>
-      <c r="F447" s="4" t="n"/>
-      <c r="G447" s="2" t="n"/>
-    </row>
-    <row r="448">
+      <c r="F447" s="8" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G447" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="16" customHeight="1">
       <c r="A448" s="2" t="n"/>
       <c r="B448" s="2" t="inlineStr">
         <is>
@@ -13679,10 +13769,14 @@
         </is>
       </c>
       <c r="E448" s="2" t="n"/>
-      <c r="F448" s="4" t="n"/>
+      <c r="F448" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G448" s="2" t="n"/>
     </row>
-    <row r="449">
+    <row r="449" ht="16" customHeight="1">
       <c r="A449" s="2" t="n"/>
       <c r="B449" s="2" t="inlineStr">
         <is>
@@ -13700,10 +13794,18 @@
         </is>
       </c>
       <c r="E449" s="2" t="n"/>
-      <c r="F449" s="4" t="n"/>
-      <c r="G449" s="2" t="n"/>
-    </row>
-    <row r="450">
+      <c r="F449" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】重命名标签</t>
+        </is>
+      </c>
+      <c r="G449" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="16" customHeight="1">
       <c r="A450" s="2" t="n"/>
       <c r="B450" s="2" t="inlineStr">
         <is>
@@ -13721,10 +13823,14 @@
         </is>
       </c>
       <c r="E450" s="2" t="n"/>
-      <c r="F450" s="4" t="n"/>
+      <c r="F450" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G450" s="2" t="n"/>
     </row>
-    <row r="451">
+    <row r="451" ht="16" customHeight="1">
       <c r="A451" s="2" t="n"/>
       <c r="B451" s="2" t="inlineStr">
         <is>
@@ -13742,7 +13848,11 @@
         </is>
       </c>
       <c r="E451" s="2" t="n"/>
-      <c r="F451" s="4" t="n"/>
+      <c r="F451" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G451" s="2" t="n"/>
     </row>
     <row r="452">
@@ -13763,10 +13873,18 @@
         </is>
       </c>
       <c r="E452" s="2" t="n"/>
-      <c r="F452" s="4" t="n"/>
-      <c r="G452" s="2" t="n"/>
-    </row>
-    <row r="453">
+      <c r="F452" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G452" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="32" customHeight="1">
       <c r="A453" s="2" t="n"/>
       <c r="B453" s="2" t="inlineStr">
         <is>
@@ -13784,8 +13902,17 @@
         </is>
       </c>
       <c r="E453" s="2" t="n"/>
-      <c r="F453" s="4" t="n"/>
-      <c r="G453" s="2" t="n"/>
+      <c r="F453" s="7" t="inlineStr">
+        <is>
+          <t>纯ID数组 — 97.4%
+含profileId的对象数组 — 2.4%</t>
+        </is>
+      </c>
+      <c r="G453" s="4" t="inlineStr">
+        <is>
+          <t>⚠️契约不一致(第3个同类实例):97.4%真实流量用纯campaignId字符串数组，被后端拒绝(HTTP 400)；仅{profileId,campaignId}对象数组格式(2.4%)被接受。与Campaigns模块的CheckTargetROASToggling/delete同一模式，建议合并排查</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -13805,10 +13932,18 @@
         </is>
       </c>
       <c r="E454" s="2" t="n"/>
-      <c r="F454" s="4" t="n"/>
-      <c r="G454" s="2" t="n"/>
-    </row>
-    <row r="455">
+      <c r="F454" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G454" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="16" customHeight="1">
       <c r="A455" s="2" t="n"/>
       <c r="B455" s="2" t="inlineStr">
         <is>
@@ -13826,10 +13961,18 @@
         </is>
       </c>
       <c r="E455" s="2" t="n"/>
-      <c r="F455" s="4" t="n"/>
-      <c r="G455" s="2" t="n"/>
-    </row>
-    <row r="456">
+      <c r="F455" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】设置Tag目标ACOS/ROAS</t>
+        </is>
+      </c>
+      <c r="G455" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="16" customHeight="1">
       <c r="A456" s="2" t="n"/>
       <c r="B456" s="2" t="inlineStr">
         <is>
@@ -13847,8 +13990,16 @@
         </is>
       </c>
       <c r="E456" s="2" t="n"/>
-      <c r="F456" s="4" t="n"/>
-      <c r="G456" s="2" t="n"/>
+      <c r="F456" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】变更标签负责人</t>
+        </is>
+      </c>
+      <c r="G456" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -653,9 +653,19 @@
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="F5" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>92%(12执行,写操作4条未执行不计入)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>61% (11/18)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3929,7 +3939,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="16" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -3951,10 +3961,14 @@
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
-      <c r="F63" s="4" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="16" customHeight="1">
       <c r="A64" s="2" t="n"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
@@ -3972,10 +3986,18 @@
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="2" t="n"/>
-    </row>
-    <row r="65">
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】创建广告组</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
       <c r="A65" s="2" t="n"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
@@ -3993,8 +4015,16 @@
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="2" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】更新广告组名称</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -4014,8 +4044,16 @@
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="2" t="n"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -4035,10 +4073,18 @@
         </is>
       </c>
       <c r="E67" s="2" t="n"/>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="2" t="n"/>
-    </row>
-    <row r="68">
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
       <c r="A68" s="2" t="n"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
@@ -4056,10 +4102,14 @@
         </is>
       </c>
       <c r="E68" s="2" t="n"/>
-      <c r="F68" s="4" t="n"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="64" customHeight="1">
       <c r="A69" s="2" t="n"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
@@ -4077,7 +4127,14 @@
         </is>
       </c>
       <c r="E69" s="2" t="n"/>
-      <c r="F69" s="4" t="n"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[ids+]+无Tag过滤 — 74.6%
+不传profileIds+不传tagIds — 13.4%
+profileIds=[ids+]+按Tag过滤 — 5.8%
+profileIds=[]+无Tag过滤 — 5.4%</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="n"/>
     </row>
     <row r="70">
@@ -4098,10 +4155,18 @@
         </is>
       </c>
       <c r="E70" s="2" t="n"/>
-      <c r="F70" s="4" t="n"/>
-      <c r="G70" s="2" t="n"/>
-    </row>
-    <row r="71">
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
       <c r="A71" s="2" t="n"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
@@ -4119,7 +4184,11 @@
         </is>
       </c>
       <c r="E71" s="2" t="n"/>
-      <c r="F71" s="4" t="n"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>默认调用</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="n"/>
     </row>
     <row r="72">
@@ -4140,10 +4209,18 @@
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
-      <c r="F72" s="4" t="n"/>
-      <c r="G72" s="2" t="n"/>
-    </row>
-    <row r="73">
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
       <c r="A73" s="2" t="n"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
@@ -4161,8 +4238,16 @@
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="2" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】执行广告组附加信息任务(用途待人工确认)</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -4182,8 +4267,16 @@
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="2" t="n"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -4203,10 +4296,18 @@
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="2" t="n"/>
-    </row>
-    <row r="76">
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
       <c r="A76" s="2" t="n"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
@@ -4224,10 +4325,19 @@
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="2" t="n"/>
-    </row>
-    <row r="77">
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>AdGroupIds=[] — 60.2%
+AdGroupIds=[ids+] — 39.8%</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：AdGroupIds传空数组时报错"Value cannot be null (Parameter source)"(业务码405)，该场景占真实流量60.2%，高频场景下稳定复现，建议报Jira</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
       <c r="A77" s="2" t="n"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
@@ -4245,10 +4355,14 @@
         </is>
       </c>
       <c r="E77" s="2" t="n"/>
-      <c r="F77" s="4" t="n"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="2" t="n"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
@@ -4266,10 +4380,16 @@
         </is>
       </c>
       <c r="E78" s="2" t="n"/>
-      <c r="F78" s="4" t="n"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>不传isAddTo — 55.2%
+isAddTo=true — 38.0%
+isAddTo=false — 6.8%</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="16" customHeight="1">
       <c r="A79" s="2" t="n"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
@@ -4287,8 +4407,16 @@
         </is>
       </c>
       <c r="E79" s="2" t="n"/>
-      <c r="F79" s="4" t="n"/>
-      <c r="G79" s="2" t="n"/>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】修改广告组状态</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -4308,8 +4436,16 @@
         </is>
       </c>
       <c r="E80" s="2" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="2" t="n"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15.95" customHeight="1">
       <c r="A81" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1771,9 +1771,19 @@
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
+      <c r="F49" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>91%(10执行,写操作2条未执行不计入)</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>39% (7/18)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -30686,7 +30696,7 @@
       <c r="F1101" s="4" t="n"/>
       <c r="G1101" s="2" t="n"/>
     </row>
-    <row r="1102">
+    <row r="1102" ht="16" customHeight="1">
       <c r="A1102" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -30708,10 +30718,14 @@
         </is>
       </c>
       <c r="E1102" s="2" t="n"/>
-      <c r="F1102" s="4" t="n"/>
+      <c r="F1102" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1102" s="2" t="n"/>
     </row>
-    <row r="1103">
+    <row r="1103" ht="16" customHeight="1">
       <c r="A1103" s="2" t="n"/>
       <c r="B1103" s="2" t="inlineStr">
         <is>
@@ -30729,10 +30743,18 @@
         </is>
       </c>
       <c r="E1103" s="2" t="n"/>
-      <c r="F1103" s="4" t="n"/>
-      <c r="G1103" s="2" t="n"/>
-    </row>
-    <row r="1104">
+      <c r="F1103" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】创建Media(发起上传)</t>
+        </is>
+      </c>
+      <c r="G1103" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104" ht="32" customHeight="1">
       <c r="A1104" s="2" t="n"/>
       <c r="B1104" s="2" t="inlineStr">
         <is>
@@ -30750,8 +30772,16 @@
         </is>
       </c>
       <c r="E1104" s="2" t="n"/>
-      <c r="F1104" s="4" t="n"/>
-      <c r="G1104" s="2" t="n"/>
+      <c r="F1104" s="8" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1104" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1105">
       <c r="A1105" s="2" t="n"/>
@@ -30771,8 +30801,16 @@
         </is>
       </c>
       <c r="E1105" s="2" t="n"/>
-      <c r="F1105" s="4" t="n"/>
-      <c r="G1105" s="2" t="n"/>
+      <c r="F1105" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1105" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1106">
       <c r="A1106" s="2" t="n"/>
@@ -30792,8 +30830,16 @@
         </is>
       </c>
       <c r="E1106" s="2" t="n"/>
-      <c r="F1106" s="4" t="n"/>
-      <c r="G1106" s="2" t="n"/>
+      <c r="F1106" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1106" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1107">
       <c r="A1107" s="2" t="n"/>
@@ -30813,8 +30859,16 @@
         </is>
       </c>
       <c r="E1107" s="2" t="n"/>
-      <c r="F1107" s="4" t="n"/>
-      <c r="G1107" s="2" t="n"/>
+      <c r="F1107" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1107" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1108">
       <c r="A1108" s="2" t="n"/>
@@ -30834,10 +30888,18 @@
         </is>
       </c>
       <c r="E1108" s="2" t="n"/>
-      <c r="F1108" s="4" t="n"/>
-      <c r="G1108" s="2" t="n"/>
-    </row>
-    <row r="1109">
+      <c r="F1108" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1108" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109" ht="16" customHeight="1">
       <c r="A1109" s="2" t="n"/>
       <c r="B1109" s="2" t="inlineStr">
         <is>
@@ -30855,7 +30917,11 @@
         </is>
       </c>
       <c r="E1109" s="2" t="n"/>
-      <c r="F1109" s="4" t="n"/>
+      <c r="F1109" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1109" s="2" t="n"/>
     </row>
     <row r="1110">
@@ -30876,8 +30942,16 @@
         </is>
       </c>
       <c r="E1110" s="2" t="n"/>
-      <c r="F1110" s="4" t="n"/>
-      <c r="G1110" s="2" t="n"/>
+      <c r="F1110" s="4" t="inlineStr">
+        <is>
+          <t>文件上传，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1110" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口(vtt字幕文件)，无法用JSON表示，不生成case，需人工用真实文件测试(365d 39次)</t>
+        </is>
+      </c>
     </row>
     <row r="1111">
       <c r="A1111" s="2" t="n"/>
@@ -30897,10 +30971,18 @@
         </is>
       </c>
       <c r="E1111" s="2" t="n"/>
-      <c r="F1111" s="4" t="n"/>
-      <c r="G1111" s="2" t="n"/>
-    </row>
-    <row r="1112">
+      <c r="F1111" s="4" t="inlineStr">
+        <is>
+          <t>文件上传，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1111" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口(vtt字幕文件)，无法用JSON表示，不生成case，需人工用真实文件测试(365d 20次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112" ht="16" customHeight="1">
       <c r="A1112" s="2" t="n"/>
       <c r="B1112" s="2" t="inlineStr">
         <is>
@@ -30918,8 +31000,16 @@
         </is>
       </c>
       <c r="E1112" s="2" t="n"/>
-      <c r="F1112" s="4" t="n"/>
-      <c r="G1112" s="2" t="n"/>
+      <c r="F1112" s="8" t="inlineStr">
+        <is>
+          <t>【仅生成未执行】完成媒体上传</t>
+        </is>
+      </c>
+      <c r="G1112" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="1113">
       <c r="A1113" s="2" t="n"/>
@@ -30939,8 +31029,16 @@
         </is>
       </c>
       <c r="E1113" s="2" t="n"/>
-      <c r="F1113" s="4" t="n"/>
-      <c r="G1113" s="2" t="n"/>
+      <c r="F1113" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1113" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 16次)</t>
+        </is>
+      </c>
     </row>
     <row r="1114">
       <c r="A1114" s="2" t="n"/>
@@ -30960,10 +31058,18 @@
         </is>
       </c>
       <c r="E1114" s="2" t="n"/>
-      <c r="F1114" s="4" t="n"/>
-      <c r="G1114" s="2" t="n"/>
-    </row>
-    <row r="1115">
+      <c r="F1114" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1114" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 16次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115" ht="96" customHeight="1">
       <c r="A1115" s="2" t="n"/>
       <c r="B1115" s="2" t="inlineStr">
         <is>
@@ -30981,10 +31087,23 @@
         </is>
       </c>
       <c r="E1115" s="2" t="n"/>
-      <c r="F1115" s="4" t="n"/>
-      <c r="G1115" s="2" t="n"/>
-    </row>
-    <row r="1116">
+      <c r="F1115" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[]+无Campaign过滤 — 52.6%
+profileIds=[ids+]+无Campaign过滤 — 25.6%
+profileIds=[ids+]+按Campaign过滤 — 12.4%
+profileIds=[]+按Campaign过滤 — 4.6%
+profileIds=[ids+]+不传campaignIds — 3.6%
+profileIds=[]+不传campaignIds — 1.0%</t>
+        </is>
+      </c>
+      <c r="G1115" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：profileIds传空数组且不传campaignIds时报SQL异常"Invalid column name Spend"(System.Data.SqlClient.SqlException)，建议报Jira</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116" ht="16" customHeight="1">
       <c r="A1116" s="2" t="n"/>
       <c r="B1116" s="2" t="inlineStr">
         <is>
@@ -31002,10 +31121,14 @@
         </is>
       </c>
       <c r="E1116" s="2" t="n"/>
-      <c r="F1116" s="4" t="n"/>
+      <c r="F1116" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1116" s="2" t="n"/>
     </row>
-    <row r="1117">
+    <row r="1117" ht="32" customHeight="1">
       <c r="A1117" s="2" t="n"/>
       <c r="B1117" s="2" t="inlineStr">
         <is>
@@ -31023,7 +31146,12 @@
         </is>
       </c>
       <c r="E1117" s="2" t="n"/>
-      <c r="F1117" s="4" t="n"/>
+      <c r="F1117" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[] — 95.6%
+profileIds=[ids+] — 4.4%</t>
+        </is>
+      </c>
       <c r="G1117" s="2" t="n"/>
     </row>
     <row r="1118">
@@ -31044,8 +31172,16 @@
         </is>
       </c>
       <c r="E1118" s="2" t="n"/>
-      <c r="F1118" s="4" t="n"/>
-      <c r="G1118" s="2" t="n"/>
+      <c r="F1118" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1118" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="n"/>
@@ -31065,8 +31201,16 @@
         </is>
       </c>
       <c r="E1119" s="2" t="n"/>
-      <c r="F1119" s="4" t="n"/>
-      <c r="G1119" s="2" t="n"/>
+      <c r="F1119" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1119" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1120">
       <c r="A1120" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -978,11 +978,11 @@
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>86%(6执行,写操作7条未执行不计入)</t>
+          <t>83%(12执行,写操作1条未确认不计入)</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -13604,14 +13604,14 @@
         </is>
       </c>
       <c r="E437" s="2" t="n"/>
-      <c r="F437" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】创建标签</t>
+      <c r="F437" s="7" t="inlineStr">
+        <is>
+          <t>创建标签→抓ID→删除(写操作·自清理)</t>
         </is>
       </c>
       <c r="G437" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14)：创建测试标签→GET抓ID→DELETE清理，2轮全PASS</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="G438" s="2" t="n"/>
     </row>
-    <row r="439" ht="16" customHeight="1">
+    <row r="439" ht="48" customHeight="1">
       <c r="A439" s="2" t="n"/>
       <c r="B439" s="2" t="inlineStr">
         <is>
@@ -13658,14 +13658,16 @@
         </is>
       </c>
       <c r="E439" s="2" t="n"/>
-      <c r="F439" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】删除标签(不可逆)</t>
+      <c r="F439" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 99.4%
+创建标签→抓ID→删除(写操作·自清理)
+更新标签并绑定Campaign(写操作·自清理)</t>
         </is>
       </c>
       <c r="G439" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14)：作为多个自清理case的删除步骤复用，2轮全PASS</t>
         </is>
       </c>
     </row>
@@ -13687,14 +13689,14 @@
         </is>
       </c>
       <c r="E440" s="2" t="n"/>
-      <c r="F440" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】更新标签(改名/改绑定Campaign)</t>
+      <c r="F440" s="7" t="inlineStr">
+        <is>
+          <t>更新标签并绑定Campaign(写操作·自清理)</t>
         </is>
       </c>
       <c r="G440" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>🔴写操作已执行，发现新后端bug(2026-09-14，稳定复现2轮)：更新标签绑定Campaign返回业务码405，内部实为NullReferenceException(CampaignTagService.RenameTag第576行→Update第454行抛出未处理异常，EF Core LINQ参数求值时对象引用为空)，非业务限制</t>
         </is>
       </c>
     </row>
@@ -13716,14 +13718,14 @@
         </is>
       </c>
       <c r="E441" s="2" t="n"/>
-      <c r="F441" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量删除标签(不可逆)</t>
+      <c r="F441" s="7" t="inlineStr">
+        <is>
+          <t>批量删除标签(写操作·自建2个)</t>
         </is>
       </c>
       <c r="G441" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14)：自建2个标签后批量删除，2轮全PASS</t>
         </is>
       </c>
     </row>
@@ -13857,9 +13859,9 @@
         </is>
       </c>
       <c r="E446" s="2" t="n"/>
-      <c r="F446" s="8" t="inlineStr">
-        <is>
-          <t>ES 无流量</t>
+      <c r="F446" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
         </is>
       </c>
       <c r="G446" s="4" t="inlineStr">
@@ -13886,9 +13888,9 @@
         </is>
       </c>
       <c r="E447" s="2" t="n"/>
-      <c r="F447" s="8" t="inlineStr">
-        <is>
-          <t>ES 无流量</t>
+      <c r="F447" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
         </is>
       </c>
       <c r="G447" s="4" t="inlineStr">
@@ -13940,14 +13942,14 @@
         </is>
       </c>
       <c r="E449" s="2" t="n"/>
-      <c r="F449" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】重命名标签</t>
+      <c r="F449" s="7" t="inlineStr">
+        <is>
+          <t>重命名标签(写操作·自清理)</t>
         </is>
       </c>
       <c r="G449" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14)：先GET记原值→改名→还原，2轮全PASS</t>
         </is>
       </c>
     </row>
@@ -14107,14 +14109,14 @@
         </is>
       </c>
       <c r="E455" s="2" t="n"/>
-      <c r="F455" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】设置Tag目标ACOS/ROAS</t>
+      <c r="F455" s="7" t="inlineStr">
+        <is>
+          <t>设置Tag目标ACOS/ROAS(写操作·自清理)</t>
         </is>
       </c>
       <c r="G455" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14)：设置目标ACOS/ROAS后还原，2轮全PASS</t>
         </is>
       </c>
     </row>
@@ -14136,14 +14138,14 @@
         </is>
       </c>
       <c r="E456" s="2" t="n"/>
-      <c r="F456" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】变更标签负责人</t>
+      <c r="F456" s="7" t="inlineStr">
+        <is>
+          <t>变更标签负责人</t>
         </is>
       </c>
       <c r="G456" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>【高风险-待确认】变更标签负责人，属不可逆操作清单，已生成case但未执行，需用户逐条确认后再跑</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -631,9 +631,19 @@
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>14% (1/7)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1161,9 +1171,19 @@
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="F24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>50% (3/6)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1291,9 +1311,19 @@
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>N/A(全零流量)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>ES 无流量 (0/6)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1421,9 +1451,19 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+      <c r="F34" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>57% (4/7)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1607,9 +1647,19 @@
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
+      <c r="F42" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>36% (4/11)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1673,9 +1723,19 @@
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
+      <c r="F45" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>60% (9/15)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1695,9 +1755,19 @@
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
+      <c r="F46" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>60% (9/15)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1967,9 +2037,19 @@
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
+      <c r="F57" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>53% (9/17)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2109,9 +2189,19 @@
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
+      <c r="F63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>N/A(全零流量)</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>ES 无流量 (0/3)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2175,9 +2265,19 @@
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
+      <c r="F66" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>50% (4/8)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2219,9 +2319,19 @@
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
+      <c r="F68" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>67% (4/6)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4533,8 +4643,16 @@
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="2" t="n"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖；且为异步导出/回调类接口</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -4554,10 +4672,18 @@
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="2" t="n"/>
-    </row>
-    <row r="85">
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖；且为异步导出/回调类接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
       <c r="A85" s="2" t="n"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
@@ -4575,7 +4701,11 @@
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
-      <c r="F85" s="4" t="n"/>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G85" s="2" t="n"/>
     </row>
     <row r="86">
@@ -4596,8 +4726,16 @@
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="2" t="n"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -4617,8 +4755,16 @@
         </is>
       </c>
       <c r="E87" s="2" t="n"/>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="2" t="n"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -4638,8 +4784,16 @@
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
-      <c r="F88" s="4" t="n"/>
-      <c r="G88" s="2" t="n"/>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -4659,8 +4813,16 @@
         </is>
       </c>
       <c r="E89" s="2" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="2" t="n"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -16345,8 +16507,16 @@
         </is>
       </c>
       <c r="E552" s="2" t="n"/>
-      <c r="F552" s="4" t="n"/>
-      <c r="G552" s="2" t="n"/>
+      <c r="F552" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G552" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，且365d 0次流量，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n"/>
@@ -16366,10 +16536,18 @@
         </is>
       </c>
       <c r="E553" s="2" t="n"/>
-      <c r="F553" s="4" t="n"/>
-      <c r="G553" s="2" t="n"/>
-    </row>
-    <row r="554">
+      <c r="F553" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G553" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调接口，由后端任务触发，暂不覆盖(365d 69次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="112" customHeight="1">
       <c r="A554" s="2" t="n"/>
       <c r="B554" s="2" t="inlineStr">
         <is>
@@ -16387,7 +16565,17 @@
         </is>
       </c>
       <c r="E554" s="2" t="n"/>
-      <c r="F554" s="4" t="n"/>
+      <c r="F554" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=1+按Campaign过滤 — 44.2%
+tabGroupBy=1+不传campaignIds — 27.8%
+tabGroupBy=1+无Campaign过滤 — 15.4%
+不传tabGroupBy+按Campaign过滤 — 5.4%
+tabGroupBy=2+无Campaign过滤 — 2.4%
+tabGroupBy=2+按Campaign过滤 — 2.4%
+不传tabGroupBy+不传campaignIds — 1.4%</t>
+        </is>
+      </c>
       <c r="G554" s="2" t="n"/>
     </row>
     <row r="555">
@@ -16408,10 +16596,18 @@
         </is>
       </c>
       <c r="E555" s="2" t="n"/>
-      <c r="F555" s="4" t="n"/>
-      <c r="G555" s="2" t="n"/>
-    </row>
-    <row r="556">
+      <c r="F555" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G555" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="112" customHeight="1">
       <c r="A556" s="2" t="n"/>
       <c r="B556" s="2" t="inlineStr">
         <is>
@@ -16429,10 +16625,20 @@
         </is>
       </c>
       <c r="E556" s="2" t="n"/>
-      <c r="F556" s="4" t="n"/>
+      <c r="F556" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=1+按Campaign过滤 — 39.4%
+tabGroupBy=1+不传campaignIds — 31.0%
+tabGroupBy=1+无Campaign过滤 — 15.4%
+不传tabGroupBy+按Campaign过滤 — 5.2%
+tabGroupBy=2+按Campaign过滤 — 3.8%
+tabGroupBy=2+无Campaign过滤 — 3.0%
+tabGroupBy=2+不传campaignIds — 1.4%</t>
+        </is>
+      </c>
       <c r="G556" s="2" t="n"/>
     </row>
-    <row r="557">
+    <row r="557" ht="80" customHeight="1">
       <c r="A557" s="2" t="n"/>
       <c r="B557" s="2" t="inlineStr">
         <is>
@@ -16450,7 +16656,15 @@
         </is>
       </c>
       <c r="E557" s="2" t="n"/>
-      <c r="F557" s="4" t="n"/>
+      <c r="F557" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+tabGroupBy=1 — 84.2%
+  dim  =ytd+tabGroupBy=2 — 7.6%
+  dim  =ytd+不传tabGroupBy — 4.4%
+  dim  =date+tabGroupBy=1 — 1.8%
+不传  dim  +不传tabGroupBy — 1.2%</t>
+        </is>
+      </c>
       <c r="G557" s="2" t="n"/>
     </row>
     <row r="558">
@@ -24817,8 +25031,16 @@
         </is>
       </c>
       <c r="E856" s="2" t="n"/>
-      <c r="F856" s="4" t="n"/>
-      <c r="G856" s="2" t="n"/>
+      <c r="F856" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G856" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n"/>
@@ -24838,8 +25060,16 @@
         </is>
       </c>
       <c r="E857" s="2" t="n"/>
-      <c r="F857" s="4" t="n"/>
-      <c r="G857" s="2" t="n"/>
+      <c r="F857" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G857" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n"/>
@@ -24859,8 +25089,16 @@
         </is>
       </c>
       <c r="E858" s="2" t="n"/>
-      <c r="F858" s="4" t="n"/>
-      <c r="G858" s="2" t="n"/>
+      <c r="F858" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G858" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n"/>
@@ -24880,8 +25118,16 @@
         </is>
       </c>
       <c r="E859" s="2" t="n"/>
-      <c r="F859" s="4" t="n"/>
-      <c r="G859" s="2" t="n"/>
+      <c r="F859" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G859" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n"/>
@@ -24901,8 +25147,16 @@
         </is>
       </c>
       <c r="E860" s="2" t="n"/>
-      <c r="F860" s="4" t="n"/>
-      <c r="G860" s="2" t="n"/>
+      <c r="F860" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G860" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n"/>
@@ -24922,8 +25176,16 @@
         </is>
       </c>
       <c r="E861" s="2" t="n"/>
-      <c r="F861" s="4" t="n"/>
-      <c r="G861" s="2" t="n"/>
+      <c r="F861" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G861" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" s="2" t="inlineStr">
@@ -26153,8 +26415,16 @@
         </is>
       </c>
       <c r="E909" s="2" t="n"/>
-      <c r="F909" s="4" t="n"/>
-      <c r="G909" s="2" t="n"/>
+      <c r="F909" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G909" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 16次)</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n"/>
@@ -26174,10 +26444,18 @@
         </is>
       </c>
       <c r="E910" s="2" t="n"/>
-      <c r="F910" s="4" t="n"/>
-      <c r="G910" s="2" t="n"/>
-    </row>
-    <row r="911">
+      <c r="F910" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G910" s="4" t="inlineStr">
+        <is>
+          <t>导出回调接口，由导出任务异步触发，暂不覆盖(365d 16次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="911" ht="80" customHeight="1">
       <c r="A911" s="2" t="n"/>
       <c r="B911" s="2" t="inlineStr">
         <is>
@@ -26195,10 +26473,18 @@
         </is>
       </c>
       <c r="E911" s="2" t="n"/>
-      <c r="F911" s="4" t="n"/>
+      <c r="F911" s="7" t="inlineStr">
+        <is>
+          <t>无ItemTag过滤+  dim  =ytd — 63.0%
+按ItemTag过滤+  dim  =ytd — 16.0%
+无ItemTag过滤+  dim  =date — 11.2%
+无ItemTag过滤+  dim  =week — 6.6%
+按ItemTag过滤+  dim  =date — 2.4%</t>
+        </is>
+      </c>
       <c r="G911" s="2" t="n"/>
     </row>
-    <row r="912">
+    <row r="912" ht="64" customHeight="1">
       <c r="A912" s="2" t="n"/>
       <c r="B912" s="2" t="inlineStr">
         <is>
@@ -26216,7 +26502,14 @@
         </is>
       </c>
       <c r="E912" s="2" t="n"/>
-      <c r="F912" s="4" t="n"/>
+      <c r="F912" s="7" t="inlineStr">
+        <is>
+          <t>无ItemTag过滤+  dim  =ytd — 83.3%
+按ItemTag过滤+  dim  =ytd — 8.6%
+无ItemTag过滤+  dim  =date — 3.8%
+按ItemTag过滤+  dim  =date — 2.9%</t>
+        </is>
+      </c>
       <c r="G912" s="2" t="n"/>
     </row>
     <row r="913">
@@ -26237,10 +26530,18 @@
         </is>
       </c>
       <c r="E913" s="2" t="n"/>
-      <c r="F913" s="4" t="n"/>
-      <c r="G913" s="2" t="n"/>
-    </row>
-    <row r="914">
+      <c r="F913" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G913" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="914" ht="80" customHeight="1">
       <c r="A914" s="2" t="n"/>
       <c r="B914" s="2" t="inlineStr">
         <is>
@@ -26258,10 +26559,18 @@
         </is>
       </c>
       <c r="E914" s="2" t="n"/>
-      <c r="F914" s="4" t="n"/>
+      <c r="F914" s="7" t="inlineStr">
+        <is>
+          <t>无ItemTag过滤+  dim  =ytd — 62.6%
+按ItemTag过滤+  dim  =ytd — 17.2%
+无ItemTag过滤+  dim  =date — 10.6%
+无ItemTag过滤+  dim  =week — 7.0%
+按ItemTag过滤+  dim  =date — 1.6%</t>
+        </is>
+      </c>
       <c r="G914" s="2" t="n"/>
     </row>
-    <row r="915">
+    <row r="915" ht="80" customHeight="1">
       <c r="A915" s="2" t="n"/>
       <c r="B915" s="2" t="inlineStr">
         <is>
@@ -26279,7 +26588,15 @@
         </is>
       </c>
       <c r="E915" s="2" t="n"/>
-      <c r="F915" s="4" t="n"/>
+      <c r="F915" s="7" t="inlineStr">
+        <is>
+          <t>无ItemTag过滤+  dim  =ytd — 60.6%
+按ItemTag过滤+  dim  =ytd — 16.8%
+无ItemTag过滤+  dim  =date — 11.8%
+无ItemTag过滤+  dim  =week — 7.2%
+按ItemTag过滤+  dim  =date — 2.8%</t>
+        </is>
+      </c>
       <c r="G915" s="2" t="n"/>
     </row>
     <row r="916">
@@ -28107,8 +28424,16 @@
         </is>
       </c>
       <c r="E990" s="2" t="n"/>
-      <c r="F990" s="4" t="n"/>
-      <c r="G990" s="2" t="n"/>
+      <c r="F990" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G990" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="991">
       <c r="A991" s="2" t="n"/>
@@ -28128,8 +28453,16 @@
         </is>
       </c>
       <c r="E991" s="2" t="n"/>
-      <c r="F991" s="4" t="n"/>
-      <c r="G991" s="2" t="n"/>
+      <c r="F991" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G991" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n"/>
@@ -28149,8 +28482,16 @@
         </is>
       </c>
       <c r="E992" s="2" t="n"/>
-      <c r="F992" s="4" t="n"/>
-      <c r="G992" s="2" t="n"/>
+      <c r="F992" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G992" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" s="2" t="n"/>
@@ -28170,8 +28511,16 @@
         </is>
       </c>
       <c r="E993" s="2" t="n"/>
-      <c r="F993" s="4" t="n"/>
-      <c r="G993" s="2" t="n"/>
+      <c r="F993" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G993" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n"/>
@@ -28191,8 +28540,16 @@
         </is>
       </c>
       <c r="E994" s="2" t="n"/>
-      <c r="F994" s="4" t="n"/>
-      <c r="G994" s="2" t="n"/>
+      <c r="F994" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G994" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 340次)</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" s="2" t="n"/>
@@ -28212,10 +28569,18 @@
         </is>
       </c>
       <c r="E995" s="2" t="n"/>
-      <c r="F995" s="4" t="n"/>
-      <c r="G995" s="2" t="n"/>
-    </row>
-    <row r="996">
+      <c r="F995" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G995" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调接口，由后端任务触发，暂不覆盖(365d 340次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="996" ht="80" customHeight="1">
       <c r="A996" s="2" t="n"/>
       <c r="B996" s="2" t="inlineStr">
         <is>
@@ -28233,10 +28598,18 @@
         </is>
       </c>
       <c r="E996" s="2" t="n"/>
-      <c r="F996" s="4" t="n"/>
+      <c r="F996" s="7" t="inlineStr">
+        <is>
+          <t>不传  dim  +按ItemTag过滤 — 50.2%
+  dim  =ytd+无ItemTag过滤 — 24.0%
+  dim  =ytd+按ItemTag过滤 — 20.8%
+  dim  =week+无ItemTag过滤 — 1.8%
+  dim  =week+按ItemTag过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G996" s="2" t="n"/>
     </row>
-    <row r="997">
+    <row r="997" ht="48" customHeight="1">
       <c r="A997" s="2" t="n"/>
       <c r="B997" s="2" t="inlineStr">
         <is>
@@ -28254,7 +28627,13 @@
         </is>
       </c>
       <c r="E997" s="2" t="n"/>
-      <c r="F997" s="4" t="n"/>
+      <c r="F997" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+无ItemTag过滤 — 63.2%
+  dim  =ytd+按ItemTag过滤 — 33.6%
+  dim  =date+按ItemTag过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G997" s="2" t="n"/>
     </row>
     <row r="998">
@@ -28275,10 +28654,18 @@
         </is>
       </c>
       <c r="E998" s="2" t="n"/>
-      <c r="F998" s="4" t="n"/>
-      <c r="G998" s="2" t="n"/>
-    </row>
-    <row r="999">
+      <c r="F998" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G998" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="999" ht="64" customHeight="1">
       <c r="A999" s="2" t="n"/>
       <c r="B999" s="2" t="inlineStr">
         <is>
@@ -28296,10 +28683,17 @@
         </is>
       </c>
       <c r="E999" s="2" t="n"/>
-      <c r="F999" s="4" t="n"/>
+      <c r="F999" s="7" t="inlineStr">
+        <is>
+          <t>不传  dim  +按ItemTag过滤 — 56.8%
+  dim  =ytd+无ItemTag过滤 — 26.8%
+  dim  =ytd+按ItemTag过滤 — 14.0%
+  dim  =week+无ItemTag过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G999" s="2" t="n"/>
     </row>
-    <row r="1000">
+    <row r="1000" ht="96" customHeight="1">
       <c r="A1000" s="2" t="n"/>
       <c r="B1000" s="2" t="inlineStr">
         <is>
@@ -28317,7 +28711,16 @@
         </is>
       </c>
       <c r="E1000" s="2" t="n"/>
-      <c r="F1000" s="4" t="n"/>
+      <c r="F1000" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+无ItemTag过滤 — 40.2%
+  dim  =ytd+按ItemTag过滤 — 30.6%
+不传  dim  +按ItemTag过滤 — 22.0%
+  dim  =week+无ItemTag过滤 — 3.0%
+  dim  =month+按ItemTag过滤 — 1.6%
+  dim  =date+按ItemTag过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1000" s="2" t="n"/>
     </row>
     <row r="1001">
@@ -28748,7 +29151,7 @@
       <c r="F1020" s="4" t="n"/>
       <c r="G1020" s="2" t="n"/>
     </row>
-    <row r="1021">
+    <row r="1021" ht="80" customHeight="1">
       <c r="A1021" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -28770,7 +29173,15 @@
         </is>
       </c>
       <c r="E1021" s="2" t="n"/>
-      <c r="F1021" s="4" t="n"/>
+      <c r="F1021" s="7" t="inlineStr">
+        <is>
+          <t>按Acos排序 — 23.9%
+按Spend排序 — 23.9%
+按Sales排序 — 23.9%
+按spend排序 — 23.9%
+不传orderBy(按周/月趋势维度) — 4.3%</t>
+        </is>
+      </c>
       <c r="G1021" s="2" t="n"/>
     </row>
     <row r="1022">
@@ -28791,8 +29202,16 @@
         </is>
       </c>
       <c r="E1022" s="2" t="n"/>
-      <c r="F1022" s="4" t="n"/>
-      <c r="G1022" s="2" t="n"/>
+      <c r="F1022" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1022" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 5621次)</t>
+        </is>
+      </c>
     </row>
     <row r="1023">
       <c r="A1023" s="2" t="n"/>
@@ -28812,10 +29231,18 @@
         </is>
       </c>
       <c r="E1023" s="2" t="n"/>
-      <c r="F1023" s="4" t="n"/>
-      <c r="G1023" s="2" t="n"/>
-    </row>
-    <row r="1024">
+      <c r="F1023" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1023" s="4" t="inlineStr">
+        <is>
+          <t>导出回调接口(由导出任务回调触发)，无法单接口独立验证，暂不覆盖(365d 11244次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024" ht="64" customHeight="1">
       <c r="A1024" s="2" t="n"/>
       <c r="B1024" s="2" t="inlineStr">
         <is>
@@ -28833,10 +29260,17 @@
         </is>
       </c>
       <c r="E1024" s="2" t="n"/>
-      <c r="F1024" s="4" t="n"/>
+      <c r="F1024" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+kindType=Default — 84.6%
+  dim  =ytd+kindType=Targeting — 10.0%
+不传  dim  +kindType=Targeting — 3.8%
+  dim  =date+kindType=Default — 1.0%</t>
+        </is>
+      </c>
       <c r="G1024" s="2" t="n"/>
     </row>
-    <row r="1025">
+    <row r="1025" ht="64" customHeight="1">
       <c r="A1025" s="2" t="n"/>
       <c r="B1025" s="2" t="inlineStr">
         <is>
@@ -28854,7 +29288,14 @@
         </is>
       </c>
       <c r="E1025" s="2" t="n"/>
-      <c r="F1025" s="4" t="n"/>
+      <c r="F1025" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =week+tabGroupBy=AdGroup — 39.4%
+  dim  =date+tabGroupBy=AdGroup — 30.3%
+  dim  =month+tabGroupBy=AdGroup — 15.2%
+  dim  =month+tabGroupBy=Keyword — 7.6%</t>
+        </is>
+      </c>
       <c r="G1025" s="2" t="n"/>
     </row>
     <row r="1026">
@@ -28875,10 +29316,18 @@
         </is>
       </c>
       <c r="E1026" s="2" t="n"/>
-      <c r="F1026" s="4" t="n"/>
-      <c r="G1026" s="2" t="n"/>
-    </row>
-    <row r="1027">
+      <c r="F1026" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1026" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027" ht="64" customHeight="1">
       <c r="A1027" s="2" t="n"/>
       <c r="B1027" s="2" t="inlineStr">
         <is>
@@ -28896,7 +29345,14 @@
         </is>
       </c>
       <c r="E1027" s="2" t="n"/>
-      <c r="F1027" s="4" t="n"/>
+      <c r="F1027" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+kindType=Default — 84.2%
+  dim  =ytd+kindType=Targeting — 10.4%
+不传  dim  +kindType=Targeting — 3.4%
+  dim  =date+kindType=Default — 1.2%</t>
+        </is>
+      </c>
       <c r="G1027" s="2" t="n"/>
     </row>
     <row r="1028">
@@ -28917,8 +29373,16 @@
         </is>
       </c>
       <c r="E1028" s="2" t="n"/>
-      <c r="F1028" s="4" t="n"/>
-      <c r="G1028" s="2" t="n"/>
+      <c r="F1028" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1028" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" s="2" t="n"/>
@@ -28938,8 +29402,16 @@
         </is>
       </c>
       <c r="E1029" s="2" t="n"/>
-      <c r="F1029" s="4" t="n"/>
-      <c r="G1029" s="2" t="n"/>
+      <c r="F1029" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1029" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖；且为异步导出/回调类接口</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" s="2" t="n"/>
@@ -28959,10 +29431,18 @@
         </is>
       </c>
       <c r="E1030" s="2" t="n"/>
-      <c r="F1030" s="4" t="n"/>
-      <c r="G1030" s="2" t="n"/>
-    </row>
-    <row r="1031">
+      <c r="F1030" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1030" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖；且为异步导出/回调类接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031" ht="48" customHeight="1">
       <c r="A1031" s="2" t="n"/>
       <c r="B1031" s="2" t="inlineStr">
         <is>
@@ -28980,10 +29460,16 @@
         </is>
       </c>
       <c r="E1031" s="2" t="n"/>
-      <c r="F1031" s="4" t="n"/>
+      <c r="F1031" s="7" t="inlineStr">
+        <is>
+          <t>keywordMatchType=[exact]+dim=0(汇总) — 62.8%
+keywordMatchType=[phrase]+dim=0(汇总) — 21.2%
+keywordMatchType=[broad]+dim=0(汇总) — 12.4%</t>
+        </is>
+      </c>
       <c r="G1031" s="2" t="n"/>
     </row>
-    <row r="1032">
+    <row r="1032" ht="48" customHeight="1">
       <c r="A1032" s="2" t="n"/>
       <c r="B1032" s="2" t="inlineStr">
         <is>
@@ -29001,10 +29487,16 @@
         </is>
       </c>
       <c r="E1032" s="2" t="n"/>
-      <c r="F1032" s="4" t="n"/>
+      <c r="F1032" s="7" t="inlineStr">
+        <is>
+          <t>keywordMatchType=[exact] — 64.5%
+keywordMatchType=[phrase] — 21.8%
+keywordMatchType=[broad] — 12.7%</t>
+        </is>
+      </c>
       <c r="G1032" s="2" t="n"/>
     </row>
-    <row r="1033">
+    <row r="1033" ht="48" customHeight="1">
       <c r="A1033" s="2" t="n"/>
       <c r="B1033" s="2" t="inlineStr">
         <is>
@@ -29022,10 +29514,16 @@
         </is>
       </c>
       <c r="E1033" s="2" t="n"/>
-      <c r="F1033" s="4" t="n"/>
+      <c r="F1033" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+kindType=Default — 87.6%
+  dim  =ytd+kindType=Targeting — 9.6%
+  dim  =date+kindType=Default — 1.6%</t>
+        </is>
+      </c>
       <c r="G1033" s="2" t="n"/>
     </row>
-    <row r="1034">
+    <row r="1034" ht="48" customHeight="1">
       <c r="A1034" s="2" t="n"/>
       <c r="B1034" s="2" t="inlineStr">
         <is>
@@ -29043,10 +29541,16 @@
         </is>
       </c>
       <c r="E1034" s="2" t="n"/>
-      <c r="F1034" s="4" t="n"/>
+      <c r="F1034" s="7" t="inlineStr">
+        <is>
+          <t>kindType=Default+profileIds=[] — 41.0%
+kindType=Default+profileIds=[ids+] — 38.5%
+kindType=Targeting+profileIds=[ids+] — 20.5%</t>
+        </is>
+      </c>
       <c r="G1034" s="2" t="n"/>
     </row>
-    <row r="1035">
+    <row r="1035" ht="16" customHeight="1">
       <c r="A1035" s="2" t="n"/>
       <c r="B1035" s="2" t="inlineStr">
         <is>
@@ -29064,7 +29568,11 @@
         </is>
       </c>
       <c r="E1035" s="2" t="n"/>
-      <c r="F1035" s="4" t="n"/>
+      <c r="F1035" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1035" s="2" t="n"/>
     </row>
     <row r="1036">
@@ -30061,10 +30569,18 @@
         </is>
       </c>
       <c r="E1071" s="2" t="n"/>
-      <c r="F1071" s="4" t="n"/>
-      <c r="G1071" s="2" t="n"/>
-    </row>
-    <row r="1072">
+      <c r="F1071" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1071" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072" ht="16" customHeight="1">
       <c r="A1072" s="2" t="n"/>
       <c r="B1072" s="2" t="inlineStr">
         <is>
@@ -30082,7 +30598,11 @@
         </is>
       </c>
       <c r="E1072" s="2" t="n"/>
-      <c r="F1072" s="4" t="n"/>
+      <c r="F1072" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1072" s="2" t="n"/>
     </row>
     <row r="1073">
@@ -30103,8 +30623,16 @@
         </is>
       </c>
       <c r="E1073" s="2" t="n"/>
-      <c r="F1073" s="4" t="n"/>
-      <c r="G1073" s="2" t="n"/>
+      <c r="F1073" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1073" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="n"/>
@@ -30124,8 +30652,16 @@
         </is>
       </c>
       <c r="E1074" s="2" t="n"/>
-      <c r="F1074" s="4" t="n"/>
-      <c r="G1074" s="2" t="n"/>
+      <c r="F1074" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1074" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="n"/>
@@ -30145,8 +30681,16 @@
         </is>
       </c>
       <c r="E1075" s="2" t="n"/>
-      <c r="F1075" s="4" t="n"/>
-      <c r="G1075" s="2" t="n"/>
+      <c r="F1075" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1075" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 13次)</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="n"/>
@@ -30166,10 +30710,18 @@
         </is>
       </c>
       <c r="E1076" s="2" t="n"/>
-      <c r="F1076" s="4" t="n"/>
-      <c r="G1076" s="2" t="n"/>
-    </row>
-    <row r="1077">
+      <c r="F1076" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1076" s="4" t="inlineStr">
+        <is>
+          <t>导出回调接口，由导出任务异步触发，暂不覆盖(365d 13次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077" ht="80" customHeight="1">
       <c r="A1077" s="2" t="n"/>
       <c r="B1077" s="2" t="inlineStr">
         <is>
@@ -30187,10 +30739,18 @@
         </is>
       </c>
       <c r="E1077" s="2" t="n"/>
-      <c r="F1077" s="4" t="n"/>
+      <c r="F1077" s="7" t="inlineStr">
+        <is>
+          <t>无Tag过滤+不传keywordTagIds — 54.4%
+不传tagIds+按KeywordTag过滤 — 18.2%
+不传tagIds+无KeywordTag过滤 — 14.6%
+按Tag过滤+不传keywordTagIds — 11.8%
+不传tagIds+不传keywordTagIds — 1.0%</t>
+        </is>
+      </c>
       <c r="G1077" s="2" t="n"/>
     </row>
-    <row r="1078">
+    <row r="1078" ht="16" customHeight="1">
       <c r="A1078" s="2" t="n"/>
       <c r="B1078" s="2" t="inlineStr">
         <is>
@@ -30208,10 +30768,18 @@
         </is>
       </c>
       <c r="E1078" s="2" t="n"/>
-      <c r="F1078" s="4" t="n"/>
-      <c r="G1078" s="2" t="n"/>
-    </row>
-    <row r="1079">
+      <c r="F1078" s="8" t="inlineStr">
+        <is>
+          <t>疑似后端bug</t>
+        </is>
+      </c>
+      <c r="G1078" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：HTTP 500 System.InvalidOperationException "Sequence contains no elements"。复核：原始样本全部ID(含原profileIds/日期)重跑仍500；本账号profile+本账号tag作pgCampaignTagConfig仍500；仅keywordTagIds与pgCampaignTagConfig均为空数组时200(data=null)；同形态/Total接口200。后端对当前账号下无数据的Tag未做空集合保护，建议报Jira</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079" ht="16" customHeight="1">
       <c r="A1079" s="2" t="n"/>
       <c r="B1079" s="2" t="inlineStr">
         <is>
@@ -30229,10 +30797,14 @@
         </is>
       </c>
       <c r="E1079" s="2" t="n"/>
-      <c r="F1079" s="4" t="n"/>
+      <c r="F1079" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1079" s="2" t="n"/>
     </row>
-    <row r="1080">
+    <row r="1080" ht="64" customHeight="1">
       <c r="A1080" s="2" t="n"/>
       <c r="B1080" s="2" t="inlineStr">
         <is>
@@ -30250,10 +30822,17 @@
         </is>
       </c>
       <c r="E1080" s="2" t="n"/>
-      <c r="F1080" s="4" t="n"/>
+      <c r="F1080" s="7" t="inlineStr">
+        <is>
+          <t>KStype=keyword+不传campaignTagIds — 78.3%
+KStype=keyword+按CampaignTag过滤 — 8.7%
+KStype=keyword+无CampaignTag过滤 — 8.2%
+KStype=query+不传campaignTagIds — 4.8%</t>
+        </is>
+      </c>
       <c r="G1080" s="2" t="n"/>
     </row>
-    <row r="1081">
+    <row r="1081" ht="16" customHeight="1">
       <c r="A1081" s="2" t="n"/>
       <c r="B1081" s="2" t="inlineStr">
         <is>
@@ -30271,10 +30850,14 @@
         </is>
       </c>
       <c r="E1081" s="2" t="n"/>
-      <c r="F1081" s="4" t="n"/>
+      <c r="F1081" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1081" s="2" t="n"/>
     </row>
-    <row r="1082">
+    <row r="1082" ht="64" customHeight="1">
       <c r="A1082" s="2" t="n"/>
       <c r="B1082" s="2" t="inlineStr">
         <is>
@@ -30292,10 +30875,17 @@
         </is>
       </c>
       <c r="E1082" s="2" t="n"/>
-      <c r="F1082" s="4" t="n"/>
+      <c r="F1082" s="7" t="inlineStr">
+        <is>
+          <t>按KeywordTag过滤+不传  dim   — 49.8%
+无KeywordTag过滤+  dim  =ytd — 41.2%
+按KeywordTag过滤+  dim  =ytd — 5.8%
+按KeywordTag过滤+  dim  =month — 1.6%</t>
+        </is>
+      </c>
       <c r="G1082" s="2" t="n"/>
     </row>
-    <row r="1083">
+    <row r="1083" ht="80" customHeight="1">
       <c r="A1083" s="2" t="n"/>
       <c r="B1083" s="2" t="inlineStr">
         <is>
@@ -30313,10 +30903,18 @@
         </is>
       </c>
       <c r="E1083" s="2" t="n"/>
-      <c r="F1083" s="4" t="n"/>
+      <c r="F1083" s="7" t="inlineStr">
+        <is>
+          <t>无KeywordTag过滤+  dim  =ytd — 64.2%
+按KeywordTag过滤+不传  dim   — 15.6%
+按KeywordTag过滤+  dim  =ytd — 14.8%
+按KeywordTag过滤+  dim  =month — 3.6%
+无KeywordTag过滤+  dim  =date — 1.2%</t>
+        </is>
+      </c>
       <c r="G1083" s="2" t="n"/>
     </row>
-    <row r="1084">
+    <row r="1084" ht="32" customHeight="1">
       <c r="A1084" s="2" t="n"/>
       <c r="B1084" s="2" t="inlineStr">
         <is>
@@ -30334,7 +30932,12 @@
         </is>
       </c>
       <c r="E1084" s="2" t="n"/>
-      <c r="F1084" s="4" t="n"/>
+      <c r="F1084" s="7" t="inlineStr">
+        <is>
+          <t>空数组(不按CampaignTag过滤) — 53.8%
+传CampaignTagIds数组 — 46.2%</t>
+        </is>
+      </c>
       <c r="G1084" s="2" t="n"/>
     </row>
     <row r="1085">
@@ -30355,8 +30958,16 @@
         </is>
       </c>
       <c r="E1085" s="2" t="n"/>
-      <c r="F1085" s="4" t="n"/>
-      <c r="G1085" s="2" t="n"/>
+      <c r="F1085" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1085" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
@@ -33532,10 +34143,18 @@
         </is>
       </c>
       <c r="E1215" s="2" t="n"/>
-      <c r="F1215" s="4" t="n"/>
-      <c r="G1215" s="2" t="n"/>
-    </row>
-    <row r="1216">
+      <c r="F1215" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1215" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 103次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216" ht="96" customHeight="1">
       <c r="A1216" s="2" t="n"/>
       <c r="B1216" s="2" t="inlineStr">
         <is>
@@ -33553,10 +34172,19 @@
         </is>
       </c>
       <c r="E1216" s="2" t="n"/>
-      <c r="F1216" s="4" t="n"/>
+      <c r="F1216" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+profileIds=[] — 63.0%
+  dim  =ytd+profileIds=[ids+] — 26.4%
+  dim  =week+profileIds=[ids+] — 4.6%
+  dim  =month+profileIds=[ids+] — 2.8%
+  dim  =date+profileIds=[ids+] — 1.0%
+不传  dim  +profileIds=[ids+] — 1.0%</t>
+        </is>
+      </c>
       <c r="G1216" s="2" t="n"/>
     </row>
-    <row r="1217">
+    <row r="1217" ht="32" customHeight="1">
       <c r="A1217" s="2" t="n"/>
       <c r="B1217" s="2" t="inlineStr">
         <is>
@@ -33574,10 +34202,15 @@
         </is>
       </c>
       <c r="E1217" s="2" t="n"/>
-      <c r="F1217" s="4" t="n"/>
+      <c r="F1217" s="7" t="inlineStr">
+        <is>
+          <t>按天(dim=1) — 25.0%
+按周(dim=2) — 25.0%</t>
+        </is>
+      </c>
       <c r="G1217" s="2" t="n"/>
     </row>
-    <row r="1218">
+    <row r="1218" ht="16" customHeight="1">
       <c r="A1218" s="2" t="n"/>
       <c r="B1218" s="2" t="inlineStr">
         <is>
@@ -33595,10 +34228,14 @@
         </is>
       </c>
       <c r="E1218" s="2" t="n"/>
-      <c r="F1218" s="4" t="n"/>
+      <c r="F1218" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1218" s="2" t="n"/>
     </row>
-    <row r="1219">
+    <row r="1219" ht="96" customHeight="1">
       <c r="A1219" s="2" t="n"/>
       <c r="B1219" s="2" t="inlineStr">
         <is>
@@ -33616,10 +34253,19 @@
         </is>
       </c>
       <c r="E1219" s="2" t="n"/>
-      <c r="F1219" s="4" t="n"/>
+      <c r="F1219" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+profileIds=[ids+] — 41.8%
+  dim  =ytd+profileIds=[] — 41.6%
+  dim  =week+profileIds=[ids+] — 6.4%
+  dim  =month+profileIds=[ids+] — 4.6%
+  dim  =date+profileIds=[ids+] — 2.6%
+  dim  =month+profileIds=[] — 2.2%</t>
+        </is>
+      </c>
       <c r="G1219" s="2" t="n"/>
     </row>
-    <row r="1220">
+    <row r="1220" ht="16" customHeight="1">
       <c r="A1220" s="2" t="n"/>
       <c r="B1220" s="2" t="inlineStr">
         <is>
@@ -33637,7 +34283,11 @@
         </is>
       </c>
       <c r="E1220" s="2" t="n"/>
-      <c r="F1220" s="4" t="n"/>
+      <c r="F1220" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1220" s="2" t="n"/>
     </row>
     <row r="1221">
@@ -33658,8 +34308,16 @@
         </is>
       </c>
       <c r="E1221" s="2" t="n"/>
-      <c r="F1221" s="4" t="n"/>
-      <c r="G1221" s="2" t="n"/>
+      <c r="F1221" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1221" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，且为异步导出接口，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" s="2" t="n"/>
@@ -33679,10 +34337,18 @@
         </is>
       </c>
       <c r="E1222" s="2" t="n"/>
-      <c r="F1222" s="4" t="n"/>
-      <c r="G1222" s="2" t="n"/>
-    </row>
-    <row r="1223">
+      <c r="F1222" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1222" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调接口，由导出任务回调触发，无同步响应，暂不覆盖(365d 988次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223" ht="64" customHeight="1">
       <c r="A1223" s="2" t="n"/>
       <c r="B1223" s="2" t="inlineStr">
         <is>
@@ -33700,7 +34366,14 @@
         </is>
       </c>
       <c r="E1223" s="2" t="n"/>
-      <c r="F1223" s="4" t="n"/>
+      <c r="F1223" s="7" t="inlineStr">
+        <is>
+          <t>不传campaignTagIds+含startDateCompared — 35.2%
+按CampaignTag过滤+含startDateCompared — 29.0%
+不传campaignTagIds+不含startDateCompared — 24.4%
+按CampaignTag过滤+不含startDateCompared — 11.4%</t>
+        </is>
+      </c>
       <c r="G1223" s="2" t="n"/>
     </row>
     <row r="1224">
@@ -33721,8 +34394,16 @@
         </is>
       </c>
       <c r="E1224" s="2" t="n"/>
-      <c r="F1224" s="4" t="n"/>
-      <c r="G1224" s="2" t="n"/>
+      <c r="F1224" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1224" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" s="2" t="n"/>
@@ -33742,10 +34423,18 @@
         </is>
       </c>
       <c r="E1225" s="2" t="n"/>
-      <c r="F1225" s="4" t="n"/>
-      <c r="G1225" s="2" t="n"/>
-    </row>
-    <row r="1226">
+      <c r="F1225" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1225" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226" ht="64" customHeight="1">
       <c r="A1226" s="2" t="n"/>
       <c r="B1226" s="2" t="inlineStr">
         <is>
@@ -33763,7 +34452,14 @@
         </is>
       </c>
       <c r="E1226" s="2" t="n"/>
-      <c r="F1226" s="4" t="n"/>
+      <c r="F1226" s="7" t="inlineStr">
+        <is>
+          <t>不传campaignTagIds+targetingTypes=[] — 79.0%
+按CampaignTag过滤+targetingTypes=[ids+] — 10.2%
+按CampaignTag过滤+targetingTypes=[] — 7.2%
+不传campaignTagIds+targetingTypes=[ids+] — 3.6%</t>
+        </is>
+      </c>
       <c r="G1226" s="2" t="n"/>
     </row>
     <row r="1227">
@@ -33784,10 +34480,18 @@
         </is>
       </c>
       <c r="E1227" s="2" t="n"/>
-      <c r="F1227" s="4" t="n"/>
-      <c r="G1227" s="2" t="n"/>
-    </row>
-    <row r="1228">
+      <c r="F1227" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1227" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 859次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228" ht="112" customHeight="1">
       <c r="A1228" s="2" t="n"/>
       <c r="B1228" s="2" t="inlineStr">
         <is>
@@ -33805,7 +34509,17 @@
         </is>
       </c>
       <c r="E1228" s="2" t="n"/>
-      <c r="F1228" s="4" t="n"/>
+      <c r="F1228" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+不传campaignTagIds — 64.2%
+  dim  =ytd+无CampaignTag过滤 — 21.0%
+  dim  =month+不传campaignTagIds — 5.2%
+  dim  =ytd+按CampaignTag过滤 — 4.2%
+  dim  =week+不传campaignTagIds — 1.8%
+  dim  =month+无CampaignTag过滤 — 1.2%
+  dim  =date+不传campaignTagIds — 1.0%</t>
+        </is>
+      </c>
       <c r="G1228" s="2" t="n"/>
     </row>
     <row r="1229">
@@ -33826,8 +34540,16 @@
         </is>
       </c>
       <c r="E1229" s="2" t="n"/>
-      <c r="F1229" s="4" t="n"/>
-      <c r="G1229" s="2" t="n"/>
+      <c r="F1229" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1229" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1230">
       <c r="A1230" s="2" t="n"/>
@@ -33847,10 +34569,18 @@
         </is>
       </c>
       <c r="E1230" s="2" t="n"/>
-      <c r="F1230" s="4" t="n"/>
-      <c r="G1230" s="2" t="n"/>
-    </row>
-    <row r="1231">
+      <c r="F1230" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1230" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231" ht="112" customHeight="1">
       <c r="A1231" s="2" t="n"/>
       <c r="B1231" s="2" t="inlineStr">
         <is>
@@ -33868,7 +34598,17 @@
         </is>
       </c>
       <c r="E1231" s="2" t="n"/>
-      <c r="F1231" s="4" t="n"/>
+      <c r="F1231" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dim  =ytd+不传campaignTagIds — 65.2%
+  dim  =ytd+无CampaignTag过滤 — 18.2%
+  dim  =month+不传campaignTagIds — 5.2%
+  dim  =ytd+按CampaignTag过滤 — 3.4%
+  dim  =date+不传campaignTagIds — 2.8%
+  dim  =week+不传campaignTagIds — 2.0%
+  dim  =date+无CampaignTag过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1231" s="2" t="n"/>
     </row>
     <row r="1232">
@@ -36679,7 +37419,7 @@
       <c r="F1341" s="4" t="n"/>
       <c r="G1341" s="2" t="n"/>
     </row>
-    <row r="1342">
+    <row r="1342" ht="112" customHeight="1">
       <c r="A1342" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36701,10 +37441,20 @@
         </is>
       </c>
       <c r="E1342" s="2" t="n"/>
-      <c r="F1342" s="4" t="n"/>
+      <c r="F1342" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=Query-Keyword+按Campaign过滤 — 41.0%
+tabGroupBy=Query-Keyword+无Campaign过滤 — 39.6%
+tabGroupBy=Query Text+无Campaign过滤 — 6.6%
+tabGroupBy=Query-Keyword+不传campaignIds — 4.8%
+不传tabGroupBy+按Campaign过滤 — 3.0%
+tabGroupBy=Query Text+按Campaign过滤 — 2.0%
+tabGroupBy=Query-Item+无Campaign过滤 — 1.2%</t>
+        </is>
+      </c>
       <c r="G1342" s="2" t="n"/>
     </row>
-    <row r="1343">
+    <row r="1343" ht="32" customHeight="1">
       <c r="A1343" s="2" t="n"/>
       <c r="B1343" s="2" t="inlineStr">
         <is>
@@ -36722,8 +37472,17 @@
         </is>
       </c>
       <c r="E1343" s="2" t="n"/>
-      <c r="F1343" s="4" t="n"/>
-      <c r="G1343" s="2" t="n"/>
+      <c r="F1343" s="7" t="inlineStr">
+        <is>
+          <t>带filters(ClickROAS LessOrEqual) — 53.7%
+filters为空 — 46.3%</t>
+        </is>
+      </c>
+      <c r="G1343" s="4" t="inlineStr">
+        <is>
+          <t>疑似后端bug：filters 的 Value 传非数字字符串(线上样本值为邮箱 diane@pureplayecommerce.com，Field=ClickROAS Operand=LessOrEqual，41条样本中出现22次)时返回 HTTP 500 Internal Server Error，detail=「Code: 53. DB::Exception: Cannot convert string 'diane@pureplayecommerce.com'…」(ClickHouse 类型转换异常)。后端缺少参数校验，非法值直接下推数据库，建议报Jira(应返回400参数错误)。同接口 filters 为空的场景通过</t>
+        </is>
+      </c>
     </row>
     <row r="1344">
       <c r="A1344" s="2" t="n"/>
@@ -36743,8 +37502,16 @@
         </is>
       </c>
       <c r="E1344" s="2" t="n"/>
-      <c r="F1344" s="4" t="n"/>
-      <c r="G1344" s="2" t="n"/>
+      <c r="F1344" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1344" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，无同步响应，暂不覆盖(365d 2569次)</t>
+        </is>
+      </c>
     </row>
     <row r="1345">
       <c r="A1345" s="2" t="n"/>
@@ -36764,10 +37531,18 @@
         </is>
       </c>
       <c r="E1345" s="2" t="n"/>
-      <c r="F1345" s="4" t="n"/>
-      <c r="G1345" s="2" t="n"/>
-    </row>
-    <row r="1346">
+      <c r="F1345" s="4" t="inlineStr">
+        <is>
+          <t>异步导出/回调，不覆盖</t>
+        </is>
+      </c>
+      <c r="G1345" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调接口，由导出任务回调触发，无同步响应，暂不覆盖(365d 24989次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346" ht="96" customHeight="1">
       <c r="A1346" s="2" t="n"/>
       <c r="B1346" s="2" t="inlineStr">
         <is>
@@ -36785,7 +37560,16 @@
         </is>
       </c>
       <c r="E1346" s="2" t="n"/>
-      <c r="F1346" s="4" t="n"/>
+      <c r="F1346" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=Query-Keyword+isExplorer=false — 69.0%
+tabGroupBy=Query-Keyword+isExplorer=true — 17.6%
+tabGroupBy=Query Text+isExplorer=false — 6.6%
+不传tabGroupBy+不传isExplorer — 2.2%
+tabGroupBy=Query Text+isExplorer=true — 1.4%
+tabGroupBy=Query-Item+isExplorer=true — 1.0%</t>
+        </is>
+      </c>
       <c r="G1346" s="2" t="n"/>
     </row>
     <row r="1347">
@@ -36806,8 +37590,16 @@
         </is>
       </c>
       <c r="E1347" s="2" t="n"/>
-      <c r="F1347" s="4" t="n"/>
-      <c r="G1347" s="2" t="n"/>
+      <c r="F1347" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1347" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" s="2" t="n"/>
@@ -36827,10 +37619,18 @@
         </is>
       </c>
       <c r="E1348" s="2" t="n"/>
-      <c r="F1348" s="4" t="n"/>
-      <c r="G1348" s="2" t="n"/>
-    </row>
-    <row r="1349">
+      <c r="F1348" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1348" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349" ht="128" customHeight="1">
       <c r="A1349" s="2" t="n"/>
       <c r="B1349" s="2" t="inlineStr">
         <is>
@@ -36848,7 +37648,18 @@
         </is>
       </c>
       <c r="E1349" s="2" t="n"/>
-      <c r="F1349" s="4" t="n"/>
+      <c r="F1349" s="7" t="inlineStr">
+        <is>
+          <t>tabGroupBy=Query-Keyword+无Campaign过滤 — 43.6%
+tabGroupBy=Query-Keyword+按Campaign过滤 — 34.0%
+tabGroupBy=Query-Keyword+不传campaignIds — 7.0%
+tabGroupBy=Query Text+无Campaign过滤 — 4.6%
+tabGroupBy=Query Text+按Campaign过滤 — 3.4%
+不传tabGroupBy+不传campaignIds — 2.8%
+tabGroupBy=Query Text+不传campaignIds — 1.8%
+tabGroupBy=Query-Item+无Campaign过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1349" s="2" t="n"/>
     </row>
     <row r="1350">
@@ -37234,8 +38045,16 @@
         </is>
       </c>
       <c r="E1367" s="2" t="n"/>
-      <c r="F1367" s="4" t="n"/>
-      <c r="G1367" s="2" t="n"/>
+      <c r="F1367" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1367" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1368">
       <c r="A1368" s="2" t="n"/>
@@ -37255,8 +38074,16 @@
         </is>
       </c>
       <c r="E1368" s="2" t="n"/>
-      <c r="F1368" s="4" t="n"/>
-      <c r="G1368" s="2" t="n"/>
+      <c r="F1368" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1368" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1369">
       <c r="A1369" s="2" t="n"/>
@@ -37276,8 +38103,16 @@
         </is>
       </c>
       <c r="E1369" s="2" t="n"/>
-      <c r="F1369" s="4" t="n"/>
-      <c r="G1369" s="2" t="n"/>
+      <c r="F1369" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1369" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1370">
       <c r="A1370" s="2" t="inlineStr">
@@ -37578,10 +38413,18 @@
         </is>
       </c>
       <c r="E1383" s="2" t="n"/>
-      <c r="F1383" s="4" t="n"/>
-      <c r="G1383" s="2" t="n"/>
-    </row>
-    <row r="1384">
+      <c r="F1383" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1383" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖；且为异步导出类接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384" ht="48" customHeight="1">
       <c r="A1384" s="2" t="n"/>
       <c r="B1384" s="2" t="inlineStr">
         <is>
@@ -37599,10 +38442,16 @@
         </is>
       </c>
       <c r="E1384" s="2" t="n"/>
-      <c r="F1384" s="4" t="n"/>
+      <c r="F1384" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[ids+]+不含startDateCompared — 52.4%
+profileIds=[]+不含startDateCompared — 40.3%
+profileIds=[]+含startDateCompared — 4.8%</t>
+        </is>
+      </c>
       <c r="G1384" s="2" t="n"/>
     </row>
-    <row r="1385">
+    <row r="1385" ht="16" customHeight="1">
       <c r="A1385" s="2" t="n"/>
       <c r="B1385" s="2" t="inlineStr">
         <is>
@@ -37620,7 +38469,11 @@
         </is>
       </c>
       <c r="E1385" s="2" t="n"/>
-      <c r="F1385" s="4" t="n"/>
+      <c r="F1385" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1385" s="2" t="n"/>
     </row>
     <row r="1386">
@@ -37641,10 +38494,18 @@
         </is>
       </c>
       <c r="E1386" s="2" t="n"/>
-      <c r="F1386" s="4" t="n"/>
-      <c r="G1386" s="2" t="n"/>
-    </row>
-    <row r="1387">
+      <c r="F1386" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1386" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387" ht="48" customHeight="1">
       <c r="A1387" s="2" t="n"/>
       <c r="B1387" s="2" t="inlineStr">
         <is>
@@ -37662,10 +38523,16 @@
         </is>
       </c>
       <c r="E1387" s="2" t="n"/>
-      <c r="F1387" s="4" t="n"/>
+      <c r="F1387" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[ids+]+不含startDateCompared — 52.0%
+profileIds=[]+不含startDateCompared — 40.7%
+profileIds=[]+含startDateCompared — 4.9%</t>
+        </is>
+      </c>
       <c r="G1387" s="2" t="n"/>
     </row>
-    <row r="1388">
+    <row r="1388" ht="48" customHeight="1">
       <c r="A1388" s="2" t="n"/>
       <c r="B1388" s="2" t="inlineStr">
         <is>
@@ -37683,7 +38550,13 @@
         </is>
       </c>
       <c r="E1388" s="2" t="n"/>
-      <c r="F1388" s="4" t="n"/>
+      <c r="F1388" s="7" t="inlineStr">
+        <is>
+          <t>profileIds=[ids+]+不含startDateCompared — 50.0%
+profileIds=[]+不含startDateCompared — 43.9%
+profileIds=[]+含startDateCompared — 3.5%</t>
+        </is>
+      </c>
       <c r="G1388" s="2" t="n"/>
     </row>
     <row r="1389">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>92%(12执行,写操作4条未执行不计入)</t>
+          <t>94%(16执行,写操作1条未确认不计入)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -4106,14 +4106,14 @@
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】创建广告组</t>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>创建广告组(写操作·创建后暂停)</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：创建测试广告组后PATCH status=0暂停归档。无DELETE /api/AdGroups接口，已实测campaign一旦上线过则status=2(删除)会被业务拒绝，故按创建+暂停处理，不强求删除</t>
         </is>
       </c>
     </row>
@@ -4135,14 +4135,14 @@
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】更新广告组名称</t>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>更新广告组名称(写操作·自建后改名验证并暂停)</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：自建测试广告组→改名→暂停归档，避免影响历史真实命名广告组</t>
         </is>
       </c>
     </row>
@@ -4358,9 +4358,9 @@
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】执行广告组附加信息任务(用途待人工确认)</t>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>执行广告组附加信息任务</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -4527,14 +4527,14 @@
         </is>
       </c>
       <c r="E79" s="2" t="n"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】修改广告组状态</t>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>修改广告组状态(写操作·自建后切换状态还原)</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：自建广告组暂停(0)→启用(1)验证双向可行→最终暂停归档。实测status=2(删除)在campaign已上线场景下被业务拒绝</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1096,11 +1096,11 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>96%(47执行,写操作2条未执行不计入)</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -14910,14 +14910,14 @@
         </is>
       </c>
       <c r="E482" s="2" t="n"/>
-      <c r="F482" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】关注搜索词</t>
+      <c r="F482" s="7" t="inlineStr">
+        <is>
+          <t>关注搜索词(写操作·自清理)</t>
         </is>
       </c>
       <c r="G482" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：用自造无意义关键词关注后立即取消关注(合并进同一自清理case)，无独立GET列表接口核实，仅验证接口可达+互逆两步均成功</t>
         </is>
       </c>
     </row>
@@ -14946,7 +14946,7 @@
       </c>
       <c r="G483" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：作为followedKeyword关注case的清理步骤合并执行，不再单独占一条case</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -727,9 +727,19 @@
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="F7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>86%(7执行,写操作4条未确认不计入)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>43% (9/21)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5548,7 +5558,7 @@
       </c>
       <c r="G115" s="2" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" ht="16" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5570,8 +5580,16 @@
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="2" t="n"/>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>创建AdItem(写操作·验证业务校验)</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>写操作已执行(2026-09-14，2轮一致)：实测该接口对itemId做campaign商品池(item group)校验，本profile真实目录商品但不在目标campaign商品池内时优雅拒绝(200+successCount=0)，非bug；未找到可读接口查询某campaign的允许商品池，未构造出真正成功场景</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -5591,10 +5609,18 @@
         </is>
       </c>
       <c r="E117" s="2" t="n"/>
-      <c r="F117" s="4" t="n"/>
-      <c r="G117" s="2" t="n"/>
-    </row>
-    <row r="118">
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1">
       <c r="A118" s="2" t="n"/>
       <c r="B118" s="2" t="inlineStr">
         <is>
@@ -5612,10 +5638,18 @@
         </is>
       </c>
       <c r="E118" s="2" t="n"/>
-      <c r="F118" s="4" t="n"/>
-      <c r="G118" s="2" t="n"/>
-    </row>
-    <row r="119">
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>修改AdItem出价</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>【技术受限未执行】body只有ids(内部AdItem关联ID)，无profile/campaign信息；已排查ByAdgroups/byProfile/adGroupsByItemId等只读接口均不返回该ID，无法安全获取测试账号真实ids(不能猜数字ID防止误改其他客户数据)，需人工从前端UI获取真实ids后测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
       <c r="A119" s="2" t="n"/>
       <c r="B119" s="2" t="inlineStr">
         <is>
@@ -5633,8 +5667,16 @@
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="2" t="n"/>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量改出价</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：ByCondition批量操作，属高危清单，需人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -5654,8 +5696,16 @@
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="2" t="n"/>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -5675,10 +5725,18 @@
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
-      <c r="F121" s="4" t="n"/>
-      <c r="G121" s="2" t="n"/>
-    </row>
-    <row r="122">
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
       <c r="A122" s="2" t="n"/>
       <c r="B122" s="2" t="inlineStr">
         <is>
@@ -5696,8 +5754,17 @@
         </is>
       </c>
       <c r="E122" s="2" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="2" t="n"/>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>profileIds+adgroupIds对象形式
+纯数组形式(旧调用约定)</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>⚠️契约不一致(第4个同类实例):19.2%真实流量直接传adgroupId数组作为请求体根(无profileIds包裹)，被后端拒绝(HTTP 400 "Cannot deserialize JSON array into...Request")，仅对象形式{adgroupIds,profileIds}(80.6%)被接受。与Campaigns的CheckTargetROASToggling/delete、CampaignTags的tagsByCampaignIds同一模式，建议合并报Jira</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -5717,8 +5784,16 @@
         </is>
       </c>
       <c r="E123" s="2" t="n"/>
-      <c r="F123" s="4" t="n"/>
-      <c r="G123" s="2" t="n"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -5738,8 +5813,16 @@
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
-      <c r="F124" s="4" t="n"/>
-      <c r="G124" s="2" t="n"/>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -5759,8 +5842,16 @@
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
-      <c r="F125" s="4" t="n"/>
-      <c r="G125" s="2" t="n"/>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -5780,8 +5871,16 @@
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
-      <c r="F126" s="4" t="n"/>
-      <c r="G126" s="2" t="n"/>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -5801,8 +5900,16 @@
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
-      <c r="F127" s="4" t="n"/>
-      <c r="G127" s="2" t="n"/>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -5822,10 +5929,18 @@
         </is>
       </c>
       <c r="E128" s="2" t="n"/>
-      <c r="F128" s="4" t="n"/>
-      <c r="G128" s="2" t="n"/>
-    </row>
-    <row r="129">
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>路径禁用关键词，不调用</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"refresh"(2026-09-14用户新规则)，不调用；且365d 0次流量</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="32" customHeight="1">
       <c r="A129" s="2" t="n"/>
       <c r="B129" s="2" t="inlineStr">
         <is>
@@ -5843,7 +5958,12 @@
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
-      <c r="F129" s="4" t="n"/>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>默认调用(空搜索)
+按searchItemIds过滤</t>
+        </is>
+      </c>
       <c r="G129" s="2" t="n"/>
     </row>
     <row r="130">
@@ -5864,10 +5984,18 @@
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
-      <c r="F130" s="4" t="n"/>
-      <c r="G130" s="2" t="n"/>
-    </row>
-    <row r="131">
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
       <c r="A131" s="2" t="n"/>
       <c r="B131" s="2" t="inlineStr">
         <is>
@@ -5885,10 +6013,14 @@
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" s="4" t="n"/>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>默认调用</t>
+        </is>
+      </c>
       <c r="G131" s="2" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" s="2" t="n"/>
       <c r="B132" s="2" t="inlineStr">
         <is>
@@ -5906,8 +6038,16 @@
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
-      <c r="F132" s="4" t="n"/>
-      <c r="G132" s="2" t="n"/>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>修改AdItem状态</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>【技术受限未执行】原因同PATCH /api/AdItems/bid：无法通过只读接口安全获取测试账号真实的AdItem内部ID</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -5927,10 +6067,18 @@
         </is>
       </c>
       <c r="E133" s="2" t="n"/>
-      <c r="F133" s="4" t="n"/>
-      <c r="G133" s="2" t="n"/>
-    </row>
-    <row r="134">
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="16" customHeight="1">
       <c r="A134" s="2" t="n"/>
       <c r="B134" s="2" t="inlineStr">
         <is>
@@ -5948,8 +6096,16 @@
         </is>
       </c>
       <c r="E134" s="2" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="2" t="n"/>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量改状态</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：ByCondition批量操作，属高危清单，需人工评估后再决定是否执行</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -5969,10 +6125,18 @@
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
-      <c r="F135" s="4" t="n"/>
-      <c r="G135" s="2" t="n"/>
-    </row>
-    <row r="136">
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
       <c r="A136" s="2" t="n"/>
       <c r="B136" s="2" t="inlineStr">
         <is>
@@ -5990,8 +6154,16 @@
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="2" t="n"/>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>刷新商品信息(写操作·幂等安全)</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：名称含Update但实为按itemId从Walmart目录刷新商品元数据的幂等操作，不修改业务实体</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1852,16 +1852,16 @@
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="n"/>
       <c r="F49" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>91%(10执行,写操作2条未执行不计入)</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>39% (7/18)</t>
+          <t>50% (9/18)</t>
         </is>
       </c>
     </row>
@@ -31528,14 +31528,14 @@
         </is>
       </c>
       <c r="E1103" s="2" t="n"/>
-      <c r="F1103" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】创建Media(发起上传)</t>
+      <c r="F1103" s="7" t="inlineStr">
+        <is>
+          <t>上传视频素材(写操作·自清理，已用真实文件人工验证)</t>
         </is>
       </c>
       <c r="G1103" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：发起上传返回Azure Blob SAS链接。真实字节上传步骤run-cases.py框架不支持(需二进制PUT)，已用用户提供的真实mp4文件单独人工验证一次全流程成功(HTTP201上传+200 complete，mediaId 55092)。自动化case覆盖create+complete的JSON交互+DELETE清理</t>
         </is>
       </c>
     </row>
@@ -31557,9 +31557,10 @@
         </is>
       </c>
       <c r="E1104" s="2" t="n"/>
-      <c r="F1104" s="8" t="inlineStr">
-        <is>
-          <t>ES 无流量</t>
+      <c r="F1104" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%
+上传视频素材(写操作·自清理，已用真实文件人工验证)</t>
         </is>
       </c>
       <c r="G1104" s="4" t="inlineStr">
@@ -31593,7 +31594,7 @@
       </c>
       <c r="G1105" s="4" t="inlineStr">
         <is>
-          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+          <t>补充发现：Swagger里存在此DELETE接口，此前生成case时遗漏。写操作已执行并通过(2026-09-14，2轮验证)：作为上传流程自清理步骤</t>
         </is>
       </c>
     </row>
@@ -31792,7 +31793,7 @@
       </c>
       <c r="G1112" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，2轮验证)：实测即使未真正上传字节也会返回200+新mediaId(complete阶段不同步校验blob是否存在)，为避免账号残留无效记录，每次执行后立即DELETE清理</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -13992,11 +13992,9 @@
         </is>
       </c>
       <c r="E439" s="2" t="n"/>
-      <c r="F439" s="7" t="inlineStr">
-        <is>
-          <t>默认调用 — 99.4%
-创建标签→抓ID→删除(写操作·自清理)
-更新标签并绑定Campaign(写操作·自清理)</t>
+      <c r="F439" s="8" t="inlineStr">
+        <is>
+          <t>作为清理步骤(创建标签→抓ID→删除 / 更新标签并绑定Campaign 两条case内复用)</t>
         </is>
       </c>
       <c r="G439" s="4" t="inlineStr">
@@ -31557,10 +31555,9 @@
         </is>
       </c>
       <c r="E1104" s="2" t="n"/>
-      <c r="F1104" s="7" t="inlineStr">
-        <is>
-          <t>默认调用 — 100.0%
-上传视频素材(写操作·自清理，已用真实文件人工验证)</t>
+      <c r="F1104" s="8" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
         </is>
       </c>
       <c r="G1104" s="4" t="inlineStr">
@@ -31788,7 +31785,7 @@
       <c r="E1112" s="2" t="n"/>
       <c r="F1112" s="8" t="inlineStr">
         <is>
-          <t>【仅生成未执行】完成媒体上传</t>
+          <t>上传视频素材(写操作·自清理，已用真实文件人工验证)</t>
         </is>
       </c>
       <c r="G1112" s="4" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>94%(16执行,写操作1条未确认不计入)</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已执行并通过(2026-09-14，经用户确认后执行，2轮一致)：无参数调用，返回{code:200,data:""}，无报错、无可观察副作用，未发现对测试账号广告组产生负面影响</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>83%(12执行,写操作1条未确认不计入)</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -14472,12 +14472,12 @@
       <c r="E456" s="2" t="n"/>
       <c r="F456" s="7" t="inlineStr">
         <is>
-          <t>变更标签负责人</t>
+          <t>变更标签负责人(写操作·自清理)</t>
         </is>
       </c>
       <c r="G456" s="4" t="inlineStr">
         <is>
-          <t>【高风险-待确认】变更标签负责人，属不可逆操作清单，已生成case但未执行，需用户逐条确认后再跑</t>
+          <t>经用户2026-09-15确认方案(自建标签→改负责人为测试账号自己→删除)并执行，2轮全PASS</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>96%(22执行,写操作21条未执行不计入)</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
     </row>
-    <row r="340">
+    <row r="340" ht="16" customHeight="1">
       <c r="A340" s="2" t="n"/>
       <c r="B340" s="2" t="inlineStr">
         <is>
@@ -11173,9 +11173,9 @@
         </is>
       </c>
       <c r="E340" s="2" t="n"/>
-      <c r="F340" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】更新Campaign(如结束日期/竞价策略)</t>
+      <c r="F340" s="7" t="inlineStr">
+        <is>
+          <t>修改Campaign名称(测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G340" s="4" t="inlineStr">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
     </row>
-    <row r="343">
+    <row r="343" ht="16" customHeight="1">
       <c r="A343" s="2" t="n"/>
       <c r="B343" s="2" t="inlineStr">
         <is>
@@ -11260,9 +11260,9 @@
         </is>
       </c>
       <c r="E343" s="2" t="n"/>
-      <c r="F343" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】复制AdGroup(创建新AdGroup)</t>
+      <c r="F343" s="7" t="inlineStr">
+        <is>
+          <t>复制AdGroup(测试账号campaign 426321+adGroup 770991122为源)</t>
         </is>
       </c>
       <c r="G343" s="4" t="inlineStr">
@@ -11271,7 +11271,7 @@
         </is>
       </c>
     </row>
-    <row r="344">
+    <row r="344" ht="16" customHeight="1">
       <c r="A344" s="2" t="n"/>
       <c r="B344" s="2" t="inlineStr">
         <is>
@@ -11289,9 +11289,9 @@
         </is>
       </c>
       <c r="E344" s="2" t="n"/>
-      <c r="F344" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按Placement设置竞价乘数</t>
+      <c r="F344" s="7" t="inlineStr">
+        <is>
+          <t>按Placement设置竞价乘数(测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -11300,7 +11300,7 @@
         </is>
       </c>
     </row>
-    <row r="345">
+    <row r="345" ht="16" customHeight="1">
       <c r="A345" s="2" t="n"/>
       <c r="B345" s="2" t="inlineStr">
         <is>
@@ -11318,9 +11318,9 @@
         </is>
       </c>
       <c r="E345" s="2" t="n"/>
-      <c r="F345" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量设置Placement竞价乘数</t>
+      <c r="F345" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量设置Placement竞价乘数(限定测试账号campaign 426321)</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -11416,7 +11416,7 @@
         </is>
       </c>
     </row>
-    <row r="349">
+    <row r="349" ht="16" customHeight="1">
       <c r="A349" s="2" t="n"/>
       <c r="B349" s="2" t="inlineStr">
         <is>
@@ -11434,9 +11434,9 @@
         </is>
       </c>
       <c r="E349" s="2" t="n"/>
-      <c r="F349" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按Platform(Desktop/App/Mobile)设置竞价乘数</t>
+      <c r="F349" s="7" t="inlineStr">
+        <is>
+          <t>按Platform设置竞价乘数(测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr">
@@ -11445,7 +11445,7 @@
         </is>
       </c>
     </row>
-    <row r="350">
+    <row r="350" ht="16" customHeight="1">
       <c r="A350" s="2" t="n"/>
       <c r="B350" s="2" t="inlineStr">
         <is>
@@ -11463,9 +11463,9 @@
         </is>
       </c>
       <c r="E350" s="2" t="n"/>
-      <c r="F350" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量设置Platform竞价乘数</t>
+      <c r="F350" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量设置Platform竞价乘数(限定测试账号campaign 426321)</t>
         </is>
       </c>
       <c r="G350" s="4" t="inlineStr">
@@ -11503,7 +11503,7 @@
         </is>
       </c>
     </row>
-    <row r="352">
+    <row r="352" ht="16" customHeight="1">
       <c r="A352" s="2" t="n"/>
       <c r="B352" s="2" t="inlineStr">
         <is>
@@ -11521,18 +11521,18 @@
         </is>
       </c>
       <c r="E352" s="2" t="n"/>
-      <c r="F352" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量修改日预算</t>
+      <c r="F352" s="7" t="inlineStr">
+        <is>
+          <t>批量修改日预算(测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G352" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
+          <t>2026-09-15发现同status接口同根因的bug：HTTP 500(ClickHouse同步SQL语法错误position 41)，与bulkDailyBudgetByCondition(条件版本，多数情况下正常)形成对比，疑似"直接"版本的ClickHouse同步代码路径有缺陷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="16" customHeight="1">
       <c r="A353" s="2" t="n"/>
       <c r="B353" s="2" t="inlineStr">
         <is>
@@ -11550,18 +11550,18 @@
         </is>
       </c>
       <c r="E353" s="2" t="n"/>
-      <c r="F353" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量修改日预算</t>
+      <c r="F353" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量修改日预算(限定测试账号campaign 426321)</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
+          <t>2026-09-15观察到间歇性500(与status/bulkDailyBudget同一ClickHouse同步bug特征)，多轮测试中偶发，怀疑与直接版本共享同一有缺陷的同步代码路径，只是触发不稳定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="16" customHeight="1">
       <c r="A354" s="2" t="n"/>
       <c r="B354" s="2" t="inlineStr">
         <is>
@@ -11579,9 +11579,9 @@
         </is>
       </c>
       <c r="E354" s="2" t="n"/>
-      <c r="F354" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量修改结束日期</t>
+      <c r="F354" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量修改结束日期(限定测试账号campaign 426321，未来日期)</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -11909,7 +11909,7 @@
         </is>
       </c>
     </row>
-    <row r="367">
+    <row r="367" ht="16" customHeight="1">
       <c r="A367" s="2" t="n"/>
       <c r="B367" s="2" t="inlineStr">
         <is>
@@ -11927,9 +11927,9 @@
         </is>
       </c>
       <c r="E367" s="2" t="n"/>
-      <c r="F367" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】上传Bulk批量操作文件</t>
+      <c r="F367" s="7" t="inlineStr">
+        <is>
+          <t>上传Bulk批量操作文件</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -11938,7 +11938,7 @@
         </is>
       </c>
     </row>
-    <row r="368">
+    <row r="368" ht="16" customHeight="1">
       <c r="A368" s="2" t="n"/>
       <c r="B368" s="2" t="inlineStr">
         <is>
@@ -11956,18 +11956,18 @@
         </is>
       </c>
       <c r="E368" s="2" t="n"/>
-      <c r="F368" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量修改总预算</t>
+      <c r="F368" s="7" t="inlineStr">
+        <is>
+          <t>批量修改总预算(测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G368" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
+          <t>2026-09-15发现同status接口同根因的bug：HTTP 500(ClickHouse同步SQL语法错误position 41)，与bulkTotalBudgetByCondition(条件版本，多数情况下正常)形成对比，疑似"直接"版本的ClickHouse同步代码路径有缺陷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="16" customHeight="1">
       <c r="A369" s="2" t="n"/>
       <c r="B369" s="2" t="inlineStr">
         <is>
@@ -11985,9 +11985,9 @@
         </is>
       </c>
       <c r="E369" s="2" t="n"/>
-      <c r="F369" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量修改总预算</t>
+      <c r="F369" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量修改总预算(限定测试账号campaign 426321)</t>
         </is>
       </c>
       <c r="G369" s="4" t="inlineStr">
@@ -11996,7 +11996,7 @@
         </is>
       </c>
     </row>
-    <row r="370">
+    <row r="370" ht="16" customHeight="1">
       <c r="A370" s="2" t="n"/>
       <c r="B370" s="2" t="inlineStr">
         <is>
@@ -12014,9 +12014,9 @@
         </is>
       </c>
       <c r="E370" s="2" t="n"/>
-      <c r="F370" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】复制Campaign(创建新Campaign)</t>
+      <c r="F370" s="7" t="inlineStr">
+        <is>
+          <t>复制Campaign(测试账号campaign 426321为源)</t>
         </is>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -12083,7 +12083,7 @@
         </is>
       </c>
     </row>
-    <row r="373">
+    <row r="373" ht="16" customHeight="1">
       <c r="A373" s="2" t="n"/>
       <c r="B373" s="2" t="inlineStr">
         <is>
@@ -12101,9 +12101,9 @@
         </is>
       </c>
       <c r="E373" s="2" t="n"/>
-      <c r="F373" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】设置Campaign的Placement投放开关</t>
+      <c r="F373" s="7" t="inlineStr">
+        <is>
+          <t>设置Placement投放开关(测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G373" s="4" t="inlineStr">
@@ -12170,7 +12170,7 @@
         </is>
       </c>
     </row>
-    <row r="376">
+    <row r="376" ht="16" customHeight="1">
       <c r="A376" s="2" t="n"/>
       <c r="B376" s="2" t="inlineStr">
         <is>
@@ -12188,9 +12188,9 @@
         </is>
       </c>
       <c r="E376" s="2" t="n"/>
-      <c r="F376" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】Campaign创建向导(批量创建Campaign+AdGroup)</t>
+      <c r="F376" s="7" t="inlineStr">
+        <is>
+          <t>Campaign创建向导(测试账号自建目录商品，接受少量残留)</t>
         </is>
       </c>
       <c r="G376" s="4" t="inlineStr">
@@ -12301,14 +12301,14 @@
         </is>
       </c>
       <c r="E380" s="2" t="n"/>
-      <c r="F380" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】设置账号级自定义关键词类型</t>
+      <c r="F380" s="7" t="inlineStr">
+        <is>
+          <t>设置账号级自定义关键词类型(读-改-还原)</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-15多轮测试发现该账号级配置会被意外重置为["KW"]而非保持还原后的[]，profile 16274451是团队共享沙盒账号(总campaign数6177，非独占)，怀疑是其他并发自动化在使用同一账号级配置，非本case逻辑缺陷。</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
         </is>
       </c>
     </row>
-    <row r="383">
+    <row r="383" ht="32" customHeight="1">
       <c r="A383" s="2" t="n"/>
       <c r="B383" s="2" t="inlineStr">
         <is>
@@ -12384,9 +12384,10 @@
         </is>
       </c>
       <c r="E383" s="2" t="n"/>
-      <c r="F383" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量删除(归档)Campaign</t>
+      <c r="F383" s="7" t="inlineStr">
+        <is>
+          <t>创建测试Campaign后删除(归档)(自建自清理)
+创建新Campaign(测试账号profile 16274451，创建后归档自清理)</t>
         </is>
       </c>
       <c r="G383" s="4" t="inlineStr">
@@ -12674,7 +12675,7 @@
         </is>
       </c>
     </row>
-    <row r="394">
+    <row r="394" ht="16" customHeight="1">
       <c r="A394" s="2" t="n"/>
       <c r="B394" s="2" t="inlineStr">
         <is>
@@ -12692,18 +12693,18 @@
         </is>
       </c>
       <c r="E394" s="2" t="n"/>
-      <c r="F394" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量修改Campaign状态(0/1，真实取值)</t>
+      <c r="F394" s="7" t="inlineStr">
+        <is>
+          <t>批量修改Campaign状态(测试账号campaign 426321)</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
+          <t>2026-09-15发现严重bug：HTTP层返回500(ClickHouse同步SQL语法错误position 41)，但业务状态其实已生效(经实测确认status=2→Paused真实写入成功)——调用方无法通过返回值判断是否真的执行了。因这个假象，误将测试campaign 426323的status=0(实际含义Deleted非Paused)执行成功导致其被永久删除且无法恢复，已改用426321且更正了status枚举认知(0=Deleted,1=疑似Enabled,2=Paused已验证)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="16" customHeight="1">
       <c r="A395" s="2" t="n"/>
       <c r="B395" s="2" t="inlineStr">
         <is>
@@ -12721,14 +12722,14 @@
         </is>
       </c>
       <c r="E395" s="2" t="n"/>
-      <c r="F395" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量修改状态</t>
+      <c r="F395" s="7" t="inlineStr">
+        <is>
+          <t>按条件批量修改状态(限定测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G395" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-15观察到间歇性500(与status同一ClickHouse同步bug特征)，多轮测试中偶发。</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12820,7 @@
         </is>
       </c>
     </row>
-    <row r="399">
+    <row r="399" ht="16" customHeight="1">
       <c r="A399" s="2" t="n"/>
       <c r="B399" s="2" t="inlineStr">
         <is>
@@ -12837,14 +12838,14 @@
         </is>
       </c>
       <c r="E399" s="2" t="n"/>
-      <c r="F399" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】设置Target ROAS/ACOS目标</t>
+      <c r="F399" s="7" t="inlineStr">
+        <is>
+          <t>设置Target ACOS/ROAS(测试账号campaign 426321，改后还原)</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-15发现同status接口同根因的bug：HTTP 500(ClickHouse同步SQL语法错误position 41)。</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1354,11 +1354,11 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>78%(29执行,写操作9条未执行不计入)</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="G825" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-15发现创建响应体字段是adGroupID(大写ID非adGroupId)，且campaign级已配预算时ad group级不能再设预算(405)，已修正。⚠️无DELETE接口，name一旦用过永久占用，同名重跑会405"already exists"，非bug，重跑需换新name。</t>
         </is>
       </c>
     </row>
@@ -24356,9 +24356,9 @@
         </is>
       </c>
       <c r="E826" s="2" t="n"/>
-      <c r="F826" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】更新广告组设置</t>
+      <c r="F826" s="7" t="inlineStr">
+        <is>
+          <t>更新广告组设置(自建后改+核实原值还原)</t>
         </is>
       </c>
       <c r="G826" s="4" t="inlineStr">
@@ -24528,9 +24528,9 @@
         </is>
       </c>
       <c r="E832" s="2" t="n"/>
-      <c r="F832" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量设置BaseBid</t>
+      <c r="F832" s="7" t="inlineStr">
+        <is>
+          <t>批量设置BaseBid(自建adGroup+还原)</t>
         </is>
       </c>
       <c r="G832" s="4" t="inlineStr">
@@ -24557,9 +24557,9 @@
         </is>
       </c>
       <c r="E833" s="2" t="n"/>
-      <c r="F833" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量设置MaxBid</t>
+      <c r="F833" s="7" t="inlineStr">
+        <is>
+          <t>批量设置MaxBid(自建adGroup+还原)</t>
         </is>
       </c>
       <c r="G833" s="4" t="inlineStr">
@@ -24669,9 +24669,9 @@
         </is>
       </c>
       <c r="E837" s="2" t="n"/>
-      <c r="F837" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】删除创意关联(不可逆)</t>
+      <c r="F837" s="7" t="inlineStr">
+        <is>
+          <t>关联创意到广告组→更新跟踪URL→解除关联(完整链路)</t>
         </is>
       </c>
       <c r="G837" s="4" t="inlineStr">
@@ -24709,7 +24709,7 @@
         </is>
       </c>
     </row>
-    <row r="839" ht="32" customHeight="1">
+    <row r="839" ht="48" customHeight="1">
       <c r="A839" s="2" t="n"/>
       <c r="B839" s="2" t="inlineStr">
         <is>
@@ -24730,7 +24730,8 @@
       <c r="F839" s="7" t="inlineStr">
         <is>
           <t>action=1(暂停) — 40.0%
-action=0(启用) — 60.0%</t>
+action=0(启用) — 60.0%
+创建广告组(创建后暂停)</t>
         </is>
       </c>
       <c r="G839" s="2" t="n"/>
@@ -24778,9 +24779,9 @@
         </is>
       </c>
       <c r="E841" s="2" t="n"/>
-      <c r="F841" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】新建预测方案(无对应删除接口)</t>
+      <c r="F841" s="7" t="inlineStr">
+        <is>
+          <t>新建预测方案(接受少量残留)</t>
         </is>
       </c>
       <c r="G841" s="4" t="inlineStr">
@@ -25078,14 +25079,14 @@
         </is>
       </c>
       <c r="E852" s="2" t="n"/>
-      <c r="F852" s="8" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】应用建议定向(覆盖当前定向配置)</t>
+      <c r="F852" s="7" t="inlineStr">
+        <is>
+          <t>应用建议定向(自建并暂停的测试广告组)</t>
         </is>
       </c>
       <c r="G852" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-15创建+暂停广告组两步已实测成功，但第3步查询TargetingGuidance/Suggested对新建广告组稳定500(与本模块已知TargetingGuidance系列NullReferenceException同一缺陷)，导致拿不到真实建议定向id，第3/4步暂时无法自动跑通，需等后端修复。</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>86%(7执行,写操作4条未确认不计入)</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -5669,7 +5669,7 @@
       <c r="E119" s="2" t="n"/>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>按条件批量改出价</t>
+          <t>按条件批量改出价(限定测试账号campaign+adGroup)</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -6098,7 +6098,7 @@
       <c r="E134" s="2" t="n"/>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>按条件批量改状态</t>
+          <t>按条件批量改状态(限定测试账号campaign+adGroup)</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1235,9 +1235,19 @@
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="F26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>47% (18/38)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -17012,7 +17022,11 @@
       </c>
       <c r="E565" s="2" t="n"/>
       <c r="F565" s="4" t="n"/>
-      <c r="G565" s="2" t="n"/>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15发现真实后端bug：稳定复现HTTP 500(NullReferenceException)，无法创建成功。ES 365天0次真实调用，疑似前端已弃用此通用CRUD入口(实际走campaignPerformance专用入口)，建议确认是否为遗留死代码。</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n"/>
@@ -17054,9 +17068,13 @@
       </c>
       <c r="E567" s="2" t="n"/>
       <c r="F567" s="4" t="n"/>
-      <c r="G567" s="2" t="n"/>
-    </row>
-    <row r="568">
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>依赖的POST /Report/custom创建接口有真实bug(500)，本接口无法测试，阻塞状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="64" customHeight="1">
       <c r="A568" s="2" t="n"/>
       <c r="B568" s="2" t="inlineStr">
         <is>
@@ -17074,8 +17092,19 @@
         </is>
       </c>
       <c r="E568" s="2" t="n"/>
-      <c r="F568" s="4" t="n"/>
-      <c r="G568" s="2" t="n"/>
+      <c r="F568" s="7" t="inlineStr">
+        <is>
+          <t>创建基础自定义报表
+更新自定义报表
+删除自定义报表
+切换报表启用状态</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>依赖的POST /Report/custom创建接口有真实bug(500)，本接口无法测试，阻塞状态。</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n"/>
@@ -17096,9 +17125,13 @@
       </c>
       <c r="E569" s="2" t="n"/>
       <c r="F569" s="4" t="n"/>
-      <c r="G569" s="2" t="n"/>
-    </row>
-    <row r="570">
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>依赖的POST /Report/custom创建接口有真实bug(500)，本接口无法测试，阻塞状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="16" customHeight="1">
       <c r="A570" s="2" t="n"/>
       <c r="B570" s="2" t="inlineStr">
         <is>
@@ -17116,10 +17149,18 @@
         </is>
       </c>
       <c r="E570" s="2" t="n"/>
-      <c r="F570" s="4" t="n"/>
-      <c r="G570" s="2" t="n"/>
-    </row>
-    <row r="571">
+      <c r="F570" s="7" t="inlineStr">
+        <is>
+          <t>创建Campaign Performance报表(含后置清理)</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15发现疑似限流/并发缺陷：同一批次中若非当次第一次调用，稳定复现500(NullReferenceException)。单独调用可成功，连续调用会失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="16" customHeight="1">
       <c r="A571" s="2" t="n"/>
       <c r="B571" s="2" t="inlineStr">
         <is>
@@ -17137,10 +17178,18 @@
         </is>
       </c>
       <c r="E571" s="2" t="n"/>
-      <c r="F571" s="4" t="n"/>
-      <c r="G571" s="2" t="n"/>
-    </row>
-    <row r="572">
+      <c r="F571" s="7" t="inlineStr">
+        <is>
+          <t>更新Campaign Performance报表(含后置清理)</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>受POST campaignPerformance限流缺陷影响(同批次非首次调用500)，非本接口自身问题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="16" customHeight="1">
       <c r="A572" s="2" t="n"/>
       <c r="B572" s="2" t="inlineStr">
         <is>
@@ -17158,10 +17207,18 @@
         </is>
       </c>
       <c r="E572" s="2" t="n"/>
-      <c r="F572" s="4" t="n"/>
-      <c r="G572" s="2" t="n"/>
-    </row>
-    <row r="573">
+      <c r="F572" s="7" t="inlineStr">
+        <is>
+          <t>删除Campaign Performance报表</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>受POST campaignPerformance限流缺陷影响(同批次非首次调用500)，非本接口自身问题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="16" customHeight="1">
       <c r="A573" s="2" t="n"/>
       <c r="B573" s="2" t="inlineStr">
         <is>
@@ -17179,8 +17236,16 @@
         </is>
       </c>
       <c r="E573" s="2" t="n"/>
-      <c r="F573" s="4" t="n"/>
-      <c r="G573" s="2" t="n"/>
+      <c r="F573" s="7" t="inlineStr">
+        <is>
+          <t>变更报表负责人(自转自·无实质转移·自清理)</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>受POST campaignPerformance限流缺陷影响(同批次非首次调用500)，非本接口自身问题；已按用户方案设计为自转自无实质转移。</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n"/>
@@ -17266,7 +17331,7 @@
       <c r="F577" s="4" t="n"/>
       <c r="G577" s="2" t="n"/>
     </row>
-    <row r="578">
+    <row r="578" ht="16" customHeight="1">
       <c r="A578" s="2" t="n"/>
       <c r="B578" s="2" t="inlineStr">
         <is>
@@ -17284,7 +17349,11 @@
         </is>
       </c>
       <c r="E578" s="2" t="n"/>
-      <c r="F578" s="4" t="n"/>
+      <c r="F578" s="7" t="inlineStr">
+        <is>
+          <t>type=30(疑似契约不一致,预期FAIL) — 100%</t>
+        </is>
+      </c>
       <c r="G578" s="2" t="n"/>
     </row>
     <row r="579">
@@ -17329,7 +17398,7 @@
       <c r="F580" s="4" t="n"/>
       <c r="G580" s="2" t="n"/>
     </row>
-    <row r="581">
+    <row r="581" ht="16" customHeight="1">
       <c r="A581" s="2" t="n"/>
       <c r="B581" s="2" t="inlineStr">
         <is>
@@ -17347,7 +17416,11 @@
         </is>
       </c>
       <c r="E581" s="2" t="n"/>
-      <c r="F581" s="4" t="n"/>
+      <c r="F581" s="7" t="inlineStr">
+        <is>
+          <t>按userId查询 — 99.0%</t>
+        </is>
+      </c>
       <c r="G581" s="2" t="n"/>
     </row>
     <row r="582">
@@ -17392,7 +17465,7 @@
       <c r="F583" s="4" t="n"/>
       <c r="G583" s="2" t="n"/>
     </row>
-    <row r="584">
+    <row r="584" ht="16" customHeight="1">
       <c r="A584" s="2" t="n"/>
       <c r="B584" s="2" t="inlineStr">
         <is>
@@ -17410,10 +17483,14 @@
         </is>
       </c>
       <c r="E584" s="2" t="n"/>
-      <c r="F584" s="4" t="n"/>
+      <c r="F584" s="7" t="inlineStr">
+        <is>
+          <t>按reportId查询 — 100%</t>
+        </is>
+      </c>
       <c r="G584" s="2" t="n"/>
     </row>
-    <row r="585">
+    <row r="585" ht="16" customHeight="1">
       <c r="A585" s="2" t="n"/>
       <c r="B585" s="2" t="inlineStr">
         <is>
@@ -17431,10 +17508,14 @@
         </is>
       </c>
       <c r="E585" s="2" t="n"/>
-      <c r="F585" s="4" t="n"/>
+      <c r="F585" s="7" t="inlineStr">
+        <is>
+          <t>isExport=true+historyId — 100%</t>
+        </is>
+      </c>
       <c r="G585" s="2" t="n"/>
     </row>
-    <row r="586">
+    <row r="586" ht="32" customHeight="1">
       <c r="A586" s="2" t="n"/>
       <c r="B586" s="2" t="inlineStr">
         <is>
@@ -17452,7 +17533,12 @@
         </is>
       </c>
       <c r="E586" s="2" t="n"/>
-      <c r="F586" s="4" t="n"/>
+      <c r="F586" s="7" t="inlineStr">
+        <is>
+          <t>仅historyId(不含SOV维度) — 52.7%
+historyId+sovDataLevel(疑似后端bug,预期FAIL) — 47.3%</t>
+        </is>
+      </c>
       <c r="G586" s="2" t="n"/>
     </row>
     <row r="587">
@@ -17497,7 +17583,7 @@
       <c r="F588" s="4" t="n"/>
       <c r="G588" s="2" t="n"/>
     </row>
-    <row r="589">
+    <row r="589" ht="64" customHeight="1">
       <c r="A589" s="2" t="n"/>
       <c r="B589" s="2" t="inlineStr">
         <is>
@@ -17515,7 +17601,14 @@
         </is>
       </c>
       <c r="E589" s="2" t="n"/>
-      <c r="F589" s="4" t="n"/>
+      <c r="F589" s="7" t="inlineStr">
+        <is>
+          <t>无campaignIds+无customDays — 54.4%
+含campaignIds+customDays — 22.2%
+含campaignIds+无customDays — 12.2%
+无campaignIds+含customDays — 11.2%</t>
+        </is>
+      </c>
       <c r="G589" s="2" t="n"/>
     </row>
     <row r="590">
@@ -17560,7 +17653,7 @@
       <c r="F591" s="4" t="n"/>
       <c r="G591" s="2" t="n"/>
     </row>
-    <row r="592">
+    <row r="592" ht="32" customHeight="1">
       <c r="A592" s="2" t="n"/>
       <c r="B592" s="2" t="inlineStr">
         <is>
@@ -17578,10 +17671,15 @@
         </is>
       </c>
       <c r="E592" s="2" t="n"/>
-      <c r="F592" s="4" t="n"/>
+      <c r="F592" s="7" t="inlineStr">
+        <is>
+          <t>SOV报表(reportType=10)+sendToMode=1 — 18.8%
+非SOV报表(reportType=0)+不传sendToMode — 6.2%</t>
+        </is>
+      </c>
       <c r="G592" s="2" t="n"/>
     </row>
-    <row r="593">
+    <row r="593" ht="32" customHeight="1">
       <c r="A593" s="2" t="n"/>
       <c r="B593" s="2" t="inlineStr">
         <is>
@@ -17599,10 +17697,15 @@
         </is>
       </c>
       <c r="E593" s="2" t="n"/>
-      <c r="F593" s="4" t="n"/>
+      <c r="F593" s="7" t="inlineStr">
+        <is>
+          <t>仅id(不含SOV维度) — 71.8%
+id+sovDataLevel — 28.2%</t>
+        </is>
+      </c>
       <c r="G593" s="2" t="n"/>
     </row>
-    <row r="594">
+    <row r="594" ht="16" customHeight="1">
       <c r="A594" s="2" t="n"/>
       <c r="B594" s="2" t="inlineStr">
         <is>
@@ -17620,7 +17723,11 @@
         </is>
       </c>
       <c r="E594" s="2" t="n"/>
-      <c r="F594" s="4" t="n"/>
+      <c r="F594" s="7" t="inlineStr">
+        <is>
+          <t>按userId过滤报表列表 — 100%</t>
+        </is>
+      </c>
       <c r="G594" s="2" t="n"/>
     </row>
     <row r="595">
@@ -17728,7 +17835,7 @@
       <c r="F599" s="4" t="n"/>
       <c r="G599" s="2" t="n"/>
     </row>
-    <row r="600">
+    <row r="600" ht="16" customHeight="1">
       <c r="A600" s="2" t="n"/>
       <c r="B600" s="2" t="inlineStr">
         <is>
@@ -17746,8 +17853,16 @@
         </is>
       </c>
       <c r="E600" s="2" t="n"/>
-      <c r="F600" s="4" t="n"/>
-      <c r="G600" s="2" t="n"/>
+      <c r="F600" s="7" t="inlineStr">
+        <is>
+          <t>设置用户可访问报表(含后置清理)</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>受POST campaignPerformance限流缺陷影响(同批次非首次调用500)，非本接口自身问题；已按用户方案限定自建报表+测试账号自身userId。</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n"/>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1807,9 +1807,19 @@
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
+      <c r="F47" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>75% (12/16)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -31256,7 +31266,7 @@
         </is>
       </c>
     </row>
-    <row r="1086">
+    <row r="1086" ht="16" customHeight="1">
       <c r="A1086" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31278,10 +31288,14 @@
         </is>
       </c>
       <c r="E1086" s="2" t="n"/>
-      <c r="F1086" s="4" t="n"/>
+      <c r="F1086" s="7" t="inlineStr">
+        <is>
+          <t>获取全部KeywordTag树 — 100%</t>
+        </is>
+      </c>
       <c r="G1086" s="2" t="n"/>
     </row>
-    <row r="1087">
+    <row r="1087" ht="16" customHeight="1">
       <c r="A1087" s="2" t="n"/>
       <c r="B1087" s="2" t="inlineStr">
         <is>
@@ -31299,10 +31313,14 @@
         </is>
       </c>
       <c r="E1087" s="2" t="n"/>
-      <c r="F1087" s="4" t="n"/>
+      <c r="F1087" s="7" t="inlineStr">
+        <is>
+          <t>创建根Tag(自清理) — 100%</t>
+        </is>
+      </c>
       <c r="G1087" s="2" t="n"/>
     </row>
-    <row r="1088">
+    <row r="1088" ht="16" customHeight="1">
       <c r="A1088" s="2" t="n"/>
       <c r="B1088" s="2" t="inlineStr">
         <is>
@@ -31320,7 +31338,11 @@
         </is>
       </c>
       <c r="E1088" s="2" t="n"/>
-      <c r="F1088" s="4" t="n"/>
+      <c r="F1088" s="7" t="inlineStr">
+        <is>
+          <t>修改Tag名称(改名后还原+自清理) — 100%</t>
+        </is>
+      </c>
       <c r="G1088" s="2" t="n"/>
     </row>
     <row r="1089">
@@ -31341,8 +31363,16 @@
         </is>
       </c>
       <c r="E1089" s="2" t="n"/>
-      <c r="F1089" s="4" t="n"/>
-      <c r="G1089" s="2" t="n"/>
+      <c r="F1089" s="4" t="inlineStr">
+        <is>
+          <t>作为清理步骤复用，见POST创建/PUT改名/POST Keywords/POST BulkTagsWithKeywords等case</t>
+        </is>
+      </c>
+      <c r="G1089" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为其余5条写case(创建根Tag/改名/按KeywordId打Tag/BulkTagsWithKeywords×2)的清理步骤复用，已随这些case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" s="2" t="n"/>
@@ -31362,8 +31392,16 @@
         </is>
       </c>
       <c r="E1090" s="2" t="n"/>
-      <c r="F1090" s="4" t="n"/>
-      <c r="G1090" s="2" t="n"/>
+      <c r="F1090" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1090" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" s="2" t="n"/>
@@ -31383,10 +31421,18 @@
         </is>
       </c>
       <c r="E1091" s="2" t="n"/>
-      <c r="F1091" s="4" t="n"/>
-      <c r="G1091" s="2" t="n"/>
-    </row>
-    <row r="1092">
+      <c r="F1091" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1091" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092" ht="16" customHeight="1">
       <c r="A1092" s="2" t="n"/>
       <c r="B1092" s="2" t="inlineStr">
         <is>
@@ -31404,10 +31450,14 @@
         </is>
       </c>
       <c r="E1092" s="2" t="n"/>
-      <c r="F1092" s="4" t="n"/>
+      <c r="F1092" s="7" t="inlineStr">
+        <is>
+          <t>批量删除Tag(自建2条自清理) — 100%</t>
+        </is>
+      </c>
       <c r="G1092" s="2" t="n"/>
     </row>
-    <row r="1093">
+    <row r="1093" ht="32" customHeight="1">
       <c r="A1093" s="2" t="n"/>
       <c r="B1093" s="2" t="inlineStr">
         <is>
@@ -31425,10 +31475,15 @@
         </is>
       </c>
       <c r="E1093" s="2" t="n"/>
-      <c r="F1093" s="4" t="n"/>
+      <c r="F1093" s="7" t="inlineStr">
+        <is>
+          <t>按KeywordText批量打Tag(isQuery=false,自清理) — 55.6%
+按SearchTerm批量打Tag(isQuery=true,自清理) — 55.6%</t>
+        </is>
+      </c>
       <c r="G1093" s="2" t="n"/>
     </row>
-    <row r="1094">
+    <row r="1094" ht="16" customHeight="1">
       <c r="A1094" s="2" t="n"/>
       <c r="B1094" s="2" t="inlineStr">
         <is>
@@ -31446,7 +31501,11 @@
         </is>
       </c>
       <c r="E1094" s="2" t="n"/>
-      <c r="F1094" s="4" t="n"/>
+      <c r="F1094" s="7" t="inlineStr">
+        <is>
+          <t>按KeywordId打Tag(自清理) — 69%</t>
+        </is>
+      </c>
       <c r="G1094" s="2" t="n"/>
     </row>
     <row r="1095">
@@ -31467,8 +31526,16 @@
         </is>
       </c>
       <c r="E1095" s="2" t="n"/>
-      <c r="F1095" s="4" t="n"/>
-      <c r="G1095" s="2" t="n"/>
+      <c r="F1095" s="4" t="inlineStr">
+        <is>
+          <t>作为detach逆操作步骤复用，见POST Keywords/POST BulkTagsWithKeywords(isQuery=false)case</t>
+        </is>
+      </c>
+      <c r="G1095" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST /api/KeywordTags/Keywords(按KeywordId打Tag)和POST BulkTagsWithKeywords(isQuery=false按KeywordText打Tag)两条写case的逆操作(detach)步骤复用，已随这些case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" s="2" t="n"/>
@@ -31488,8 +31555,16 @@
         </is>
       </c>
       <c r="E1096" s="2" t="n"/>
-      <c r="F1096" s="4" t="n"/>
-      <c r="G1096" s="2" t="n"/>
+      <c r="F1096" s="4" t="inlineStr">
+        <is>
+          <t>作为detach逆操作步骤复用，见POST BulkTagsWithKeywords(isQuery=true)case</t>
+        </is>
+      </c>
+      <c r="G1096" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST BulkTagsWithKeywords(isQuery=true按SearchTerm打Tag)写case的逆操作(detach)步骤复用，已随该case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" s="2" t="n"/>
@@ -31509,10 +31584,18 @@
         </is>
       </c>
       <c r="E1097" s="2" t="n"/>
-      <c r="F1097" s="4" t="n"/>
-      <c r="G1097" s="2" t="n"/>
-    </row>
-    <row r="1098">
+      <c r="F1097" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1097" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098" ht="16" customHeight="1">
       <c r="A1098" s="2" t="n"/>
       <c r="B1098" s="2" t="inlineStr">
         <is>
@@ -31530,10 +31613,14 @@
         </is>
       </c>
       <c r="E1098" s="2" t="n"/>
-      <c r="F1098" s="4" t="n"/>
+      <c r="F1098" s="7" t="inlineStr">
+        <is>
+          <t>按KeywordId批量查Tag — 100%</t>
+        </is>
+      </c>
       <c r="G1098" s="2" t="n"/>
     </row>
-    <row r="1099">
+    <row r="1099" ht="16" customHeight="1">
       <c r="A1099" s="2" t="n"/>
       <c r="B1099" s="2" t="inlineStr">
         <is>
@@ -31551,10 +31638,14 @@
         </is>
       </c>
       <c r="E1099" s="2" t="n"/>
-      <c r="F1099" s="4" t="n"/>
+      <c r="F1099" s="7" t="inlineStr">
+        <is>
+          <t>按KeywordText批量查Tag — 100%</t>
+        </is>
+      </c>
       <c r="G1099" s="2" t="n"/>
     </row>
-    <row r="1100">
+    <row r="1100" ht="16" customHeight="1">
       <c r="A1100" s="2" t="n"/>
       <c r="B1100" s="2" t="inlineStr">
         <is>
@@ -31572,7 +31663,11 @@
         </is>
       </c>
       <c r="E1100" s="2" t="n"/>
-      <c r="F1100" s="4" t="n"/>
+      <c r="F1100" s="7" t="inlineStr">
+        <is>
+          <t>按SearchTerm批量查Tag — 100%</t>
+        </is>
+      </c>
       <c r="G1100" s="2" t="n"/>
     </row>
     <row r="1101">
@@ -31593,8 +31688,16 @@
         </is>
       </c>
       <c r="E1101" s="2" t="n"/>
-      <c r="F1101" s="4" t="n"/>
-      <c r="G1101" s="2" t="n"/>
+      <c r="F1101" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1101" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1102" ht="16" customHeight="1">
       <c r="A1102" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1699,9 +1699,19 @@
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
+      <c r="F43" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>62% (8/13)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -29020,7 +29030,7 @@
       </c>
       <c r="G1000" s="2" t="n"/>
     </row>
-    <row r="1001">
+    <row r="1001" ht="16" customHeight="1">
       <c r="A1001" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29042,10 +29052,14 @@
         </is>
       </c>
       <c r="E1001" s="2" t="n"/>
-      <c r="F1001" s="4" t="n"/>
+      <c r="F1001" s="7" t="inlineStr">
+        <is>
+          <t>获取全部ItemTag树 — 100%</t>
+        </is>
+      </c>
       <c r="G1001" s="2" t="n"/>
     </row>
-    <row r="1002">
+    <row r="1002" ht="16" customHeight="1">
       <c r="A1002" s="2" t="n"/>
       <c r="B1002" s="2" t="inlineStr">
         <is>
@@ -29063,10 +29077,14 @@
         </is>
       </c>
       <c r="E1002" s="2" t="n"/>
-      <c r="F1002" s="4" t="n"/>
+      <c r="F1002" s="7" t="inlineStr">
+        <is>
+          <t>创建根Tag(自清理) — 100%</t>
+        </is>
+      </c>
       <c r="G1002" s="2" t="n"/>
     </row>
-    <row r="1003">
+    <row r="1003" ht="16" customHeight="1">
       <c r="A1003" s="2" t="n"/>
       <c r="B1003" s="2" t="inlineStr">
         <is>
@@ -29084,7 +29102,11 @@
         </is>
       </c>
       <c r="E1003" s="2" t="n"/>
-      <c r="F1003" s="4" t="n"/>
+      <c r="F1003" s="7" t="inlineStr">
+        <is>
+          <t>修改Tag名称(改名后还原+自清理) — 100%</t>
+        </is>
+      </c>
       <c r="G1003" s="2" t="n"/>
     </row>
     <row r="1004">
@@ -29105,8 +29127,16 @@
         </is>
       </c>
       <c r="E1004" s="2" t="n"/>
-      <c r="F1004" s="4" t="n"/>
-      <c r="G1004" s="2" t="n"/>
+      <c r="F1004" s="4" t="inlineStr">
+        <is>
+          <t>作为清理步骤复用，见POST创建/PUT改名/POST BulkTagsWithItems case</t>
+        </is>
+      </c>
+      <c r="G1004" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST创建根Tag/PUT改名/POST BulkTagsWithItems三条写case的清理步骤复用，已随这些case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" s="2" t="n"/>
@@ -29126,8 +29156,16 @@
         </is>
       </c>
       <c r="E1005" s="2" t="n"/>
-      <c r="F1005" s="4" t="n"/>
-      <c r="G1005" s="2" t="n"/>
+      <c r="F1005" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1005" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" s="2" t="n"/>
@@ -29147,8 +29185,16 @@
         </is>
       </c>
       <c r="E1006" s="2" t="n"/>
-      <c r="F1006" s="4" t="n"/>
-      <c r="G1006" s="2" t="n"/>
+      <c r="F1006" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1006" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="n"/>
@@ -29168,10 +29214,18 @@
         </is>
       </c>
       <c r="E1007" s="2" t="n"/>
-      <c r="F1007" s="4" t="n"/>
-      <c r="G1007" s="2" t="n"/>
-    </row>
-    <row r="1008">
+      <c r="F1007" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1007" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008" ht="16" customHeight="1">
       <c r="A1008" s="2" t="n"/>
       <c r="B1008" s="2" t="inlineStr">
         <is>
@@ -29189,7 +29243,11 @@
         </is>
       </c>
       <c r="E1008" s="2" t="n"/>
-      <c r="F1008" s="4" t="n"/>
+      <c r="F1008" s="7" t="inlineStr">
+        <is>
+          <t>按ItemId批量打Tag(自清理) — 99.6%</t>
+        </is>
+      </c>
       <c r="G1008" s="2" t="n"/>
     </row>
     <row r="1009">
@@ -29210,8 +29268,16 @@
         </is>
       </c>
       <c r="E1009" s="2" t="n"/>
-      <c r="F1009" s="4" t="n"/>
-      <c r="G1009" s="2" t="n"/>
+      <c r="F1009" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1009" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行；本模块写操作改用BulkTagsWithItems(1093次/365天)承担attach职责，与DELETE Items配对</t>
+        </is>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" s="2" t="n"/>
@@ -29231,10 +29297,18 @@
         </is>
       </c>
       <c r="E1010" s="2" t="n"/>
-      <c r="F1010" s="4" t="n"/>
-      <c r="G1010" s="2" t="n"/>
-    </row>
-    <row r="1011">
+      <c r="F1010" s="4" t="inlineStr">
+        <is>
+          <t>作为detach逆操作步骤复用，见POST BulkTagsWithItems case</t>
+        </is>
+      </c>
+      <c r="G1010" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST BulkTagsWithItems(按ItemId打Tag)写case的逆操作(detach)步骤复用，已随该case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011" ht="64" customHeight="1">
       <c r="A1011" s="2" t="n"/>
       <c r="B1011" s="2" t="inlineStr">
         <is>
@@ -29252,10 +29326,17 @@
         </is>
       </c>
       <c r="E1011" s="2" t="n"/>
-      <c r="F1011" s="4" t="n"/>
+      <c r="F1011" s="7" t="inlineStr">
+        <is>
+          <t>按Tag/关键词搜索Item列表 — 92.6%
+全字段为空(旧版调用) — 2.2%
+按数字关键词搜索 — 1.8%
+按tagIds过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1011" s="2" t="n"/>
     </row>
-    <row r="1012">
+    <row r="1012" ht="16" customHeight="1">
       <c r="A1012" s="2" t="n"/>
       <c r="B1012" s="2" t="inlineStr">
         <is>
@@ -29273,7 +29354,11 @@
         </is>
       </c>
       <c r="E1012" s="2" t="n"/>
-      <c r="F1012" s="4" t="n"/>
+      <c r="F1012" s="7" t="inlineStr">
+        <is>
+          <t>按ItemId批量查Tag — 100%</t>
+        </is>
+      </c>
       <c r="G1012" s="2" t="n"/>
     </row>
     <row r="1013">
@@ -29294,8 +29379,16 @@
         </is>
       </c>
       <c r="E1013" s="2" t="n"/>
-      <c r="F1013" s="4" t="n"/>
-      <c r="G1013" s="2" t="n"/>
+      <c r="F1013" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1013" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1083,9 +1083,19 @@
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="F20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>8% (1/13)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -14643,8 +14653,16 @@
         </is>
       </c>
       <c r="E462" s="2" t="n"/>
-      <c r="F462" s="4" t="n"/>
-      <c r="G462" s="2" t="n"/>
+      <c r="F462" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G462" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -14664,8 +14682,16 @@
         </is>
       </c>
       <c r="E463" s="2" t="n"/>
-      <c r="F463" s="4" t="n"/>
-      <c r="G463" s="2" t="n"/>
+      <c r="F463" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G463" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -14685,8 +14711,16 @@
         </is>
       </c>
       <c r="E464" s="2" t="n"/>
-      <c r="F464" s="4" t="n"/>
-      <c r="G464" s="2" t="n"/>
+      <c r="F464" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G464" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -14706,8 +14740,16 @@
         </is>
       </c>
       <c r="E465" s="2" t="n"/>
-      <c r="F465" s="4" t="n"/>
-      <c r="G465" s="2" t="n"/>
+      <c r="F465" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G465" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -14727,8 +14769,16 @@
         </is>
       </c>
       <c r="E466" s="2" t="n"/>
-      <c r="F466" s="4" t="n"/>
-      <c r="G466" s="2" t="n"/>
+      <c r="F466" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G466" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -14748,8 +14798,16 @@
         </is>
       </c>
       <c r="E467" s="2" t="n"/>
-      <c r="F467" s="4" t="n"/>
-      <c r="G467" s="2" t="n"/>
+      <c r="F467" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G467" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -14769,8 +14827,16 @@
         </is>
       </c>
       <c r="E468" s="2" t="n"/>
-      <c r="F468" s="4" t="n"/>
-      <c r="G468" s="2" t="n"/>
+      <c r="F468" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G468" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -14790,10 +14856,18 @@
         </is>
       </c>
       <c r="E469" s="2" t="n"/>
-      <c r="F469" s="4" t="n"/>
-      <c r="G469" s="2" t="n"/>
-    </row>
-    <row r="470">
+      <c r="F469" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G469" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="16" customHeight="1">
       <c r="A470" s="2" t="n"/>
       <c r="B470" s="2" t="inlineStr">
         <is>
@@ -14811,7 +14885,11 @@
         </is>
       </c>
       <c r="E470" s="2" t="n"/>
-      <c r="F470" s="4" t="n"/>
+      <c r="F470" s="7" t="inlineStr">
+        <is>
+          <t>查SearchTerm对应的Category树 — 100%</t>
+        </is>
+      </c>
       <c r="G470" s="2" t="n"/>
     </row>
     <row r="471">
@@ -14832,8 +14910,16 @@
         </is>
       </c>
       <c r="E471" s="2" t="n"/>
-      <c r="F471" s="4" t="n"/>
-      <c r="G471" s="2" t="n"/>
+      <c r="F471" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G471" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -14853,8 +14939,16 @@
         </is>
       </c>
       <c r="E472" s="2" t="n"/>
-      <c r="F472" s="4" t="n"/>
-      <c r="G472" s="2" t="n"/>
+      <c r="F472" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G472" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -14874,8 +14968,16 @@
         </is>
       </c>
       <c r="E473" s="2" t="n"/>
-      <c r="F473" s="4" t="n"/>
-      <c r="G473" s="2" t="n"/>
+      <c r="F473" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G473" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -14895,8 +14997,16 @@
         </is>
       </c>
       <c r="E474" s="2" t="n"/>
-      <c r="F474" s="4" t="n"/>
-      <c r="G474" s="2" t="n"/>
+      <c r="F474" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量+路径含禁用关键词</t>
+        </is>
+      </c>
+      <c r="G474" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，且路径含禁用关键词Sync，双重原因不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="48" customHeight="1">
       <c r="A475" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2347,9 +2347,19 @@
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
+      <c r="F67" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>76% (13/17)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -38277,8 +38287,16 @@
         </is>
       </c>
       <c r="E1350" s="2" t="n"/>
-      <c r="F1350" s="4" t="n"/>
-      <c r="G1350" s="2" t="n"/>
+      <c r="F1350" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1350" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行；接口用途是批量补历史数据字段(运维用一次性脚本类接口)，非常规用户操作</t>
+        </is>
+      </c>
     </row>
     <row r="1351">
       <c r="A1351" s="2" t="n"/>
@@ -38298,10 +38316,18 @@
         </is>
       </c>
       <c r="E1351" s="2" t="n"/>
-      <c r="F1351" s="4" t="n"/>
-      <c r="G1351" s="2" t="n"/>
-    </row>
-    <row r="1352">
+      <c r="F1351" s="4" t="inlineStr">
+        <is>
+          <t>作为清理步骤复用，见POST shareLink/POST sovShare shareLink case</t>
+        </is>
+      </c>
+      <c r="G1351" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST shareLink创建/POST sovShare shareLink创建两条写case的清理步骤复用，已随这些case真实执行验证(2轮PASS，含跨SOV/普通两种类型均生效)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352" ht="48" customHeight="1">
       <c r="A1352" s="2" t="n"/>
       <c r="B1352" s="2" t="inlineStr">
         <is>
@@ -38319,10 +38345,16 @@
         </is>
       </c>
       <c r="E1352" s="2" t="n"/>
-      <c r="F1352" s="4" t="n"/>
+      <c r="F1352" s="7" t="inlineStr">
+        <is>
+          <t>列表(dashboardTypes含值) — 48.0%
+列表(dashboardTypes为空) — 49.8%
+列表(不传userIds) — 1.8%</t>
+        </is>
+      </c>
       <c r="G1352" s="2" t="n"/>
     </row>
-    <row r="1353">
+    <row r="1353" ht="16" customHeight="1">
       <c r="A1353" s="2" t="n"/>
       <c r="B1353" s="2" t="inlineStr">
         <is>
@@ -38340,7 +38372,11 @@
         </is>
       </c>
       <c r="E1353" s="2" t="n"/>
-      <c r="F1353" s="4" t="n"/>
+      <c r="F1353" s="7" t="inlineStr">
+        <is>
+          <t>SOV ShareLink列表 — 100%</t>
+        </is>
+      </c>
       <c r="G1353" s="2" t="n"/>
     </row>
     <row r="1354">
@@ -38361,10 +38397,18 @@
         </is>
       </c>
       <c r="E1354" s="2" t="n"/>
-      <c r="F1354" s="4" t="n"/>
-      <c r="G1354" s="2" t="n"/>
-    </row>
-    <row r="1355">
+      <c r="F1354" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1354" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行；接口用途是批量替换CategoryIds(运维用一次性脚本类接口)，非常规用户操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355" ht="16" customHeight="1">
       <c r="A1355" s="2" t="n"/>
       <c r="B1355" s="2" t="inlineStr">
         <is>
@@ -38382,10 +38426,14 @@
         </is>
       </c>
       <c r="E1355" s="2" t="n"/>
-      <c r="F1355" s="4" t="n"/>
+      <c r="F1355" s="7" t="inlineStr">
+        <is>
+          <t>创建ShareLink+改DateRange+改Description+改Setting(自清理) — 100%</t>
+        </is>
+      </c>
       <c r="G1355" s="2" t="n"/>
     </row>
-    <row r="1356">
+    <row r="1356" ht="16" customHeight="1">
       <c r="A1356" s="2" t="n"/>
       <c r="B1356" s="2" t="inlineStr">
         <is>
@@ -38403,10 +38451,14 @@
         </is>
       </c>
       <c r="E1356" s="2" t="n"/>
-      <c r="F1356" s="4" t="n"/>
+      <c r="F1356" s="7" t="inlineStr">
+        <is>
+          <t>按secretKey查ShareLink信息 — 100%</t>
+        </is>
+      </c>
       <c r="G1356" s="2" t="n"/>
     </row>
-    <row r="1357">
+    <row r="1357" ht="16" customHeight="1">
       <c r="A1357" s="2" t="n"/>
       <c r="B1357" s="2" t="inlineStr">
         <is>
@@ -38424,10 +38476,14 @@
         </is>
       </c>
       <c r="E1357" s="2" t="n"/>
-      <c r="F1357" s="4" t="n"/>
+      <c r="F1357" s="7" t="inlineStr">
+        <is>
+          <t>按id查ShareLink — 100%</t>
+        </is>
+      </c>
       <c r="G1357" s="2" t="n"/>
     </row>
-    <row r="1358">
+    <row r="1358" ht="16" customHeight="1">
       <c r="A1358" s="2" t="n"/>
       <c r="B1358" s="2" t="inlineStr">
         <is>
@@ -38445,10 +38501,14 @@
         </is>
       </c>
       <c r="E1358" s="2" t="n"/>
-      <c r="F1358" s="4" t="n"/>
+      <c r="F1358" s="7" t="inlineStr">
+        <is>
+          <t>按secretKey查shareToken — 100%</t>
+        </is>
+      </c>
       <c r="G1358" s="2" t="n"/>
     </row>
-    <row r="1359">
+    <row r="1359" ht="16" customHeight="1">
       <c r="A1359" s="2" t="n"/>
       <c r="B1359" s="2" t="inlineStr">
         <is>
@@ -38466,10 +38526,14 @@
         </is>
       </c>
       <c r="E1359" s="2" t="n"/>
-      <c r="F1359" s="4" t="n"/>
+      <c r="F1359" s="7" t="inlineStr">
+        <is>
+          <t>创建SOV ShareLink+改Setting(自清理) — 100%</t>
+        </is>
+      </c>
       <c r="G1359" s="2" t="n"/>
     </row>
-    <row r="1360">
+    <row r="1360" ht="16" customHeight="1">
       <c r="A1360" s="2" t="n"/>
       <c r="B1360" s="2" t="inlineStr">
         <is>
@@ -38487,7 +38551,11 @@
         </is>
       </c>
       <c r="E1360" s="2" t="n"/>
-      <c r="F1360" s="4" t="n"/>
+      <c r="F1360" s="7" t="inlineStr">
+        <is>
+          <t>按secretKey查SovShareLink信息 — 100%</t>
+        </is>
+      </c>
       <c r="G1360" s="2" t="n"/>
     </row>
     <row r="1361">
@@ -38508,8 +38576,16 @@
         </is>
       </c>
       <c r="E1361" s="2" t="n"/>
-      <c r="F1361" s="4" t="n"/>
-      <c r="G1361" s="2" t="n"/>
+      <c r="F1361" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1361" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1362">
       <c r="A1362" s="2" t="n"/>
@@ -38529,8 +38605,16 @@
         </is>
       </c>
       <c r="E1362" s="2" t="n"/>
-      <c r="F1362" s="4" t="n"/>
-      <c r="G1362" s="2" t="n"/>
+      <c r="F1362" s="4" t="inlineStr">
+        <is>
+          <t>作为步骤复用，见POST shareLink case</t>
+        </is>
+      </c>
+      <c r="G1362" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST shareLink创建case内的改日期范围步骤复用，已随该case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1363">
       <c r="A1363" s="2" t="n"/>
@@ -38550,8 +38634,16 @@
         </is>
       </c>
       <c r="E1363" s="2" t="n"/>
-      <c r="F1363" s="4" t="n"/>
-      <c r="G1363" s="2" t="n"/>
+      <c r="F1363" s="4" t="inlineStr">
+        <is>
+          <t>作为步骤复用，见POST shareLink case</t>
+        </is>
+      </c>
+      <c r="G1363" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST shareLink创建case内的改描述步骤复用，已随该case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1364">
       <c r="A1364" s="2" t="n"/>
@@ -38571,8 +38663,16 @@
         </is>
       </c>
       <c r="E1364" s="2" t="n"/>
-      <c r="F1364" s="4" t="n"/>
-      <c r="G1364" s="2" t="n"/>
+      <c r="F1364" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1364" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1365">
       <c r="A1365" s="2" t="n"/>
@@ -38592,8 +38692,16 @@
         </is>
       </c>
       <c r="E1365" s="2" t="n"/>
-      <c r="F1365" s="4" t="n"/>
-      <c r="G1365" s="2" t="n"/>
+      <c r="F1365" s="4" t="inlineStr">
+        <is>
+          <t>作为步骤复用，见POST shareLink case</t>
+        </is>
+      </c>
+      <c r="G1365" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST shareLink创建case内的改整体设置步骤复用，已随该case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" s="2" t="n"/>
@@ -38613,8 +38721,16 @@
         </is>
       </c>
       <c r="E1366" s="2" t="n"/>
-      <c r="F1366" s="4" t="n"/>
-      <c r="G1366" s="2" t="n"/>
+      <c r="F1366" s="4" t="inlineStr">
+        <is>
+          <t>作为步骤复用，见POST sovShare shareLink case</t>
+        </is>
+      </c>
+      <c r="G1366" s="4" t="inlineStr">
+        <is>
+          <t>未单独成case，作为POST sovShare shareLink创建case内的改设置步骤复用，已随该case真实执行验证(2轮PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -889,9 +889,19 @@
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="F13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>6% (1/17)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8481,8 +8491,16 @@
         </is>
       </c>
       <c r="E226" s="2" t="n"/>
-      <c r="F226" s="4" t="n"/>
-      <c r="G226" s="2" t="n"/>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -8502,8 +8520,16 @@
         </is>
       </c>
       <c r="E227" s="2" t="n"/>
-      <c r="F227" s="4" t="n"/>
-      <c r="G227" s="2" t="n"/>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -8523,8 +8549,16 @@
         </is>
       </c>
       <c r="E228" s="2" t="n"/>
-      <c r="F228" s="4" t="n"/>
-      <c r="G228" s="2" t="n"/>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -8544,8 +8578,16 @@
         </is>
       </c>
       <c r="E229" s="2" t="n"/>
-      <c r="F229" s="4" t="n"/>
-      <c r="G229" s="2" t="n"/>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -8565,8 +8607,16 @@
         </is>
       </c>
       <c r="E230" s="2" t="n"/>
-      <c r="F230" s="4" t="n"/>
-      <c r="G230" s="2" t="n"/>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -8586,8 +8636,16 @@
         </is>
       </c>
       <c r="E231" s="2" t="n"/>
-      <c r="F231" s="4" t="n"/>
-      <c r="G231" s="2" t="n"/>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -8607,8 +8665,16 @@
         </is>
       </c>
       <c r="E232" s="2" t="n"/>
-      <c r="F232" s="4" t="n"/>
-      <c r="G232" s="2" t="n"/>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量+文件上传类型</t>
+        </is>
+      </c>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行；且为multipart/form-data文件上传接口，即使未来有流量也无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -8628,8 +8694,16 @@
         </is>
       </c>
       <c r="E233" s="2" t="n"/>
-      <c r="F233" s="4" t="n"/>
-      <c r="G233" s="2" t="n"/>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量+文件上传类型</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行；且为multipart/form-data文件上传接口，即使未来有流量也无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -8649,8 +8723,16 @@
         </is>
       </c>
       <c r="E234" s="2" t="n"/>
-      <c r="F234" s="4" t="n"/>
-      <c r="G234" s="2" t="n"/>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -8670,8 +8752,16 @@
         </is>
       </c>
       <c r="E235" s="2" t="n"/>
-      <c r="F235" s="4" t="n"/>
-      <c r="G235" s="2" t="n"/>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -8691,8 +8781,16 @@
         </is>
       </c>
       <c r="E236" s="2" t="n"/>
-      <c r="F236" s="4" t="n"/>
-      <c r="G236" s="2" t="n"/>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -8712,8 +8810,16 @@
         </is>
       </c>
       <c r="E237" s="2" t="n"/>
-      <c r="F237" s="4" t="n"/>
-      <c r="G237" s="2" t="n"/>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -8733,8 +8839,16 @@
         </is>
       </c>
       <c r="E238" s="2" t="n"/>
-      <c r="F238" s="4" t="n"/>
-      <c r="G238" s="2" t="n"/>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -8754,8 +8868,16 @@
         </is>
       </c>
       <c r="E239" s="2" t="n"/>
-      <c r="F239" s="4" t="n"/>
-      <c r="G239" s="2" t="n"/>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -8775,8 +8897,16 @@
         </is>
       </c>
       <c r="E240" s="2" t="n"/>
-      <c r="F240" s="4" t="n"/>
-      <c r="G240" s="2" t="n"/>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量+文件上传类型</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行；且为multipart/form-data文件上传接口，即使未来有流量也无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -8796,10 +8926,18 @@
         </is>
       </c>
       <c r="E241" s="2" t="n"/>
-      <c r="F241" s="4" t="n"/>
-      <c r="G241" s="2" t="n"/>
-    </row>
-    <row r="242">
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量+文件上传类型</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行；且为multipart/form-data文件上传接口，即使未来有流量也无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="48" customHeight="1">
       <c r="A242" s="2" t="n"/>
       <c r="B242" s="2" t="inlineStr">
         <is>
@@ -8817,7 +8955,13 @@
         </is>
       </c>
       <c r="E242" s="2" t="n"/>
-      <c r="F242" s="4" t="n"/>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>分页列表(默认无过滤) — 62.4%
+按profileIds+已审核状态过滤 — 30.8%
+按status/brandName字段查询(旧版参数) — 4.2%</t>
+        </is>
+      </c>
       <c r="G242" s="2" t="n"/>
     </row>
     <row r="243">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -921,9 +921,19 @@
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="F14" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>76% (13/17)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -8964,7 +8974,7 @@
       </c>
       <c r="G242" s="2" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" ht="96" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8986,10 +8996,19 @@
         </is>
       </c>
       <c r="E243" s="2" t="n"/>
-      <c r="F243" s="4" t="n"/>
+      <c r="F243" s="7" t="inlineStr">
+        <is>
+          <t>无Campaign过滤+不传campaignTagIds — 57.6%
+不传campaignIds+按CampaignTag过滤 — 30.2%
+不传campaignIds+无CampaignTag过滤 — 6.0%
+按Campaign过滤+不传campaignTagIds — 2.2%
+不传campaignIds+不传campaignTagIds — 2.0%
+无Campaign过滤+无CampaignTag过滤 — 2.0%</t>
+        </is>
+      </c>
       <c r="G243" s="2" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" ht="112" customHeight="1">
       <c r="A244" s="2" t="n"/>
       <c r="B244" s="2" t="inlineStr">
         <is>
@@ -9007,10 +9026,20 @@
         </is>
       </c>
       <c r="E244" s="2" t="n"/>
-      <c r="F244" s="4" t="n"/>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>timeType=monthOfYear+不传isShowIRoas — 35.0%
+timeType=date+不传isShowIRoas — 33.4%
+timeType=ytd+不传isShowIRoas — 12.6%
+timeType=monthOfYear+isShowIRoas=true — 8.4%
+timeType=date+isShowIRoas=true — 7.6%
+timeType=date+isShowIRoas=false — 1.4%
+timeType=ytd+isShowIRoas=false — 1.0%</t>
+        </is>
+      </c>
       <c r="G244" s="2" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" ht="128" customHeight="1">
       <c r="A245" s="2" t="n"/>
       <c r="B245" s="2" t="inlineStr">
         <is>
@@ -9028,10 +9057,21 @@
         </is>
       </c>
       <c r="E245" s="2" t="n"/>
-      <c r="F245" s="4" t="n"/>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>timeType=date+不传isShowIRoas — 42.4%
+timeType=monthOfYear+不传isShowIRoas — 29.2%
+timeType=ytd+不传isShowIRoas — 16.6%
+timeType=monthOfYear+isShowIRoas=false — 3.6%
+timeType=monthOfYear+isShowIRoas=true — 2.6%
+timeType=date+isShowIRoas=false — 2.4%
+timeType=ytd+isShowIRoas=false — 1.8%
+timeType=date+isShowIRoas=true — 1.4%</t>
+        </is>
+      </c>
       <c r="G245" s="2" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" ht="112" customHeight="1">
       <c r="A246" s="2" t="n"/>
       <c r="B246" s="2" t="inlineStr">
         <is>
@@ -9049,10 +9089,20 @@
         </is>
       </c>
       <c r="E246" s="2" t="n"/>
-      <c r="F246" s="4" t="n"/>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>无Campaign过滤+按CampaignTag过滤+不传itemType+timeType=ytd — 40.4%
+无Campaign过滤+按CampaignTag过滤+itemType=1+timeType=ytd — 38.0%
+无Campaign过滤+按CampaignTag过滤+不传itemType+timeType=monthOfYear — 8.6%
+按Campaign过滤+无CampaignTag过滤+itemType=1+timeType=ytd — 6.4%
+无Campaign过滤+无CampaignTag过滤+不传itemType+timeType=ytd — 2.4%
+按Campaign过滤+无CampaignTag过滤+不传itemType+timeType=monthOfYear — 2.2%
+无Campaign过滤+无CampaignTag过滤+itemType=1+timeType=ytd — 1.0%</t>
+        </is>
+      </c>
       <c r="G246" s="2" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" ht="16" customHeight="1">
       <c r="A247" s="2" t="n"/>
       <c r="B247" s="2" t="inlineStr">
         <is>
@@ -9070,7 +9120,11 @@
         </is>
       </c>
       <c r="E247" s="2" t="n"/>
-      <c r="F247" s="4" t="n"/>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>按AdGroupTag改预算(业务校验限制，未构造出成功案例)</t>
+        </is>
+      </c>
       <c r="G247" s="2" t="n"/>
     </row>
     <row r="248">
@@ -9091,10 +9145,18 @@
         </is>
       </c>
       <c r="E248" s="2" t="n"/>
-      <c r="F248" s="4" t="n"/>
-      <c r="G248" s="2" t="n"/>
-    </row>
-    <row r="249">
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="16" customHeight="1">
       <c r="A249" s="2" t="n"/>
       <c r="B249" s="2" t="inlineStr">
         <is>
@@ -9112,7 +9174,11 @@
         </is>
       </c>
       <c r="E249" s="2" t="n"/>
-      <c r="F249" s="4" t="n"/>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>改Display Campaign预算后还原 — 100%</t>
+        </is>
+      </c>
       <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
@@ -9133,8 +9199,16 @@
         </is>
       </c>
       <c r="E250" s="2" t="n"/>
-      <c r="F250" s="4" t="n"/>
-      <c r="G250" s="2" t="n"/>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -9154,10 +9228,18 @@
         </is>
       </c>
       <c r="E251" s="2" t="n"/>
-      <c r="F251" s="4" t="n"/>
-      <c r="G251" s="2" t="n"/>
-    </row>
-    <row r="252">
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="16" customHeight="1">
       <c r="A252" s="2" t="n"/>
       <c r="B252" s="2" t="inlineStr">
         <is>
@@ -9175,10 +9257,14 @@
         </is>
       </c>
       <c r="E252" s="2" t="n"/>
-      <c r="F252" s="4" t="n"/>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G252" s="2" t="n"/>
     </row>
-    <row r="253">
+    <row r="253" ht="32" customHeight="1">
       <c r="A253" s="2" t="n"/>
       <c r="B253" s="2" t="inlineStr">
         <is>
@@ -9196,10 +9282,15 @@
         </is>
       </c>
       <c r="E253" s="2" t="n"/>
-      <c r="F253" s="4" t="n"/>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>itemType=1+按Tag过滤 — 95.4%
+itemType=1+无Tag过滤 — 3.8%</t>
+        </is>
+      </c>
       <c r="G253" s="2" t="n"/>
     </row>
-    <row r="254">
+    <row r="254" ht="16" customHeight="1">
       <c r="A254" s="2" t="n"/>
       <c r="B254" s="2" t="inlineStr">
         <is>
@@ -9217,10 +9308,14 @@
         </is>
       </c>
       <c r="E254" s="2" t="n"/>
-      <c r="F254" s="4" t="n"/>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G254" s="2" t="n"/>
     </row>
-    <row r="255">
+    <row r="255" ht="48" customHeight="1">
       <c r="A255" s="2" t="n"/>
       <c r="B255" s="2" t="inlineStr">
         <is>
@@ -9238,10 +9333,16 @@
         </is>
       </c>
       <c r="E255" s="2" t="n"/>
-      <c r="F255" s="4" t="n"/>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>按CampaignTag过滤+不传itemType — 71.0%
+按CampaignTag过滤+itemType=1 — 25.6%
+不传campaignTagIds+不传itemType — 3.0%</t>
+        </is>
+      </c>
       <c r="G255" s="2" t="n"/>
     </row>
-    <row r="256">
+    <row r="256" ht="16" customHeight="1">
       <c r="A256" s="2" t="n"/>
       <c r="B256" s="2" t="inlineStr">
         <is>
@@ -9259,10 +9360,14 @@
         </is>
       </c>
       <c r="E256" s="2" t="n"/>
-      <c r="F256" s="4" t="n"/>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>查当前用户可见Profile列表 — 100%</t>
+        </is>
+      </c>
       <c r="G256" s="2" t="n"/>
     </row>
-    <row r="257">
+    <row r="257" ht="96" customHeight="1">
       <c r="A257" s="2" t="n"/>
       <c r="B257" s="2" t="inlineStr">
         <is>
@@ -9280,7 +9385,16 @@
         </is>
       </c>
       <c r="E257" s="2" t="n"/>
-      <c r="F257" s="4" t="n"/>
+      <c r="F257" s="7" t="inlineStr">
+        <is>
+          <t>timeType=monthOfYear+不传isShowIRoas — 67.2%
+timeType=date+不传isShowIRoas — 14.4%
+timeType=monthOfYear+isShowIRoas=true — 10.0%
+timeType=ytd+不传isShowIRoas — 4.4%
+timeType=date+isShowIRoas=true — 2.2%
+timeType=date+isShowIRoas=false — 1.0%</t>
+        </is>
+      </c>
       <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
@@ -9301,10 +9415,18 @@
         </is>
       </c>
       <c r="E258" s="2" t="n"/>
-      <c r="F258" s="4" t="n"/>
-      <c r="G258" s="2" t="n"/>
-    </row>
-    <row r="259">
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="16" customHeight="1">
       <c r="A259" s="2" t="n"/>
       <c r="B259" s="2" t="inlineStr">
         <is>
@@ -9322,7 +9444,11 @@
         </is>
       </c>
       <c r="E259" s="2" t="n"/>
-      <c r="F259" s="4" t="n"/>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>改预算后还原 — 100%</t>
+        </is>
+      </c>
       <c r="G259" s="2" t="n"/>
     </row>
     <row r="260" ht="15.95" customHeight="1">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2313,9 +2313,19 @@
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
+      <c r="F65" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>18% (3/17)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -37931,7 +37941,7 @@
       <c r="F1324" s="4" t="n"/>
       <c r="G1324" s="2" t="n"/>
     </row>
-    <row r="1325">
+    <row r="1325" ht="16" customHeight="1">
       <c r="A1325" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37953,10 +37963,14 @@
         </is>
       </c>
       <c r="E1325" s="2" t="n"/>
-      <c r="F1325" s="4" t="n"/>
+      <c r="F1325" s="7" t="inlineStr">
+        <is>
+          <t>按campaignId查SbaProfile — 100%</t>
+        </is>
+      </c>
       <c r="G1325" s="2" t="n"/>
     </row>
-    <row r="1326">
+    <row r="1326" ht="16" customHeight="1">
       <c r="A1326" s="2" t="n"/>
       <c r="B1326" s="2" t="inlineStr">
         <is>
@@ -37974,7 +37988,11 @@
         </is>
       </c>
       <c r="E1326" s="2" t="n"/>
-      <c r="F1326" s="4" t="n"/>
+      <c r="F1326" s="7" t="inlineStr">
+        <is>
+          <t>创建SbaProfile(测试账号无SBA-eligible campaign，验证业务校验) — 3.4%</t>
+        </is>
+      </c>
       <c r="G1326" s="2" t="n"/>
     </row>
     <row r="1327">
@@ -37995,8 +38013,16 @@
         </is>
       </c>
       <c r="E1327" s="2" t="n"/>
-      <c r="F1327" s="4" t="n"/>
-      <c r="G1327" s="2" t="n"/>
+      <c r="F1327" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，见POST /api/SbaProfile case说明</t>
+        </is>
+      </c>
+      <c r="G1327" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：需要一个已存在的sbaProfileId才能更新，而测试账号现有campaign均为KeywordBidded类型无法创建出SbaProfile(见POST /api/SbaProfile case)，无法安全构造测试数据</t>
+        </is>
+      </c>
     </row>
     <row r="1328">
       <c r="A1328" s="2" t="n"/>
@@ -38016,8 +38042,16 @@
         </is>
       </c>
       <c r="E1328" s="2" t="n"/>
-      <c r="F1328" s="4" t="n"/>
-      <c r="G1328" s="2" t="n"/>
+      <c r="F1328" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，见POST /api/SbaProfile case说明</t>
+        </is>
+      </c>
+      <c r="G1328" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：同PUT /api/SbaProfile，依赖已存在的sbaProfileId</t>
+        </is>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" s="2" t="n"/>
@@ -38037,8 +38071,16 @@
         </is>
       </c>
       <c r="E1329" s="2" t="n"/>
-      <c r="F1329" s="4" t="n"/>
-      <c r="G1329" s="2" t="n"/>
+      <c r="F1329" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，见POST /api/SbaProfile case说明</t>
+        </is>
+      </c>
+      <c r="G1329" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：依赖已存在的sbaProfileId+已上传的品牌Logo文件引用，测试账号无法创建出SbaProfile基础数据</t>
+        </is>
+      </c>
     </row>
     <row r="1330">
       <c r="A1330" s="2" t="n"/>
@@ -38058,8 +38100,16 @@
         </is>
       </c>
       <c r="E1330" s="2" t="n"/>
-      <c r="F1330" s="4" t="n"/>
-      <c r="G1330" s="2" t="n"/>
+      <c r="F1330" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1330" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1331">
       <c r="A1331" s="2" t="n"/>
@@ -38079,8 +38129,16 @@
         </is>
       </c>
       <c r="E1331" s="2" t="n"/>
-      <c r="F1331" s="4" t="n"/>
-      <c r="G1331" s="2" t="n"/>
+      <c r="F1331" s="4" t="inlineStr">
+        <is>
+          <t>异步导出，仅标注</t>
+        </is>
+      </c>
+      <c r="G1331" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口，仅标注不生成执行(同Report/Dashboard等模块的Export接口处理方式)</t>
+        </is>
+      </c>
     </row>
     <row r="1332">
       <c r="A1332" s="2" t="n"/>
@@ -38100,10 +38158,18 @@
         </is>
       </c>
       <c r="E1332" s="2" t="n"/>
-      <c r="F1332" s="4" t="n"/>
-      <c r="G1332" s="2" t="n"/>
-    </row>
-    <row r="1333">
+      <c r="F1332" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调，仅标注</t>
+        </is>
+      </c>
+      <c r="G1332" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调接口，仅标注不生成执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333" ht="192" customHeight="1">
       <c r="A1333" s="2" t="n"/>
       <c r="B1333" s="2" t="inlineStr">
         <is>
@@ -38121,7 +38187,22 @@
         </is>
       </c>
       <c r="E1333" s="2" t="n"/>
-      <c r="F1333" s="4" t="n"/>
+      <c r="F1333" s="7" t="inlineStr">
+        <is>
+          <t>无Campaign过滤+无CampaignTag过滤+multiSortList=[{'sortData': 'campaignName', 'sortType': 'desc'}] — 32.4%
+无Campaign过滤+无CampaignTag过滤+multiSortList=[{'sortData': 'brandName', 'sortType': 'desc'}] — 19.2%
+按Campaign过滤+无CampaignTag过滤+multiSortList=[{'sortData': 'brandName', 'sortType': 'desc'}] — 15.6%
+无Campaign过滤+无CampaignTag过滤+multiSortList=[{'sortData': 'spend', 'sortType': 'desc'}] — 6.8%
+按Campaign过滤+无CampaignTag过滤+multiSortList=[{'sortData': 'spend', 'sortType': 'desc'}] — 5.4%
+无Campaign过滤+按CampaignTag过滤+multiSortList=[{'sortData': 'brandName', 'sortType': 'desc'}] — 4.8%
+无Campaign过滤+按CampaignTag过滤+multiSortList=[{'sortData': 'campaignName', 'sortType': 'desc'}] — 3.4%
+不传campaignIds+无CampaignTag过滤+multiSortList=[{'sortData': 'brandName', 'sortType': 'desc'}] — 2.8%
+无Campaign过滤+按CampaignTag过滤+multiSortList=[{'sortData': 'spend', 'sortType': 'desc'}] — 2.6%
+按Campaign过滤+无CampaignTag过滤+multiSortList=[{'sortData': 'campaignName', 'sortType': 'desc'}] — 2.4%
+不传campaignIds+按CampaignTag过滤+multiSortList=[{'sortData': 'brandName', 'sortType': 'desc'}] — 1.2%
+不传campaignIds+不传campaignTagIds+multiSortList=[{'sortData': 'brandName', 'sortType': 'desc'}] — 1.0%</t>
+        </is>
+      </c>
       <c r="G1333" s="2" t="n"/>
     </row>
     <row r="1334">
@@ -38142,8 +38223,16 @@
         </is>
       </c>
       <c r="E1334" s="2" t="n"/>
-      <c r="F1334" s="4" t="n"/>
-      <c r="G1334" s="2" t="n"/>
+      <c r="F1334" s="4" t="inlineStr">
+        <is>
+          <t>文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1334" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口，无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="1335">
       <c r="A1335" s="2" t="n"/>
@@ -38163,8 +38252,16 @@
         </is>
       </c>
       <c r="E1335" s="2" t="n"/>
-      <c r="F1335" s="4" t="n"/>
-      <c r="G1335" s="2" t="n"/>
+      <c r="F1335" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，见POST /api/SbaProfile case说明</t>
+        </is>
+      </c>
+      <c r="G1335" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：依赖已存在的自定义图片关联(需先有SbaProfile)，测试账号无法构造出基础数据</t>
+        </is>
+      </c>
     </row>
     <row r="1336">
       <c r="A1336" s="2" t="n"/>
@@ -38184,8 +38281,16 @@
         </is>
       </c>
       <c r="E1336" s="2" t="n"/>
-      <c r="F1336" s="4" t="n"/>
-      <c r="G1336" s="2" t="n"/>
+      <c r="F1336" s="4" t="inlineStr">
+        <is>
+          <t>文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1336" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data类型接口(虽名字含Url，Swagger声明的content-type仍是multipart)，无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="1337">
       <c r="A1337" s="2" t="n"/>
@@ -38205,8 +38310,16 @@
         </is>
       </c>
       <c r="E1337" s="2" t="n"/>
-      <c r="F1337" s="4" t="n"/>
-      <c r="G1337" s="2" t="n"/>
+      <c r="F1337" s="4" t="inlineStr">
+        <is>
+          <t>文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1337" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口，无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="1338">
       <c r="A1338" s="2" t="n"/>
@@ -38226,8 +38339,16 @@
         </is>
       </c>
       <c r="E1338" s="2" t="n"/>
-      <c r="F1338" s="4" t="n"/>
-      <c r="G1338" s="2" t="n"/>
+      <c r="F1338" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1338" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1339">
       <c r="A1339" s="2" t="n"/>
@@ -38247,8 +38368,16 @@
         </is>
       </c>
       <c r="E1339" s="2" t="n"/>
-      <c r="F1339" s="4" t="n"/>
-      <c r="G1339" s="2" t="n"/>
+      <c r="F1339" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，见POST /api/SbaProfile case说明</t>
+        </is>
+      </c>
+      <c r="G1339" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：JSON接口但依赖已上传文件的filePath引用+SBA-eligible的campaign，测试账号无法构造出基础数据</t>
+        </is>
+      </c>
     </row>
     <row r="1340">
       <c r="A1340" s="2" t="n"/>
@@ -38268,8 +38397,16 @@
         </is>
       </c>
       <c r="E1340" s="2" t="n"/>
-      <c r="F1340" s="4" t="n"/>
-      <c r="G1340" s="2" t="n"/>
+      <c r="F1340" s="4" t="inlineStr">
+        <is>
+          <t>文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1340" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口，无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="1341">
       <c r="A1341" s="2" t="n"/>
@@ -38289,8 +38426,16 @@
         </is>
       </c>
       <c r="E1341" s="2" t="n"/>
-      <c r="F1341" s="4" t="n"/>
-      <c r="G1341" s="2" t="n"/>
+      <c r="F1341" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量+路径含禁用关键词</t>
+        </is>
+      </c>
+      <c r="G1341" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，且路径含禁用关键词Sync，双重原因不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1342" ht="112" customHeight="1">
       <c r="A1342" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1189,9 +1189,19 @@
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="F23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>25% (7/28)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -16494,7 +16504,7 @@
       <c r="F523" s="4" t="n"/>
       <c r="G523" s="2" t="n"/>
     </row>
-    <row r="524">
+    <row r="524" ht="16" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16516,10 +16526,14 @@
         </is>
       </c>
       <c r="E524" s="2" t="n"/>
-      <c r="F524" s="4" t="n"/>
+      <c r="F524" s="7" t="inlineStr">
+        <is>
+          <t>批量触发异步预览生成 — 100%</t>
+        </is>
+      </c>
       <c r="G524" s="2" t="n"/>
     </row>
-    <row r="525">
+    <row r="525" ht="16" customHeight="1">
       <c r="A525" s="2" t="n"/>
       <c r="B525" s="2" t="inlineStr">
         <is>
@@ -16537,10 +16551,14 @@
         </is>
       </c>
       <c r="E525" s="2" t="n"/>
-      <c r="F525" s="4" t="n"/>
+      <c r="F525" s="7" t="inlineStr">
+        <is>
+          <t>生成背景色AI建议 — 100%</t>
+        </is>
+      </c>
       <c r="G525" s="2" t="n"/>
     </row>
-    <row r="526">
+    <row r="526" ht="16" customHeight="1">
       <c r="A526" s="2" t="n"/>
       <c r="B526" s="2" t="inlineStr">
         <is>
@@ -16558,7 +16576,11 @@
         </is>
       </c>
       <c r="E526" s="2" t="n"/>
-      <c r="F526" s="4" t="n"/>
+      <c r="F526" s="7" t="inlineStr">
+        <is>
+          <t>查询背景色AI建议生成状态 — 100%</t>
+        </is>
+      </c>
       <c r="G526" s="2" t="n"/>
     </row>
     <row r="527">
@@ -16579,8 +16601,16 @@
         </is>
       </c>
       <c r="E527" s="2" t="n"/>
-      <c r="F527" s="4" t="n"/>
-      <c r="G527" s="2" t="n"/>
+      <c r="F527" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G527" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n"/>
@@ -16600,8 +16630,16 @@
         </is>
       </c>
       <c r="E528" s="2" t="n"/>
-      <c r="F528" s="4" t="n"/>
-      <c r="G528" s="2" t="n"/>
+      <c r="F528" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G528" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n"/>
@@ -16621,8 +16659,16 @@
         </is>
       </c>
       <c r="E529" s="2" t="n"/>
-      <c r="F529" s="4" t="n"/>
-      <c r="G529" s="2" t="n"/>
+      <c r="F529" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G529" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n"/>
@@ -16642,8 +16688,16 @@
         </is>
       </c>
       <c r="E530" s="2" t="n"/>
-      <c r="F530" s="4" t="n"/>
-      <c r="G530" s="2" t="n"/>
+      <c r="F530" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G530" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n"/>
@@ -16663,8 +16717,16 @@
         </is>
       </c>
       <c r="E531" s="2" t="n"/>
-      <c r="F531" s="4" t="n"/>
-      <c r="G531" s="2" t="n"/>
+      <c r="F531" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，需先人工上传测试素材</t>
+        </is>
+      </c>
+      <c r="G531" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：clone/deleteList/move/submit均为真实修改Creative实体状态的写操作，测试账号Display Creative素材库为空(无自建Creative)，且这4个接口若对真实客户的Creative执行会造成实际破坏(克隆/删除/移动/提交审核)，不能用他人真实creativeId执行；需先通过multipart文件上传接口人工创建测试素材后才能安全测试</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n"/>
@@ -16684,8 +16746,16 @@
         </is>
       </c>
       <c r="E532" s="2" t="n"/>
-      <c r="F532" s="4" t="n"/>
-      <c r="G532" s="2" t="n"/>
+      <c r="F532" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G532" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n"/>
@@ -16705,8 +16775,16 @@
         </is>
       </c>
       <c r="E533" s="2" t="n"/>
-      <c r="F533" s="4" t="n"/>
-      <c r="G533" s="2" t="n"/>
+      <c r="F533" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词</t>
+        </is>
+      </c>
+      <c r="G533" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词Sync，不生成不执行(尽管365天848次真实流量较高，仍按硬性规则拦截)</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n"/>
@@ -16726,8 +16804,16 @@
         </is>
       </c>
       <c r="E534" s="2" t="n"/>
-      <c r="F534" s="4" t="n"/>
-      <c r="G534" s="2" t="n"/>
+      <c r="F534" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G534" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n"/>
@@ -16747,10 +16833,18 @@
         </is>
       </c>
       <c r="E535" s="2" t="n"/>
-      <c r="F535" s="4" t="n"/>
-      <c r="G535" s="2" t="n"/>
-    </row>
-    <row r="536">
+      <c r="F535" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，需先人工上传测试素材</t>
+        </is>
+      </c>
+      <c r="G535" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：同POST /api/Creative/clone说明，删除操作若误用真实客户creativeId后果不可逆</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="80" customHeight="1">
       <c r="A536" s="2" t="n"/>
       <c r="B536" s="2" t="inlineStr">
         <is>
@@ -16768,10 +16862,18 @@
         </is>
       </c>
       <c r="E536" s="2" t="n"/>
-      <c r="F536" s="4" t="n"/>
+      <c r="F536" s="7" t="inlineStr">
+        <is>
+          <t>不含adgroupId+mediaType=[ONSITE DISPLAY TEMPLATE]+含searchName — 55.0%
+含adgroupId+mediaType=[ONSITE DISPLAY TEMPLATE]+含searchName — 29.6%
+含adgroupId+mediaType=[None]+含searchName — 9.6%
+不含adgroupId+mediaType=[VIDEO DISPLAY TEMPLATE]+含searchName — 2.6%
+不含adgroupId+mediaType=[None]+含searchName — 2.0%</t>
+        </is>
+      </c>
       <c r="G536" s="2" t="n"/>
     </row>
-    <row r="537">
+    <row r="537" ht="96" customHeight="1">
       <c r="A537" s="2" t="n"/>
       <c r="B537" s="2" t="inlineStr">
         <is>
@@ -16789,7 +16891,16 @@
         </is>
       </c>
       <c r="E537" s="2" t="n"/>
-      <c r="F537" s="4" t="n"/>
+      <c r="F537" s="7" t="inlineStr">
+        <is>
+          <t>不传libraryStatus+mediaType=[]+status=[] — 62.2%
+libraryStatus=[]+mediaType=[]+不传status — 22.4%
+libraryStatus=[]+mediaType=[]+status=[] — 3.6%
+不传libraryStatus+mediaType=[ids+]+status=[] — 2.6%
+libraryStatus=[]+mediaType=[ids+]+不传status — 1.4%
+不传libraryStatus+mediaType=[]+status=[Rejected] — 1.2%</t>
+        </is>
+      </c>
       <c r="G537" s="2" t="n"/>
     </row>
     <row r="538">
@@ -16810,8 +16921,16 @@
         </is>
       </c>
       <c r="E538" s="2" t="n"/>
-      <c r="F538" s="4" t="n"/>
-      <c r="G538" s="2" t="n"/>
+      <c r="F538" s="4" t="inlineStr">
+        <is>
+          <t>文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G538" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口，无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n"/>
@@ -16831,8 +16950,16 @@
         </is>
       </c>
       <c r="E539" s="2" t="n"/>
-      <c r="F539" s="4" t="n"/>
-      <c r="G539" s="2" t="n"/>
+      <c r="F539" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G539" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n"/>
@@ -16852,8 +16979,16 @@
         </is>
       </c>
       <c r="E540" s="2" t="n"/>
-      <c r="F540" s="4" t="n"/>
-      <c r="G540" s="2" t="n"/>
+      <c r="F540" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G540" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n"/>
@@ -16873,10 +17008,18 @@
         </is>
       </c>
       <c r="E541" s="2" t="n"/>
-      <c r="F541" s="4" t="n"/>
-      <c r="G541" s="2" t="n"/>
-    </row>
-    <row r="542">
+      <c r="F541" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，需先人工上传测试素材</t>
+        </is>
+      </c>
+      <c r="G541" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：同POST /api/Creative/clone说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="16" customHeight="1">
       <c r="A542" s="2" t="n"/>
       <c r="B542" s="2" t="inlineStr">
         <is>
@@ -16894,10 +17037,14 @@
         </is>
       </c>
       <c r="E542" s="2" t="n"/>
-      <c r="F542" s="4" t="n"/>
+      <c r="F542" s="7" t="inlineStr">
+        <is>
+          <t>查询Creative预览 — 100%</t>
+        </is>
+      </c>
       <c r="G542" s="2" t="n"/>
     </row>
-    <row r="543">
+    <row r="543" ht="48" customHeight="1">
       <c r="A543" s="2" t="n"/>
       <c r="B543" s="2" t="inlineStr">
         <is>
@@ -16915,7 +17062,13 @@
         </is>
       </c>
       <c r="E543" s="2" t="n"/>
-      <c r="F543" s="4" t="n"/>
+      <c r="F543" s="7" t="inlineStr">
+        <is>
+          <t>type=0 — 55.4%
+type=2 — 33.2%
+type=1 — 11.4%</t>
+        </is>
+      </c>
       <c r="G543" s="2" t="n"/>
     </row>
     <row r="544">
@@ -16936,8 +17089,16 @@
         </is>
       </c>
       <c r="E544" s="2" t="n"/>
-      <c r="F544" s="4" t="n"/>
-      <c r="G544" s="2" t="n"/>
+      <c r="F544" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G544" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n"/>
@@ -16957,8 +17118,16 @@
         </is>
       </c>
       <c r="E545" s="2" t="n"/>
-      <c r="F545" s="4" t="n"/>
-      <c r="G545" s="2" t="n"/>
+      <c r="F545" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G545" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n"/>
@@ -16978,8 +17147,16 @@
         </is>
       </c>
       <c r="E546" s="2" t="n"/>
-      <c r="F546" s="4" t="n"/>
-      <c r="G546" s="2" t="n"/>
+      <c r="F546" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G546" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n"/>
@@ -16999,8 +17176,16 @@
         </is>
       </c>
       <c r="E547" s="2" t="n"/>
-      <c r="F547" s="4" t="n"/>
-      <c r="G547" s="2" t="n"/>
+      <c r="F547" s="4" t="inlineStr">
+        <is>
+          <t>技术受限，需先人工上传测试素材</t>
+        </is>
+      </c>
+      <c r="G547" s="4" t="inlineStr">
+        <is>
+          <t>技术受限：同POST /api/Creative/clone说明，提交审核操作若误用真实客户creativeId会影响其真实审核流程</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n"/>
@@ -17020,8 +17205,16 @@
         </is>
       </c>
       <c r="E548" s="2" t="n"/>
-      <c r="F548" s="4" t="n"/>
-      <c r="G548" s="2" t="n"/>
+      <c r="F548" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G548" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n"/>
@@ -17041,8 +17234,16 @@
         </is>
       </c>
       <c r="E549" s="2" t="n"/>
-      <c r="F549" s="4" t="n"/>
-      <c r="G549" s="2" t="n"/>
+      <c r="F549" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量+路径含禁用关键词</t>
+        </is>
+      </c>
+      <c r="G549" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，且路径含禁用关键词Sync，双重原因不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n"/>
@@ -17062,8 +17263,16 @@
         </is>
       </c>
       <c r="E550" s="2" t="n"/>
-      <c r="F550" s="4" t="n"/>
-      <c r="G550" s="2" t="n"/>
+      <c r="F550" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词</t>
+        </is>
+      </c>
+      <c r="G550" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词test，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n"/>
@@ -17083,8 +17292,16 @@
         </is>
       </c>
       <c r="E551" s="2" t="n"/>
-      <c r="F551" s="4" t="n"/>
-      <c r="G551" s="2" t="n"/>
+      <c r="F551" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G551" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1167,9 +1167,19 @@
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="F22" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>60% (15/25)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -15975,7 +15985,7 @@
       </c>
       <c r="G498" s="2" t="n"/>
     </row>
-    <row r="499">
+    <row r="499" ht="48" customHeight="1">
       <c r="A499" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15997,10 +16007,16 @@
         </is>
       </c>
       <c r="E499" s="2" t="n"/>
-      <c r="F499" s="4" t="n"/>
+      <c r="F499" s="7" t="inlineStr">
+        <is>
+          <t>按{"Field": "Sales", "order": "desc"}排序+count=10+groupBy=None — 50.0%
+按{"Field": "Spend", "order": "desc"}排序+count=1000+groupBy=None — 33.3%
+按{"Field": "Spend", "order": "desc"}排序+count=1000+groupBy= — 16.7%</t>
+        </is>
+      </c>
       <c r="G499" s="2" t="n"/>
     </row>
-    <row r="500">
+    <row r="500" ht="16" customHeight="1">
       <c r="A500" s="2" t="n"/>
       <c r="B500" s="2" t="inlineStr">
         <is>
@@ -16018,7 +16034,11 @@
         </is>
       </c>
       <c r="E500" s="2" t="n"/>
-      <c r="F500" s="4" t="n"/>
+      <c r="F500" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G500" s="2" t="n"/>
     </row>
     <row r="501">
@@ -16039,10 +16059,18 @@
         </is>
       </c>
       <c r="E501" s="2" t="n"/>
-      <c r="F501" s="4" t="n"/>
-      <c r="G501" s="2" t="n"/>
-    </row>
-    <row r="502">
+      <c r="F501" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G501" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="48" customHeight="1">
       <c r="A502" s="2" t="n"/>
       <c r="B502" s="2" t="inlineStr">
         <is>
@@ -16060,7 +16088,13 @@
         </is>
       </c>
       <c r="E502" s="2" t="n"/>
-      <c r="F502" s="4" t="n"/>
+      <c r="F502" s="7" t="inlineStr">
+        <is>
+          <t>filter=[{'Field': 'ASINNum', 'Operand': 'Equal', 'Value': '109804147] — 33.3%
+filter=None — 33.3%
+filter=[{'Field': 'ASINNum', 'Operand': 'Contains', 'Value': 'ID1098] — 33.3%</t>
+        </is>
+      </c>
       <c r="G502" s="2" t="n"/>
     </row>
     <row r="503">
@@ -16081,8 +16115,16 @@
         </is>
       </c>
       <c r="E503" s="2" t="n"/>
-      <c r="F503" s="4" t="n"/>
-      <c r="G503" s="2" t="n"/>
+      <c r="F503" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G503" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n"/>
@@ -16102,8 +16144,16 @@
         </is>
       </c>
       <c r="E504" s="2" t="n"/>
-      <c r="F504" s="4" t="n"/>
-      <c r="G504" s="2" t="n"/>
+      <c r="F504" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G504" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n"/>
@@ -16123,10 +16173,18 @@
         </is>
       </c>
       <c r="E505" s="2" t="n"/>
-      <c r="F505" s="4" t="n"/>
-      <c r="G505" s="2" t="n"/>
-    </row>
-    <row r="506">
+      <c r="F505" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G505" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="80" customHeight="1">
       <c r="A506" s="2" t="n"/>
       <c r="B506" s="2" t="inlineStr">
         <is>
@@ -16144,10 +16202,18 @@
         </is>
       </c>
       <c r="E506" s="2" t="n"/>
-      <c r="F506" s="4" t="n"/>
+      <c r="F506" s="7" t="inlineStr">
+        <is>
+          <t>filter=None+按{"Field": "Spend", "order": "desc"}排序+不传campaignTagIds — 60.9%
+filter=[]+按{"Field": "OnlineROASChange", "order": "asc"}排序+按CampaignTag过滤 — 13.0%
+filter=[]+按{"Field": "SalesChange", "order": "asc"}排序+按CampaignTag过滤 — 13.0%
+filter=None+按{"Field": "ROASChange", "order": "asc"}排序+不传campaignTagIds — 8.7%
+filter=[{'Field': 'SpendChange', 'Operand': 'Greater', 'Value': '0'}]+按{"Field": "SpendChange", "order": "desc"}排序+不传campaignTagIds — 4.3%</t>
+        </is>
+      </c>
       <c r="G506" s="2" t="n"/>
     </row>
-    <row r="507">
+    <row r="507" ht="128" customHeight="1">
       <c r="A507" s="2" t="n"/>
       <c r="B507" s="2" t="inlineStr">
         <is>
@@ -16165,10 +16231,21 @@
         </is>
       </c>
       <c r="E507" s="2" t="n"/>
-      <c r="F507" s="4" t="n"/>
+      <c r="F507" s="7" t="inlineStr">
+        <is>
+          <t>filter=None+按{"Field": "Sales", "order": "desc"}排序+count=10+status=None+不传campaignIds+不传campaignTagIds+不传campaignSubTagIds — 35.3%
+filter=None+按{"Field": "Spend", "order": "desc"}排序+count=1000+status=None+不传campaignIds+不传campaignTagIds+不传campaignSubTagIds — 29.4%
+filter=[]+按{"Field": "ROAS", "order": "desc"}排序+count=1000+status=None+无Campaign过滤+不传campaignTagIds+不传campaignSubTagIds — 11.8%
+filter=[]+按{"Field": "Spend", "order": "desc"}排序+count=1000+status=None+无Campaign过滤+不传campaignTagIds+不传campaignSubTagIds — 8.8%
+filter=None+按{"Field": "Sales", "order": "desc"}排序+count=1000+status=None+不传campaignIds+不传campaignTagIds+不传campaignSubTagIds — 5.9%
+filter=None+按{"Field": "Spend", "order": "desc"}排序+count=1000+status=[OutofBudget]+不传campaignIds+不传campaignTagIds+不传campaignSubTagIds — 2.9%
+filter=[]+按{"Field": "Spend", "order": "desc"}排序+count=1000+status=None+无Campaign过滤+按CampaignTag过滤+不传campaignSubTagIds — 2.9%
+filter=[]+按{"Field": "Spend", "order": "desc"}排序+count=1000+status=None+不传campaignIds+按CampaignTag过滤+campaignSubTagIds=[ids+] — 2.9%</t>
+        </is>
+      </c>
       <c r="G507" s="2" t="n"/>
     </row>
-    <row r="508">
+    <row r="508" ht="48" customHeight="1">
       <c r="A508" s="2" t="n"/>
       <c r="B508" s="2" t="inlineStr">
         <is>
@@ -16186,7 +16263,13 @@
         </is>
       </c>
       <c r="E508" s="2" t="n"/>
-      <c r="F508" s="4" t="n"/>
+      <c r="F508" s="7" t="inlineStr">
+        <is>
+          <t>filter=[]+无Campaign过滤+不传campaignTagIds+不传campaignSubTagIds — 50.0%
+filter=None+不传campaignIds+不传campaignTagIds+不传campaignSubTagIds — 25.0%
+filter=[]+不传campaignIds+按CampaignTag过滤+campaignSubTagIds=[ids+] — 25.0%</t>
+        </is>
+      </c>
       <c r="G508" s="2" t="n"/>
     </row>
     <row r="509">
@@ -16207,10 +16290,18 @@
         </is>
       </c>
       <c r="E509" s="2" t="n"/>
-      <c r="F509" s="4" t="n"/>
-      <c r="G509" s="2" t="n"/>
-    </row>
-    <row r="510">
+      <c r="F509" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G509" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="16" customHeight="1">
       <c r="A510" s="2" t="n"/>
       <c r="B510" s="2" t="inlineStr">
         <is>
@@ -16228,7 +16319,11 @@
         </is>
       </c>
       <c r="E510" s="2" t="n"/>
-      <c r="F510" s="4" t="n"/>
+      <c r="F510" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G510" s="2" t="n"/>
     </row>
     <row r="511">
@@ -16249,10 +16344,18 @@
         </is>
       </c>
       <c r="E511" s="2" t="n"/>
-      <c r="F511" s="4" t="n"/>
-      <c r="G511" s="2" t="n"/>
-    </row>
-    <row r="512">
+      <c r="F511" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G511" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="32" customHeight="1">
       <c r="A512" s="2" t="n"/>
       <c r="B512" s="2" t="inlineStr">
         <is>
@@ -16270,10 +16373,15 @@
         </is>
       </c>
       <c r="E512" s="2" t="n"/>
-      <c r="F512" s="4" t="n"/>
+      <c r="F512" s="7" t="inlineStr">
+        <is>
+          <t>filter=[{'Field': 'KeywordText', 'Operand': 'Equal', 'Value': 'unsce]+按{"Field": "ClickChange", "order": "desc"}排序 — 66.7%
+filter=[{'Field': 'CPC', 'Operand': 'Greater', 'Value': 'SuggestedBi]+按{"Field": "CPCChange", "order": "desc"}排序 — 33.3%</t>
+        </is>
+      </c>
       <c r="G512" s="2" t="n"/>
     </row>
-    <row r="513">
+    <row r="513" ht="112" customHeight="1">
       <c r="A513" s="2" t="n"/>
       <c r="B513" s="2" t="inlineStr">
         <is>
@@ -16291,7 +16399,17 @@
         </is>
       </c>
       <c r="E513" s="2" t="n"/>
-      <c r="F513" s="4" t="n"/>
+      <c r="F513" s="7" t="inlineStr">
+        <is>
+          <t>filter=None+按{"Field": "OnlineSales", "order": "desc"}排序+count=5+groupBy=None+不传campaignTagIds+不传campaignSubTagIds — 34.0%
+filter=[{'Field': 'KeywordText', 'Operand': 'Contains', 'Value': 'co]+按{"Field": "Spend", "order": "desc"}排序+count=1000+groupBy=None+不传campaignTagIds+不传campaignSubTagIds — 27.7%
+filter=[{'Field': 'KeywordText', 'Operand': 'Equal', 'Value': 'diape]+按{"Field": "CPC", "order": "asc"}排序+count=1000+groupBy=None+不传campaignTagIds+不传campaignSubTagIds — 25.5%
+filter=[{'Field': 'KeywordText', 'Operand': 'Contains', 'Value': 'de]+按{"Field": "OnlineSales", "order": "desc"}排序+count=30+groupBy=None+不传campaignTagIds+不传campaignSubTagIds — 4.3%
+filter=None+按{"Field": "Spend", "order": "desc"}排序+count=1000+groupBy=None+不传campaignTagIds+不传campaignSubTagIds — 4.3%
+filter=[]+按{"Field": "Sales", "order": "desc"}排序+count=1000+groupBy=None+按CampaignTag过滤+campaignSubTagIds=[ids+] — 2.1%
+filter=None+按{"Field": "Spend", "order": "desc"}排序+count=1000+groupBy=+不传campaignTagIds+不传campaignSubTagIds — 2.1%</t>
+        </is>
+      </c>
       <c r="G513" s="2" t="n"/>
     </row>
     <row r="514">
@@ -16312,10 +16430,18 @@
         </is>
       </c>
       <c r="E514" s="2" t="n"/>
-      <c r="F514" s="4" t="n"/>
-      <c r="G514" s="2" t="n"/>
-    </row>
-    <row r="515">
+      <c r="F514" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G514" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="16" customHeight="1">
       <c r="A515" s="2" t="n"/>
       <c r="B515" s="2" t="inlineStr">
         <is>
@@ -16333,7 +16459,11 @@
         </is>
       </c>
       <c r="E515" s="2" t="n"/>
-      <c r="F515" s="4" t="n"/>
+      <c r="F515" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G515" s="2" t="n"/>
     </row>
     <row r="516">
@@ -16354,10 +16484,18 @@
         </is>
       </c>
       <c r="E516" s="2" t="n"/>
-      <c r="F516" s="4" t="n"/>
-      <c r="G516" s="2" t="n"/>
-    </row>
-    <row r="517">
+      <c r="F516" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G516" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="32" customHeight="1">
       <c r="A517" s="2" t="n"/>
       <c r="B517" s="2" t="inlineStr">
         <is>
@@ -16375,10 +16513,15 @@
         </is>
       </c>
       <c r="E517" s="2" t="n"/>
-      <c r="F517" s="4" t="n"/>
+      <c r="F517" s="7" t="inlineStr">
+        <is>
+          <t>filter=None+status=[Enable] — 50.0%
+filter=[{'Field': 'ASINNum', 'Operand': 'Equal', 'Value': 'frozen ha]+status=None — 50.0%</t>
+        </is>
+      </c>
       <c r="G517" s="2" t="n"/>
     </row>
-    <row r="518">
+    <row r="518" ht="16" customHeight="1">
       <c r="A518" s="2" t="n"/>
       <c r="B518" s="2" t="inlineStr">
         <is>
@@ -16396,10 +16539,14 @@
         </is>
       </c>
       <c r="E518" s="2" t="n"/>
-      <c r="F518" s="4" t="n"/>
+      <c r="F518" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G518" s="2" t="n"/>
     </row>
-    <row r="519">
+    <row r="519" ht="32" customHeight="1">
       <c r="A519" s="2" t="n"/>
       <c r="B519" s="2" t="inlineStr">
         <is>
@@ -16417,10 +16564,15 @@
         </is>
       </c>
       <c r="E519" s="2" t="n"/>
-      <c r="F519" s="4" t="n"/>
+      <c r="F519" s="7" t="inlineStr">
+        <is>
+          <t>groupBy= — 50.0%
+groupBy=None — 50.0%</t>
+        </is>
+      </c>
       <c r="G519" s="2" t="n"/>
     </row>
-    <row r="520">
+    <row r="520" ht="16" customHeight="1">
       <c r="A520" s="2" t="n"/>
       <c r="B520" s="2" t="inlineStr">
         <is>
@@ -16438,7 +16590,11 @@
         </is>
       </c>
       <c r="E520" s="2" t="n"/>
-      <c r="F520" s="4" t="n"/>
+      <c r="F520" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G520" s="2" t="n"/>
     </row>
     <row r="521">
@@ -16459,10 +16615,18 @@
         </is>
       </c>
       <c r="E521" s="2" t="n"/>
-      <c r="F521" s="4" t="n"/>
-      <c r="G521" s="2" t="n"/>
-    </row>
-    <row r="522">
+      <c r="F521" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G521" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="16" customHeight="1">
       <c r="A522" s="2" t="n"/>
       <c r="B522" s="2" t="inlineStr">
         <is>
@@ -16480,7 +16644,11 @@
         </is>
       </c>
       <c r="E522" s="2" t="n"/>
-      <c r="F522" s="4" t="n"/>
+      <c r="F522" s="7" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G522" s="2" t="n"/>
     </row>
     <row r="523">
@@ -16501,8 +16669,16 @@
         </is>
       </c>
       <c r="E523" s="2" t="n"/>
-      <c r="F523" s="4" t="n"/>
-      <c r="G523" s="2" t="n"/>
+      <c r="F523" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G523" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="524" ht="16" customHeight="1">
       <c r="A524" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -867,9 +867,19 @@
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="F12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>28% (5/18)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8150,9 +8160,13 @@
       </c>
       <c r="E208" s="2" t="n"/>
       <c r="F208" s="4" t="n"/>
-      <c r="G208" s="2" t="n"/>
-    </row>
-    <row r="209">
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="48" customHeight="1">
       <c r="A209" s="2" t="n"/>
       <c r="B209" s="2" t="inlineStr">
         <is>
@@ -8170,7 +8184,13 @@
         </is>
       </c>
       <c r="E209" s="2" t="n"/>
-      <c r="F209" s="4" t="n"/>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>CampaignTag预算报表(timeType=ytd) — 37.5%
+CampaignTag预算报表(timeType=date) — 37.5%
+旧版前端参数(citrus/criteoPageInfo) — 25%</t>
+        </is>
+      </c>
       <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
@@ -8192,9 +8212,13 @@
       </c>
       <c r="E210" s="2" t="n"/>
       <c r="F210" s="4" t="n"/>
-      <c r="G210" s="2" t="n"/>
-    </row>
-    <row r="211">
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="32" customHeight="1">
       <c r="A211" s="2" t="n"/>
       <c r="B211" s="2" t="inlineStr">
         <is>
@@ -8212,10 +8236,15 @@
         </is>
       </c>
       <c r="E211" s="2" t="n"/>
-      <c r="F211" s="4" t="n"/>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>按campaignId查询实际花费 — 90%
+按tagId查询实际花费 — 10%</t>
+        </is>
+      </c>
       <c r="G211" s="2" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" ht="16" customHeight="1">
       <c r="A212" s="2" t="n"/>
       <c r="B212" s="2" t="inlineStr">
         <is>
@@ -8233,7 +8262,11 @@
         </is>
       </c>
       <c r="E212" s="2" t="n"/>
-      <c r="F212" s="4" t="n"/>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>按profileIds+campaignIds批量查询</t>
+        </is>
+      </c>
       <c r="G212" s="2" t="n"/>
     </row>
     <row r="213">
@@ -8255,7 +8288,11 @@
       </c>
       <c r="E213" s="2" t="n"/>
       <c r="F213" s="4" t="n"/>
-      <c r="G213" s="2" t="n"/>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -8276,9 +8313,13 @@
       </c>
       <c r="E214" s="2" t="n"/>
       <c r="F214" s="4" t="n"/>
-      <c r="G214" s="2" t="n"/>
-    </row>
-    <row r="215">
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="16" customHeight="1">
       <c r="A215" s="2" t="n"/>
       <c r="B215" s="2" t="inlineStr">
         <is>
@@ -8296,7 +8337,11 @@
         </is>
       </c>
       <c r="E215" s="2" t="n"/>
-      <c r="F215" s="4" t="n"/>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>查询当前用户可用Profile</t>
+        </is>
+      </c>
       <c r="G215" s="2" t="n"/>
     </row>
     <row r="216">
@@ -8318,7 +8363,11 @@
       </c>
       <c r="E216" s="2" t="n"/>
       <c r="F216" s="4" t="n"/>
-      <c r="G216" s="2" t="n"/>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d仅3次真实流量(均为其他client)，直接插入一行Campaign/AdGroup维度日报数据(impressions/clicks/spend/sales等)。全部18个Automation接口中未发现对应删除/回滚endpoint，一旦写入无法撤销，判定为不可逆高危操作，按规则需用户逐条确认方案后才能执行，暂不生成/执行case。另当前数据库故障(见UpdateTargeting备注)也会阻止执行。</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -8339,7 +8388,11 @@
       </c>
       <c r="E217" s="2" t="n"/>
       <c r="F217" s="4" t="n"/>
-      <c r="G217" s="2" t="n"/>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -8360,7 +8413,11 @@
       </c>
       <c r="E218" s="2" t="n"/>
       <c r="F218" s="4" t="n"/>
-      <c r="G218" s="2" t="n"/>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -8381,7 +8438,11 @@
       </c>
       <c r="E219" s="2" t="n"/>
       <c r="F219" s="4" t="n"/>
-      <c r="G219" s="2" t="n"/>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -8402,7 +8463,11 @@
       </c>
       <c r="E220" s="2" t="n"/>
       <c r="F220" s="4" t="n"/>
-      <c r="G220" s="2" t="n"/>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -8423,9 +8488,13 @@
       </c>
       <c r="E221" s="2" t="n"/>
       <c r="F221" s="4" t="n"/>
-      <c r="G221" s="2" t="n"/>
-    </row>
-    <row r="222">
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="16" customHeight="1">
       <c r="A222" s="2" t="n"/>
       <c r="B222" s="2" t="inlineStr">
         <is>
@@ -8443,7 +8512,11 @@
         </is>
       </c>
       <c r="E222" s="2" t="n"/>
-      <c r="F222" s="4" t="n"/>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>按CampaignTag查询自动化报表</t>
+        </is>
+      </c>
       <c r="G222" s="2" t="n"/>
     </row>
     <row r="223">
@@ -8465,7 +8538,11 @@
       </c>
       <c r="E223" s="2" t="n"/>
       <c r="F223" s="4" t="n"/>
-      <c r="G223" s="2" t="n"/>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -8486,7 +8563,11 @@
       </c>
       <c r="E224" s="2" t="n"/>
       <c r="F224" s="4" t="n"/>
-      <c r="G224" s="2" t="n"/>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -8507,7 +8588,11 @@
       </c>
       <c r="E225" s="2" t="n"/>
       <c r="F225" s="4" t="n"/>
-      <c r="G225" s="2" t="n"/>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d真实流量352次(campaignIds或campaignTagIds维度设置targetROAS/targetACOS)。已设计可执行方案：测试campaign 426322(profile 16274451)当前targetACOS/targetROAS均为null，可读原值(null)→改为测试值→尝试复原。探测调用时命中HTTP 500数据库故障"transaction log for database walmart_pacvue is full due to REPLICATION"(与2026-09-15已知故障同一签名，疑似复发)，写操作暂全部无法执行，待数据库恢复后补测，非case设计问题。</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -868,7 +868,7 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>28% (5/18)</t>
+          <t>33% (6/18)</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       <c r="F216" s="4" t="n"/>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>写操作，365d仅3次真实流量(均为其他client)，直接插入一行Campaign/AdGroup维度日报数据(impressions/clicks/spend/sales等)。全部18个Automation接口中未发现对应删除/回滚endpoint，一旦写入无法撤销，判定为不可逆高危操作，按规则需用户逐条确认方案后才能执行，暂不生成/执行case。另当前数据库故障(见UpdateTargeting备注)也会阻止执行。</t>
+          <t>写操作，365d仅3次真实流量(均为其他client)，直接插入一行Campaign/AdGroup维度日报数据(impressions/clicks/spend/sales等)。全部18个Automation接口中未发现对应删除/回滚endpoint，一旦写入无法撤销，判定为不可逆高危操作，按规则需用户逐条确认方案后才能执行，暂不生成/执行case(与数据库故障无关，数据库已恢复但此项仍待用户确认)。</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="16" customHeight="1">
       <c r="A225" s="2" t="n"/>
       <c r="B225" s="2" t="inlineStr">
         <is>
@@ -8587,10 +8587,14 @@
         </is>
       </c>
       <c r="E225" s="2" t="n"/>
-      <c r="F225" s="4" t="n"/>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>按campaignIds设置targetROAS/targetACOS — 84%</t>
+        </is>
+      </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>写操作，365d真实流量352次(campaignIds或campaignTagIds维度设置targetROAS/targetACOS)。已设计可执行方案：测试campaign 426322(profile 16274451)当前targetACOS/targetROAS均为null，可读原值(null)→改为测试值→尝试复原。探测调用时命中HTTP 500数据库故障"transaction log for database walmart_pacvue is full due to REPLICATION"(与2026-09-15已知故障同一签名，疑似复发)，写操作暂全部无法执行，待数据库恢复后补测，非case设计问题。</t>
+          <t>写操作已真实执行(数据库故障已恢复)：测试campaign 426322(profile 16274451)设置targetACOS=15.0/targetROAS=10，2轮验证PASS。探测确认该接口无法还原为null(HTTP 400 Decimal非nullable)，按既有先例接受在完全自控的Paused测试campaign上残留固定测试值，case本身幂等可安全重跑。tagIds/campaignTagIds路径(约16%流量)因无法确认测试账号内tag归属，未覆盖。</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -8365,7 +8365,7 @@
       <c r="F216" s="4" t="n"/>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>写操作，365d仅3次真实流量(均为其他client)，直接插入一行Campaign/AdGroup维度日报数据(impressions/clicks/spend/sales等)。全部18个Automation接口中未发现对应删除/回滚endpoint，一旦写入无法撤销，判定为不可逆高危操作，按规则需用户逐条确认方案后才能执行，暂不生成/执行case(与数据库故障无关，数据库已恢复但此项仍待用户确认)。</t>
+          <t>写操作，365d仅3次真实流量(均为其他client)，直接插入一行Campaign/AdGroup维度日报数据(impressions/clicks/spend/sales等)。全部18个Automation接口中未发现对应删除/回滚endpoint，一旦写入无法撤销，判定为不可逆高危操作。已与用户确认(2026-09-16)：不插入测试/异常数据，本接口不执行，仅记录不覆盖。</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -845,9 +845,19 @@
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>0% (0/17)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7798,8 +7808,16 @@
         </is>
       </c>
       <c r="E191" s="2" t="n"/>
-      <c r="F191" s="4" t="n"/>
-      <c r="G191" s="2" t="n"/>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -7819,8 +7837,16 @@
         </is>
       </c>
       <c r="E192" s="2" t="n"/>
-      <c r="F192" s="4" t="n"/>
-      <c r="G192" s="2" t="n"/>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -7840,8 +7866,16 @@
         </is>
       </c>
       <c r="E193" s="2" t="n"/>
-      <c r="F193" s="4" t="n"/>
-      <c r="G193" s="2" t="n"/>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -7861,8 +7895,16 @@
         </is>
       </c>
       <c r="E194" s="2" t="n"/>
-      <c r="F194" s="4" t="n"/>
-      <c r="G194" s="2" t="n"/>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -7882,8 +7924,16 @@
         </is>
       </c>
       <c r="E195" s="2" t="n"/>
-      <c r="F195" s="4" t="n"/>
-      <c r="G195" s="2" t="n"/>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -7903,8 +7953,16 @@
         </is>
       </c>
       <c r="E196" s="2" t="n"/>
-      <c r="F196" s="4" t="n"/>
-      <c r="G196" s="2" t="n"/>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -7924,8 +7982,16 @@
         </is>
       </c>
       <c r="E197" s="2" t="n"/>
-      <c r="F197" s="4" t="n"/>
-      <c r="G197" s="2" t="n"/>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -7945,8 +8011,16 @@
         </is>
       </c>
       <c r="E198" s="2" t="n"/>
-      <c r="F198" s="4" t="n"/>
-      <c r="G198" s="2" t="n"/>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -7966,8 +8040,16 @@
         </is>
       </c>
       <c r="E199" s="2" t="n"/>
-      <c r="F199" s="4" t="n"/>
-      <c r="G199" s="2" t="n"/>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -7987,8 +8069,16 @@
         </is>
       </c>
       <c r="E200" s="2" t="n"/>
-      <c r="F200" s="4" t="n"/>
-      <c r="G200" s="2" t="n"/>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -8008,8 +8098,16 @@
         </is>
       </c>
       <c r="E201" s="2" t="n"/>
-      <c r="F201" s="4" t="n"/>
-      <c r="G201" s="2" t="n"/>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -8029,8 +8127,16 @@
         </is>
       </c>
       <c r="E202" s="2" t="n"/>
-      <c r="F202" s="4" t="n"/>
-      <c r="G202" s="2" t="n"/>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -8050,8 +8156,16 @@
         </is>
       </c>
       <c r="E203" s="2" t="n"/>
-      <c r="F203" s="4" t="n"/>
-      <c r="G203" s="2" t="n"/>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -8071,8 +8185,16 @@
         </is>
       </c>
       <c r="E204" s="2" t="n"/>
-      <c r="F204" s="4" t="n"/>
-      <c r="G204" s="2" t="n"/>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -8092,8 +8214,16 @@
         </is>
       </c>
       <c r="E205" s="2" t="n"/>
-      <c r="F205" s="4" t="n"/>
-      <c r="G205" s="2" t="n"/>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -8113,8 +8243,16 @@
         </is>
       </c>
       <c r="E206" s="2" t="n"/>
-      <c r="F206" s="4" t="n"/>
-      <c r="G206" s="2" t="n"/>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -8134,8 +8272,16 @@
         </is>
       </c>
       <c r="E207" s="2" t="n"/>
-      <c r="F207" s="4" t="n"/>
-      <c r="G207" s="2" t="n"/>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2179,9 +2179,19 @@
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
+      <c r="F58" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>35% (6/17)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -36145,7 +36155,11 @@
       </c>
       <c r="E1232" s="2" t="n"/>
       <c r="F1232" s="4" t="n"/>
-      <c r="G1232" s="2" t="n"/>
+      <c r="G1232" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d真实流量601次，按recommendationIds直接批量应用推荐(会直接修改推荐所指向的真实Campaign/AdGroup/Keyword等实体的出价/预算/定向)。实测本测试账号(profile 16274451等4个)当前待处理推荐totalCount=0，无自有recommendationId可用；ES真实样本里的recommendationId均属于其他真实客户，应用会直接改动其真实广告设置，不符合"只能动测试账号自己的实体"规则，不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" s="2" t="n"/>
@@ -36166,7 +36180,11 @@
       </c>
       <c r="E1233" s="2" t="n"/>
       <c r="F1233" s="4" t="n"/>
-      <c r="G1233" s="2" t="n"/>
+      <c r="G1233" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d真实流量12次，按recommendationIds批量设置出价(setBidType+targetBid/rate/dValue/max/min)。原因同BatchApply：测试账号无自有待处理推荐，真实recommendationId均属于其他客户，不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="1234">
       <c r="A1234" s="2" t="n"/>
@@ -36187,7 +36205,11 @@
       </c>
       <c r="E1234" s="2" t="n"/>
       <c r="F1234" s="4" t="n"/>
-      <c r="G1234" s="2" t="n"/>
+      <c r="G1234" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d真实流量4次，按recommendationIds批量设置预算，结构与PATCH bid相同。原因同BatchApply：测试账号无自有待处理推荐，不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="1235">
       <c r="A1235" s="2" t="n"/>
@@ -36208,7 +36230,11 @@
       </c>
       <c r="E1235" s="2" t="n"/>
       <c r="F1235" s="4" t="n"/>
-      <c r="G1235" s="2" t="n"/>
+      <c r="G1235" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d真实流量177次，按recommendationIds修改推荐记录的status(接受/忽略等)。原因同BatchApply：测试账号无自有recommendationId，会修改其他客户的推荐记录，不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" s="2" t="n"/>
@@ -36229,7 +36255,11 @@
       </c>
       <c r="E1236" s="2" t="n"/>
       <c r="F1236" s="4" t="n"/>
-      <c r="G1236" s="2" t="n"/>
+      <c r="G1236" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d真实流量1870次，批量插入推荐的"最近14天变更"历史记录(before/after值+profileId/campaignId等)，未发现对应删除/回滚接口。已与用户确认(2026-09-16同类决定)：不插入测试/伪造历史数据，本接口不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" s="2" t="n"/>
@@ -36249,10 +36279,18 @@
         </is>
       </c>
       <c r="E1237" s="2" t="n"/>
-      <c r="F1237" s="4" t="n"/>
-      <c r="G1237" s="2" t="n"/>
-    </row>
-    <row r="1238">
+      <c r="F1237" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1237" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238" ht="16" customHeight="1">
       <c r="A1238" s="2" t="n"/>
       <c r="B1238" s="2" t="inlineStr">
         <is>
@@ -36270,10 +36308,14 @@
         </is>
       </c>
       <c r="E1238" s="2" t="n"/>
-      <c r="F1238" s="4" t="n"/>
+      <c r="F1238" s="7" t="inlineStr">
+        <is>
+          <t>默认场景 — 32%</t>
+        </is>
+      </c>
       <c r="G1238" s="2" t="n"/>
     </row>
-    <row r="1239">
+    <row r="1239" ht="16" customHeight="1">
       <c r="A1239" s="2" t="n"/>
       <c r="B1239" s="2" t="inlineStr">
         <is>
@@ -36291,10 +36333,14 @@
         </is>
       </c>
       <c r="E1239" s="2" t="n"/>
-      <c r="F1239" s="4" t="n"/>
+      <c r="F1239" s="7" t="inlineStr">
+        <is>
+          <t>查询审计汇总</t>
+        </is>
+      </c>
       <c r="G1239" s="2" t="n"/>
     </row>
-    <row r="1240">
+    <row r="1240" ht="16" customHeight="1">
       <c r="A1240" s="2" t="n"/>
       <c r="B1240" s="2" t="inlineStr">
         <is>
@@ -36312,10 +36358,14 @@
         </is>
       </c>
       <c r="E1240" s="2" t="n"/>
-      <c r="F1240" s="4" t="n"/>
+      <c r="F1240" s="7" t="inlineStr">
+        <is>
+          <t>默认场景 — 14%</t>
+        </is>
+      </c>
       <c r="G1240" s="2" t="n"/>
     </row>
-    <row r="1241">
+    <row r="1241" ht="32" customHeight="1">
       <c r="A1241" s="2" t="n"/>
       <c r="B1241" s="2" t="inlineStr">
         <is>
@@ -36333,10 +36383,15 @@
         </is>
       </c>
       <c r="E1241" s="2" t="n"/>
-      <c r="F1241" s="4" t="n"/>
+      <c r="F1241" s="7" t="inlineStr">
+        <is>
+          <t>reportAdType=2 — 38%
+reportAdType=1 — 18%</t>
+        </is>
+      </c>
       <c r="G1241" s="2" t="n"/>
     </row>
-    <row r="1242">
+    <row r="1242" ht="32" customHeight="1">
       <c r="A1242" s="2" t="n"/>
       <c r="B1242" s="2" t="inlineStr">
         <is>
@@ -36354,10 +36409,15 @@
         </is>
       </c>
       <c r="E1242" s="2" t="n"/>
-      <c r="F1242" s="4" t="n"/>
+      <c r="F1242" s="7" t="inlineStr">
+        <is>
+          <t>pageSize=5+reportAdType=2 — 12%
+pageSize=20+reportAdType=1</t>
+        </is>
+      </c>
       <c r="G1242" s="2" t="n"/>
     </row>
-    <row r="1243">
+    <row r="1243" ht="16" customHeight="1">
       <c r="A1243" s="2" t="n"/>
       <c r="B1243" s="2" t="inlineStr">
         <is>
@@ -36375,7 +36435,11 @@
         </is>
       </c>
       <c r="E1243" s="2" t="n"/>
-      <c r="F1243" s="4" t="n"/>
+      <c r="F1243" s="7" t="inlineStr">
+        <is>
+          <t>查询目标ROAS-ACOS设置</t>
+        </is>
+      </c>
       <c r="G1243" s="2" t="n"/>
     </row>
     <row r="1244">
@@ -36397,7 +36461,11 @@
       </c>
       <c r="E1244" s="2" t="n"/>
       <c r="F1244" s="4" t="n"/>
-      <c r="G1244" s="2" t="n"/>
+      <c r="G1244" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365d真实流量16次，接口语义为整体覆盖式保存(detail数组)。实测本clientId(62)当前已有1条真实历史设置(profileId 243137)，探测执行时被Claude Code auto模式安全分类器以"Modify Shared Resources"拦截(请求体包含非测试账号的profileId 243137)，未强行绕过。未执行，需要人工在UI上验证或获得更高权限后再补测。</t>
+        </is>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" s="2" t="n"/>
@@ -36418,7 +36486,11 @@
       </c>
       <c r="E1245" s="2" t="n"/>
       <c r="F1245" s="4" t="n"/>
-      <c r="G1245" s="2" t="n"/>
+      <c r="G1245" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，按规则一律不能调用(无论读写分类)，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" s="2" t="n"/>
@@ -36439,7 +36511,11 @@
       </c>
       <c r="E1246" s="2" t="n"/>
       <c r="F1246" s="4" t="n"/>
-      <c r="G1246" s="2" t="n"/>
+      <c r="G1246" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1247">
       <c r="A1247" s="2" t="n"/>
@@ -36460,7 +36536,11 @@
       </c>
       <c r="E1247" s="2" t="n"/>
       <c r="F1247" s="4" t="n"/>
-      <c r="G1247" s="2" t="n"/>
+      <c r="G1247" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，按规则一律不能调用，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" s="2" t="n"/>
@@ -36481,7 +36561,11 @@
       </c>
       <c r="E1248" s="2" t="n"/>
       <c r="F1248" s="4" t="n"/>
-      <c r="G1248" s="2" t="n"/>
+      <c r="G1248" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，按规则一律不能调用，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1249">
       <c r="A1249" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2049,9 +2049,19 @@
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
+      <c r="F53" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>94% (15/16)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -33925,7 +33935,7 @@
       <c r="F1146" s="4" t="n"/>
       <c r="G1146" s="2" t="n"/>
     </row>
-    <row r="1147">
+    <row r="1147" ht="16" customHeight="1">
       <c r="A1147" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -33947,7 +33957,11 @@
         </is>
       </c>
       <c r="E1147" s="2" t="n"/>
-      <c r="F1147" s="4" t="n"/>
+      <c r="F1147" s="7" t="inlineStr">
+        <is>
+          <t>查询通知总览</t>
+        </is>
+      </c>
       <c r="G1147" s="2" t="n"/>
     </row>
     <row r="1148">
@@ -33971,7 +33985,7 @@
       <c r="F1148" s="4" t="n"/>
       <c r="G1148" s="2" t="n"/>
     </row>
-    <row r="1149">
+    <row r="1149" ht="16" customHeight="1">
       <c r="A1149" s="2" t="n"/>
       <c r="B1149" s="2" t="inlineStr">
         <is>
@@ -33989,7 +34003,11 @@
         </is>
       </c>
       <c r="E1149" s="2" t="n"/>
-      <c r="F1149" s="4" t="n"/>
+      <c r="F1149" s="7" t="inlineStr">
+        <is>
+          <t>设置实际花费提醒后还原</t>
+        </is>
+      </c>
       <c r="G1149" s="2" t="n"/>
     </row>
     <row r="1150">
@@ -34013,7 +34031,7 @@
       <c r="F1150" s="4" t="n"/>
       <c r="G1150" s="2" t="n"/>
     </row>
-    <row r="1151">
+    <row r="1151" ht="16" customHeight="1">
       <c r="A1151" s="2" t="n"/>
       <c r="B1151" s="2" t="inlineStr">
         <is>
@@ -34031,10 +34049,14 @@
         </is>
       </c>
       <c r="E1151" s="2" t="n"/>
-      <c r="F1151" s="4" t="n"/>
+      <c r="F1151" s="7" t="inlineStr">
+        <is>
+          <t>首次设置预算不足提醒</t>
+        </is>
+      </c>
       <c r="G1151" s="2" t="n"/>
     </row>
-    <row r="1152">
+    <row r="1152" ht="16" customHeight="1">
       <c r="A1152" s="2" t="n"/>
       <c r="B1152" s="2" t="inlineStr">
         <is>
@@ -34052,7 +34074,11 @@
         </is>
       </c>
       <c r="E1152" s="2" t="n"/>
-      <c r="F1152" s="4" t="n"/>
+      <c r="F1152" s="7" t="inlineStr">
+        <is>
+          <t>设置商品健康度提醒后还原</t>
+        </is>
+      </c>
       <c r="G1152" s="2" t="n"/>
     </row>
     <row r="1153">
@@ -34097,7 +34123,7 @@
       <c r="F1154" s="4" t="n"/>
       <c r="G1154" s="2" t="n"/>
     </row>
-    <row r="1155">
+    <row r="1155" ht="16" customHeight="1">
       <c r="A1155" s="2" t="n"/>
       <c r="B1155" s="2" t="inlineStr">
         <is>
@@ -34115,10 +34141,14 @@
         </is>
       </c>
       <c r="E1155" s="2" t="n"/>
-      <c r="F1155" s="4" t="n"/>
+      <c r="F1155" s="7" t="inlineStr">
+        <is>
+          <t>设置日预算耗尽提醒后还原</t>
+        </is>
+      </c>
       <c r="G1155" s="2" t="n"/>
     </row>
-    <row r="1156">
+    <row r="1156" ht="16" customHeight="1">
       <c r="A1156" s="2" t="n"/>
       <c r="B1156" s="2" t="inlineStr">
         <is>
@@ -34136,7 +34166,11 @@
         </is>
       </c>
       <c r="E1156" s="2" t="n"/>
-      <c r="F1156" s="4" t="n"/>
+      <c r="F1156" s="7" t="inlineStr">
+        <is>
+          <t>创建自定义提醒规则后清理</t>
+        </is>
+      </c>
       <c r="G1156" s="2" t="n"/>
     </row>
     <row r="1157">
@@ -34181,7 +34215,7 @@
       <c r="F1158" s="4" t="n"/>
       <c r="G1158" s="2" t="n"/>
     </row>
-    <row r="1159">
+    <row r="1159" ht="16" customHeight="1">
       <c r="A1159" s="2" t="n"/>
       <c r="B1159" s="2" t="inlineStr">
         <is>
@@ -34199,7 +34233,11 @@
         </is>
       </c>
       <c r="E1159" s="2" t="n"/>
-      <c r="F1159" s="4" t="n"/>
+      <c r="F1159" s="7" t="inlineStr">
+        <is>
+          <t>按targetType查询</t>
+        </is>
+      </c>
       <c r="G1159" s="2" t="n"/>
     </row>
     <row r="1160">
@@ -34220,10 +34258,18 @@
         </is>
       </c>
       <c r="E1160" s="2" t="n"/>
-      <c r="F1160" s="4" t="n"/>
-      <c r="G1160" s="2" t="n"/>
-    </row>
-    <row r="1161">
+      <c r="F1160" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1160" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161" ht="16" customHeight="1">
       <c r="A1161" s="2" t="n"/>
       <c r="B1161" s="2" t="inlineStr">
         <is>
@@ -34241,10 +34287,14 @@
         </is>
       </c>
       <c r="E1161" s="2" t="n"/>
-      <c r="F1161" s="4" t="n"/>
+      <c r="F1161" s="7" t="inlineStr">
+        <is>
+          <t>切换推荐提醒开关</t>
+        </is>
+      </c>
       <c r="G1161" s="2" t="n"/>
     </row>
-    <row r="1162">
+    <row r="1162" ht="16" customHeight="1">
       <c r="A1162" s="2" t="n"/>
       <c r="B1162" s="2" t="inlineStr">
         <is>
@@ -34262,7 +34312,11 @@
         </is>
       </c>
       <c r="E1162" s="2" t="n"/>
-      <c r="F1162" s="4" t="n"/>
+      <c r="F1162" s="7" t="inlineStr">
+        <is>
+          <t>切换分类通知开关后还原</t>
+        </is>
+      </c>
       <c r="G1162" s="2" t="n"/>
     </row>
     <row r="1163">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1649,9 +1649,19 @@
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="F38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>8% (1/13)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -29070,8 +29080,16 @@
         </is>
       </c>
       <c r="E957" s="2" t="n"/>
-      <c r="F957" s="4" t="n"/>
-      <c r="G957" s="2" t="n"/>
+      <c r="F957" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G957" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n"/>
@@ -29091,8 +29109,16 @@
         </is>
       </c>
       <c r="E958" s="2" t="n"/>
-      <c r="F958" s="4" t="n"/>
-      <c r="G958" s="2" t="n"/>
+      <c r="F958" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G958" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" s="2" t="n"/>
@@ -29112,8 +29138,16 @@
         </is>
       </c>
       <c r="E959" s="2" t="n"/>
-      <c r="F959" s="4" t="n"/>
-      <c r="G959" s="2" t="n"/>
+      <c r="F959" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G959" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n"/>
@@ -29133,8 +29167,16 @@
         </is>
       </c>
       <c r="E960" s="2" t="n"/>
-      <c r="F960" s="4" t="n"/>
-      <c r="G960" s="2" t="n"/>
+      <c r="F960" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G960" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" s="2" t="n"/>
@@ -29154,10 +29196,18 @@
         </is>
       </c>
       <c r="E961" s="2" t="n"/>
-      <c r="F961" s="4" t="n"/>
-      <c r="G961" s="2" t="n"/>
-    </row>
-    <row r="962">
+      <c r="F961" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G961" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="962" ht="32" customHeight="1">
       <c r="A962" s="2" t="n"/>
       <c r="B962" s="2" t="inlineStr">
         <is>
@@ -29175,7 +29225,12 @@
         </is>
       </c>
       <c r="E962" s="2" t="n"/>
-      <c r="F962" s="4" t="n"/>
+      <c r="F962" s="7" t="inlineStr">
+        <is>
+          <t>timeType=weekly主流场景 — 90.6%
+timeType=custom场景 — 3.1%</t>
+        </is>
+      </c>
       <c r="G962" s="2" t="n"/>
     </row>
     <row r="963">
@@ -29196,8 +29251,16 @@
         </is>
       </c>
       <c r="E963" s="2" t="n"/>
-      <c r="F963" s="4" t="n"/>
-      <c r="G963" s="2" t="n"/>
+      <c r="F963" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G963" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n"/>
@@ -29217,8 +29280,16 @@
         </is>
       </c>
       <c r="E964" s="2" t="n"/>
-      <c r="F964" s="4" t="n"/>
-      <c r="G964" s="2" t="n"/>
+      <c r="F964" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G964" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" s="2" t="n"/>
@@ -29238,8 +29309,16 @@
         </is>
       </c>
       <c r="E965" s="2" t="n"/>
-      <c r="F965" s="4" t="n"/>
-      <c r="G965" s="2" t="n"/>
+      <c r="F965" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G965" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n"/>
@@ -29259,8 +29338,16 @@
         </is>
       </c>
       <c r="E966" s="2" t="n"/>
-      <c r="F966" s="4" t="n"/>
-      <c r="G966" s="2" t="n"/>
+      <c r="F966" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G966" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="967">
       <c r="A967" s="2" t="n"/>
@@ -29280,8 +29367,16 @@
         </is>
       </c>
       <c r="E967" s="2" t="n"/>
-      <c r="F967" s="4" t="n"/>
-      <c r="G967" s="2" t="n"/>
+      <c r="F967" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G967" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n"/>
@@ -29301,8 +29396,16 @@
         </is>
       </c>
       <c r="E968" s="2" t="n"/>
-      <c r="F968" s="4" t="n"/>
-      <c r="G968" s="2" t="n"/>
+      <c r="F968" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G968" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="969">
       <c r="A969" s="2" t="n"/>
@@ -29322,8 +29425,16 @@
         </is>
       </c>
       <c r="E969" s="2" t="n"/>
-      <c r="F969" s="4" t="n"/>
-      <c r="G969" s="2" t="n"/>
+      <c r="F969" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G969" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="970">
       <c r="A970" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2361,9 +2361,19 @@
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>0% (0/13)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -40137,8 +40147,16 @@
         </is>
       </c>
       <c r="E1370" s="2" t="n"/>
-      <c r="F1370" s="4" t="n"/>
-      <c r="G1370" s="2" t="n"/>
+      <c r="F1370" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1370" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已用不排除clientId的宽松查询交叉验证过，确认非查询bug)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1371">
       <c r="A1371" s="2" t="n"/>
@@ -40158,8 +40176,16 @@
         </is>
       </c>
       <c r="E1371" s="2" t="n"/>
-      <c r="F1371" s="4" t="n"/>
-      <c r="G1371" s="2" t="n"/>
+      <c r="F1371" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1371" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1372">
       <c r="A1372" s="2" t="n"/>
@@ -40180,7 +40206,11 @@
       </c>
       <c r="E1372" s="2" t="n"/>
       <c r="F1372" s="4" t="n"/>
-      <c r="G1372" s="2" t="n"/>
+      <c r="G1372" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Init"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1373">
       <c r="A1373" s="2" t="n"/>
@@ -40201,7 +40231,11 @@
       </c>
       <c r="E1373" s="2" t="n"/>
       <c r="F1373" s="4" t="n"/>
-      <c r="G1373" s="2" t="n"/>
+      <c r="G1373" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Init"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1374">
       <c r="A1374" s="2" t="n"/>
@@ -40221,8 +40255,16 @@
         </is>
       </c>
       <c r="E1374" s="2" t="n"/>
-      <c r="F1374" s="4" t="n"/>
-      <c r="G1374" s="2" t="n"/>
+      <c r="F1374" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1374" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1375">
       <c r="A1375" s="2" t="n"/>
@@ -40242,8 +40284,16 @@
         </is>
       </c>
       <c r="E1375" s="2" t="n"/>
-      <c r="F1375" s="4" t="n"/>
-      <c r="G1375" s="2" t="n"/>
+      <c r="F1375" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1375" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" s="2" t="n"/>
@@ -40263,8 +40313,16 @@
         </is>
       </c>
       <c r="E1376" s="2" t="n"/>
-      <c r="F1376" s="4" t="n"/>
-      <c r="G1376" s="2" t="n"/>
+      <c r="F1376" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1376" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1377">
       <c r="A1377" s="2" t="n"/>
@@ -40284,8 +40342,16 @@
         </is>
       </c>
       <c r="E1377" s="2" t="n"/>
-      <c r="F1377" s="4" t="n"/>
-      <c r="G1377" s="2" t="n"/>
+      <c r="F1377" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1377" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1378">
       <c r="A1378" s="2" t="n"/>
@@ -40305,8 +40371,16 @@
         </is>
       </c>
       <c r="E1378" s="2" t="n"/>
-      <c r="F1378" s="4" t="n"/>
-      <c r="G1378" s="2" t="n"/>
+      <c r="F1378" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1378" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已用不排除clientId的宽松查询交叉验证过)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1379">
       <c r="A1379" s="2" t="n"/>
@@ -40326,8 +40400,16 @@
         </is>
       </c>
       <c r="E1379" s="2" t="n"/>
-      <c r="F1379" s="4" t="n"/>
-      <c r="G1379" s="2" t="n"/>
+      <c r="F1379" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1379" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已用不排除clientId的宽松查询交叉验证过)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1380">
       <c r="A1380" s="2" t="n"/>
@@ -40347,8 +40429,16 @@
         </is>
       </c>
       <c r="E1380" s="2" t="n"/>
-      <c r="F1380" s="4" t="n"/>
-      <c r="G1380" s="2" t="n"/>
+      <c r="F1380" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1380" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1381">
       <c r="A1381" s="2" t="n"/>
@@ -40368,8 +40458,16 @@
         </is>
       </c>
       <c r="E1381" s="2" t="n"/>
-      <c r="F1381" s="4" t="n"/>
-      <c r="G1381" s="2" t="n"/>
+      <c r="F1381" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1381" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1382">
       <c r="A1382" s="2" t="n"/>
@@ -40389,8 +40487,16 @@
         </is>
       </c>
       <c r="E1382" s="2" t="n"/>
-      <c r="F1382" s="4" t="n"/>
-      <c r="G1382" s="2" t="n"/>
+      <c r="F1382" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1382" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已用不排除clientId的宽松查询交叉验证过)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1383">
       <c r="A1383" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1725,9 +1725,19 @@
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+      <c r="F41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>67% (8/12)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -29647,7 +29657,7 @@
       <c r="F978" s="4" t="n"/>
       <c r="G978" s="2" t="n"/>
     </row>
-    <row r="979">
+    <row r="979" ht="16" customHeight="1">
       <c r="A979" s="2" t="n"/>
       <c r="B979" s="2" t="inlineStr">
         <is>
@@ -29665,7 +29675,11 @@
         </is>
       </c>
       <c r="E979" s="2" t="n"/>
-      <c r="F979" s="4" t="n"/>
+      <c r="F979" s="7" t="inlineStr">
+        <is>
+          <t>创建后修改+验证+查状态</t>
+        </is>
+      </c>
       <c r="G979" s="2" t="n"/>
     </row>
     <row r="980">
@@ -29710,7 +29724,7 @@
       <c r="F981" s="4" t="n"/>
       <c r="G981" s="2" t="n"/>
     </row>
-    <row r="982">
+    <row r="982" ht="16" customHeight="1">
       <c r="A982" s="2" t="n"/>
       <c r="B982" s="2" t="inlineStr">
         <is>
@@ -29728,10 +29742,14 @@
         </is>
       </c>
       <c r="E982" s="2" t="n"/>
-      <c r="F982" s="4" t="n"/>
+      <c r="F982" s="7" t="inlineStr">
+        <is>
+          <t>默认场景(测量类型)</t>
+        </is>
+      </c>
       <c r="G982" s="2" t="n"/>
     </row>
-    <row r="983">
+    <row r="983" ht="16" customHeight="1">
       <c r="A983" s="2" t="n"/>
       <c r="B983" s="2" t="inlineStr">
         <is>
@@ -29749,7 +29767,11 @@
         </is>
       </c>
       <c r="E983" s="2" t="n"/>
-      <c r="F983" s="4" t="n"/>
+      <c r="F983" s="7" t="inlineStr">
+        <is>
+          <t>默认无过滤分页查询</t>
+        </is>
+      </c>
       <c r="G983" s="2" t="n"/>
     </row>
     <row r="984">
@@ -29770,8 +29792,16 @@
         </is>
       </c>
       <c r="E984" s="2" t="n"/>
-      <c r="F984" s="4" t="n"/>
-      <c r="G984" s="2" t="n"/>
+      <c r="F984" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G984" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n"/>
@@ -29792,7 +29822,11 @@
       </c>
       <c r="E985" s="2" t="n"/>
       <c r="F985" s="4" t="n"/>
-      <c r="G985" s="2" t="n"/>
+      <c r="G985" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，按规则一律不能调用(尽管365天1269次真实流量)，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n"/>
@@ -29812,8 +29846,16 @@
         </is>
       </c>
       <c r="E986" s="2" t="n"/>
-      <c r="F986" s="4" t="n"/>
-      <c r="G986" s="2" t="n"/>
+      <c r="F986" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G986" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n"/>
@@ -29834,7 +29876,11 @@
       </c>
       <c r="E987" s="2" t="n"/>
       <c r="F987" s="4" t="n"/>
-      <c r="G987" s="2" t="n"/>
+      <c r="G987" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n"/>
@@ -29857,7 +29903,7 @@
       <c r="F988" s="4" t="n"/>
       <c r="G988" s="2" t="n"/>
     </row>
-    <row r="989">
+    <row r="989" ht="16" customHeight="1">
       <c r="A989" s="2" t="n"/>
       <c r="B989" s="2" t="inlineStr">
         <is>
@@ -29875,7 +29921,11 @@
         </is>
       </c>
       <c r="E989" s="2" t="n"/>
-      <c r="F989" s="4" t="n"/>
+      <c r="F989" s="7" t="inlineStr">
+        <is>
+          <t>改名(发现问题)</t>
+        </is>
+      </c>
       <c r="G989" s="2" t="n"/>
     </row>
     <row r="990">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2025,9 +2025,19 @@
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>10% (1/10)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -33699,7 +33709,7 @@
       <c r="F1127" s="4" t="n"/>
       <c r="G1127" s="2" t="n"/>
     </row>
-    <row r="1128">
+    <row r="1128" ht="16" customHeight="1">
       <c r="A1128" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -33721,7 +33731,11 @@
         </is>
       </c>
       <c r="E1128" s="2" t="n"/>
-      <c r="F1128" s="4" t="n"/>
+      <c r="F1128" s="7" t="inlineStr">
+        <is>
+          <t>查询监控关键词标签列表</t>
+        </is>
+      </c>
       <c r="G1128" s="2" t="n"/>
     </row>
     <row r="1129">
@@ -33742,8 +33756,16 @@
         </is>
       </c>
       <c r="E1129" s="2" t="n"/>
-      <c r="F1129" s="4" t="n"/>
-      <c r="G1129" s="2" t="n"/>
+      <c r="F1129" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1129" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId的宽松查询交叉验证同样为0，非查询bug)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" s="2" t="n"/>
@@ -33763,8 +33785,16 @@
         </is>
       </c>
       <c r="E1130" s="2" t="n"/>
-      <c r="F1130" s="4" t="n"/>
-      <c r="G1130" s="2" t="n"/>
+      <c r="F1130" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1130" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1131">
       <c r="A1131" s="2" t="n"/>
@@ -33784,8 +33814,16 @@
         </is>
       </c>
       <c r="E1131" s="2" t="n"/>
-      <c r="F1131" s="4" t="n"/>
-      <c r="G1131" s="2" t="n"/>
+      <c r="F1131" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1131" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1132">
       <c r="A1132" s="2" t="n"/>
@@ -33805,8 +33843,16 @@
         </is>
       </c>
       <c r="E1132" s="2" t="n"/>
-      <c r="F1132" s="4" t="n"/>
-      <c r="G1132" s="2" t="n"/>
+      <c r="F1132" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1132" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1133">
       <c r="A1133" s="2" t="n"/>
@@ -33826,8 +33872,16 @@
         </is>
       </c>
       <c r="E1133" s="2" t="n"/>
-      <c r="F1133" s="4" t="n"/>
-      <c r="G1133" s="2" t="n"/>
+      <c r="F1133" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1133" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1134">
       <c r="A1134" s="2" t="n"/>
@@ -33847,8 +33901,16 @@
         </is>
       </c>
       <c r="E1134" s="2" t="n"/>
-      <c r="F1134" s="4" t="n"/>
-      <c r="G1134" s="2" t="n"/>
+      <c r="F1134" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1134" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已用宽松查询交叉验证)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1135">
       <c r="A1135" s="2" t="n"/>
@@ -33868,8 +33930,16 @@
         </is>
       </c>
       <c r="E1135" s="2" t="n"/>
-      <c r="F1135" s="4" t="n"/>
-      <c r="G1135" s="2" t="n"/>
+      <c r="F1135" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1135" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1136">
       <c r="A1136" s="2" t="n"/>
@@ -33889,8 +33959,16 @@
         </is>
       </c>
       <c r="E1136" s="2" t="n"/>
-      <c r="F1136" s="4" t="n"/>
-      <c r="G1136" s="2" t="n"/>
+      <c r="F1136" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1136" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已用宽松查询交叉验证)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" s="2" t="n"/>
@@ -33910,8 +33988,16 @@
         </is>
       </c>
       <c r="E1137" s="2" t="n"/>
-      <c r="F1137" s="4" t="n"/>
-      <c r="G1137" s="2" t="n"/>
+      <c r="F1137" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1137" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1138">
       <c r="A1138" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -823,9 +823,19 @@
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="F10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>44% (4/9)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7653,7 +7663,7 @@
         </is>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="16" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7675,7 +7685,11 @@
         </is>
       </c>
       <c r="E182" s="2" t="n"/>
-      <c r="F182" s="4" t="n"/>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>创建ITEM PROPENSITY类型受众后修改</t>
+        </is>
+      </c>
       <c r="G182" s="2" t="n"/>
     </row>
     <row r="183">
@@ -7717,8 +7731,16 @@
         </is>
       </c>
       <c r="E184" s="2" t="n"/>
-      <c r="F184" s="4" t="n"/>
-      <c r="G184" s="2" t="n"/>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -7738,10 +7760,18 @@
         </is>
       </c>
       <c r="E185" s="2" t="n"/>
-      <c r="F185" s="4" t="n"/>
-      <c r="G185" s="2" t="n"/>
-    </row>
-    <row r="186">
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="32" customHeight="1">
       <c r="A186" s="2" t="n"/>
       <c r="B186" s="2" t="inlineStr">
         <is>
@@ -7759,7 +7789,12 @@
         </is>
       </c>
       <c r="E186" s="2" t="n"/>
-      <c r="F186" s="4" t="n"/>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>RULE BASED购买行为估算
+ADVANCED空条件(边界场景)</t>
+        </is>
+      </c>
       <c r="G186" s="2" t="n"/>
     </row>
     <row r="187">
@@ -7781,9 +7816,13 @@
       </c>
       <c r="E187" s="2" t="n"/>
       <c r="F187" s="4" t="n"/>
-      <c r="G187" s="2" t="n"/>
-    </row>
-    <row r="188">
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"sync"，按规则一律不能调用(尽管365天297次真实流量)，不生成/执行case</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="16" customHeight="1">
       <c r="A188" s="2" t="n"/>
       <c r="B188" s="2" t="inlineStr">
         <is>
@@ -7801,7 +7840,11 @@
         </is>
       </c>
       <c r="E188" s="2" t="n"/>
-      <c r="F188" s="4" t="n"/>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询受众列表</t>
+        </is>
+      </c>
       <c r="G188" s="2" t="n"/>
     </row>
     <row r="189">
@@ -7822,8 +7865,16 @@
         </is>
       </c>
       <c r="E189" s="2" t="n"/>
-      <c r="F189" s="4" t="n"/>
-      <c r="G189" s="2" t="n"/>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -7844,7 +7895,11 @@
       </c>
       <c r="E190" s="2" t="n"/>
       <c r="F190" s="4" t="n"/>
-      <c r="G190" s="2" t="n"/>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"sync"，且365天仅4次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1529,9 +1529,19 @@
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="F33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>22% (2/9)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -27672,10 +27682,18 @@
         </is>
       </c>
       <c r="E900" s="2" t="n"/>
-      <c r="F900" s="4" t="n"/>
-      <c r="G900" s="2" t="n"/>
-    </row>
-    <row r="901">
+      <c r="F900" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G900" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="901" ht="16" customHeight="1">
       <c r="A901" s="2" t="n"/>
       <c r="B901" s="2" t="inlineStr">
         <is>
@@ -27693,7 +27711,11 @@
         </is>
       </c>
       <c r="E901" s="2" t="n"/>
-      <c r="F901" s="4" t="n"/>
+      <c r="F901" s="7" t="inlineStr">
+        <is>
+          <t>ProfileId为空字符串(高频真实场景，发现bug)</t>
+        </is>
+      </c>
       <c r="G901" s="2" t="n"/>
     </row>
     <row r="902">
@@ -27714,8 +27736,16 @@
         </is>
       </c>
       <c r="E902" s="2" t="n"/>
-      <c r="F902" s="4" t="n"/>
-      <c r="G902" s="2" t="n"/>
+      <c r="F902" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G902" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n"/>
@@ -27735,8 +27765,16 @@
         </is>
       </c>
       <c r="E903" s="2" t="n"/>
-      <c r="F903" s="4" t="n"/>
-      <c r="G903" s="2" t="n"/>
+      <c r="F903" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G903" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n"/>
@@ -27756,8 +27794,16 @@
         </is>
       </c>
       <c r="E904" s="2" t="n"/>
-      <c r="F904" s="4" t="n"/>
-      <c r="G904" s="2" t="n"/>
+      <c r="F904" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G904" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n"/>
@@ -27778,7 +27824,11 @@
       </c>
       <c r="E905" s="2" t="n"/>
       <c r="F905" s="4" t="n"/>
-      <c r="G905" s="2" t="n"/>
+      <c r="G905" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n"/>
@@ -27799,9 +27849,13 @@
       </c>
       <c r="E906" s="2" t="n"/>
       <c r="F906" s="4" t="n"/>
-      <c r="G906" s="2" t="n"/>
-    </row>
-    <row r="907">
+      <c r="G906" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="907" ht="16" customHeight="1">
       <c r="A907" s="2" t="n"/>
       <c r="B907" s="2" t="inlineStr">
         <is>
@@ -27819,7 +27873,11 @@
         </is>
       </c>
       <c r="E907" s="2" t="n"/>
-      <c r="F907" s="4" t="n"/>
+      <c r="F907" s="7" t="inlineStr">
+        <is>
+          <t>查询文件夹树</t>
+        </is>
+      </c>
       <c r="G907" s="2" t="n"/>
     </row>
     <row r="908">
@@ -27840,8 +27898,16 @@
         </is>
       </c>
       <c r="E908" s="2" t="n"/>
-      <c r="F908" s="4" t="n"/>
-      <c r="G908" s="2" t="n"/>
+      <c r="F908" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G908" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2077,9 +2077,19 @@
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
+      <c r="F52" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>44% (4/9)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -34142,8 +34152,16 @@
         </is>
       </c>
       <c r="E1138" s="2" t="n"/>
-      <c r="F1138" s="4" t="n"/>
-      <c r="G1138" s="2" t="n"/>
+      <c r="F1138" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1138" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" s="2" t="n"/>
@@ -34163,8 +34181,16 @@
         </is>
       </c>
       <c r="E1139" s="2" t="n"/>
-      <c r="F1139" s="4" t="n"/>
-      <c r="G1139" s="2" t="n"/>
+      <c r="F1139" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1139" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" s="2" t="n"/>
@@ -34187,7 +34213,7 @@
       <c r="F1140" s="4" t="n"/>
       <c r="G1140" s="2" t="n"/>
     </row>
-    <row r="1141">
+    <row r="1141" ht="16" customHeight="1">
       <c r="A1141" s="2" t="n"/>
       <c r="B1141" s="2" t="inlineStr">
         <is>
@@ -34205,7 +34231,11 @@
         </is>
       </c>
       <c r="E1141" s="2" t="n"/>
-      <c r="F1141" s="4" t="n"/>
+      <c r="F1141" s="7" t="inlineStr">
+        <is>
+          <t>创建后禁用</t>
+        </is>
+      </c>
       <c r="G1141" s="2" t="n"/>
     </row>
     <row r="1142">
@@ -34226,10 +34256,18 @@
         </is>
       </c>
       <c r="E1142" s="2" t="n"/>
-      <c r="F1142" s="4" t="n"/>
-      <c r="G1142" s="2" t="n"/>
-    </row>
-    <row r="1143">
+      <c r="F1142" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1142" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，且属于按筛选条件批量操作(ByCondition)的高危类别，双重原因不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143" ht="16" customHeight="1">
       <c r="A1143" s="2" t="n"/>
       <c r="B1143" s="2" t="inlineStr">
         <is>
@@ -34247,10 +34285,14 @@
         </is>
       </c>
       <c r="E1143" s="2" t="n"/>
-      <c r="F1143" s="4" t="n"/>
+      <c r="F1143" s="7" t="inlineStr">
+        <is>
+          <t>校验可否作为否定词添加</t>
+        </is>
+      </c>
       <c r="G1143" s="2" t="n"/>
     </row>
-    <row r="1144">
+    <row r="1144" ht="16" customHeight="1">
       <c r="A1144" s="2" t="n"/>
       <c r="B1144" s="2" t="inlineStr">
         <is>
@@ -34268,7 +34310,11 @@
         </is>
       </c>
       <c r="E1144" s="2" t="n"/>
-      <c r="F1144" s="4" t="n"/>
+      <c r="F1144" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询</t>
+        </is>
+      </c>
       <c r="G1144" s="2" t="n"/>
     </row>
     <row r="1145">
@@ -34290,7 +34336,11 @@
       </c>
       <c r="E1145" s="2" t="n"/>
       <c r="F1145" s="4" t="n"/>
-      <c r="G1145" s="2" t="n"/>
+      <c r="G1145" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调接口(请求体含PageInfo/ExportedColumns，365天106次真实调用)，按项目惯例异步导出类接口只标注不生成执行</t>
+        </is>
+      </c>
     </row>
     <row r="1146">
       <c r="A1146" s="2" t="n"/>
@@ -34310,8 +34360,16 @@
         </is>
       </c>
       <c r="E1146" s="2" t="n"/>
-      <c r="F1146" s="4" t="n"/>
-      <c r="G1146" s="2" t="n"/>
+      <c r="F1146" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1146" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，且属于按筛选条件批量操作(ByCondition)的高危类别，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1147" ht="16" customHeight="1">
       <c r="A1147" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1475,9 +1475,19 @@
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>50% (4/8)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -26657,7 +26667,7 @@
         </is>
       </c>
     </row>
-    <row r="862">
+    <row r="862" ht="16" customHeight="1">
       <c r="A862" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26679,7 +26689,11 @@
         </is>
       </c>
       <c r="E862" s="2" t="n"/>
-      <c r="F862" s="4" t="n"/>
+      <c r="F862" s="7" t="inlineStr">
+        <is>
+          <t>创建后改名+暂停+关联ItemSet</t>
+        </is>
+      </c>
       <c r="G862" s="2" t="n"/>
     </row>
     <row r="863">
@@ -26722,7 +26736,11 @@
       </c>
       <c r="E864" s="2" t="n"/>
       <c r="F864" s="4" t="n"/>
-      <c r="G864" s="2" t="n"/>
+      <c r="G864" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365天46次真实调用，需要一个已存在的真实adGroupId作为复制模板(campaignCreatedRequest+adGroupRequestParams[{adGroupId,...}])。测试账号display sandbox profile 16354252下探测DisplayAdGroups/list未查到可用adGroupId(返回空列表)，未能安全构造出使用自有adGroupId的测试用例，技术受限未执行，未使用ES真实样本中其他客户的adGroupId(会复制生成基于他人配置的新campaign)。</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n"/>
@@ -26743,7 +26761,11 @@
       </c>
       <c r="E865" s="2" t="n"/>
       <c r="F865" s="4" t="n"/>
-      <c r="G865" s="2" t="n"/>
+      <c r="G865" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365天64次真实调用，同adGroupCopied需要真实adGroupId模板，技术受限原因相同，未执行。</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n"/>
@@ -26805,8 +26827,16 @@
         </is>
       </c>
       <c r="E868" s="2" t="n"/>
-      <c r="F868" s="4" t="n"/>
-      <c r="G868" s="2" t="n"/>
+      <c r="F868" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G868" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n"/>
@@ -26826,8 +26856,16 @@
         </is>
       </c>
       <c r="E869" s="2" t="n"/>
-      <c r="F869" s="4" t="n"/>
-      <c r="G869" s="2" t="n"/>
+      <c r="F869" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G869" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，可能实际由Report/campaign/list等其他接口承担列表查询职责)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="870" ht="48" customHeight="1">
       <c r="A870" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2033,9 +2033,19 @@
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
+      <c r="F50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>25% (2/8)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -33728,8 +33738,16 @@
         </is>
       </c>
       <c r="E1120" s="2" t="n"/>
-      <c r="F1120" s="4" t="n"/>
-      <c r="G1120" s="2" t="n"/>
+      <c r="F1120" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1120" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1121">
       <c r="A1121" s="2" t="n"/>
@@ -33749,10 +33767,18 @@
         </is>
       </c>
       <c r="E1121" s="2" t="n"/>
-      <c r="F1121" s="4" t="n"/>
-      <c r="G1121" s="2" t="n"/>
-    </row>
-    <row r="1122">
+      <c r="F1121" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1121" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122" ht="16" customHeight="1">
       <c r="A1122" s="2" t="n"/>
       <c r="B1122" s="2" t="inlineStr">
         <is>
@@ -33770,10 +33796,14 @@
         </is>
       </c>
       <c r="E1122" s="2" t="n"/>
-      <c r="F1122" s="4" t="n"/>
+      <c r="F1122" s="7" t="inlineStr">
+        <is>
+          <t>AI审核辅助分析</t>
+        </is>
+      </c>
       <c r="G1122" s="2" t="n"/>
     </row>
-    <row r="1123">
+    <row r="1123" ht="16" customHeight="1">
       <c r="A1123" s="2" t="n"/>
       <c r="B1123" s="2" t="inlineStr">
         <is>
@@ -33791,7 +33821,11 @@
         </is>
       </c>
       <c r="E1123" s="2" t="n"/>
-      <c r="F1123" s="4" t="n"/>
+      <c r="F1123" s="7" t="inlineStr">
+        <is>
+          <t>查询审核意见</t>
+        </is>
+      </c>
       <c r="G1123" s="2" t="n"/>
     </row>
     <row r="1124">
@@ -33813,7 +33847,11 @@
       </c>
       <c r="E1124" s="2" t="n"/>
       <c r="F1124" s="4" t="n"/>
-      <c r="G1124" s="2" t="n"/>
+      <c r="G1124" s="4" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口(advertiserId+creativeId+type表单字段+文件)，365天仅4次真实调用，无法用JSON表示，按规则不生成case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="1125">
       <c r="A1125" s="2" t="n"/>
@@ -33834,7 +33872,11 @@
       </c>
       <c r="E1125" s="2" t="n"/>
       <c r="F1125" s="4" t="n"/>
-      <c r="G1125" s="2" t="n"/>
+      <c r="G1125" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"test"，按规则一律不能调用，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1126">
       <c r="A1126" s="2" t="n"/>
@@ -33855,7 +33897,11 @@
       </c>
       <c r="E1126" s="2" t="n"/>
       <c r="F1126" s="4" t="n"/>
-      <c r="G1126" s="2" t="n"/>
+      <c r="G1126" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"test"和"init"，按规则一律不能调用，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" s="2" t="n"/>
@@ -33876,7 +33922,11 @@
       </c>
       <c r="E1127" s="2" t="n"/>
       <c r="F1127" s="4" t="n"/>
-      <c r="G1127" s="2" t="n"/>
+      <c r="G1127" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"test"，按规则一律不能调用，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1128" ht="16" customHeight="1">
       <c r="A1128" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2215,9 +2215,19 @@
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
+      <c r="F56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>62% (5/8)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -36048,7 +36058,7 @@
       </c>
       <c r="G1206" s="2" t="n"/>
     </row>
-    <row r="1207">
+    <row r="1207" ht="16" customHeight="1">
       <c r="A1207" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36070,10 +36080,14 @@
         </is>
       </c>
       <c r="E1207" s="2" t="n"/>
-      <c r="F1207" s="4" t="n"/>
+      <c r="F1207" s="7" t="inlineStr">
+        <is>
+          <t>查询Display Profile列表</t>
+        </is>
+      </c>
       <c r="G1207" s="2" t="n"/>
     </row>
-    <row r="1208">
+    <row r="1208" ht="16" customHeight="1">
       <c r="A1208" s="2" t="n"/>
       <c r="B1208" s="2" t="inlineStr">
         <is>
@@ -36091,10 +36105,14 @@
         </is>
       </c>
       <c r="E1208" s="2" t="n"/>
-      <c r="F1208" s="4" t="n"/>
+      <c r="F1208" s="7" t="inlineStr">
+        <is>
+          <t>查询API访问权限</t>
+        </is>
+      </c>
       <c r="G1208" s="2" t="n"/>
     </row>
-    <row r="1209">
+    <row r="1209" ht="16" customHeight="1">
       <c r="A1209" s="2" t="n"/>
       <c r="B1209" s="2" t="inlineStr">
         <is>
@@ -36112,7 +36130,11 @@
         </is>
       </c>
       <c r="E1209" s="2" t="n"/>
-      <c r="F1209" s="4" t="n"/>
+      <c r="F1209" s="7" t="inlineStr">
+        <is>
+          <t>按profileId查询API访问详情</t>
+        </is>
+      </c>
       <c r="G1209" s="2" t="n"/>
     </row>
     <row r="1210">
@@ -36133,10 +36155,18 @@
         </is>
       </c>
       <c r="E1210" s="2" t="n"/>
-      <c r="F1210" s="4" t="n"/>
-      <c r="G1210" s="2" t="n"/>
-    </row>
-    <row r="1211">
+      <c r="F1210" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1210" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211" ht="16" customHeight="1">
       <c r="A1211" s="2" t="n"/>
       <c r="B1211" s="2" t="inlineStr">
         <is>
@@ -36154,7 +36184,11 @@
         </is>
       </c>
       <c r="E1211" s="2" t="n"/>
-      <c r="F1211" s="4" t="n"/>
+      <c r="F1211" s="7" t="inlineStr">
+        <is>
+          <t>按profileId查询已批准品牌</t>
+        </is>
+      </c>
       <c r="G1211" s="2" t="n"/>
     </row>
     <row r="1212">
@@ -36175,8 +36209,16 @@
         </is>
       </c>
       <c r="E1212" s="2" t="n"/>
-      <c r="F1212" s="4" t="n"/>
-      <c r="G1212" s="2" t="n"/>
+      <c r="F1212" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1212" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1213">
       <c r="A1213" s="2" t="n"/>
@@ -36197,9 +36239,13 @@
       </c>
       <c r="E1213" s="2" t="n"/>
       <c r="F1213" s="4" t="n"/>
-      <c r="G1213" s="2" t="n"/>
-    </row>
-    <row r="1214">
+      <c r="G1213" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214" ht="16" customHeight="1">
       <c r="A1214" s="2" t="n"/>
       <c r="B1214" s="2" t="inlineStr">
         <is>
@@ -36217,7 +36263,11 @@
         </is>
       </c>
       <c r="E1214" s="2" t="n"/>
-      <c r="F1214" s="4" t="n"/>
+      <c r="F1214" s="7" t="inlineStr">
+        <is>
+          <t>查询Sponsor Profile列表</t>
+        </is>
+      </c>
       <c r="G1214" s="2" t="n"/>
     </row>
     <row r="1215">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1293,9 +1293,19 @@
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>0% (0/7)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -18084,7 +18094,11 @@
       </c>
       <c r="E558" s="2" t="n"/>
       <c r="F558" s="4" t="n"/>
-      <c r="G558" s="2" t="n"/>
+      <c r="G558" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365天31次真实调用，请求体需要真实已上传图片的assetId+pacvueUrl(多个尺寸的marquee广告位素材)，测试账号Display素材库为空(同Creative/Media模块已确认的先例)，无法安全构造出真实成功案例，技术受限未执行，未使用他人真实assetId(会引用他人上传的素材文件)。</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n"/>
@@ -18105,7 +18119,11 @@
       </c>
       <c r="E559" s="2" t="n"/>
       <c r="F559" s="4" t="n"/>
-      <c r="G559" s="2" t="n"/>
+      <c r="G559" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，且依赖上面POST创建出的creativeId(技术受限未创建成功)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n"/>
@@ -18126,7 +18144,11 @@
       </c>
       <c r="E560" s="2" t="n"/>
       <c r="F560" s="4" t="n"/>
-      <c r="G560" s="2" t="n"/>
+      <c r="G560" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，同上依赖创建，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n"/>
@@ -18147,7 +18169,11 @@
       </c>
       <c r="E561" s="2" t="n"/>
       <c r="F561" s="4" t="n"/>
-      <c r="G561" s="2" t="n"/>
+      <c r="G561" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，同上依赖创建，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n"/>
@@ -18168,7 +18194,11 @@
       </c>
       <c r="E562" s="2" t="n"/>
       <c r="F562" s="4" t="n"/>
-      <c r="G562" s="2" t="n"/>
+      <c r="G562" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，同上依赖创建，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n"/>
@@ -18189,7 +18219,11 @@
       </c>
       <c r="E563" s="2" t="n"/>
       <c r="F563" s="4" t="n"/>
-      <c r="G563" s="2" t="n"/>
+      <c r="G563" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n"/>
@@ -18210,7 +18244,11 @@
       </c>
       <c r="E564" s="2" t="n"/>
       <c r="F564" s="4" t="n"/>
-      <c r="G564" s="2" t="n"/>
+      <c r="G564" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"migrate"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1861,9 +1861,19 @@
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
+      <c r="F44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>43% (3/7)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -30868,8 +30878,16 @@
         </is>
       </c>
       <c r="E1014" s="2" t="n"/>
-      <c r="F1014" s="4" t="n"/>
-      <c r="G1014" s="2" t="n"/>
+      <c r="F1014" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1014" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1015">
       <c r="A1015" s="2" t="n"/>
@@ -30889,10 +30907,18 @@
         </is>
       </c>
       <c r="E1015" s="2" t="n"/>
-      <c r="F1015" s="4" t="n"/>
-      <c r="G1015" s="2" t="n"/>
-    </row>
-    <row r="1016">
+      <c r="F1015" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1015" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016" ht="16" customHeight="1">
       <c r="A1016" s="2" t="n"/>
       <c r="B1016" s="2" t="inlineStr">
         <is>
@@ -30910,10 +30936,14 @@
         </is>
       </c>
       <c r="E1016" s="2" t="n"/>
-      <c r="F1016" s="4" t="n"/>
+      <c r="F1016" s="7" t="inlineStr">
+        <is>
+          <t>查询已应用推荐</t>
+        </is>
+      </c>
       <c r="G1016" s="2" t="n"/>
     </row>
-    <row r="1017">
+    <row r="1017" ht="16" customHeight="1">
       <c r="A1017" s="2" t="n"/>
       <c r="B1017" s="2" t="inlineStr">
         <is>
@@ -30931,10 +30961,14 @@
         </is>
       </c>
       <c r="E1017" s="2" t="n"/>
-      <c r="F1017" s="4" t="n"/>
+      <c r="F1017" s="7" t="inlineStr">
+        <is>
+          <t>批量应用关键词推荐</t>
+        </is>
+      </c>
       <c r="G1017" s="2" t="n"/>
     </row>
-    <row r="1018">
+    <row r="1018" ht="16" customHeight="1">
       <c r="A1018" s="2" t="n"/>
       <c r="B1018" s="2" t="inlineStr">
         <is>
@@ -30952,7 +30986,11 @@
         </is>
       </c>
       <c r="E1018" s="2" t="n"/>
-      <c r="F1018" s="4" t="n"/>
+      <c r="F1018" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询关键词推荐</t>
+        </is>
+      </c>
       <c r="G1018" s="2" t="n"/>
     </row>
     <row r="1019">
@@ -30974,7 +31012,11 @@
       </c>
       <c r="E1019" s="2" t="n"/>
       <c r="F1019" s="4" t="n"/>
-      <c r="G1019" s="2" t="n"/>
+      <c r="G1019" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口(365天7次真实调用)，按项目惯例异步导出类接口只标注不生成执行</t>
+        </is>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" s="2" t="n"/>
@@ -30995,7 +31037,11 @@
       </c>
       <c r="E1020" s="2" t="n"/>
       <c r="F1020" s="4" t="n"/>
-      <c r="G1020" s="2" t="n"/>
+      <c r="G1020" s="4" t="inlineStr">
+        <is>
+          <t>异步导出回调接口(365天7次真实调用)，按项目惯例只标注不生成执行</t>
+        </is>
+      </c>
     </row>
     <row r="1021" ht="80" customHeight="1">
       <c r="A1021" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2407,9 +2407,19 @@
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n"/>
+      <c r="F62" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>29% (2/7)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -39236,10 +39246,18 @@
         </is>
       </c>
       <c r="E1318" s="2" t="n"/>
-      <c r="F1318" s="4" t="n"/>
-      <c r="G1318" s="2" t="n"/>
-    </row>
-    <row r="1319">
+      <c r="F1318" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1318" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319" ht="16" customHeight="1">
       <c r="A1319" s="2" t="n"/>
       <c r="B1319" s="2" t="inlineStr">
         <is>
@@ -39257,7 +39275,11 @@
         </is>
       </c>
       <c r="E1319" s="2" t="n"/>
-      <c r="F1319" s="4" t="n"/>
+      <c r="F1319" s="7" t="inlineStr">
+        <is>
+          <t>提交campaign审核(业务限制，非bug)</t>
+        </is>
+      </c>
       <c r="G1319" s="2" t="n"/>
     </row>
     <row r="1320">
@@ -39279,7 +39301,11 @@
       </c>
       <c r="E1320" s="2" t="n"/>
       <c r="F1320" s="4" t="n"/>
-      <c r="G1320" s="2" t="n"/>
+      <c r="G1320" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365天185次真实调用，按reviewIds操作，需要一个已存在的真实reviewId。测试账号campaign 426321无法提交审核(见POST Review的业务限制发现)，没有可用的自有reviewId，技术受限未执行，未使用他人真实reviewId(会修改其他客户的审核记录)。</t>
+        </is>
+      </c>
     </row>
     <row r="1321">
       <c r="A1321" s="2" t="n"/>
@@ -39300,7 +39326,11 @@
       </c>
       <c r="E1321" s="2" t="n"/>
       <c r="F1321" s="4" t="n"/>
-      <c r="G1321" s="2" t="n"/>
+      <c r="G1321" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365天403次真实调用，按reviewIds批量取消，原因同PUT Review：测试账号无自有reviewId，技术受限未执行。</t>
+        </is>
+      </c>
     </row>
     <row r="1322">
       <c r="A1322" s="2" t="n"/>
@@ -39320,10 +39350,18 @@
         </is>
       </c>
       <c r="E1322" s="2" t="n"/>
-      <c r="F1322" s="4" t="n"/>
-      <c r="G1322" s="2" t="n"/>
-    </row>
-    <row r="1323">
+      <c r="F1322" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1322" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323" ht="16" customHeight="1">
       <c r="A1323" s="2" t="n"/>
       <c r="B1323" s="2" t="inlineStr">
         <is>
@@ -39341,7 +39379,11 @@
         </is>
       </c>
       <c r="E1323" s="2" t="n"/>
-      <c r="F1323" s="4" t="n"/>
+      <c r="F1323" s="7" t="inlineStr">
+        <is>
+          <t>按campaignId查询审核状态</t>
+        </is>
+      </c>
       <c r="G1323" s="2" t="n"/>
     </row>
     <row r="1324">
@@ -39362,8 +39404,16 @@
         </is>
       </c>
       <c r="E1324" s="2" t="n"/>
-      <c r="F1324" s="4" t="n"/>
-      <c r="G1324" s="2" t="n"/>
+      <c r="F1324" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1324" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1325" ht="16" customHeight="1">
       <c r="A1325" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1721,9 +1721,19 @@
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
+      <c r="F39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>17% (1/6)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -29713,7 +29723,7 @@
         </is>
       </c>
     </row>
-    <row r="970">
+    <row r="970" ht="32" customHeight="1">
       <c r="A970" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29735,7 +29745,12 @@
         </is>
       </c>
       <c r="E970" s="2" t="n"/>
-      <c r="F970" s="4" t="n"/>
+      <c r="F970" s="7" t="inlineStr">
+        <is>
+          <t>onlyActive=true主流场景 — 81.5%
+onlyActive=false场景 — 18.5%</t>
+        </is>
+      </c>
       <c r="G970" s="2" t="n"/>
     </row>
     <row r="971">
@@ -29756,8 +29771,16 @@
         </is>
       </c>
       <c r="E971" s="2" t="n"/>
-      <c r="F971" s="4" t="n"/>
-      <c r="G971" s="2" t="n"/>
+      <c r="F971" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G971" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n"/>
@@ -29777,8 +29800,16 @@
         </is>
       </c>
       <c r="E972" s="2" t="n"/>
-      <c r="F972" s="4" t="n"/>
-      <c r="G972" s="2" t="n"/>
+      <c r="F972" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G972" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="973">
       <c r="A973" s="2" t="n"/>
@@ -29798,8 +29829,16 @@
         </is>
       </c>
       <c r="E973" s="2" t="n"/>
-      <c r="F973" s="4" t="n"/>
-      <c r="G973" s="2" t="n"/>
+      <c r="F973" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G973" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n"/>
@@ -29819,8 +29858,16 @@
         </is>
       </c>
       <c r="E974" s="2" t="n"/>
-      <c r="F974" s="4" t="n"/>
-      <c r="G974" s="2" t="n"/>
+      <c r="F974" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G974" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" s="2" t="n"/>
@@ -29840,8 +29887,16 @@
         </is>
       </c>
       <c r="E975" s="2" t="n"/>
-      <c r="F975" s="4" t="n"/>
-      <c r="G975" s="2" t="n"/>
+      <c r="F975" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G975" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="976">
       <c r="A976" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2751,9 +2751,19 @@
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
+      <c r="F74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>17% (1/6)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43135,8 +43145,16 @@
         </is>
       </c>
       <c r="E1474" s="2" t="n"/>
-      <c r="F1474" s="4" t="n"/>
-      <c r="G1474" s="2" t="n"/>
+      <c r="F1474" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1474" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1475">
       <c r="A1475" s="2" t="n"/>
@@ -43156,8 +43174,16 @@
         </is>
       </c>
       <c r="E1475" s="2" t="n"/>
-      <c r="F1475" s="4" t="n"/>
-      <c r="G1475" s="2" t="n"/>
+      <c r="F1475" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1475" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1476">
       <c r="A1476" s="2" t="n"/>
@@ -43177,8 +43203,16 @@
         </is>
       </c>
       <c r="E1476" s="2" t="n"/>
-      <c r="F1476" s="4" t="n"/>
-      <c r="G1476" s="2" t="n"/>
+      <c r="F1476" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1476" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1477">
       <c r="A1477" s="2" t="n"/>
@@ -43198,10 +43232,18 @@
         </is>
       </c>
       <c r="E1477" s="2" t="n"/>
-      <c r="F1477" s="4" t="n"/>
-      <c r="G1477" s="2" t="n"/>
-    </row>
-    <row r="1478">
+      <c r="F1477" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1477" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478" ht="16" customHeight="1">
       <c r="A1478" s="2" t="n"/>
       <c r="B1478" s="2" t="inlineStr">
         <is>
@@ -43219,7 +43261,11 @@
         </is>
       </c>
       <c r="E1478" s="2" t="n"/>
-      <c r="F1478" s="4" t="n"/>
+      <c r="F1478" s="7" t="inlineStr">
+        <is>
+          <t>isAll=true — 80%</t>
+        </is>
+      </c>
       <c r="G1478" s="2" t="n"/>
     </row>
     <row r="1479">
@@ -43240,8 +43286,16 @@
         </is>
       </c>
       <c r="E1479" s="2" t="n"/>
-      <c r="F1479" s="4" t="n"/>
-      <c r="G1479" s="2" t="n"/>
+      <c r="F1479" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1479" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1111,9 +1111,19 @@
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="F19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -15282,7 +15292,7 @@
         </is>
       </c>
     </row>
-    <row r="457">
+    <row r="457" ht="16" customHeight="1">
       <c r="A457" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15304,10 +15314,14 @@
         </is>
       </c>
       <c r="E457" s="2" t="n"/>
-      <c r="F457" s="4" t="n"/>
+      <c r="F457" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询品牌</t>
+        </is>
+      </c>
       <c r="G457" s="2" t="n"/>
     </row>
-    <row r="458">
+    <row r="458" ht="16" customHeight="1">
       <c r="A458" s="2" t="n"/>
       <c r="B458" s="2" t="inlineStr">
         <is>
@@ -15325,10 +15339,14 @@
         </is>
       </c>
       <c r="E458" s="2" t="n"/>
-      <c r="F458" s="4" t="n"/>
+      <c r="F458" s="7" t="inlineStr">
+        <is>
+          <t>查询商品品牌</t>
+        </is>
+      </c>
       <c r="G458" s="2" t="n"/>
     </row>
-    <row r="459">
+    <row r="459" ht="16" customHeight="1">
       <c r="A459" s="2" t="n"/>
       <c r="B459" s="2" t="inlineStr">
         <is>
@@ -15346,10 +15364,14 @@
         </is>
       </c>
       <c r="E459" s="2" t="n"/>
-      <c r="F459" s="4" t="n"/>
+      <c r="F459" s="7" t="inlineStr">
+        <is>
+          <t>查询商品分类</t>
+        </is>
+      </c>
       <c r="G459" s="2" t="n"/>
     </row>
-    <row r="460">
+    <row r="460" ht="16" customHeight="1">
       <c r="A460" s="2" t="n"/>
       <c r="B460" s="2" t="inlineStr">
         <is>
@@ -15367,10 +15389,14 @@
         </is>
       </c>
       <c r="E460" s="2" t="n"/>
-      <c r="F460" s="4" t="n"/>
+      <c r="F460" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询商品列表</t>
+        </is>
+      </c>
       <c r="G460" s="2" t="n"/>
     </row>
-    <row r="461">
+    <row r="461" ht="16" customHeight="1">
       <c r="A461" s="2" t="n"/>
       <c r="B461" s="2" t="inlineStr">
         <is>
@@ -15388,7 +15414,11 @@
         </is>
       </c>
       <c r="E461" s="2" t="n"/>
-      <c r="F461" s="4" t="n"/>
+      <c r="F461" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询分类树</t>
+        </is>
+      </c>
       <c r="G461" s="2" t="n"/>
     </row>
     <row r="462">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1677,9 +1677,19 @@
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>0% (0/5)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -29298,8 +29308,16 @@
         </is>
       </c>
       <c r="E952" s="2" t="n"/>
-      <c r="F952" s="4" t="n"/>
-      <c r="G952" s="2" t="n"/>
+      <c r="F952" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G952" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" s="2" t="n"/>
@@ -29319,8 +29337,16 @@
         </is>
       </c>
       <c r="E953" s="2" t="n"/>
-      <c r="F953" s="4" t="n"/>
-      <c r="G953" s="2" t="n"/>
+      <c r="F953" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G953" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n"/>
@@ -29340,8 +29366,16 @@
         </is>
       </c>
       <c r="E954" s="2" t="n"/>
-      <c r="F954" s="4" t="n"/>
-      <c r="G954" s="2" t="n"/>
+      <c r="F954" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G954" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" s="2" t="n"/>
@@ -29361,8 +29395,16 @@
         </is>
       </c>
       <c r="E955" s="2" t="n"/>
-      <c r="F955" s="4" t="n"/>
-      <c r="G955" s="2" t="n"/>
+      <c r="F955" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G955" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n"/>
@@ -29383,7 +29425,11 @@
       </c>
       <c r="E956" s="2" t="n"/>
       <c r="F956" s="4" t="n"/>
-      <c r="G956" s="2" t="n"/>
+      <c r="G956" s="4" t="inlineStr">
+        <is>
+          <t>365天不排除clientId有1076次调用，但全部来自clientId 0/62(测试/内部账号噪音，非真实客户流量)，排除后为0，按规则暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="957">
       <c r="A957" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2661,9 +2661,19 @@
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
+      <c r="F69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>0% (0/4)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -41417,7 +41427,11 @@
       </c>
       <c r="E1389" s="2" t="n"/>
       <c r="F1389" s="4" t="n"/>
-      <c r="G1389" s="2" t="n"/>
+      <c r="G1389" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，按规则一律不能调用(尽管365天311次真实流量)，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1390">
       <c r="A1390" s="2" t="n"/>
@@ -41438,7 +41452,11 @@
       </c>
       <c r="E1390" s="2" t="n"/>
       <c r="F1390" s="4" t="n"/>
-      <c r="G1390" s="2" t="n"/>
+      <c r="G1390" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，按规则一律不能调用(尽管365天16553次真实流量，本模块流量最高)，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1391">
       <c r="A1391" s="2" t="n"/>
@@ -41459,7 +41477,11 @@
       </c>
       <c r="E1391" s="2" t="n"/>
       <c r="F1391" s="4" t="n"/>
-      <c r="G1391" s="2" t="n"/>
+      <c r="G1391" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，按规则一律不能调用(尽管365天874次真实流量)，不生成/执行case</t>
+        </is>
+      </c>
     </row>
     <row r="1392">
       <c r="A1392" s="2" t="n"/>
@@ -41480,7 +41502,11 @@
       </c>
       <c r="E1392" s="2" t="n"/>
       <c r="F1392" s="4" t="n"/>
-      <c r="G1392" s="2" t="n"/>
+      <c r="G1392" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"Sync"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1393">
       <c r="A1393" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2715,9 +2715,19 @@
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
+      <c r="F71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>0% (0/4)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -41531,7 +41541,11 @@
       </c>
       <c r="E1393" s="2" t="n"/>
       <c r="F1393" s="4" t="n"/>
-      <c r="G1393" s="2" t="n"/>
+      <c r="G1393" s="4" t="inlineStr">
+        <is>
+          <t>写操作，365天705次真实调用，请求体需要一个已存在的真实targetId(引用CampaignTags等标签体系的标签，targetType枚举0/4/5/6/7含义Swagger未声明)。快速探测创建CampaignTags标签失败(HTTP 500，请求体格式与本次会话未复用早期经验)，未继续深挖targetType精确映射，技术受限未执行，未使用ES真实样本中他人的targetId。</t>
+        </is>
+      </c>
     </row>
     <row r="1394">
       <c r="A1394" s="2" t="n"/>
@@ -41551,8 +41565,16 @@
         </is>
       </c>
       <c r="E1394" s="2" t="n"/>
-      <c r="F1394" s="4" t="n"/>
-      <c r="G1394" s="2" t="n"/>
+      <c r="F1394" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1394" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，且依赖上面POST创建结果，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1395">
       <c r="A1395" s="2" t="n"/>
@@ -41572,8 +41594,16 @@
         </is>
       </c>
       <c r="E1395" s="2" t="n"/>
-      <c r="F1395" s="4" t="n"/>
-      <c r="G1395" s="2" t="n"/>
+      <c r="F1395" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1395" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，同上依赖创建，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1396">
       <c r="A1396" s="2" t="n"/>
@@ -41594,7 +41624,11 @@
       </c>
       <c r="E1396" s="2" t="n"/>
       <c r="F1396" s="4" t="n"/>
-      <c r="G1396" s="2" t="n"/>
+      <c r="G1396" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"run"，且365天仅2次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1397">
       <c r="A1397" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2393,9 +2393,19 @@
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
+      <c r="F60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>67% (2/3)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -39294,10 +39304,18 @@
         </is>
       </c>
       <c r="E1313" s="2" t="n"/>
-      <c r="F1313" s="4" t="n"/>
-      <c r="G1313" s="2" t="n"/>
-    </row>
-    <row r="1314">
+      <c r="F1313" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1313" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314" ht="16" customHeight="1">
       <c r="A1314" s="2" t="n"/>
       <c r="B1314" s="2" t="inlineStr">
         <is>
@@ -39315,10 +39333,14 @@
         </is>
       </c>
       <c r="E1314" s="2" t="n"/>
-      <c r="F1314" s="4" t="n"/>
+      <c r="F1314" s="7" t="inlineStr">
+        <is>
+          <t>查询默认搜索词趋势图</t>
+        </is>
+      </c>
       <c r="G1314" s="2" t="n"/>
     </row>
-    <row r="1315">
+    <row r="1315" ht="16" customHeight="1">
       <c r="A1315" s="2" t="n"/>
       <c r="B1315" s="2" t="inlineStr">
         <is>
@@ -39336,7 +39358,11 @@
         </is>
       </c>
       <c r="E1315" s="2" t="n"/>
-      <c r="F1315" s="4" t="n"/>
+      <c r="F1315" s="7" t="inlineStr">
+        <is>
+          <t>查询指定搜索词趋势图</t>
+        </is>
+      </c>
       <c r="G1315" s="2" t="n"/>
     </row>
     <row r="1316">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1623,9 +1623,19 @@
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>50% (1/2)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -28353,10 +28363,18 @@
         </is>
       </c>
       <c r="E916" s="2" t="n"/>
-      <c r="F916" s="4" t="n"/>
-      <c r="G916" s="2" t="n"/>
-    </row>
-    <row r="917">
+      <c r="F916" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G916" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="917" ht="16" customHeight="1">
       <c r="A917" s="2" t="n"/>
       <c r="B917" s="2" t="inlineStr">
         <is>
@@ -28374,7 +28392,11 @@
         </is>
       </c>
       <c r="E917" s="2" t="n"/>
-      <c r="F917" s="4" t="n"/>
+      <c r="F917" s="7" t="inlineStr">
+        <is>
+          <t>查询预算重分配建议</t>
+        </is>
+      </c>
       <c r="G917" s="2" t="n"/>
     </row>
     <row r="918" ht="16" customHeight="1">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1783,9 +1783,19 @@
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>0% (0/2)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -30058,8 +30068,16 @@
         </is>
       </c>
       <c r="E976" s="2" t="n"/>
-      <c r="F976" s="4" t="n"/>
-      <c r="G976" s="2" t="n"/>
+      <c r="F976" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G976" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)。不带/api前缀的基础设施健康检查端点，可能不经过本ES采集的access log(供负载均衡器/监控探针调用，非常规客户端调用路径)，按规则暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n"/>
@@ -30079,8 +30097,16 @@
         </is>
       </c>
       <c r="E977" s="2" t="n"/>
-      <c r="F977" s="4" t="n"/>
-      <c r="G977" s="2" t="n"/>
+      <c r="F977" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G977" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，同上不带/api前缀的基础设施端点，按规则暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2445,9 +2445,19 @@
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
+      <c r="F61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -39413,7 +39423,7 @@
       </c>
       <c r="G1315" s="2" t="n"/>
     </row>
-    <row r="1316">
+    <row r="1316" ht="16" customHeight="1">
       <c r="A1316" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39435,10 +39445,14 @@
         </is>
       </c>
       <c r="E1316" s="2" t="n"/>
-      <c r="F1316" s="4" t="n"/>
+      <c r="F1316" s="7" t="inlineStr">
+        <is>
+          <t>查询月度采纳报表</t>
+        </is>
+      </c>
       <c r="G1316" s="2" t="n"/>
     </row>
-    <row r="1317">
+    <row r="1317" ht="16" customHeight="1">
       <c r="A1317" s="2" t="n"/>
       <c r="B1317" s="2" t="inlineStr">
         <is>
@@ -39456,7 +39470,11 @@
         </is>
       </c>
       <c r="E1317" s="2" t="n"/>
-      <c r="F1317" s="4" t="n"/>
+      <c r="F1317" s="7" t="inlineStr">
+        <is>
+          <t>查询TopN客户</t>
+        </is>
+      </c>
       <c r="G1317" s="2" t="n"/>
     </row>
     <row r="1318">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2787,9 +2787,19 @@
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
+      <c r="F72" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -41722,7 +41732,7 @@
         </is>
       </c>
     </row>
-    <row r="1397">
+    <row r="1397" ht="16" customHeight="1">
       <c r="A1397" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -41744,10 +41754,14 @@
         </is>
       </c>
       <c r="E1397" s="2" t="n"/>
-      <c r="F1397" s="4" t="n"/>
+      <c r="F1397" s="7" t="inlineStr">
+        <is>
+          <t>按BEHAVIORAL/CUSTOM查询受众</t>
+        </is>
+      </c>
       <c r="G1397" s="2" t="n"/>
     </row>
-    <row r="1398">
+    <row r="1398" ht="16" customHeight="1">
       <c r="A1398" s="2" t="n"/>
       <c r="B1398" s="2" t="inlineStr">
         <is>
@@ -41765,7 +41779,11 @@
         </is>
       </c>
       <c r="E1398" s="2" t="n"/>
-      <c r="F1398" s="4" t="n"/>
+      <c r="F1398" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询</t>
+        </is>
+      </c>
       <c r="G1398" s="2" t="n"/>
     </row>
     <row r="1399">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2231,9 +2231,19 @@
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
+      <c r="F54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -35186,7 +35196,7 @@
       </c>
       <c r="G1162" s="2" t="n"/>
     </row>
-    <row r="1163">
+    <row r="1163" ht="16" customHeight="1">
       <c r="A1163" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35208,7 +35218,11 @@
         </is>
       </c>
       <c r="E1163" s="2" t="n"/>
-      <c r="F1163" s="4" t="n"/>
+      <c r="F1163" s="7" t="inlineStr">
+        <is>
+          <t>检查Tag是否被BudgetManager使用</t>
+        </is>
+      </c>
       <c r="G1163" s="2" t="n"/>
     </row>
     <row r="1164" ht="16" customHeight="1">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2829,9 +2829,19 @@
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
+      <c r="F73" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>43% (20/46)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -42435,8 +42445,16 @@
         </is>
       </c>
       <c r="E1428" s="2" t="n"/>
-      <c r="F1428" s="4" t="n"/>
-      <c r="G1428" s="2" t="n"/>
+      <c r="F1428" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1428" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1429">
       <c r="A1429" s="2" t="n"/>
@@ -42456,8 +42474,16 @@
         </is>
       </c>
       <c r="E1429" s="2" t="n"/>
-      <c r="F1429" s="4" t="n"/>
-      <c r="G1429" s="2" t="n"/>
+      <c r="F1429" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1429" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1430">
       <c r="A1430" s="2" t="n"/>
@@ -42477,10 +42503,18 @@
         </is>
       </c>
       <c r="E1430" s="2" t="n"/>
-      <c r="F1430" s="4" t="n"/>
-      <c r="G1430" s="2" t="n"/>
-    </row>
-    <row r="1431">
+      <c r="F1430" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1430" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431" ht="16" customHeight="1">
       <c r="A1431" s="2" t="n"/>
       <c r="B1431" s="2" t="inlineStr">
         <is>
@@ -42498,7 +42532,11 @@
         </is>
       </c>
       <c r="E1431" s="2" t="n"/>
-      <c r="F1431" s="4" t="n"/>
+      <c r="F1431" s="7" t="inlineStr">
+        <is>
+          <t>查询AdGroup树</t>
+        </is>
+      </c>
       <c r="G1431" s="2" t="n"/>
     </row>
     <row r="1432">
@@ -42519,10 +42557,18 @@
         </is>
       </c>
       <c r="E1432" s="2" t="n"/>
-      <c r="F1432" s="4" t="n"/>
-      <c r="G1432" s="2" t="n"/>
-    </row>
-    <row r="1433">
+      <c r="F1432" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1432" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433" ht="16" customHeight="1">
       <c r="A1433" s="2" t="n"/>
       <c r="B1433" s="2" t="inlineStr">
         <is>
@@ -42540,10 +42586,14 @@
         </is>
       </c>
       <c r="E1433" s="2" t="n"/>
-      <c r="F1433" s="4" t="n"/>
+      <c r="F1433" s="7" t="inlineStr">
+        <is>
+          <t>查询Campaign(ignoreAuto=true)</t>
+        </is>
+      </c>
       <c r="G1433" s="2" t="n"/>
     </row>
-    <row r="1434">
+    <row r="1434" ht="16" customHeight="1">
       <c r="A1434" s="2" t="n"/>
       <c r="B1434" s="2" t="inlineStr">
         <is>
@@ -42561,7 +42611,11 @@
         </is>
       </c>
       <c r="E1434" s="2" t="n"/>
-      <c r="F1434" s="4" t="n"/>
+      <c r="F1434" s="7" t="inlineStr">
+        <is>
+          <t>默认场景查询Campaign(供Zip定向)</t>
+        </is>
+      </c>
       <c r="G1434" s="2" t="n"/>
     </row>
     <row r="1435">
@@ -42582,10 +42636,18 @@
         </is>
       </c>
       <c r="E1435" s="2" t="n"/>
-      <c r="F1435" s="4" t="n"/>
-      <c r="G1435" s="2" t="n"/>
-    </row>
-    <row r="1436">
+      <c r="F1435" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1435" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436" ht="16" customHeight="1">
       <c r="A1436" s="2" t="n"/>
       <c r="B1436" s="2" t="inlineStr">
         <is>
@@ -42603,7 +42665,11 @@
         </is>
       </c>
       <c r="E1436" s="2" t="n"/>
-      <c r="F1436" s="4" t="n"/>
+      <c r="F1436" s="7" t="inlineStr">
+        <is>
+          <t>查询支持信息</t>
+        </is>
+      </c>
       <c r="G1436" s="2" t="n"/>
     </row>
     <row r="1437">
@@ -42624,8 +42690,16 @@
         </is>
       </c>
       <c r="E1437" s="2" t="n"/>
-      <c r="F1437" s="4" t="n"/>
-      <c r="G1437" s="2" t="n"/>
+      <c r="F1437" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1437" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1438">
       <c r="A1438" s="2" t="n"/>
@@ -42645,10 +42719,18 @@
         </is>
       </c>
       <c r="E1438" s="2" t="n"/>
-      <c r="F1438" s="4" t="n"/>
-      <c r="G1438" s="2" t="n"/>
-    </row>
-    <row r="1439">
+      <c r="F1438" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1438" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439" ht="16" customHeight="1">
       <c r="A1439" s="2" t="n"/>
       <c r="B1439" s="2" t="inlineStr">
         <is>
@@ -42666,10 +42748,14 @@
         </is>
       </c>
       <c r="E1439" s="2" t="n"/>
-      <c r="F1439" s="4" t="n"/>
+      <c r="F1439" s="7" t="inlineStr">
+        <is>
+          <t>更新新手引导步骤</t>
+        </is>
+      </c>
       <c r="G1439" s="2" t="n"/>
     </row>
-    <row r="1440">
+    <row r="1440" ht="16" customHeight="1">
       <c r="A1440" s="2" t="n"/>
       <c r="B1440" s="2" t="inlineStr">
         <is>
@@ -42687,7 +42773,11 @@
         </is>
       </c>
       <c r="E1440" s="2" t="n"/>
-      <c r="F1440" s="4" t="n"/>
+      <c r="F1440" s="7" t="inlineStr">
+        <is>
+          <t>查询新手引导进度</t>
+        </is>
+      </c>
       <c r="G1440" s="2" t="n"/>
     </row>
     <row r="1441">
@@ -42709,7 +42799,11 @@
       </c>
       <c r="E1441" s="2" t="n"/>
       <c r="F1441" s="4" t="n"/>
-      <c r="G1441" s="2" t="n"/>
+      <c r="G1441" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词"init"，且365天0次真实流量，双重原因不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1442">
       <c r="A1442" s="2" t="n"/>
@@ -42729,8 +42823,16 @@
         </is>
       </c>
       <c r="E1442" s="2" t="n"/>
-      <c r="F1442" s="4" t="n"/>
-      <c r="G1442" s="2" t="n"/>
+      <c r="F1442" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1442" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1443">
       <c r="A1443" s="2" t="n"/>
@@ -42750,8 +42852,16 @@
         </is>
       </c>
       <c r="E1443" s="2" t="n"/>
-      <c r="F1443" s="4" t="n"/>
-      <c r="G1443" s="2" t="n"/>
+      <c r="F1443" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1443" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1444">
       <c r="A1444" s="2" t="n"/>
@@ -42771,8 +42881,16 @@
         </is>
       </c>
       <c r="E1444" s="2" t="n"/>
-      <c r="F1444" s="4" t="n"/>
-      <c r="G1444" s="2" t="n"/>
+      <c r="F1444" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1444" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1445">
       <c r="A1445" s="2" t="n"/>
@@ -42792,8 +42910,16 @@
         </is>
       </c>
       <c r="E1445" s="2" t="n"/>
-      <c r="F1445" s="4" t="n"/>
-      <c r="G1445" s="2" t="n"/>
+      <c r="F1445" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1445" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1446">
       <c r="A1446" s="2" t="n"/>
@@ -42813,10 +42939,18 @@
         </is>
       </c>
       <c r="E1446" s="2" t="n"/>
-      <c r="F1446" s="4" t="n"/>
-      <c r="G1446" s="2" t="n"/>
-    </row>
-    <row r="1447">
+      <c r="F1446" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1446" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447" ht="16" customHeight="1">
       <c r="A1447" s="2" t="n"/>
       <c r="B1447" s="2" t="inlineStr">
         <is>
@@ -42834,10 +42968,14 @@
         </is>
       </c>
       <c r="E1447" s="2" t="n"/>
-      <c r="F1447" s="4" t="n"/>
+      <c r="F1447" s="7" t="inlineStr">
+        <is>
+          <t>切换Profile管理状态</t>
+        </is>
+      </c>
       <c r="G1447" s="2" t="n"/>
     </row>
-    <row r="1448">
+    <row r="1448" ht="16" customHeight="1">
       <c r="A1448" s="2" t="n"/>
       <c r="B1448" s="2" t="inlineStr">
         <is>
@@ -42855,10 +42993,14 @@
         </is>
       </c>
       <c r="E1448" s="2" t="n"/>
-      <c r="F1448" s="4" t="n"/>
+      <c r="F1448" s="7" t="inlineStr">
+        <is>
+          <t>查询Profile操作日志</t>
+        </is>
+      </c>
       <c r="G1448" s="2" t="n"/>
     </row>
-    <row r="1449">
+    <row r="1449" ht="16" customHeight="1">
       <c r="A1449" s="2" t="n"/>
       <c r="B1449" s="2" t="inlineStr">
         <is>
@@ -42876,10 +43018,14 @@
         </is>
       </c>
       <c r="E1449" s="2" t="n"/>
-      <c r="F1449" s="4" t="n"/>
+      <c r="F1449" s="7" t="inlineStr">
+        <is>
+          <t>查询用户Profile列表</t>
+        </is>
+      </c>
       <c r="G1449" s="2" t="n"/>
     </row>
-    <row r="1450">
+    <row r="1450" ht="16" customHeight="1">
       <c r="A1450" s="2" t="n"/>
       <c r="B1450" s="2" t="inlineStr">
         <is>
@@ -42897,10 +43043,14 @@
         </is>
       </c>
       <c r="E1450" s="2" t="n"/>
-      <c r="F1450" s="4" t="n"/>
+      <c r="F1450" s="7" t="inlineStr">
+        <is>
+          <t>修改Profile别名</t>
+        </is>
+      </c>
       <c r="G1450" s="2" t="n"/>
     </row>
-    <row r="1451">
+    <row r="1451" ht="16" customHeight="1">
       <c r="A1451" s="2" t="n"/>
       <c r="B1451" s="2" t="inlineStr">
         <is>
@@ -42918,10 +43068,14 @@
         </is>
       </c>
       <c r="E1451" s="2" t="n"/>
-      <c r="F1451" s="4" t="n"/>
+      <c r="F1451" s="7" t="inlineStr">
+        <is>
+          <t>查询Profile及其Campaign</t>
+        </is>
+      </c>
       <c r="G1451" s="2" t="n"/>
     </row>
-    <row r="1452">
+    <row r="1452" ht="16" customHeight="1">
       <c r="A1452" s="2" t="n"/>
       <c r="B1452" s="2" t="inlineStr">
         <is>
@@ -42939,10 +43093,14 @@
         </is>
       </c>
       <c r="E1452" s="2" t="n"/>
-      <c r="F1452" s="4" t="n"/>
+      <c r="F1452" s="7" t="inlineStr">
+        <is>
+          <t>写入Redis键值</t>
+        </is>
+      </c>
       <c r="G1452" s="2" t="n"/>
     </row>
-    <row r="1453">
+    <row r="1453" ht="16" customHeight="1">
       <c r="A1453" s="2" t="n"/>
       <c r="B1453" s="2" t="inlineStr">
         <is>
@@ -42960,7 +43118,11 @@
         </is>
       </c>
       <c r="E1453" s="2" t="n"/>
-      <c r="F1453" s="4" t="n"/>
+      <c r="F1453" s="7" t="inlineStr">
+        <is>
+          <t>查询Redis键值</t>
+        </is>
+      </c>
       <c r="G1453" s="2" t="n"/>
     </row>
     <row r="1454">
@@ -42981,8 +43143,16 @@
         </is>
       </c>
       <c r="E1454" s="2" t="n"/>
-      <c r="F1454" s="4" t="n"/>
-      <c r="G1454" s="2" t="n"/>
+      <c r="F1454" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1454" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1455">
       <c r="A1455" s="2" t="n"/>
@@ -43002,8 +43172,16 @@
         </is>
       </c>
       <c r="E1455" s="2" t="n"/>
-      <c r="F1455" s="4" t="n"/>
-      <c r="G1455" s="2" t="n"/>
+      <c r="F1455" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1455" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1456">
       <c r="A1456" s="2" t="n"/>
@@ -43023,8 +43201,16 @@
         </is>
       </c>
       <c r="E1456" s="2" t="n"/>
-      <c r="F1456" s="4" t="n"/>
-      <c r="G1456" s="2" t="n"/>
+      <c r="F1456" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1456" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1457">
       <c r="A1457" s="2" t="n"/>
@@ -43044,8 +43230,16 @@
         </is>
       </c>
       <c r="E1457" s="2" t="n"/>
-      <c r="F1457" s="4" t="n"/>
-      <c r="G1457" s="2" t="n"/>
+      <c r="F1457" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1457" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1458">
       <c r="A1458" s="2" t="n"/>
@@ -43065,10 +43259,18 @@
         </is>
       </c>
       <c r="E1458" s="2" t="n"/>
-      <c r="F1458" s="4" t="n"/>
-      <c r="G1458" s="2" t="n"/>
-    </row>
-    <row r="1459">
+      <c r="F1458" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1458" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459" ht="16" customHeight="1">
       <c r="A1459" s="2" t="n"/>
       <c r="B1459" s="2" t="inlineStr">
         <is>
@@ -43086,10 +43288,14 @@
         </is>
       </c>
       <c r="E1459" s="2" t="n"/>
-      <c r="F1459" s="4" t="n"/>
+      <c r="F1459" s="7" t="inlineStr">
+        <is>
+          <t>保存SOV分类偏好</t>
+        </is>
+      </c>
       <c r="G1459" s="2" t="n"/>
     </row>
-    <row r="1460">
+    <row r="1460" ht="16" customHeight="1">
       <c r="A1460" s="2" t="n"/>
       <c r="B1460" s="2" t="inlineStr">
         <is>
@@ -43107,10 +43313,14 @@
         </is>
       </c>
       <c r="E1460" s="2" t="n"/>
-      <c r="F1460" s="4" t="n"/>
+      <c r="F1460" s="7" t="inlineStr">
+        <is>
+          <t>查询SOV分类偏好</t>
+        </is>
+      </c>
       <c r="G1460" s="2" t="n"/>
     </row>
-    <row r="1461">
+    <row r="1461" ht="16" customHeight="1">
       <c r="A1461" s="2" t="n"/>
       <c r="B1461" s="2" t="inlineStr">
         <is>
@@ -43128,7 +43338,11 @@
         </is>
       </c>
       <c r="E1461" s="2" t="n"/>
-      <c r="F1461" s="4" t="n"/>
+      <c r="F1461" s="7" t="inlineStr">
+        <is>
+          <t>查询子用户列表</t>
+        </is>
+      </c>
       <c r="G1461" s="2" t="n"/>
     </row>
     <row r="1462">
@@ -43149,8 +43363,16 @@
         </is>
       </c>
       <c r="E1462" s="2" t="n"/>
-      <c r="F1462" s="4" t="n"/>
-      <c r="G1462" s="2" t="n"/>
+      <c r="F1462" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1462" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1463">
       <c r="A1463" s="2" t="n"/>
@@ -43170,10 +43392,18 @@
         </is>
       </c>
       <c r="E1463" s="2" t="n"/>
-      <c r="F1463" s="4" t="n"/>
-      <c r="G1463" s="2" t="n"/>
-    </row>
-    <row r="1464">
+      <c r="F1463" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1463" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464" ht="16" customHeight="1">
       <c r="A1464" s="2" t="n"/>
       <c r="B1464" s="2" t="inlineStr">
         <is>
@@ -43191,7 +43421,11 @@
         </is>
       </c>
       <c r="E1464" s="2" t="n"/>
-      <c r="F1464" s="4" t="n"/>
+      <c r="F1464" s="7" t="inlineStr">
+        <is>
+          <t>解绑Profile管理</t>
+        </is>
+      </c>
       <c r="G1464" s="2" t="n"/>
     </row>
     <row r="1465">
@@ -43212,8 +43446,16 @@
         </is>
       </c>
       <c r="E1465" s="2" t="n"/>
-      <c r="F1465" s="4" t="n"/>
-      <c r="G1465" s="2" t="n"/>
+      <c r="F1465" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1465" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1466">
       <c r="A1466" s="2" t="n"/>
@@ -43233,8 +43475,16 @@
         </is>
       </c>
       <c r="E1466" s="2" t="n"/>
-      <c r="F1466" s="4" t="n"/>
-      <c r="G1466" s="2" t="n"/>
+      <c r="F1466" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1466" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1467">
       <c r="A1467" s="2" t="n"/>
@@ -43254,8 +43504,16 @@
         </is>
       </c>
       <c r="E1467" s="2" t="n"/>
-      <c r="F1467" s="4" t="n"/>
-      <c r="G1467" s="2" t="n"/>
+      <c r="F1467" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1467" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1468">
       <c r="A1468" s="2" t="n"/>
@@ -43275,10 +43533,18 @@
         </is>
       </c>
       <c r="E1468" s="2" t="n"/>
-      <c r="F1468" s="4" t="n"/>
-      <c r="G1468" s="2" t="n"/>
-    </row>
-    <row r="1469">
+      <c r="F1468" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1468" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469" ht="16" customHeight="1">
       <c r="A1469" s="2" t="n"/>
       <c r="B1469" s="2" t="inlineStr">
         <is>
@@ -43296,10 +43562,14 @@
         </is>
       </c>
       <c r="E1469" s="2" t="n"/>
-      <c r="F1469" s="4" t="n"/>
+      <c r="F1469" s="7" t="inlineStr">
+        <is>
+          <t>查询当前用户信息</t>
+        </is>
+      </c>
       <c r="G1469" s="2" t="n"/>
     </row>
-    <row r="1470">
+    <row r="1470" ht="16" customHeight="1">
       <c r="A1470" s="2" t="n"/>
       <c r="B1470" s="2" t="inlineStr">
         <is>
@@ -43317,10 +43587,14 @@
         </is>
       </c>
       <c r="E1470" s="2" t="n"/>
-      <c r="F1470" s="4" t="n"/>
+      <c r="F1470" s="7" t="inlineStr">
+        <is>
+          <t>查询用户Profile(isExport=false)</t>
+        </is>
+      </c>
       <c r="G1470" s="2" t="n"/>
     </row>
-    <row r="1471">
+    <row r="1471" ht="16" customHeight="1">
       <c r="A1471" s="2" t="n"/>
       <c r="B1471" s="2" t="inlineStr">
         <is>
@@ -43338,7 +43612,11 @@
         </is>
       </c>
       <c r="E1471" s="2" t="n"/>
-      <c r="F1471" s="4" t="n"/>
+      <c r="F1471" s="7" t="inlineStr">
+        <is>
+          <t>查询用户列表</t>
+        </is>
+      </c>
       <c r="G1471" s="2" t="n"/>
     </row>
     <row r="1472">
@@ -43359,8 +43637,16 @@
         </is>
       </c>
       <c r="E1472" s="2" t="n"/>
-      <c r="F1472" s="4" t="n"/>
-      <c r="G1472" s="2" t="n"/>
+      <c r="F1472" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1472" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1473">
       <c r="A1473" s="2" t="n"/>
@@ -43380,8 +43666,16 @@
         </is>
       </c>
       <c r="E1473" s="2" t="n"/>
-      <c r="F1473" s="4" t="n"/>
-      <c r="G1473" s="2" t="n"/>
+      <c r="F1473" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1473" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1474">
       <c r="A1474" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -2044,12 +2044,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>100%(29执行,写操作8条未执行不计入)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>57% (20/35)</t>
+          <t>60% (21/35)</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
         </is>
       </c>
     </row>
-    <row r="1037">
+    <row r="1037" ht="16" customHeight="1">
       <c r="A1037" s="2" t="n"/>
       <c r="B1037" s="2" t="inlineStr">
         <is>
@@ -31787,14 +31787,14 @@
         </is>
       </c>
       <c r="E1037" s="2" t="n"/>
-      <c r="F1037" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量创建关键词</t>
+      <c r="F1037" s="7" t="inlineStr">
+        <is>
+          <t>批量创建关键词(自建测试campaign，时间戳命名，创建后置为暂停)</t>
         </is>
       </c>
       <c r="G1037" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-16 补执行(写操作)：在测试campaign 426321/adGroup 770991122 创建2个时间戳命名关键词→按唯一文本定位id→置为paused归位；两轮PASS。无删除接口且campaign曾上线不可archive，新建关键词以paused永久保留；重跑前需换时间戳。</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
         </is>
       </c>
     </row>
-    <row r="1039">
+    <row r="1039" ht="16" customHeight="1">
       <c r="A1039" s="2" t="n"/>
       <c r="B1039" s="2" t="inlineStr">
         <is>
@@ -31845,18 +31845,18 @@
         </is>
       </c>
       <c r="E1039" s="2" t="n"/>
-      <c r="F1039" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量修改关键词出价(按keywordId)</t>
+      <c r="F1039" s="7" t="inlineStr">
+        <is>
+          <t>批量修改关键词出价(自有关键词：改为0.7后还原0.5)</t>
         </is>
       </c>
       <c r="G1039" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
+          <t>2026-09-16 补执行(写操作)：自建测试关键词36520006283 出价0.5→0.7→还原0.5，用Report/keyword/list核实；两轮PASS。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040" ht="16" customHeight="1">
       <c r="A1040" s="2" t="n"/>
       <c r="B1040" s="2" t="inlineStr">
         <is>
@@ -31874,14 +31874,14 @@
         </is>
       </c>
       <c r="E1040" s="2" t="n"/>
-      <c r="F1040" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量修改关键词出价</t>
+      <c r="F1040" s="7" t="inlineStr">
+        <is>
+          <t>按筛选条件批量修改关键词出价(限定自有campaign/adGroup/关键词，改为0.4后还原0.3)</t>
         </is>
       </c>
       <c r="G1040" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-16 补执行(ByCondition写操作，限定自建实体)：同上限定范围，setBidType=0 绝对值 0.3→0.4→还原0.3，核实通过；异步接口；两轮PASS。</t>
         </is>
       </c>
     </row>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="G1063" s="2" t="n"/>
     </row>
-    <row r="1064">
+    <row r="1064" ht="16" customHeight="1">
       <c r="A1064" s="2" t="n"/>
       <c r="B1064" s="2" t="inlineStr">
         <is>
@@ -32531,18 +32531,18 @@
         </is>
       </c>
       <c r="E1064" s="2" t="n"/>
-      <c r="F1064" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量移除关键词标签</t>
+      <c r="F1064" s="7" t="inlineStr">
+        <is>
+          <t>按筛选条件批量移除关键词标签(先打标再移除，限定自有关键词)</t>
         </is>
       </c>
       <c r="G1064" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="1065">
+          <t>2026-09-16 补执行(ByCondition写操作，限定自建实体)：先POST同路径打标(前置)再DELETE移除，用Report/keyword/list核实keywordTagCount归0；两轮PASS。365天仅3次真实调用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065" ht="16" customHeight="1">
       <c r="A1065" s="2" t="n"/>
       <c r="B1065" s="2" t="inlineStr">
         <is>
@@ -32560,14 +32560,14 @@
         </is>
       </c>
       <c r="E1065" s="2" t="n"/>
-      <c r="F1065" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量打关键词标签</t>
+      <c r="F1065" s="7" t="inlineStr">
+        <is>
+          <t>按筛选条件批量打关键词标签(限定自有关键词，打标后移除)</t>
         </is>
       </c>
       <c r="G1065" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-16 补执行(ByCondition写操作，限定自建实体)：用自建固定测试标签14904(test_fixture_kwtag_byConditions)按条件打到自建关键词36520006284→核实keywordTagCount=1→DELETE移除→核实0；两轮PASS。</t>
         </is>
       </c>
     </row>
@@ -32596,7 +32596,7 @@
       </c>
       <c r="G1066" s="2" t="n"/>
     </row>
-    <row r="1067">
+    <row r="1067" ht="16" customHeight="1">
       <c r="A1067" s="2" t="n"/>
       <c r="B1067" s="2" t="inlineStr">
         <is>
@@ -32614,18 +32614,18 @@
         </is>
       </c>
       <c r="E1067" s="2" t="n"/>
-      <c r="F1067" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】将搜索词转化为正式关键词(创建)</t>
+      <c r="F1067" s="7" t="inlineStr">
+        <is>
+          <t>搜索词转正式关键词(创建，自建campaign，创建后置为暂停)</t>
         </is>
       </c>
       <c r="G1067" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="1068">
+          <t>2026-09-16 补执行(写操作)：自造搜索词转正式关键词(测试campaign 426321)→定位id→置为paused归位；两轮PASS。重跑前需换时间戳。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068" ht="16" customHeight="1">
       <c r="A1068" s="2" t="n"/>
       <c r="B1068" s="2" t="inlineStr">
         <is>
@@ -32643,18 +32643,18 @@
         </is>
       </c>
       <c r="E1068" s="2" t="n"/>
-      <c r="F1068" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】批量修改关键词状态(0/1)</t>
+      <c r="F1068" s="7" t="inlineStr">
+        <is>
+          <t>批量修改关键词状态(自有关键词：暂停后恢复启用)</t>
         </is>
       </c>
       <c r="G1068" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="1069">
+          <t>2026-09-16 补执行(写操作)：自建测试关键词36520006283 暂停(state=1)→核实→恢复(state=0)→核实；两轮PASS。已实测枚举：0=enabled、1=paused、2=archived(本campaign拒绝archive)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069" ht="16" customHeight="1">
       <c r="A1069" s="2" t="n"/>
       <c r="B1069" s="2" t="inlineStr">
         <is>
@@ -32672,14 +32672,14 @@
         </is>
       </c>
       <c r="E1069" s="2" t="n"/>
-      <c r="F1069" s="4" t="inlineStr">
-        <is>
-          <t>【仅生成未执行】按筛选条件批量修改关键词状态</t>
+      <c r="F1069" s="7" t="inlineStr">
+        <is>
+          <t>按筛选条件批量修改关键词状态(限定自有campaign/adGroup/关键词，暂停后恢复)</t>
         </is>
       </c>
       <c r="G1069" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-16 补执行(ByCondition写操作，限定自建实体)：conditions限定profile 16274451/campaign 426321/adGroup 770991122+KeywordFilters只命中自建关键词36520006284；暂停→核实→恢复；异步接口(isAsync=true)；两轮PASS。</t>
         </is>
       </c>
     </row>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>89%(9执行 8PASS；2条技术受限不执行不计入)</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%(43执行 34PASS；1条文件上传不执行不计入)</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100%(37执行，含8条写操作)</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -2743,9 +2743,19 @@
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>N/A(用户确认跳过)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>跳过 (0/29)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2830,11 +2840,11 @@
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n"/>
       <c r="F73" s="5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100%(14执行；6条写操作仅生成不执行不计入)</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -2957,8 +2967,16 @@
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>异步导出，需人工测试</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口(365d 208次)，无同步响应体，按规则不生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -3334,8 +3352,16 @@
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="2" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>异步导出，需人工测试</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口(365d 461次)，无同步响应体，按规则不生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="2" t="n"/>
@@ -3386,8 +3412,16 @@
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="2" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="2" t="n"/>
@@ -3434,8 +3468,16 @@
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>异步导出，需人工测试</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口(365d 仅1次)，无同步响应体，按规则不生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="32.1" customHeight="1">
       <c r="A22" s="2" t="n"/>
@@ -3480,8 +3522,16 @@
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="2" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="32.1" customHeight="1">
       <c r="A24" s="2" t="n"/>
@@ -3551,8 +3601,16 @@
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>异步导出接口且零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="32.1" customHeight="1">
       <c r="A27" s="2" t="n"/>
@@ -3598,8 +3656,16 @@
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="2" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="32.1" customHeight="1">
       <c r="A29" s="2" t="n"/>
@@ -7920,8 +7986,16 @@
         </is>
       </c>
       <c r="E183" s="2" t="n"/>
-      <c r="F183" s="4" t="n"/>
-      <c r="G183" s="2" t="n"/>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：创建后修改受众 — 10次/365d</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：用创建响应 data.data.audienceId(非 id)修改受众（所在case：POST /api/display/Audiences - 创建ITEM_PROPENSITY类型受众后修改），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -15102,14 +15176,14 @@
         </is>
       </c>
       <c r="E446" s="2" t="n"/>
-      <c r="F446" s="7" t="inlineStr">
-        <is>
-          <t>默认调用 — 100.0%</t>
+      <c r="F446" s="8" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G446" s="4" t="inlineStr">
         <is>
-          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖（2026-09-16 自检：此前场景列被同路径GET的场景文字串行污染，已更正）</t>
         </is>
       </c>
     </row>
@@ -15131,14 +15205,14 @@
         </is>
       </c>
       <c r="E447" s="2" t="n"/>
-      <c r="F447" s="7" t="inlineStr">
-        <is>
-          <t>默认调用 — 100.0%</t>
+      <c r="F447" s="8" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G447" s="4" t="inlineStr">
         <is>
-          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖（2026-09-16 自检：此前场景列被同路径GET的场景文字串行污染，已更正）</t>
         </is>
       </c>
     </row>
@@ -18467,8 +18541,16 @@
         </is>
       </c>
       <c r="E566" s="2" t="n"/>
-      <c r="F566" s="4" t="n"/>
-      <c r="G566" s="2" t="n"/>
+      <c r="F566" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G566" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n"/>
@@ -18686,8 +18768,16 @@
         </is>
       </c>
       <c r="E574" s="2" t="n"/>
-      <c r="F574" s="4" t="n"/>
-      <c r="G574" s="2" t="n"/>
+      <c r="F574" s="4" t="inlineStr">
+        <is>
+          <t>凭据校验类，待脱敏方案，未执行</t>
+        </is>
+      </c>
+      <c r="G574" s="4" t="inlineStr">
+        <is>
+          <t>云存储/FTP/GoogleSheet 凭据校验接口(365d 59次)：请求需真实账号密钥，ES样本中为其他客户真实凭据不可复用，脱敏/替代方案未定，未生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n"/>
@@ -18707,8 +18797,16 @@
         </is>
       </c>
       <c r="E575" s="2" t="n"/>
-      <c r="F575" s="4" t="n"/>
-      <c r="G575" s="2" t="n"/>
+      <c r="F575" s="4" t="inlineStr">
+        <is>
+          <t>凭据校验类，待脱敏方案，未执行</t>
+        </is>
+      </c>
+      <c r="G575" s="4" t="inlineStr">
+        <is>
+          <t>云存储/FTP/GoogleSheet 凭据校验接口(365d 42次)：请求需真实账号密钥，ES样本中为其他客户真实凭据不可复用，脱敏/替代方案未定，未生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n"/>
@@ -18728,8 +18826,16 @@
         </is>
       </c>
       <c r="E576" s="2" t="n"/>
-      <c r="F576" s="4" t="n"/>
-      <c r="G576" s="2" t="n"/>
+      <c r="F576" s="4" t="inlineStr">
+        <is>
+          <t>凭据校验类，待脱敏方案，未执行</t>
+        </is>
+      </c>
+      <c r="G576" s="4" t="inlineStr">
+        <is>
+          <t>云存储/FTP/GoogleSheet 凭据校验接口(365d 228次)：请求需真实账号密钥，ES样本中为其他客户真实凭据不可复用，脱敏/替代方案未定，未生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n"/>
@@ -18749,8 +18855,16 @@
         </is>
       </c>
       <c r="E577" s="2" t="n"/>
-      <c r="F577" s="4" t="n"/>
-      <c r="G577" s="2" t="n"/>
+      <c r="F577" s="4" t="inlineStr">
+        <is>
+          <t>凭据校验类，待脱敏方案，未执行</t>
+        </is>
+      </c>
+      <c r="G577" s="4" t="inlineStr">
+        <is>
+          <t>云存储/FTP/GoogleSheet 凭据校验接口(365d 5次)：请求需真实账号密钥，ES样本中为其他客户真实凭据不可复用，脱敏/替代方案未定，未生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="578" ht="16" customHeight="1">
       <c r="A578" s="2" t="n"/>
@@ -18795,8 +18909,16 @@
         </is>
       </c>
       <c r="E579" s="2" t="n"/>
-      <c r="F579" s="4" t="n"/>
-      <c r="G579" s="2" t="n"/>
+      <c r="F579" s="4" t="inlineStr">
+        <is>
+          <t>凭据校验类，待脱敏方案，未执行</t>
+        </is>
+      </c>
+      <c r="G579" s="4" t="inlineStr">
+        <is>
+          <t>云存储/FTP/GoogleSheet 凭据校验接口(365d 136次)：请求需真实账号密钥，ES样本中为其他客户真实凭据不可复用，脱敏/替代方案未定，未生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n"/>
@@ -18816,8 +18938,16 @@
         </is>
       </c>
       <c r="E580" s="2" t="n"/>
-      <c r="F580" s="4" t="n"/>
-      <c r="G580" s="2" t="n"/>
+      <c r="F580" s="4" t="inlineStr">
+        <is>
+          <t>凭据校验类，待脱敏方案，未执行</t>
+        </is>
+      </c>
+      <c r="G580" s="4" t="inlineStr">
+        <is>
+          <t>云存储/FTP/GoogleSheet 凭据校验接口(365d 24次)：请求需真实账号密钥，ES样本中为其他客户真实凭据不可复用，脱敏/替代方案未定，未生成执行case</t>
+        </is>
+      </c>
     </row>
     <row r="581" ht="16" customHeight="1">
       <c r="A581" s="2" t="n"/>
@@ -18862,8 +18992,16 @@
         </is>
       </c>
       <c r="E582" s="2" t="n"/>
-      <c r="F582" s="4" t="n"/>
-      <c r="G582" s="2" t="n"/>
+      <c r="F582" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G582" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n"/>
@@ -18883,8 +19021,16 @@
         </is>
       </c>
       <c r="E583" s="2" t="n"/>
-      <c r="F583" s="4" t="n"/>
-      <c r="G583" s="2" t="n"/>
+      <c r="F583" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G583" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="584" ht="16" customHeight="1">
       <c r="A584" s="2" t="n"/>
@@ -18980,8 +19126,16 @@
         </is>
       </c>
       <c r="E587" s="2" t="n"/>
-      <c r="F587" s="4" t="n"/>
-      <c r="G587" s="2" t="n"/>
+      <c r="F587" s="4" t="inlineStr">
+        <is>
+          <t>高危：真实发送邮件，未执行</t>
+        </is>
+      </c>
+      <c r="G587" s="4" t="inlineStr">
+        <is>
+          <t>GET 但会真实重发报表邮件给收件人(365d 48次)，属不可撤销的对外副作用，按高危规则未执行</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n"/>
@@ -19001,8 +19155,16 @@
         </is>
       </c>
       <c r="E588" s="2" t="n"/>
-      <c r="F588" s="4" t="n"/>
-      <c r="G588" s="2" t="n"/>
+      <c r="F588" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词，不可调用</t>
+        </is>
+      </c>
+      <c r="G588" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词 init，按规则不调用；且零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="589" ht="64" customHeight="1">
       <c r="A589" s="2" t="n"/>
@@ -19050,8 +19212,16 @@
         </is>
       </c>
       <c r="E590" s="2" t="n"/>
-      <c r="F590" s="4" t="n"/>
-      <c r="G590" s="2" t="n"/>
+      <c r="F590" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词，不可调用</t>
+        </is>
+      </c>
+      <c r="G590" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词 migrate(运维数据迁移脚本)，按规则不调用；且零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n"/>
@@ -19071,8 +19241,16 @@
         </is>
       </c>
       <c r="E591" s="2" t="n"/>
-      <c r="F591" s="4" t="n"/>
-      <c r="G591" s="2" t="n"/>
+      <c r="F591" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词，不可调用</t>
+        </is>
+      </c>
+      <c r="G591" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词 migrate(运维数据迁移脚本)，按规则不调用；且零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="592" ht="32" customHeight="1">
       <c r="A592" s="2" t="n"/>
@@ -19169,8 +19347,16 @@
         </is>
       </c>
       <c r="E595" s="2" t="n"/>
-      <c r="F595" s="4" t="n"/>
-      <c r="G595" s="2" t="n"/>
+      <c r="F595" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G595" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n"/>
@@ -19190,8 +19376,16 @@
         </is>
       </c>
       <c r="E596" s="2" t="n"/>
-      <c r="F596" s="4" t="n"/>
-      <c r="G596" s="2" t="n"/>
+      <c r="F596" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G596" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n"/>
@@ -19211,8 +19405,16 @@
         </is>
       </c>
       <c r="E597" s="2" t="n"/>
-      <c r="F597" s="4" t="n"/>
-      <c r="G597" s="2" t="n"/>
+      <c r="F597" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词，不可调用</t>
+        </is>
+      </c>
+      <c r="G597" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词 run(触发报表执行)，按规则不调用；且零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n"/>
@@ -19232,8 +19434,16 @@
         </is>
       </c>
       <c r="E598" s="2" t="n"/>
-      <c r="F598" s="4" t="n"/>
-      <c r="G598" s="2" t="n"/>
+      <c r="F598" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词，不可调用</t>
+        </is>
+      </c>
+      <c r="G598" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词 run(365d 8588次，高频)，按规则不调用；该接口会真实触发报表立即执行/投递，属高危副作用GET</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n"/>
@@ -19253,8 +19463,16 @@
         </is>
       </c>
       <c r="E599" s="2" t="n"/>
-      <c r="F599" s="4" t="n"/>
-      <c r="G599" s="2" t="n"/>
+      <c r="F599" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词，不可调用</t>
+        </is>
+      </c>
+      <c r="G599" s="4" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词 run(触发报表任务)，按规则不调用；且零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="600" ht="16" customHeight="1">
       <c r="A600" s="2" t="n"/>
@@ -19303,8 +19521,16 @@
         </is>
       </c>
       <c r="E601" s="2" t="n"/>
-      <c r="F601" s="4" t="n"/>
-      <c r="G601" s="2" t="n"/>
+      <c r="F601" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G601" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n"/>
@@ -19324,8 +19550,16 @@
         </is>
       </c>
       <c r="E602" s="2" t="n"/>
-      <c r="F602" s="4" t="n"/>
-      <c r="G602" s="2" t="n"/>
+      <c r="F602" s="4" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G602" s="4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="603" ht="32" customHeight="1">
       <c r="A603" s="2" t="inlineStr">
@@ -20204,14 +20438,14 @@
         </is>
       </c>
       <c r="E634" s="2" t="n"/>
-      <c r="F634" s="7" t="inlineStr">
-        <is>
-          <t>读取当前设置 — 100.0%</t>
+      <c r="F634" s="8" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G634" s="4" t="inlineStr">
         <is>
-          <t>零流量(365d 0次)，写操作接口，暂不覆盖(注: 同路径GET已覆盖)</t>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖（2026-09-16 自检：此前场景列被同路径GET的场景文字串行污染，已更正）</t>
         </is>
       </c>
     </row>
@@ -26942,8 +27176,16 @@
         </is>
       </c>
       <c r="E863" s="2" t="n"/>
-      <c r="F863" s="4" t="n"/>
-      <c r="G863" s="2" t="n"/>
+      <c r="F863" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：创建后改名 — 332次/365d</t>
+        </is>
+      </c>
+      <c r="G863" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：修改自建display campaign名称（所在case：POST /api/DisplayCampaigns - 创建后改名+暂停+关联ItemSet），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n"/>
@@ -27013,8 +27255,16 @@
         </is>
       </c>
       <c r="E866" s="2" t="n"/>
-      <c r="F866" s="4" t="n"/>
-      <c r="G866" s="2" t="n"/>
+      <c r="F866" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：创建后暂停 — 75次/365d</t>
+        </is>
+      </c>
+      <c r="G866" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：把自建display campaign置为暂停降低残留风险（所在case：POST /api/DisplayCampaigns - 创建后改名+暂停+关联ItemSet），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n"/>
@@ -27034,8 +27284,16 @@
         </is>
       </c>
       <c r="E867" s="2" t="n"/>
-      <c r="F867" s="4" t="n"/>
-      <c r="G867" s="2" t="n"/>
+      <c r="F867" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：关联ItemSet — 77次/365d</t>
+        </is>
+      </c>
+      <c r="G867" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：关联同session自建的ItemSet 123639462（所在case：POST /api/DisplayCampaigns - 创建后改名+暂停+关联ItemSet），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n"/>
@@ -30170,8 +30428,16 @@
         </is>
       </c>
       <c r="E978" s="2" t="n"/>
-      <c r="F978" s="4" t="n"/>
-      <c r="G978" s="2" t="n"/>
+      <c r="F978" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：查异步校验状态 — 18次/365d</t>
+        </is>
+      </c>
+      <c r="G978" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：查询新建ItemSet的异步校验状态(Async 为用户确认的关键词例外)（所在case：POST /api/ItemSet/CreateItemSet - 创建后修改+验证+查状态），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="979" ht="16" customHeight="1">
       <c r="A979" s="2" t="n"/>
@@ -30216,8 +30482,16 @@
         </is>
       </c>
       <c r="E980" s="2" t="n"/>
-      <c r="F980" s="4" t="n"/>
-      <c r="G980" s="2" t="n"/>
+      <c r="F980" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：查看ItemSet商品 — 45次/365d</t>
+        </is>
+      </c>
+      <c r="G980" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：查看自建ItemSet的商品（所在case：POST /api/ItemSet/CreateItemSet - 创建后修改+验证+查状态），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n"/>
@@ -30237,8 +30511,16 @@
         </is>
       </c>
       <c r="E981" s="2" t="n"/>
-      <c r="F981" s="4" t="n"/>
-      <c r="G981" s="2" t="n"/>
+      <c r="F981" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：查ItemSet商品列表 — 218次/365d</t>
+        </is>
+      </c>
+      <c r="G981" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：查自建ItemSet商品列表（所在case：POST /api/ItemSet/CreateItemSet - 创建后修改+验证+查状态），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="982" ht="16" customHeight="1">
       <c r="A982" s="2" t="n"/>
@@ -30416,8 +30698,16 @@
         </is>
       </c>
       <c r="E988" s="2" t="n"/>
-      <c r="F988" s="4" t="n"/>
-      <c r="G988" s="2" t="n"/>
+      <c r="F988" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：修改自建ItemSet — 20次/365d</t>
+        </is>
+      </c>
+      <c r="G988" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：修改自建ItemSet（所在case：POST /api/ItemSet/CreateItemSet - 创建后修改+验证+查状态），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="989" ht="16" customHeight="1">
       <c r="A989" s="2" t="n"/>
@@ -33641,12 +33931,12 @@
       <c r="E1104" s="2" t="n"/>
       <c r="F1104" s="8" t="inlineStr">
         <is>
-          <t>默认调用 — 100.0%</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1104" s="4" t="inlineStr">
         <is>
-          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖</t>
+          <t>零流量(365d 0次，已排除测试clientId)，暂不覆盖（2026-09-16 自检：此前场景列被同路径GET的场景文字串行污染，已更正）</t>
         </is>
       </c>
     </row>
@@ -34661,8 +34951,16 @@
         </is>
       </c>
       <c r="E1140" s="2" t="n"/>
-      <c r="F1140" s="4" t="n"/>
-      <c r="G1140" s="2" t="n"/>
+      <c r="F1140" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：创建后禁用(status=0) — 483次/365d</t>
+        </is>
+      </c>
+      <c r="G1140" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：把自建否定关键词 status 改为0(无Delete接口，用禁用代替删除)（所在case：POST /api/NegativeKeyword/bulk - 创建后禁用），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="1141" ht="16" customHeight="1">
       <c r="A1141" s="2" t="n"/>
@@ -34869,8 +35167,16 @@
         </is>
       </c>
       <c r="E1148" s="2" t="n"/>
-      <c r="F1148" s="4" t="n"/>
-      <c r="G1148" s="2" t="n"/>
+      <c r="F1148" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：读取当前设置(前置/还原核对) — 196次/365d</t>
+        </is>
+      </c>
+      <c r="G1148" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：读取登录用户当前通知偏好作为原值，供POST设置后还原（所在case：POST /api/Notification/ActualSpend - 设置提醒后还原），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="1149" ht="16" customHeight="1">
       <c r="A1149" s="2" t="n"/>
@@ -34915,8 +35221,16 @@
         </is>
       </c>
       <c r="E1150" s="2" t="n"/>
-      <c r="F1150" s="4" t="n"/>
-      <c r="G1150" s="2" t="n"/>
+      <c r="F1150" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：读取当前设置(前置/还原核对) — 142次/365d</t>
+        </is>
+      </c>
+      <c r="G1150" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：读取登录用户当前通知偏好作为原值，供POST设置后还原（所在case：POST /api/Notification/insufficientBudget - 设置提醒后还原），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="1151" ht="16" customHeight="1">
       <c r="A1151" s="2" t="n"/>
@@ -34986,8 +35300,16 @@
         </is>
       </c>
       <c r="E1153" s="2" t="n"/>
-      <c r="F1153" s="4" t="n"/>
-      <c r="G1153" s="2" t="n"/>
+      <c r="F1153" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：读取当前设置(前置/还原核对) — 152次/365d</t>
+        </is>
+      </c>
+      <c r="G1153" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：读取登录用户当前通知偏好作为原值，供POST设置后还原（所在case：POST /api/Notification/ItemLowHealth - 设置提醒后还原），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="1154">
       <c r="A1154" s="2" t="n"/>
@@ -35007,8 +35329,16 @@
         </is>
       </c>
       <c r="E1154" s="2" t="n"/>
-      <c r="F1154" s="4" t="n"/>
-      <c r="G1154" s="2" t="n"/>
+      <c r="F1154" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：读取当前设置(前置/还原核对) — 378次/365d</t>
+        </is>
+      </c>
+      <c r="G1154" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：读取登录用户当前通知偏好作为原值，供POST设置后还原（所在case：POST /api/Notification/OutOfDailyBudget - 设置提醒后还原），已PASS；无独立场景行</t>
+        </is>
+      </c>
     </row>
     <row r="1155" ht="16" customHeight="1">
       <c r="A1155" s="2" t="n"/>
@@ -35078,8 +35408,16 @@
         </is>
       </c>
       <c r="E1157" s="2" t="n"/>
-      <c r="F1157" s="4" t="n"/>
-      <c r="G1157" s="2" t="n"/>
+      <c r="F1157" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：清理自建提醒规则(自身零流量)</t>
+        </is>
+      </c>
+      <c r="G1157" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：删除本case创建的Performance提醒规则（所在case：POST /api/Notification/Performance - 创建自定义提醒规则后清理），已PASS；无独立场景行；该端点自身365d 0次真实调用</t>
+        </is>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" s="2" t="n"/>
@@ -35099,8 +35437,16 @@
         </is>
       </c>
       <c r="E1158" s="2" t="n"/>
-      <c r="F1158" s="4" t="n"/>
-      <c r="G1158" s="2" t="n"/>
+      <c r="F1158" s="4" t="inlineStr">
+        <is>
+          <t>链式步骤：切换自建规则状态(自身零流量)</t>
+        </is>
+      </c>
+      <c r="G1158" s="4" t="inlineStr">
+        <is>
+          <t>作为链式case步骤真实执行：暂停/恢复本case创建的规则（所在case：POST /api/Notification/Performance - 创建自定义提醒规则后清理），已PASS；无独立场景行；该端点自身365d 0次真实调用</t>
+        </is>
+      </c>
     </row>
     <row r="1159" ht="16" customHeight="1">
       <c r="A1159" s="2" t="n"/>
@@ -41832,8 +42178,16 @@
         </is>
       </c>
       <c r="E1399" s="2" t="n"/>
-      <c r="F1399" s="4" t="n"/>
-      <c r="G1399" s="2" t="n"/>
+      <c r="F1399" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1399" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1400">
       <c r="A1400" s="2" t="n"/>
@@ -41853,8 +42207,16 @@
         </is>
       </c>
       <c r="E1400" s="2" t="n"/>
-      <c r="F1400" s="4" t="n"/>
-      <c r="G1400" s="2" t="n"/>
+      <c r="F1400" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1400" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1401">
       <c r="A1401" s="2" t="n"/>
@@ -41874,8 +42236,16 @@
         </is>
       </c>
       <c r="E1401" s="2" t="n"/>
-      <c r="F1401" s="4" t="n"/>
-      <c r="G1401" s="2" t="n"/>
+      <c r="F1401" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1401" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1402">
       <c r="A1402" s="2" t="n"/>
@@ -41895,8 +42265,16 @@
         </is>
       </c>
       <c r="E1402" s="2" t="n"/>
-      <c r="F1402" s="4" t="n"/>
-      <c r="G1402" s="2" t="n"/>
+      <c r="F1402" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1402" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1403">
       <c r="A1403" s="2" t="n"/>
@@ -41916,8 +42294,16 @@
         </is>
       </c>
       <c r="E1403" s="2" t="n"/>
-      <c r="F1403" s="4" t="n"/>
-      <c r="G1403" s="2" t="n"/>
+      <c r="F1403" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1403" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1404">
       <c r="A1404" s="2" t="n"/>
@@ -41937,8 +42323,16 @@
         </is>
       </c>
       <c r="E1404" s="2" t="n"/>
-      <c r="F1404" s="4" t="n"/>
-      <c r="G1404" s="2" t="n"/>
+      <c r="F1404" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1404" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1405">
       <c r="A1405" s="2" t="n"/>
@@ -41958,8 +42352,16 @@
         </is>
       </c>
       <c r="E1405" s="2" t="n"/>
-      <c r="F1405" s="4" t="n"/>
-      <c r="G1405" s="2" t="n"/>
+      <c r="F1405" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1405" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1406">
       <c r="A1406" s="2" t="n"/>
@@ -41979,8 +42381,16 @@
         </is>
       </c>
       <c r="E1406" s="2" t="n"/>
-      <c r="F1406" s="4" t="n"/>
-      <c r="G1406" s="2" t="n"/>
+      <c r="F1406" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1406" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1407">
       <c r="A1407" s="2" t="n"/>
@@ -42000,8 +42410,16 @@
         </is>
       </c>
       <c r="E1407" s="2" t="n"/>
-      <c r="F1407" s="4" t="n"/>
-      <c r="G1407" s="2" t="n"/>
+      <c r="F1407" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1407" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1408">
       <c r="A1408" s="2" t="n"/>
@@ -42021,8 +42439,16 @@
         </is>
       </c>
       <c r="E1408" s="2" t="n"/>
-      <c r="F1408" s="4" t="n"/>
-      <c r="G1408" s="2" t="n"/>
+      <c r="F1408" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1408" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1409">
       <c r="A1409" s="2" t="n"/>
@@ -42042,8 +42468,16 @@
         </is>
       </c>
       <c r="E1409" s="2" t="n"/>
-      <c r="F1409" s="4" t="n"/>
-      <c r="G1409" s="2" t="n"/>
+      <c r="F1409" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1409" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1410">
       <c r="A1410" s="2" t="n"/>
@@ -42063,8 +42497,16 @@
         </is>
       </c>
       <c r="E1410" s="2" t="n"/>
-      <c r="F1410" s="4" t="n"/>
-      <c r="G1410" s="2" t="n"/>
+      <c r="F1410" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1410" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1411">
       <c r="A1411" s="2" t="n"/>
@@ -42084,8 +42526,16 @@
         </is>
       </c>
       <c r="E1411" s="2" t="n"/>
-      <c r="F1411" s="4" t="n"/>
-      <c r="G1411" s="2" t="n"/>
+      <c r="F1411" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1411" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1412">
       <c r="A1412" s="2" t="n"/>
@@ -42105,8 +42555,16 @@
         </is>
       </c>
       <c r="E1412" s="2" t="n"/>
-      <c r="F1412" s="4" t="n"/>
-      <c r="G1412" s="2" t="n"/>
+      <c r="F1412" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1412" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1413">
       <c r="A1413" s="2" t="n"/>
@@ -42126,8 +42584,16 @@
         </is>
       </c>
       <c r="E1413" s="2" t="n"/>
-      <c r="F1413" s="4" t="n"/>
-      <c r="G1413" s="2" t="n"/>
+      <c r="F1413" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1413" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1414">
       <c r="A1414" s="2" t="n"/>
@@ -42147,8 +42613,16 @@
         </is>
       </c>
       <c r="E1414" s="2" t="n"/>
-      <c r="F1414" s="4" t="n"/>
-      <c r="G1414" s="2" t="n"/>
+      <c r="F1414" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1414" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1415">
       <c r="A1415" s="2" t="n"/>
@@ -42168,8 +42642,16 @@
         </is>
       </c>
       <c r="E1415" s="2" t="n"/>
-      <c r="F1415" s="4" t="n"/>
-      <c r="G1415" s="2" t="n"/>
+      <c r="F1415" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1415" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1416">
       <c r="A1416" s="2" t="n"/>
@@ -42189,8 +42671,16 @@
         </is>
       </c>
       <c r="E1416" s="2" t="n"/>
-      <c r="F1416" s="4" t="n"/>
-      <c r="G1416" s="2" t="n"/>
+      <c r="F1416" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1416" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1417">
       <c r="A1417" s="2" t="n"/>
@@ -42210,8 +42700,16 @@
         </is>
       </c>
       <c r="E1417" s="2" t="n"/>
-      <c r="F1417" s="4" t="n"/>
-      <c r="G1417" s="2" t="n"/>
+      <c r="F1417" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1417" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1418">
       <c r="A1418" s="2" t="n"/>
@@ -42231,8 +42729,16 @@
         </is>
       </c>
       <c r="E1418" s="2" t="n"/>
-      <c r="F1418" s="4" t="n"/>
-      <c r="G1418" s="2" t="n"/>
+      <c r="F1418" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1418" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1419">
       <c r="A1419" s="2" t="n"/>
@@ -42252,8 +42758,16 @@
         </is>
       </c>
       <c r="E1419" s="2" t="n"/>
-      <c r="F1419" s="4" t="n"/>
-      <c r="G1419" s="2" t="n"/>
+      <c r="F1419" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1419" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1420">
       <c r="A1420" s="2" t="n"/>
@@ -42273,8 +42787,16 @@
         </is>
       </c>
       <c r="E1420" s="2" t="n"/>
-      <c r="F1420" s="4" t="n"/>
-      <c r="G1420" s="2" t="n"/>
+      <c r="F1420" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1420" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1421">
       <c r="A1421" s="2" t="n"/>
@@ -42294,8 +42816,16 @@
         </is>
       </c>
       <c r="E1421" s="2" t="n"/>
-      <c r="F1421" s="4" t="n"/>
-      <c r="G1421" s="2" t="n"/>
+      <c r="F1421" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1421" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1422">
       <c r="A1422" s="2" t="n"/>
@@ -42315,8 +42845,16 @@
         </is>
       </c>
       <c r="E1422" s="2" t="n"/>
-      <c r="F1422" s="4" t="n"/>
-      <c r="G1422" s="2" t="n"/>
+      <c r="F1422" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1422" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1423">
       <c r="A1423" s="2" t="n"/>
@@ -42336,8 +42874,16 @@
         </is>
       </c>
       <c r="E1423" s="2" t="n"/>
-      <c r="F1423" s="4" t="n"/>
-      <c r="G1423" s="2" t="n"/>
+      <c r="F1423" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1423" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1424">
       <c r="A1424" s="2" t="n"/>
@@ -42357,8 +42903,16 @@
         </is>
       </c>
       <c r="E1424" s="2" t="n"/>
-      <c r="F1424" s="4" t="n"/>
-      <c r="G1424" s="2" t="n"/>
+      <c r="F1424" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1424" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1425">
       <c r="A1425" s="2" t="n"/>
@@ -42378,8 +42932,16 @@
         </is>
       </c>
       <c r="E1425" s="2" t="n"/>
-      <c r="F1425" s="4" t="n"/>
-      <c r="G1425" s="2" t="n"/>
+      <c r="F1425" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1425" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1426">
       <c r="A1426" s="2" t="n"/>
@@ -42399,8 +42961,16 @@
         </is>
       </c>
       <c r="E1426" s="2" t="n"/>
-      <c r="F1426" s="4" t="n"/>
-      <c r="G1426" s="2" t="n"/>
+      <c r="F1426" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1426" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1427">
       <c r="A1427" s="2" t="n"/>
@@ -42420,8 +42990,16 @@
         </is>
       </c>
       <c r="E1427" s="2" t="n"/>
-      <c r="F1427" s="4" t="n"/>
-      <c r="G1427" s="2" t="n"/>
+      <c r="F1427" s="4" t="inlineStr">
+        <is>
+          <t>用户确认跳过，不纳入覆盖</t>
+        </is>
+      </c>
+      <c r="G1427" s="4" t="inlineStr">
+        <is>
+          <t>TEST tag(29接口)经用户2026-09-14确认为内部测试/调试模块，不纳入单接口case覆盖范围</t>
+        </is>
+      </c>
     </row>
     <row r="1428">
       <c r="A1428" s="2" t="inlineStr">

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -1468,12 +1468,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>79%(43执行 34PASS；1条技术受限不执行不计入)</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>84% (26/31)</t>
+          <t>74% (23/31)</t>
         </is>
       </c>
     </row>
@@ -12130,12 +12130,12 @@
       <c r="E339" s="2" t="n"/>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>【仅生成未执行】创建/更新Campaign(单条，含campaignId表示更新)</t>
+          <t>创建新Campaign(测试账号profile 16274451，创建后归档自清理) — 写操作已执行</t>
         </is>
       </c>
       <c r="G339" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>写操作已按2026-09-14新规则真实执行(2026-09-15，2轮验证PASS)：测试账号下创建campaign→用响应data.campaignID→delete归档清理。</t>
         </is>
       </c>
     </row>
@@ -15318,7 +15318,11 @@
           <t>默认调用 — 100.0%</t>
         </is>
       </c>
-      <c r="G451" s="2" t="n"/>
+      <c r="G451" s="4" t="inlineStr">
+        <is>
+          <t>（2026-09-14 禁用关键词规则生效前已执行，结果保留；规则生效后不再调用）</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -16216,7 +16220,7 @@
       <c r="E483" s="2" t="n"/>
       <c r="F483" s="8" t="inlineStr">
         <is>
-          <t>【仅生成未执行】取消关注搜索词</t>
+          <t>作为关注case的清理步骤执行：取消关注搜索词 — 已执行PASS</t>
         </is>
       </c>
       <c r="G483" s="4" t="inlineStr">
@@ -20871,7 +20875,11 @@
           <t>空数组触发刷新 — 100.0%</t>
         </is>
       </c>
-      <c r="G650" s="2" t="n"/>
+      <c r="G650" s="4" t="inlineStr">
+        <is>
+          <t>（2026-09-14 禁用关键词规则生效前已执行，结果保留；规则生效后不再调用）</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n"/>
@@ -26099,12 +26107,12 @@
       <c r="E825" s="2" t="n"/>
       <c r="F825" s="8" t="inlineStr">
         <is>
-          <t>【仅生成未执行】创建广告组</t>
+          <t>创建广告组(创建后暂停) — 写操作已执行PASS</t>
         </is>
       </c>
       <c r="G825" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15发现创建响应体字段是adGroupID(大写ID非adGroupId)，且campaign级已配预算时ad group级不能再设预算(405)，已修正。⚠️无DELETE接口，name一旦用过永久占用，同名重跑会405"already exists"，非bug，重跑需换新name。</t>
+          <t>2026-09-15发现创建响应体字段是adGroupID(大写ID非adGroupId)，且campaign级已配预算时ad group级不能再设预算(405)，已修正。⚠️无DELETE接口，name一旦用过永久占用，同名重跑会405"already exists"，非bug，重跑需换新name。 写操作已真实执行(2026-09-15，2轮PASS)，自建广告组以暂停状态保留。</t>
         </is>
       </c>
     </row>
@@ -26383,12 +26391,12 @@
       <c r="E835" s="2" t="n"/>
       <c r="F835" s="8" t="inlineStr">
         <is>
-          <t>【仅生成未执行】关联创意到广告组</t>
+          <t>技术受限：需真实creativeId，未真正验证</t>
         </is>
       </c>
       <c r="G835" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-16 二次自检更正：2026-09-15 的执行把未定义变量 {{test_creative_id}} 以字面量发送，服务端仍返回200被误记PASS，该记录已作废并从report移除。测试账号Display素材库为空、无自有creativeId，需人工上传素材取得creativeId后再验证。附带观察：三个端点对无效creativeId不做校验直接返回200。</t>
         </is>
       </c>
     </row>
@@ -26412,12 +26420,12 @@
       <c r="E836" s="2" t="n"/>
       <c r="F836" s="8" t="inlineStr">
         <is>
-          <t>【仅生成未执行】更新创意跟踪URL</t>
+          <t>技术受限：需真实creativeId，未真正验证</t>
         </is>
       </c>
       <c r="G836" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-16 二次自检更正：2026-09-15 的执行把未定义变量 {{test_creative_id}} 以字面量发送，服务端仍返回200被误记PASS，该记录已作废并从report移除。测试账号Display素材库为空、无自有creativeId，需人工上传素材取得creativeId后再验证。附带观察：三个端点对无效creativeId不做校验直接返回200。</t>
         </is>
       </c>
     </row>
@@ -26439,14 +26447,14 @@
         </is>
       </c>
       <c r="E837" s="2" t="n"/>
-      <c r="F837" s="7" t="inlineStr">
-        <is>
-          <t>关联创意到广告组→更新跟踪URL→解除关联(完整链路)</t>
+      <c r="F837" s="8" t="inlineStr">
+        <is>
+          <t>技术受限：需真实creativeId，未真正验证</t>
         </is>
       </c>
       <c r="G837" s="4" t="inlineStr">
         <is>
-          <t>已生成case(未执行)：写操作类接口，人工评估后再决定是否执行</t>
+          <t>2026-09-16 二次自检更正：2026-09-15 的执行把未定义变量 {{test_creative_id}} 以字面量发送，服务端仍返回200被误记PASS，该记录已作废并从report移除。测试账号Display素材库为空、无自有creativeId，需人工上传素材取得creativeId后再验证。附带观察：三个端点对无效creativeId不做校验直接返回200。</t>
         </is>
       </c>
     </row>
@@ -34283,7 +34291,11 @@
           <t>默认调用 — 100.0%</t>
         </is>
       </c>
-      <c r="G1116" s="2" t="n"/>
+      <c r="G1116" s="4" t="inlineStr">
+        <is>
+          <t>（2026-09-14 禁用关键词规则生效前已执行，结果保留；规则生效后不再调用）</t>
+        </is>
+      </c>
     </row>
     <row r="1117" ht="32" customHeight="1">
       <c r="A1117" s="2" t="n"/>
@@ -35608,7 +35620,11 @@
           <t>默认调用 — 100.0%</t>
         </is>
       </c>
-      <c r="G1164" s="2" t="n"/>
+      <c r="G1164" s="4" t="inlineStr">
+        <is>
+          <t>（2026-09-14 禁用关键词规则生效前已执行，结果保留；规则生效后不再调用）</t>
+        </is>
+      </c>
     </row>
     <row r="1165" ht="16" customHeight="1">
       <c r="A1165" s="2" t="n"/>

--- a/single-api/walmart-api/swagger_modules.xlsx
+++ b/single-api/walmart-api/swagger_modules.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -131,6 +131,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -556,6 +559,11 @@
           <t>接口覆盖率</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>模块路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -595,6 +603,11 @@
           <t>42% (13/31)</t>
         </is>
       </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\AdGroupReport</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -634,6 +647,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\AdGroupTag</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -673,6 +691,11 @@
           <t>14% (1/7)</t>
         </is>
       </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\AdGroupTagReport</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -712,6 +735,11 @@
           <t>61% (11/18)</t>
         </is>
       </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\AdGroups</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -751,6 +779,11 @@
           <t>54% (14/26)</t>
         </is>
       </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\AdItemReport</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -790,6 +823,11 @@
           <t>43% (9/21)</t>
         </is>
       </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\AdItems</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -829,6 +867,11 @@
           <t>43% (13/30)</t>
         </is>
       </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\AdgroupReport</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -868,6 +911,11 @@
           <t>2% (1/45)</t>
         </is>
       </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -907,6 +955,11 @@
           <t>44% (4/9)</t>
         </is>
       </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Audiences</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -946,6 +999,11 @@
           <t>0% (0/17)</t>
         </is>
       </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Audit</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -985,6 +1043,11 @@
           <t>33% (6/18)</t>
         </is>
       </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Automation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1024,6 +1087,11 @@
           <t>6% (1/17)</t>
         </is>
       </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\BrandAsset</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1063,6 +1131,11 @@
           <t>76% (13/17)</t>
         </is>
       </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Budget</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1102,6 +1175,11 @@
           <t>59% (46/78)</t>
         </is>
       </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\CampaignReport</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1141,6 +1219,11 @@
           <t>50% (17/34)</t>
         </is>
       </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\CampaignTagReport</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1180,6 +1263,11 @@
           <t>65% (13/20)</t>
         </is>
       </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\CampaignTags</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1219,6 +1307,11 @@
           <t>48% (31/65)</t>
         </is>
       </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Campaigns</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1258,6 +1351,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1297,6 +1395,11 @@
           <t>8% (1/13)</t>
         </is>
       </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Category</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1336,6 +1439,11 @@
           <t>83% (20/24)</t>
         </is>
       </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\CategoryIntelligence</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1375,6 +1483,11 @@
           <t>60% (15/25)</t>
         </is>
       </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Copilot</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1414,6 +1527,11 @@
           <t>25% (7/28)</t>
         </is>
       </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Creative</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1453,6 +1571,11 @@
           <t>50% (3/6)</t>
         </is>
       </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\CreativeReport</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1492,6 +1615,11 @@
           <t>0% (0/7)</t>
         </is>
       </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Creatives</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1531,6 +1659,11 @@
           <t>47% (18/38)</t>
         </is>
       </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\CustomReport</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1570,6 +1703,11 @@
           <t>48% (42/87)</t>
         </is>
       </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1609,6 +1747,11 @@
           <t>53% (72/135)</t>
         </is>
       </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DefaultReport</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1648,6 +1791,11 @@
           <t>ES 无流量 (0/6)</t>
         </is>
       </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayAdGroupTagReport</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1687,6 +1835,11 @@
           <t>74% (23/31)</t>
         </is>
       </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayAdGroups</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1726,6 +1879,11 @@
           <t>50% (4/8)</t>
         </is>
       </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayCampaigns</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1765,6 +1923,11 @@
           <t>87% (26/30)</t>
         </is>
       </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayDashboard</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1804,6 +1967,11 @@
           <t>22% (2/9)</t>
         </is>
       </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayFolders</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1843,6 +2011,11 @@
           <t>57% (4/7)</t>
         </is>
       </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayItemTagReport</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1882,6 +2055,11 @@
           <t>50% (1/2)</t>
         </is>
       </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayRecommendations</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1921,6 +2099,11 @@
           <t>50% (17/34)</t>
         </is>
       </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\DisplayReport</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1960,6 +2143,11 @@
           <t>0% (0/5)</t>
         </is>
       </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Event</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1999,6 +2187,11 @@
           <t>8% (1/13)</t>
         </is>
       </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Excel</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2038,6 +2231,11 @@
           <t>17% (1/6)</t>
         </is>
       </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Explorer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2077,6 +2275,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Health</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2116,6 +2319,11 @@
           <t>67% (8/12)</t>
         </is>
       </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\ItemSet</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2155,6 +2363,11 @@
           <t>36% (4/11)</t>
         </is>
       </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\ItemTagReport</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2194,6 +2407,11 @@
           <t>62% (8/13)</t>
         </is>
       </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\ItemTags</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2233,6 +2451,11 @@
           <t>43% (3/7)</t>
         </is>
       </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\KeywordRecommendation</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2272,6 +2495,11 @@
           <t>60% (9/15)</t>
         </is>
       </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\KeywordReport</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2311,6 +2539,11 @@
           <t>60% (9/15)</t>
         </is>
       </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\KeywordTagReport</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2350,6 +2583,11 @@
           <t>75% (12/16)</t>
         </is>
       </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\KeywordTags</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2389,6 +2627,11 @@
           <t>60% (21/35)</t>
         </is>
       </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Keywords</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2428,6 +2671,11 @@
           <t>50% (9/18)</t>
         </is>
       </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Media</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2467,6 +2715,11 @@
           <t>25% (2/8)</t>
         </is>
       </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Moderation</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2506,6 +2759,11 @@
           <t>10% (1/10)</t>
         </is>
       </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\MonitorKeywordTags</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2545,6 +2803,11 @@
           <t>44% (4/9)</t>
         </is>
       </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\NegativeKeyword</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2584,6 +2847,11 @@
           <t>94% (15/16)</t>
         </is>
       </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Notification</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2623,6 +2891,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Optimization</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2662,6 +2935,11 @@
           <t>49% (21/43)</t>
         </is>
       </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Product</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2701,6 +2979,11 @@
           <t>62% (5/8)</t>
         </is>
       </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Profile</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2740,6 +3023,11 @@
           <t>53% (9/17)</t>
         </is>
       </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\ProfileReport</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2779,6 +3067,11 @@
           <t>35% (6/17)</t>
         </is>
       </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Recommendations</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2818,6 +3111,11 @@
           <t>42% (27/64)</t>
         </is>
       </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Report</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2857,6 +3155,11 @@
           <t>67% (2/3)</t>
         </is>
       </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Research</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2896,6 +3199,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\RetailerAdoption</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2935,6 +3243,11 @@
           <t>29% (2/7)</t>
         </is>
       </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Review</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2974,6 +3287,11 @@
           <t>ES 无流量 (0/3)</t>
         </is>
       </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\SOV</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3013,6 +3331,11 @@
           <t>0% (0/13)</t>
         </is>
       </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\SOVDashboard</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3052,6 +3375,11 @@
           <t>18% (3/17)</t>
         </is>
       </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\SbaProfile</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3091,6 +3419,11 @@
           <t>50% (4/8)</t>
         </is>
       </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\SearchTermReport</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3130,6 +3463,11 @@
           <t>76% (13/17)</t>
         </is>
       </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\ShareLink</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3169,6 +3507,11 @@
           <t>67% (4/6)</t>
         </is>
       </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\SponsorAdGroupTagReport</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3208,6 +3551,11 @@
           <t>0% (0/4)</t>
         </is>
       </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\SyncData</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3247,6 +3595,11 @@
           <t>跳过 (0/29)</t>
         </is>
       </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\TEST</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3286,6 +3639,11 @@
           <t>0% (0/4)</t>
         </is>
       </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\TagRule</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3325,6 +3683,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\Targets</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3364,6 +3727,11 @@
           <t>43% (20/46)</t>
         </is>
       </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\User</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3401,6 +3769,11 @@
       <c r="I74" s="5" t="inlineStr">
         <is>
           <t>17% (1/6)</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\walmart-api\us\Walmart\WalmartForPacvueAdmin</t>
         </is>
       </c>
     </row>
